--- a/vtl_template.xlsx
+++ b/vtl_template.xlsx
@@ -2040,7 +2040,10 @@
     <col width="10.1640625" customWidth="1" style="4" min="86" max="86"/>
     <col hidden="1" width="10.1640625" customWidth="1" style="4" min="87" max="87"/>
     <col width="10.1640625" customWidth="1" style="4" min="88" max="89"/>
+    <col width="13" customWidth="1" min="89" max="89"/>
     <col hidden="1" width="10.1640625" customWidth="1" style="4" min="90" max="92"/>
+    <col width="13" customWidth="1" min="91" max="91"/>
+    <col width="13" customWidth="1" min="92" max="92"/>
     <col width="8.83203125" customWidth="1" style="134" min="93" max="95"/>
     <col hidden="1" width="8.83203125" customWidth="1" style="134" min="96" max="96"/>
     <col width="8.83203125" customWidth="1" style="134" min="97" max="97"/>
@@ -2763,8 +2766,16 @@
           <t>御茶園     冰釀麥萃</t>
         </is>
       </c>
-      <c r="CM4" s="35" t="n"/>
-      <c r="CN4" s="35" t="n"/>
+      <c r="CM4" s="68" t="inlineStr">
+        <is>
+          <t>御茶園     冰釀麥萃</t>
+        </is>
+      </c>
+      <c r="CN4" s="68" t="inlineStr">
+        <is>
+          <t>御茶園     冰釀麥萃</t>
+        </is>
+      </c>
       <c r="CO4" s="26" t="inlineStr">
         <is>
           <t>棧板</t>
@@ -3293,8 +3304,16 @@
           <t>590ML           路凱4入</t>
         </is>
       </c>
-      <c r="CM5" s="28" t="n"/>
-      <c r="CN5" s="32" t="n"/>
+      <c r="CM5" s="55" t="inlineStr">
+        <is>
+          <t>590ML           全台促4入</t>
+        </is>
+      </c>
+      <c r="CN5" s="56" t="inlineStr">
+        <is>
+          <t>590ML           PX11促</t>
+        </is>
+      </c>
       <c r="CO5" s="26" t="inlineStr">
         <is>
           <t>(捷盟)     RT-11</t>
@@ -3823,8 +3842,16 @@
           <t>JDP0590 4LC1</t>
         </is>
       </c>
-      <c r="CM6" s="15" t="n"/>
-      <c r="CN6" s="33" t="n"/>
+      <c r="CM6" s="74" t="inlineStr">
+        <is>
+          <t>JDP0590 4AB1</t>
+        </is>
+      </c>
+      <c r="CN6" s="74" t="inlineStr">
+        <is>
+          <t>JDP0590 1BU1</t>
+        </is>
+      </c>
       <c r="CO6" s="144" t="n"/>
       <c r="CP6" s="144" t="n"/>
       <c r="CQ6" s="144" t="n"/>
@@ -3976,11 +4003,11 @@
         <v/>
       </c>
       <c r="CP7" s="129">
-        <f>SUM(O7+P7+Q7+BL7+BM7+CB7+CC7)/65+SUM(X7+Y7)/44+SUM(AJ7+AK7+AM7+AN7+AO7+AP7+AQ7+BR7+BS7+BT7+BU7+BV7+CH7+CI7+CJ7)/45+SUM(AX7+AY7+AZ7+BA7+BF7+BG7+BH7)/60+SUM(AL7+BZ7)/50</f>
+        <f>SUM(O7+P7+Q7+BL7+BM7+CB7+CC7)/65+SUM(X7+Y7)/44+SUM(AJ7+AK7+AM7+AN7+AO7+AP7+AQ7+BR7+BS7+BT7+BU7+BV7+CH7+CI7+CJ7+CM7)/45+SUM(AX7+AY7+AZ7+BA7+BF7+BG7+BH7)/60+SUM(AL7+BZ7)/50</f>
         <v/>
       </c>
       <c r="CQ7" s="129">
-        <f>SUM(R7+S7+BN7+CD7+CE7)/65+SUM(AB7)/36+SUM(AR7+AS7+BW7+BX7+CK7)/40+SUM(BB7+BC7+BI7+BJ7)/60</f>
+        <f>SUM(R7+S7+BN7+CD7+CE7)/65+SUM(AB7)/36+SUM(AR7+AS7+BW7+BX7+CK7+CN7)/40+SUM(BB7+BC7+BI7+BJ7)/60</f>
         <v/>
       </c>
       <c r="CR7" s="129">
@@ -4135,11 +4162,11 @@
         <v/>
       </c>
       <c r="CP8" s="38">
-        <f>SUM(O8+P8+Q8+BL8+BM8+CB8+CC8)/65+SUM(X8+Y8)/44+SUM(AJ8+AK8+AM8+AN8+AO8+AP8+AQ8+BR8+BS8+BT8+BU8+BV8+CH8+CI8+CJ8)/45+SUM(AX8+AY8+AZ8+BA8+BF8+BG8+BH8)/60+SUM(AL8+BZ8)/50</f>
+        <f>SUM(O8+P8+Q8+BL8+BM8+CB8+CC8)/65+SUM(X8+Y8)/44+SUM(AJ8+AK8+AM8+AN8+AO8+AP8+AQ8+BR8+BS8+BT8+BU8+BV8+CH8+CI8+CJ8+CM8)/45+SUM(AX8+AY8+AZ8+BA8+BF8+BG8+BH8)/60+SUM(AL8+BZ8)/50</f>
         <v/>
       </c>
       <c r="CQ8" s="38">
-        <f>SUM(R8+S8+BN8+CD8+CE8)/65+SUM(AB8)/36+SUM(AR8+AS8+BW8+BX8+CK8)/40+SUM(BB8+BC8+BI8+BJ8)/60</f>
+        <f>SUM(R8+S8+BN8+CD8+CE8)/65+SUM(AB8)/36+SUM(AR8+AS8+BW8+BX8+CK8+CN8)/40+SUM(BB8+BC8+BI8+BJ8)/60</f>
         <v/>
       </c>
       <c r="CR8" s="38">
@@ -4294,11 +4321,11 @@
         <v/>
       </c>
       <c r="CP9" s="38">
-        <f>SUM(O9+P9+Q9+BL9+BM9+CB9+CC9)/65+SUM(X9+Y9)/44+SUM(AJ9+AK9+AM9+AN9+AO9+AP9+AQ9+BR9+BS9+BT9+BU9+BV9+CH9+CI9+CJ9)/45+SUM(AX9+AY9+AZ9+BA9+BF9+BG9+BH9)/60+SUM(AL9+BZ9)/50</f>
+        <f>SUM(O9+P9+Q9+BL9+BM9+CB9+CC9)/65+SUM(X9+Y9)/44+SUM(AJ9+AK9+AM9+AN9+AO9+AP9+AQ9+BR9+BS9+BT9+BU9+BV9+CH9+CI9+CJ9+CM9)/45+SUM(AX9+AY9+AZ9+BA9+BF9+BG9+BH9)/60+SUM(AL9+BZ9)/50</f>
         <v/>
       </c>
       <c r="CQ9" s="38">
-        <f>SUM(R9+S9+BN9+CD9+CE9)/65+SUM(AB9)/36+SUM(AR9+AS9+BW9+BX9+CK9)/40+SUM(BB9+BC9+BI9+BJ9)/60</f>
+        <f>SUM(R9+S9+BN9+CD9+CE9)/65+SUM(AB9)/36+SUM(AR9+AS9+BW9+BX9+CK9+CN9)/40+SUM(BB9+BC9+BI9+BJ9)/60</f>
         <v/>
       </c>
       <c r="CR9" s="38">
@@ -4453,11 +4480,11 @@
         <v/>
       </c>
       <c r="CP10" s="38">
-        <f>SUM(O10+P10+Q10+BL10+BM10+CB10+CC10)/65+SUM(X10+Y10)/44+SUM(AJ10+AK10+AM10+AN10+AO10+AP10+AQ10+BR10+BS10+BT10+BU10+BV10+CH10+CI10+CJ10)/45+SUM(AX10+AY10+AZ10+BA10+BF10+BG10+BH10)/60+SUM(AL10+BZ10)/50</f>
+        <f>SUM(O10+P10+Q10+BL10+BM10+CB10+CC10)/65+SUM(X10+Y10)/44+SUM(AJ10+AK10+AM10+AN10+AO10+AP10+AQ10+BR10+BS10+BT10+BU10+BV10+CH10+CI10+CJ10+CM10)/45+SUM(AX10+AY10+AZ10+BA10+BF10+BG10+BH10)/60+SUM(AL10+BZ10)/50</f>
         <v/>
       </c>
       <c r="CQ10" s="38">
-        <f>SUM(R10+S10+BN10+CD10+CE10)/65+SUM(AB10)/36+SUM(AR10+AS10+BW10+BX10+CK10)/40+SUM(BB10+BC10+BI10+BJ10)/60</f>
+        <f>SUM(R10+S10+BN10+CD10+CE10)/65+SUM(AB10)/36+SUM(AR10+AS10+BW10+BX10+CK10+CN10)/40+SUM(BB10+BC10+BI10+BJ10)/60</f>
         <v/>
       </c>
       <c r="CR10" s="38">
@@ -4612,11 +4639,11 @@
         <v/>
       </c>
       <c r="CP11" s="38">
-        <f>SUM(O11+P11+Q11+BL11+BM11+CB11+CC11)/65+SUM(X11+Y11)/44+SUM(AJ11+AK11+AM11+AN11+AO11+AP11+AQ11+BR11+BS11+BT11+BU11+BV11+CH11+CI11+CJ11)/45+SUM(AX11+AY11+AZ11+BA11+BF11+BG11+BH11)/60+SUM(AL11+BZ11)/50</f>
+        <f>SUM(O11+P11+Q11+BL11+BM11+CB11+CC11)/65+SUM(X11+Y11)/44+SUM(AJ11+AK11+AM11+AN11+AO11+AP11+AQ11+BR11+BS11+BT11+BU11+BV11+CH11+CI11+CJ11+CM11)/45+SUM(AX11+AY11+AZ11+BA11+BF11+BG11+BH11)/60+SUM(AL11+BZ11)/50</f>
         <v/>
       </c>
       <c r="CQ11" s="38">
-        <f>SUM(R11+S11+BN11+CD11+CE11)/65+SUM(AB11)/36+SUM(AR11+AS11+BW11+BX11+CK11)/40+SUM(BB11+BC11+BI11+BJ11)/60</f>
+        <f>SUM(R11+S11+BN11+CD11+CE11)/65+SUM(AB11)/36+SUM(AR11+AS11+BW11+BX11+CK11+CN11)/40+SUM(BB11+BC11+BI11+BJ11)/60</f>
         <v/>
       </c>
       <c r="CR11" s="38">
@@ -4771,11 +4798,11 @@
         <v/>
       </c>
       <c r="CP12" s="38">
-        <f>SUM(O12+P12+Q12+BL12+BM12+CB12+CC12)/65+SUM(X12+Y12)/44+SUM(AJ12+AK12+AM12+AN12+AO12+AP12+AQ12+BR12+BS12+BT12+BU12+BV12+CH12+CI12+CJ12)/45+SUM(AX12+AY12+AZ12+BA12+BF12+BG12+BH12)/60+SUM(AL12+BZ12)/50</f>
+        <f>SUM(O12+P12+Q12+BL12+BM12+CB12+CC12)/65+SUM(X12+Y12)/44+SUM(AJ12+AK12+AM12+AN12+AO12+AP12+AQ12+BR12+BS12+BT12+BU12+BV12+CH12+CI12+CJ12+CM12)/45+SUM(AX12+AY12+AZ12+BA12+BF12+BG12+BH12)/60+SUM(AL12+BZ12)/50</f>
         <v/>
       </c>
       <c r="CQ12" s="38">
-        <f>SUM(R12+S12+BN12+CD12+CE12)/65+SUM(AB12)/36+SUM(AR12+AS12+BW12+BX12+CK12)/40+SUM(BB12+BC12+BI12+BJ12)/60</f>
+        <f>SUM(R12+S12+BN12+CD12+CE12)/65+SUM(AB12)/36+SUM(AR12+AS12+BW12+BX12+CK12+CN12)/40+SUM(BB12+BC12+BI12+BJ12)/60</f>
         <v/>
       </c>
       <c r="CR12" s="38">
@@ -4930,11 +4957,11 @@
         <v/>
       </c>
       <c r="CP13" s="38">
-        <f>SUM(O13+P13+Q13+BL13+BM13+CB13+CC13)/65+SUM(X13+Y13)/44+SUM(AJ13+AK13+AM13+AN13+AO13+AP13+AQ13+BR13+BS13+BT13+BU13+BV13+CH13+CI13+CJ13)/45+SUM(AX13+AY13+AZ13+BA13+BF13+BG13+BH13)/60+SUM(AL13+BZ13)/50</f>
+        <f>SUM(O13+P13+Q13+BL13+BM13+CB13+CC13)/65+SUM(X13+Y13)/44+SUM(AJ13+AK13+AM13+AN13+AO13+AP13+AQ13+BR13+BS13+BT13+BU13+BV13+CH13+CI13+CJ13+CM13)/45+SUM(AX13+AY13+AZ13+BA13+BF13+BG13+BH13)/60+SUM(AL13+BZ13)/50</f>
         <v/>
       </c>
       <c r="CQ13" s="38">
-        <f>SUM(R13+S13+BN13+CD13+CE13)/65+SUM(AB13)/36+SUM(AR13+AS13+BW13+BX13+CK13)/40+SUM(BB13+BC13+BI13+BJ13)/60</f>
+        <f>SUM(R13+S13+BN13+CD13+CE13)/65+SUM(AB13)/36+SUM(AR13+AS13+BW13+BX13+CK13+CN13)/40+SUM(BB13+BC13+BI13+BJ13)/60</f>
         <v/>
       </c>
       <c r="CR13" s="38">
@@ -5089,11 +5116,11 @@
         <v/>
       </c>
       <c r="CP14" s="38">
-        <f>SUM(O14+P14+Q14+BL14+BM14+CB14+CC14)/65+SUM(X14+Y14)/44+SUM(AJ14+AK14+AM14+AN14+AO14+AP14+AQ14+BR14+BS14+BT14+BU14+BV14+CH14+CI14+CJ14)/45+SUM(AX14+AY14+AZ14+BA14+BF14+BG14+BH14)/60+SUM(AL14+BZ14)/50</f>
+        <f>SUM(O14+P14+Q14+BL14+BM14+CB14+CC14)/65+SUM(X14+Y14)/44+SUM(AJ14+AK14+AM14+AN14+AO14+AP14+AQ14+BR14+BS14+BT14+BU14+BV14+CH14+CI14+CJ14+CM14)/45+SUM(AX14+AY14+AZ14+BA14+BF14+BG14+BH14)/60+SUM(AL14+BZ14)/50</f>
         <v/>
       </c>
       <c r="CQ14" s="38">
-        <f>SUM(R14+S14+BN14+CD14+CE14)/65+SUM(AB14)/36+SUM(AR14+AS14+BW14+BX14+CK14)/40+SUM(BB14+BC14+BI14+BJ14)/60</f>
+        <f>SUM(R14+S14+BN14+CD14+CE14)/65+SUM(AB14)/36+SUM(AR14+AS14+BW14+BX14+CK14+CN14)/40+SUM(BB14+BC14+BI14+BJ14)/60</f>
         <v/>
       </c>
       <c r="CR14" s="38">
@@ -5248,11 +5275,11 @@
         <v/>
       </c>
       <c r="CP15" s="38">
-        <f>SUM(O15+P15+Q15+BL15+BM15+CB15+CC15)/65+SUM(X15+Y15)/44+SUM(AJ15+AK15+AM15+AN15+AO15+AP15+AQ15+BR15+BS15+BT15+BU15+BV15+CH15+CI15+CJ15)/45+SUM(AX15+AY15+AZ15+BA15+BF15+BG15+BH15)/60+SUM(AL15+BZ15)/50</f>
+        <f>SUM(O15+P15+Q15+BL15+BM15+CB15+CC15)/65+SUM(X15+Y15)/44+SUM(AJ15+AK15+AM15+AN15+AO15+AP15+AQ15+BR15+BS15+BT15+BU15+BV15+CH15+CI15+CJ15+CM15)/45+SUM(AX15+AY15+AZ15+BA15+BF15+BG15+BH15)/60+SUM(AL15+BZ15)/50</f>
         <v/>
       </c>
       <c r="CQ15" s="38">
-        <f>SUM(R15+S15+BN15+CD15+CE15)/65+SUM(AB15)/36+SUM(AR15+AS15+BW15+BX15+CK15)/40+SUM(BB15+BC15+BI15+BJ15)/60</f>
+        <f>SUM(R15+S15+BN15+CD15+CE15)/65+SUM(AB15)/36+SUM(AR15+AS15+BW15+BX15+CK15+CN15)/40+SUM(BB15+BC15+BI15+BJ15)/60</f>
         <v/>
       </c>
       <c r="CR15" s="38">
@@ -5407,11 +5434,11 @@
         <v/>
       </c>
       <c r="CP16" s="38">
-        <f>SUM(O16+P16+Q16+BL16+BM16+CB16+CC16)/65+SUM(X16+Y16)/44+SUM(AJ16+AK16+AM16+AN16+AO16+AP16+AQ16+BR16+BS16+BT16+BU16+BV16+CH16+CI16+CJ16)/45+SUM(AX16+AY16+AZ16+BA16+BF16+BG16+BH16)/60+SUM(AL16+BZ16)/50</f>
+        <f>SUM(O16+P16+Q16+BL16+BM16+CB16+CC16)/65+SUM(X16+Y16)/44+SUM(AJ16+AK16+AM16+AN16+AO16+AP16+AQ16+BR16+BS16+BT16+BU16+BV16+CH16+CI16+CJ16+CM16)/45+SUM(AX16+AY16+AZ16+BA16+BF16+BG16+BH16)/60+SUM(AL16+BZ16)/50</f>
         <v/>
       </c>
       <c r="CQ16" s="38">
-        <f>SUM(R16+S16+BN16+CD16+CE16)/65+SUM(AB16)/36+SUM(AR16+AS16+BW16+BX16+CK16)/40+SUM(BB16+BC16+BI16+BJ16)/60</f>
+        <f>SUM(R16+S16+BN16+CD16+CE16)/65+SUM(AB16)/36+SUM(AR16+AS16+BW16+BX16+CK16+CN16)/40+SUM(BB16+BC16+BI16+BJ16)/60</f>
         <v/>
       </c>
       <c r="CR16" s="38">
@@ -5566,11 +5593,11 @@
         <v/>
       </c>
       <c r="CP17" s="38">
-        <f>SUM(O17+P17+Q17+BL17+BM17+CB17+CC17)/65+SUM(X17+Y17)/44+SUM(AJ17+AK17+AM17+AN17+AO17+AP17+AQ17+BR17+BS17+BT17+BU17+BV17+CH17+CI17+CJ17)/45+SUM(AX17+AY17+AZ17+BA17+BF17+BG17+BH17)/60+SUM(AL17+BZ17)/50</f>
+        <f>SUM(O17+P17+Q17+BL17+BM17+CB17+CC17)/65+SUM(X17+Y17)/44+SUM(AJ17+AK17+AM17+AN17+AO17+AP17+AQ17+BR17+BS17+BT17+BU17+BV17+CH17+CI17+CJ17+CM17)/45+SUM(AX17+AY17+AZ17+BA17+BF17+BG17+BH17)/60+SUM(AL17+BZ17)/50</f>
         <v/>
       </c>
       <c r="CQ17" s="38">
-        <f>SUM(R17+S17+BN17+CD17+CE17)/65+SUM(AB17)/36+SUM(AR17+AS17+BW17+BX17+CK17)/40+SUM(BB17+BC17+BI17+BJ17)/60</f>
+        <f>SUM(R17+S17+BN17+CD17+CE17)/65+SUM(AB17)/36+SUM(AR17+AS17+BW17+BX17+CK17+CN17)/40+SUM(BB17+BC17+BI17+BJ17)/60</f>
         <v/>
       </c>
       <c r="CR17" s="38">
@@ -5725,11 +5752,11 @@
         <v/>
       </c>
       <c r="CP18" s="38">
-        <f>SUM(O18+P18+Q18+BL18+BM18+CB18+CC18)/65+SUM(X18+Y18)/44+SUM(AJ18+AK18+AM18+AN18+AO18+AP18+AQ18+BR18+BS18+BT18+BU18+BV18+CH18+CI18+CJ18)/45+SUM(AX18+AY18+AZ18+BA18+BF18+BG18+BH18)/60+SUM(AL18+BZ18)/50</f>
+        <f>SUM(O18+P18+Q18+BL18+BM18+CB18+CC18)/65+SUM(X18+Y18)/44+SUM(AJ18+AK18+AM18+AN18+AO18+AP18+AQ18+BR18+BS18+BT18+BU18+BV18+CH18+CI18+CJ18+CM18)/45+SUM(AX18+AY18+AZ18+BA18+BF18+BG18+BH18)/60+SUM(AL18+BZ18)/50</f>
         <v/>
       </c>
       <c r="CQ18" s="38">
-        <f>SUM(R18+S18+BN18+CD18+CE18)/65+SUM(AB18)/36+SUM(AR18+AS18+BW18+BX18+CK18)/40+SUM(BB18+BC18+BI18+BJ18)/60</f>
+        <f>SUM(R18+S18+BN18+CD18+CE18)/65+SUM(AB18)/36+SUM(AR18+AS18+BW18+BX18+CK18+CN18)/40+SUM(BB18+BC18+BI18+BJ18)/60</f>
         <v/>
       </c>
       <c r="CR18" s="38">
@@ -5884,11 +5911,11 @@
         <v/>
       </c>
       <c r="CP19" s="38">
-        <f>SUM(O19+P19+Q19+BL19+BM19+CB19+CC19)/65+SUM(X19+Y19)/44+SUM(AJ19+AK19+AM19+AN19+AO19+AP19+AQ19+BR19+BS19+BT19+BU19+BV19+CH19+CI19+CJ19)/45+SUM(AX19+AY19+AZ19+BA19+BF19+BG19+BH19)/60+SUM(AL19+BZ19)/50</f>
+        <f>SUM(O19+P19+Q19+BL19+BM19+CB19+CC19)/65+SUM(X19+Y19)/44+SUM(AJ19+AK19+AM19+AN19+AO19+AP19+AQ19+BR19+BS19+BT19+BU19+BV19+CH19+CI19+CJ19+CM19)/45+SUM(AX19+AY19+AZ19+BA19+BF19+BG19+BH19)/60+SUM(AL19+BZ19)/50</f>
         <v/>
       </c>
       <c r="CQ19" s="38">
-        <f>SUM(R19+S19+BN19+CD19+CE19)/65+SUM(AB19)/36+SUM(AR19+AS19+BW19+BX19+CK19)/40+SUM(BB19+BC19+BI19+BJ19)/60</f>
+        <f>SUM(R19+S19+BN19+CD19+CE19)/65+SUM(AB19)/36+SUM(AR19+AS19+BW19+BX19+CK19+CN19)/40+SUM(BB19+BC19+BI19+BJ19)/60</f>
         <v/>
       </c>
       <c r="CR19" s="38">
@@ -6043,11 +6070,11 @@
         <v/>
       </c>
       <c r="CP20" s="38">
-        <f>SUM(O20+P20+Q20+BL20+BM20+CB20+CC20)/65+SUM(X20+Y20)/44+SUM(AJ20+AK20+AM20+AN20+AO20+AP20+AQ20+BR20+BS20+BT20+BU20+BV20+CH20+CI20+CJ20)/45+SUM(AX20+AY20+AZ20+BA20+BF20+BG20+BH20)/60+SUM(AL20+BZ20)/50</f>
+        <f>SUM(O20+P20+Q20+BL20+BM20+CB20+CC20)/65+SUM(X20+Y20)/44+SUM(AJ20+AK20+AM20+AN20+AO20+AP20+AQ20+BR20+BS20+BT20+BU20+BV20+CH20+CI20+CJ20+CM20)/45+SUM(AX20+AY20+AZ20+BA20+BF20+BG20+BH20)/60+SUM(AL20+BZ20)/50</f>
         <v/>
       </c>
       <c r="CQ20" s="38">
-        <f>SUM(R20+S20+BN20+CD20+CE20)/65+SUM(AB20)/36+SUM(AR20+AS20+BW20+BX20+CK20)/40+SUM(BB20+BC20+BI20+BJ20)/60</f>
+        <f>SUM(R20+S20+BN20+CD20+CE20)/65+SUM(AB20)/36+SUM(AR20+AS20+BW20+BX20+CK20+CN20)/40+SUM(BB20+BC20+BI20+BJ20)/60</f>
         <v/>
       </c>
       <c r="CR20" s="38">
@@ -6202,11 +6229,11 @@
         <v/>
       </c>
       <c r="CP21" s="38">
-        <f>SUM(O21+P21+Q21+BL21+BM21+CB21+CC21)/65+SUM(X21+Y21)/44+SUM(AJ21+AK21+AM21+AN21+AO21+AP21+AQ21+BR21+BS21+BT21+BU21+BV21+CH21+CI21+CJ21)/45+SUM(AX21+AY21+AZ21+BA21+BF21+BG21+BH21)/60+SUM(AL21+BZ21)/50</f>
+        <f>SUM(O21+P21+Q21+BL21+BM21+CB21+CC21)/65+SUM(X21+Y21)/44+SUM(AJ21+AK21+AM21+AN21+AO21+AP21+AQ21+BR21+BS21+BT21+BU21+BV21+CH21+CI21+CJ21+CM21)/45+SUM(AX21+AY21+AZ21+BA21+BF21+BG21+BH21)/60+SUM(AL21+BZ21)/50</f>
         <v/>
       </c>
       <c r="CQ21" s="38">
-        <f>SUM(R21+S21+BN21+CD21+CE21)/65+SUM(AB21)/36+SUM(AR21+AS21+BW21+BX21+CK21)/40+SUM(BB21+BC21+BI21+BJ21)/60</f>
+        <f>SUM(R21+S21+BN21+CD21+CE21)/65+SUM(AB21)/36+SUM(AR21+AS21+BW21+BX21+CK21+CN21)/40+SUM(BB21+BC21+BI21+BJ21)/60</f>
         <v/>
       </c>
       <c r="CR21" s="38">
@@ -6361,11 +6388,11 @@
         <v/>
       </c>
       <c r="CP22" s="38">
-        <f>SUM(O22+P22+Q22+BL22+BM22+CB22+CC22)/65+SUM(X22+Y22)/44+SUM(AJ22+AK22+AM22+AN22+AO22+AP22+AQ22+BR22+BS22+BT22+BU22+BV22+CH22+CI22+CJ22)/45+SUM(AX22+AY22+AZ22+BA22+BF22+BG22+BH22)/60+SUM(AL22+BZ22)/50</f>
+        <f>SUM(O22+P22+Q22+BL22+BM22+CB22+CC22)/65+SUM(X22+Y22)/44+SUM(AJ22+AK22+AM22+AN22+AO22+AP22+AQ22+BR22+BS22+BT22+BU22+BV22+CH22+CI22+CJ22+CM22)/45+SUM(AX22+AY22+AZ22+BA22+BF22+BG22+BH22)/60+SUM(AL22+BZ22)/50</f>
         <v/>
       </c>
       <c r="CQ22" s="38">
-        <f>SUM(R22+S22+BN22+CD22+CE22)/65+SUM(AB22)/36+SUM(AR22+AS22+BW22+BX22+CK22)/40+SUM(BB22+BC22+BI22+BJ22)/60</f>
+        <f>SUM(R22+S22+BN22+CD22+CE22)/65+SUM(AB22)/36+SUM(AR22+AS22+BW22+BX22+CK22+CN22)/40+SUM(BB22+BC22+BI22+BJ22)/60</f>
         <v/>
       </c>
       <c r="CR22" s="38">
@@ -6520,11 +6547,11 @@
         <v/>
       </c>
       <c r="CP23" s="38">
-        <f>SUM(O23+P23+Q23+BL23+BM23+CB23+CC23)/65+SUM(X23+Y23)/44+SUM(AJ23+AK23+AM23+AN23+AO23+AP23+AQ23+BR23+BS23+BT23+BU23+BV23+CH23+CI23+CJ23)/45+SUM(AX23+AY23+AZ23+BA23+BF23+BG23+BH23)/60+SUM(AL23+BZ23)/50</f>
+        <f>SUM(O23+P23+Q23+BL23+BM23+CB23+CC23)/65+SUM(X23+Y23)/44+SUM(AJ23+AK23+AM23+AN23+AO23+AP23+AQ23+BR23+BS23+BT23+BU23+BV23+CH23+CI23+CJ23+CM23)/45+SUM(AX23+AY23+AZ23+BA23+BF23+BG23+BH23)/60+SUM(AL23+BZ23)/50</f>
         <v/>
       </c>
       <c r="CQ23" s="38">
-        <f>SUM(R23+S23+BN23+CD23+CE23)/65+SUM(AB23)/36+SUM(AR23+AS23+BW23+BX23+CK23)/40+SUM(BB23+BC23+BI23+BJ23)/60</f>
+        <f>SUM(R23+S23+BN23+CD23+CE23)/65+SUM(AB23)/36+SUM(AR23+AS23+BW23+BX23+CK23+CN23)/40+SUM(BB23+BC23+BI23+BJ23)/60</f>
         <v/>
       </c>
       <c r="CR23" s="38">
@@ -6679,11 +6706,11 @@
         <v/>
       </c>
       <c r="CP24" s="38">
-        <f>SUM(O24+P24+Q24+BL24+BM24+CB24+CC24)/65+SUM(X24+Y24)/44+SUM(AJ24+AK24+AM24+AN24+AO24+AP24+AQ24+BR24+BS24+BT24+BU24+BV24+CH24+CI24+CJ24)/45+SUM(AX24+AY24+AZ24+BA24+BF24+BG24+BH24)/60+SUM(AL24+BZ24)/50</f>
+        <f>SUM(O24+P24+Q24+BL24+BM24+CB24+CC24)/65+SUM(X24+Y24)/44+SUM(AJ24+AK24+AM24+AN24+AO24+AP24+AQ24+BR24+BS24+BT24+BU24+BV24+CH24+CI24+CJ24+CM24)/45+SUM(AX24+AY24+AZ24+BA24+BF24+BG24+BH24)/60+SUM(AL24+BZ24)/50</f>
         <v/>
       </c>
       <c r="CQ24" s="38">
-        <f>SUM(R24+S24+BN24+CD24+CE24)/65+SUM(AB24)/36+SUM(AR24+AS24+BW24+BX24+CK24)/40+SUM(BB24+BC24+BI24+BJ24)/60</f>
+        <f>SUM(R24+S24+BN24+CD24+CE24)/65+SUM(AB24)/36+SUM(AR24+AS24+BW24+BX24+CK24+CN24)/40+SUM(BB24+BC24+BI24+BJ24)/60</f>
         <v/>
       </c>
       <c r="CR24" s="38">
@@ -6838,11 +6865,11 @@
         <v/>
       </c>
       <c r="CP25" s="38">
-        <f>SUM(O25+P25+Q25+BL25+BM25+CB25+CC25)/65+SUM(X25+Y25)/44+SUM(AJ25+AK25+AM25+AN25+AO25+AP25+AQ25+BR25+BS25+BT25+BU25+BV25+CH25+CI25+CJ25)/45+SUM(AX25+AY25+AZ25+BA25+BF25+BG25+BH25)/60+SUM(AL25+BZ25)/50</f>
+        <f>SUM(O25+P25+Q25+BL25+BM25+CB25+CC25)/65+SUM(X25+Y25)/44+SUM(AJ25+AK25+AM25+AN25+AO25+AP25+AQ25+BR25+BS25+BT25+BU25+BV25+CH25+CI25+CJ25+CM25)/45+SUM(AX25+AY25+AZ25+BA25+BF25+BG25+BH25)/60+SUM(AL25+BZ25)/50</f>
         <v/>
       </c>
       <c r="CQ25" s="38">
-        <f>SUM(R25+S25+BN25+CD25+CE25)/65+SUM(AB25)/36+SUM(AR25+AS25+BW25+BX25+CK25)/40+SUM(BB25+BC25+BI25+BJ25)/60</f>
+        <f>SUM(R25+S25+BN25+CD25+CE25)/65+SUM(AB25)/36+SUM(AR25+AS25+BW25+BX25+CK25+CN25)/40+SUM(BB25+BC25+BI25+BJ25)/60</f>
         <v/>
       </c>
       <c r="CR25" s="38">
@@ -6997,11 +7024,11 @@
         <v/>
       </c>
       <c r="CP26" s="38">
-        <f>SUM(O26+P26+Q26+BL26+BM26+CB26+CC26)/65+SUM(X26+Y26)/44+SUM(AJ26+AK26+AM26+AN26+AO26+AP26+AQ26+BR26+BS26+BT26+BU26+BV26+CH26+CI26+CJ26)/45+SUM(AX26+AY26+AZ26+BA26+BF26+BG26+BH26)/60+SUM(AL26+BZ26)/50</f>
+        <f>SUM(O26+P26+Q26+BL26+BM26+CB26+CC26)/65+SUM(X26+Y26)/44+SUM(AJ26+AK26+AM26+AN26+AO26+AP26+AQ26+BR26+BS26+BT26+BU26+BV26+CH26+CI26+CJ26+CM26)/45+SUM(AX26+AY26+AZ26+BA26+BF26+BG26+BH26)/60+SUM(AL26+BZ26)/50</f>
         <v/>
       </c>
       <c r="CQ26" s="38">
-        <f>SUM(R26+S26+BN26+CD26+CE26)/65+SUM(AB26)/36+SUM(AR26+AS26+BW26+BX26+CK26)/40+SUM(BB26+BC26+BI26+BJ26)/60</f>
+        <f>SUM(R26+S26+BN26+CD26+CE26)/65+SUM(AB26)/36+SUM(AR26+AS26+BW26+BX26+CK26+CN26)/40+SUM(BB26+BC26+BI26+BJ26)/60</f>
         <v/>
       </c>
       <c r="CR26" s="38">
@@ -7156,11 +7183,11 @@
         <v/>
       </c>
       <c r="CP27" s="38">
-        <f>SUM(O27+P27+Q27+BL27+BM27+CB27+CC27)/65+SUM(X27+Y27)/44+SUM(AJ27+AK27+AM27+AN27+AO27+AP27+AQ27+BR27+BS27+BT27+BU27+BV27+CH27+CI27+CJ27)/45+SUM(AX27+AY27+AZ27+BA27+BF27+BG27+BH27)/60+SUM(AL27+BZ27)/50</f>
+        <f>SUM(O27+P27+Q27+BL27+BM27+CB27+CC27)/65+SUM(X27+Y27)/44+SUM(AJ27+AK27+AM27+AN27+AO27+AP27+AQ27+BR27+BS27+BT27+BU27+BV27+CH27+CI27+CJ27+CM27)/45+SUM(AX27+AY27+AZ27+BA27+BF27+BG27+BH27)/60+SUM(AL27+BZ27)/50</f>
         <v/>
       </c>
       <c r="CQ27" s="38">
-        <f>SUM(R27+S27+BN27+CD27+CE27)/65+SUM(AB27)/36+SUM(AR27+AS27+BW27+BX27+CK27)/40+SUM(BB27+BC27+BI27+BJ27)/60</f>
+        <f>SUM(R27+S27+BN27+CD27+CE27)/65+SUM(AB27)/36+SUM(AR27+AS27+BW27+BX27+CK27+CN27)/40+SUM(BB27+BC27+BI27+BJ27)/60</f>
         <v/>
       </c>
       <c r="CR27" s="38">
@@ -7315,11 +7342,11 @@
         <v/>
       </c>
       <c r="CP28" s="38">
-        <f>SUM(O28+P28+Q28+BL28+BM28+CB28+CC28)/65+SUM(X28+Y28)/44+SUM(AJ28+AK28+AM28+AN28+AO28+AP28+AQ28+BR28+BS28+BT28+BU28+BV28+CH28+CI28+CJ28)/45+SUM(AX28+AY28+AZ28+BA28+BF28+BG28+BH28)/60+SUM(AL28+BZ28)/50</f>
+        <f>SUM(O28+P28+Q28+BL28+BM28+CB28+CC28)/65+SUM(X28+Y28)/44+SUM(AJ28+AK28+AM28+AN28+AO28+AP28+AQ28+BR28+BS28+BT28+BU28+BV28+CH28+CI28+CJ28+CM28)/45+SUM(AX28+AY28+AZ28+BA28+BF28+BG28+BH28)/60+SUM(AL28+BZ28)/50</f>
         <v/>
       </c>
       <c r="CQ28" s="38">
-        <f>SUM(R28+S28+BN28+CD28+CE28)/65+SUM(AB28)/36+SUM(AR28+AS28+BW28+BX28+CK28)/40+SUM(BB28+BC28+BI28+BJ28)/60</f>
+        <f>SUM(R28+S28+BN28+CD28+CE28)/65+SUM(AB28)/36+SUM(AR28+AS28+BW28+BX28+CK28+CN28)/40+SUM(BB28+BC28+BI28+BJ28)/60</f>
         <v/>
       </c>
       <c r="CR28" s="38">
@@ -7474,11 +7501,11 @@
         <v/>
       </c>
       <c r="CP29" s="38">
-        <f>SUM(O29+P29+Q29+BL29+BM29+CB29+CC29)/65+SUM(X29+Y29)/44+SUM(AJ29+AK29+AM29+AN29+AO29+AP29+AQ29+BR29+BS29+BT29+BU29+BV29+CH29+CI29+CJ29)/45+SUM(AX29+AY29+AZ29+BA29+BF29+BG29+BH29)/60+SUM(AL29+BZ29)/50</f>
+        <f>SUM(O29+P29+Q29+BL29+BM29+CB29+CC29)/65+SUM(X29+Y29)/44+SUM(AJ29+AK29+AM29+AN29+AO29+AP29+AQ29+BR29+BS29+BT29+BU29+BV29+CH29+CI29+CJ29+CM29)/45+SUM(AX29+AY29+AZ29+BA29+BF29+BG29+BH29)/60+SUM(AL29+BZ29)/50</f>
         <v/>
       </c>
       <c r="CQ29" s="38">
-        <f>SUM(R29+S29+BN29+CD29+CE29)/65+SUM(AB29)/36+SUM(AR29+AS29+BW29+BX29+CK29)/40+SUM(BB29+BC29+BI29+BJ29)/60</f>
+        <f>SUM(R29+S29+BN29+CD29+CE29)/65+SUM(AB29)/36+SUM(AR29+AS29+BW29+BX29+CK29+CN29)/40+SUM(BB29+BC29+BI29+BJ29)/60</f>
         <v/>
       </c>
       <c r="CR29" s="38">
@@ -7633,11 +7660,11 @@
         <v/>
       </c>
       <c r="CP30" s="38">
-        <f>SUM(O30+P30+Q30+BL30+BM30+CB30+CC30)/65+SUM(X30+Y30)/44+SUM(AJ30+AK30+AM30+AN30+AO30+AP30+AQ30+BR30+BS30+BT30+BU30+BV30+CH30+CI30+CJ30)/45+SUM(AX30+AY30+AZ30+BA30+BF30+BG30+BH30)/60+SUM(AL30+BZ30)/50</f>
+        <f>SUM(O30+P30+Q30+BL30+BM30+CB30+CC30)/65+SUM(X30+Y30)/44+SUM(AJ30+AK30+AM30+AN30+AO30+AP30+AQ30+BR30+BS30+BT30+BU30+BV30+CH30+CI30+CJ30+CM30)/45+SUM(AX30+AY30+AZ30+BA30+BF30+BG30+BH30)/60+SUM(AL30+BZ30)/50</f>
         <v/>
       </c>
       <c r="CQ30" s="38">
-        <f>SUM(R30+S30+BN30+CD30+CE30)/65+SUM(AB30)/36+SUM(AR30+AS30+BW30+BX30+CK30)/40+SUM(BB30+BC30+BI30+BJ30)/60</f>
+        <f>SUM(R30+S30+BN30+CD30+CE30)/65+SUM(AB30)/36+SUM(AR30+AS30+BW30+BX30+CK30+CN30)/40+SUM(BB30+BC30+BI30+BJ30)/60</f>
         <v/>
       </c>
       <c r="CR30" s="38">
@@ -7792,11 +7819,11 @@
         <v/>
       </c>
       <c r="CP31" s="38">
-        <f>SUM(O31+P31+Q31+BL31+BM31+CB31+CC31)/65+SUM(X31+Y31)/44+SUM(AJ31+AK31+AM31+AN31+AO31+AP31+AQ31+BR31+BS31+BT31+BU31+BV31+CH31+CI31+CJ31)/45+SUM(AX31+AY31+AZ31+BA31+BF31+BG31+BH31)/60+SUM(AL31+BZ31)/50</f>
+        <f>SUM(O31+P31+Q31+BL31+BM31+CB31+CC31)/65+SUM(X31+Y31)/44+SUM(AJ31+AK31+AM31+AN31+AO31+AP31+AQ31+BR31+BS31+BT31+BU31+BV31+CH31+CI31+CJ31+CM31)/45+SUM(AX31+AY31+AZ31+BA31+BF31+BG31+BH31)/60+SUM(AL31+BZ31)/50</f>
         <v/>
       </c>
       <c r="CQ31" s="38">
-        <f>SUM(R31+S31+BN31+CD31+CE31)/65+SUM(AB31)/36+SUM(AR31+AS31+BW31+BX31+CK31)/40+SUM(BB31+BC31+BI31+BJ31)/60</f>
+        <f>SUM(R31+S31+BN31+CD31+CE31)/65+SUM(AB31)/36+SUM(AR31+AS31+BW31+BX31+CK31+CN31)/40+SUM(BB31+BC31+BI31+BJ31)/60</f>
         <v/>
       </c>
       <c r="CR31" s="38">
@@ -7951,11 +7978,11 @@
         <v/>
       </c>
       <c r="CP32" s="38">
-        <f>SUM(O32+P32+Q32+BL32+BM32+CB32+CC32)/65+SUM(X32+Y32)/44+SUM(AJ32+AK32+AM32+AN32+AO32+AP32+AQ32+BR32+BS32+BT32+BU32+BV32+CH32+CI32+CJ32)/45+SUM(AX32+AY32+AZ32+BA32+BF32+BG32+BH32)/60+SUM(AL32+BZ32)/50</f>
+        <f>SUM(O32+P32+Q32+BL32+BM32+CB32+CC32)/65+SUM(X32+Y32)/44+SUM(AJ32+AK32+AM32+AN32+AO32+AP32+AQ32+BR32+BS32+BT32+BU32+BV32+CH32+CI32+CJ32+CM32)/45+SUM(AX32+AY32+AZ32+BA32+BF32+BG32+BH32)/60+SUM(AL32+BZ32)/50</f>
         <v/>
       </c>
       <c r="CQ32" s="38">
-        <f>SUM(R32+S32+BN32+CD32+CE32)/65+SUM(AB32)/36+SUM(AR32+AS32+BW32+BX32+CK32)/40+SUM(BB32+BC32+BI32+BJ32)/60</f>
+        <f>SUM(R32+S32+BN32+CD32+CE32)/65+SUM(AB32)/36+SUM(AR32+AS32+BW32+BX32+CK32+CN32)/40+SUM(BB32+BC32+BI32+BJ32)/60</f>
         <v/>
       </c>
       <c r="CR32" s="38">
@@ -8110,11 +8137,11 @@
         <v/>
       </c>
       <c r="CP33" s="38">
-        <f>SUM(O33+P33+Q33+BL33+BM33+CB33+CC33)/65+SUM(X33+Y33)/44+SUM(AJ33+AK33+AM33+AN33+AO33+AP33+AQ33+BR33+BS33+BT33+BU33+BV33+CH33+CI33+CJ33)/45+SUM(AX33+AY33+AZ33+BA33+BF33+BG33+BH33)/60+SUM(AL33+BZ33)/50</f>
+        <f>SUM(O33+P33+Q33+BL33+BM33+CB33+CC33)/65+SUM(X33+Y33)/44+SUM(AJ33+AK33+AM33+AN33+AO33+AP33+AQ33+BR33+BS33+BT33+BU33+BV33+CH33+CI33+CJ33+CM33)/45+SUM(AX33+AY33+AZ33+BA33+BF33+BG33+BH33)/60+SUM(AL33+BZ33)/50</f>
         <v/>
       </c>
       <c r="CQ33" s="38">
-        <f>SUM(R33+S33+BN33+CD33+CE33)/65+SUM(AB33)/36+SUM(AR33+AS33+BW33+BX33+CK33)/40+SUM(BB33+BC33+BI33+BJ33)/60</f>
+        <f>SUM(R33+S33+BN33+CD33+CE33)/65+SUM(AB33)/36+SUM(AR33+AS33+BW33+BX33+CK33+CN33)/40+SUM(BB33+BC33+BI33+BJ33)/60</f>
         <v/>
       </c>
       <c r="CR33" s="38">
@@ -8269,11 +8296,11 @@
         <v/>
       </c>
       <c r="CP34" s="38">
-        <f>SUM(O34+P34+Q34+BL34+BM34+CB34+CC34)/65+SUM(X34+Y34)/44+SUM(AJ34+AK34+AM34+AN34+AO34+AP34+AQ34+BR34+BS34+BT34+BU34+BV34+CH34+CI34+CJ34)/45+SUM(AX34+AY34+AZ34+BA34+BF34+BG34+BH34)/60+SUM(AL34+BZ34)/50</f>
+        <f>SUM(O34+P34+Q34+BL34+BM34+CB34+CC34)/65+SUM(X34+Y34)/44+SUM(AJ34+AK34+AM34+AN34+AO34+AP34+AQ34+BR34+BS34+BT34+BU34+BV34+CH34+CI34+CJ34+CM34)/45+SUM(AX34+AY34+AZ34+BA34+BF34+BG34+BH34)/60+SUM(AL34+BZ34)/50</f>
         <v/>
       </c>
       <c r="CQ34" s="38">
-        <f>SUM(R34+S34+BN34+CD34+CE34)/65+SUM(AB34)/36+SUM(AR34+AS34+BW34+BX34+CK34)/40+SUM(BB34+BC34+BI34+BJ34)/60</f>
+        <f>SUM(R34+S34+BN34+CD34+CE34)/65+SUM(AB34)/36+SUM(AR34+AS34+BW34+BX34+CK34+CN34)/40+SUM(BB34+BC34+BI34+BJ34)/60</f>
         <v/>
       </c>
       <c r="CR34" s="38">
@@ -8428,11 +8455,11 @@
         <v/>
       </c>
       <c r="CP35" s="38">
-        <f>SUM(O35+P35+Q35+BL35+BM35+CB35+CC35)/65+SUM(X35+Y35)/44+SUM(AJ35+AK35+AM35+AN35+AO35+AP35+AQ35+BR35+BS35+BT35+BU35+BV35+CH35+CI35+CJ35)/45+SUM(AX35+AY35+AZ35+BA35+BF35+BG35+BH35)/60+SUM(AL35+BZ35)/50</f>
+        <f>SUM(O35+P35+Q35+BL35+BM35+CB35+CC35)/65+SUM(X35+Y35)/44+SUM(AJ35+AK35+AM35+AN35+AO35+AP35+AQ35+BR35+BS35+BT35+BU35+BV35+CH35+CI35+CJ35+CM35)/45+SUM(AX35+AY35+AZ35+BA35+BF35+BG35+BH35)/60+SUM(AL35+BZ35)/50</f>
         <v/>
       </c>
       <c r="CQ35" s="38">
-        <f>SUM(R35+S35+BN35+CD35+CE35)/65+SUM(AB35)/36+SUM(AR35+AS35+BW35+BX35+CK35)/40+SUM(BB35+BC35+BI35+BJ35)/60</f>
+        <f>SUM(R35+S35+BN35+CD35+CE35)/65+SUM(AB35)/36+SUM(AR35+AS35+BW35+BX35+CK35+CN35)/40+SUM(BB35+BC35+BI35+BJ35)/60</f>
         <v/>
       </c>
       <c r="CR35" s="38">
@@ -8587,11 +8614,11 @@
         <v/>
       </c>
       <c r="CP36" s="38">
-        <f>SUM(O36+P36+Q36+BL36+BM36+CB36+CC36)/65+SUM(X36+Y36)/44+SUM(AJ36+AK36+AM36+AN36+AO36+AP36+AQ36+BR36+BS36+BT36+BU36+BV36+CH36+CI36+CJ36)/45+SUM(AX36+AY36+AZ36+BA36+BF36+BG36+BH36)/60+SUM(AL36+BZ36)/50</f>
+        <f>SUM(O36+P36+Q36+BL36+BM36+CB36+CC36)/65+SUM(X36+Y36)/44+SUM(AJ36+AK36+AM36+AN36+AO36+AP36+AQ36+BR36+BS36+BT36+BU36+BV36+CH36+CI36+CJ36+CM36)/45+SUM(AX36+AY36+AZ36+BA36+BF36+BG36+BH36)/60+SUM(AL36+BZ36)/50</f>
         <v/>
       </c>
       <c r="CQ36" s="38">
-        <f>SUM(R36+S36+BN36+CD36+CE36)/65+SUM(AB36)/36+SUM(AR36+AS36+BW36+BX36+CK36)/40+SUM(BB36+BC36+BI36+BJ36)/60</f>
+        <f>SUM(R36+S36+BN36+CD36+CE36)/65+SUM(AB36)/36+SUM(AR36+AS36+BW36+BX36+CK36+CN36)/40+SUM(BB36+BC36+BI36+BJ36)/60</f>
         <v/>
       </c>
       <c r="CR36" s="38">
@@ -8746,11 +8773,11 @@
         <v/>
       </c>
       <c r="CP37" s="38">
-        <f>SUM(O37+P37+Q37+BL37+BM37+CB37+CC37)/65+SUM(X37+Y37)/44+SUM(AJ37+AK37+AM37+AN37+AO37+AP37+AQ37+BR37+BS37+BT37+BU37+BV37+CH37+CI37+CJ37)/45+SUM(AX37+AY37+AZ37+BA37+BF37+BG37+BH37)/60+SUM(AL37+BZ37)/50</f>
+        <f>SUM(O37+P37+Q37+BL37+BM37+CB37+CC37)/65+SUM(X37+Y37)/44+SUM(AJ37+AK37+AM37+AN37+AO37+AP37+AQ37+BR37+BS37+BT37+BU37+BV37+CH37+CI37+CJ37+CM37)/45+SUM(AX37+AY37+AZ37+BA37+BF37+BG37+BH37)/60+SUM(AL37+BZ37)/50</f>
         <v/>
       </c>
       <c r="CQ37" s="38">
-        <f>SUM(R37+S37+BN37+CD37+CE37)/65+SUM(AB37)/36+SUM(AR37+AS37+BW37+BX37+CK37)/40+SUM(BB37+BC37+BI37+BJ37)/60</f>
+        <f>SUM(R37+S37+BN37+CD37+CE37)/65+SUM(AB37)/36+SUM(AR37+AS37+BW37+BX37+CK37+CN37)/40+SUM(BB37+BC37+BI37+BJ37)/60</f>
         <v/>
       </c>
       <c r="CR37" s="38">
@@ -8905,11 +8932,11 @@
         <v/>
       </c>
       <c r="CP38" s="38">
-        <f>SUM(O38+P38+Q38+BL38+BM38+CB38+CC38)/65+SUM(X38+Y38)/44+SUM(AJ38+AK38+AM38+AN38+AO38+AP38+AQ38+BR38+BS38+BT38+BU38+BV38+CH38+CI38+CJ38)/45+SUM(AX38+AY38+AZ38+BA38+BF38+BG38+BH38)/60+SUM(AL38+BZ38)/50</f>
+        <f>SUM(O38+P38+Q38+BL38+BM38+CB38+CC38)/65+SUM(X38+Y38)/44+SUM(AJ38+AK38+AM38+AN38+AO38+AP38+AQ38+BR38+BS38+BT38+BU38+BV38+CH38+CI38+CJ38+CM38)/45+SUM(AX38+AY38+AZ38+BA38+BF38+BG38+BH38)/60+SUM(AL38+BZ38)/50</f>
         <v/>
       </c>
       <c r="CQ38" s="38">
-        <f>SUM(R38+S38+BN38+CD38+CE38)/65+SUM(AB38)/36+SUM(AR38+AS38+BW38+BX38+CK38)/40+SUM(BB38+BC38+BI38+BJ38)/60</f>
+        <f>SUM(R38+S38+BN38+CD38+CE38)/65+SUM(AB38)/36+SUM(AR38+AS38+BW38+BX38+CK38+CN38)/40+SUM(BB38+BC38+BI38+BJ38)/60</f>
         <v/>
       </c>
       <c r="CR38" s="38">
@@ -9064,11 +9091,11 @@
         <v/>
       </c>
       <c r="CP39" s="38">
-        <f>SUM(O39+P39+Q39+BL39+BM39+CB39+CC39)/65+SUM(X39+Y39)/44+SUM(AJ39+AK39+AM39+AN39+AO39+AP39+AQ39+BR39+BS39+BT39+BU39+BV39+CH39+CI39+CJ39)/45+SUM(AX39+AY39+AZ39+BA39+BF39+BG39+BH39)/60+SUM(AL39+BZ39)/50</f>
+        <f>SUM(O39+P39+Q39+BL39+BM39+CB39+CC39)/65+SUM(X39+Y39)/44+SUM(AJ39+AK39+AM39+AN39+AO39+AP39+AQ39+BR39+BS39+BT39+BU39+BV39+CH39+CI39+CJ39+CM39)/45+SUM(AX39+AY39+AZ39+BA39+BF39+BG39+BH39)/60+SUM(AL39+BZ39)/50</f>
         <v/>
       </c>
       <c r="CQ39" s="38">
-        <f>SUM(R39+S39+BN39+CD39+CE39)/65+SUM(AB39)/36+SUM(AR39+AS39+BW39+BX39+CK39)/40+SUM(BB39+BC39+BI39+BJ39)/60</f>
+        <f>SUM(R39+S39+BN39+CD39+CE39)/65+SUM(AB39)/36+SUM(AR39+AS39+BW39+BX39+CK39+CN39)/40+SUM(BB39+BC39+BI39+BJ39)/60</f>
         <v/>
       </c>
       <c r="CR39" s="38">
@@ -9223,11 +9250,11 @@
         <v/>
       </c>
       <c r="CP40" s="38">
-        <f>SUM(O40+P40+Q40+BL40+BM40+CB40+CC40)/65+SUM(X40+Y40)/44+SUM(AJ40+AK40+AM40+AN40+AO40+AP40+AQ40+BR40+BS40+BT40+BU40+BV40+CH40+CI40+CJ40)/45+SUM(AX40+AY40+AZ40+BA40+BF40+BG40+BH40)/60+SUM(AL40+BZ40)/50</f>
+        <f>SUM(O40+P40+Q40+BL40+BM40+CB40+CC40)/65+SUM(X40+Y40)/44+SUM(AJ40+AK40+AM40+AN40+AO40+AP40+AQ40+BR40+BS40+BT40+BU40+BV40+CH40+CI40+CJ40+CM40)/45+SUM(AX40+AY40+AZ40+BA40+BF40+BG40+BH40)/60+SUM(AL40+BZ40)/50</f>
         <v/>
       </c>
       <c r="CQ40" s="38">
-        <f>SUM(R40+S40+BN40+CD40+CE40)/65+SUM(AB40)/36+SUM(AR40+AS40+BW40+BX40+CK40)/40+SUM(BB40+BC40+BI40+BJ40)/60</f>
+        <f>SUM(R40+S40+BN40+CD40+CE40)/65+SUM(AB40)/36+SUM(AR40+AS40+BW40+BX40+CK40+CN40)/40+SUM(BB40+BC40+BI40+BJ40)/60</f>
         <v/>
       </c>
       <c r="CR40" s="38">
@@ -9382,11 +9409,11 @@
         <v/>
       </c>
       <c r="CP41" s="38">
-        <f>SUM(O41+P41+Q41+BL41+BM41+CB41+CC41)/65+SUM(X41+Y41)/44+SUM(AJ41+AK41+AM41+AN41+AO41+AP41+AQ41+BR41+BS41+BT41+BU41+BV41+CH41+CI41+CJ41)/45+SUM(AX41+AY41+AZ41+BA41+BF41+BG41+BH41)/60+SUM(AL41+BZ41)/50</f>
+        <f>SUM(O41+P41+Q41+BL41+BM41+CB41+CC41)/65+SUM(X41+Y41)/44+SUM(AJ41+AK41+AM41+AN41+AO41+AP41+AQ41+BR41+BS41+BT41+BU41+BV41+CH41+CI41+CJ41+CM41)/45+SUM(AX41+AY41+AZ41+BA41+BF41+BG41+BH41)/60+SUM(AL41+BZ41)/50</f>
         <v/>
       </c>
       <c r="CQ41" s="38">
-        <f>SUM(R41+S41+BN41+CD41+CE41)/65+SUM(AB41)/36+SUM(AR41+AS41+BW41+BX41+CK41)/40+SUM(BB41+BC41+BI41+BJ41)/60</f>
+        <f>SUM(R41+S41+BN41+CD41+CE41)/65+SUM(AB41)/36+SUM(AR41+AS41+BW41+BX41+CK41+CN41)/40+SUM(BB41+BC41+BI41+BJ41)/60</f>
         <v/>
       </c>
       <c r="CR41" s="38">
@@ -9541,11 +9568,11 @@
         <v/>
       </c>
       <c r="CP42" s="38">
-        <f>SUM(O42+P42+Q42+BL42+BM42+CB42+CC42)/65+SUM(X42+Y42)/44+SUM(AJ42+AK42+AM42+AN42+AO42+AP42+AQ42+BR42+BS42+BT42+BU42+BV42+CH42+CI42+CJ42)/45+SUM(AX42+AY42+AZ42+BA42+BF42+BG42+BH42)/60+SUM(AL42+BZ42)/50</f>
+        <f>SUM(O42+P42+Q42+BL42+BM42+CB42+CC42)/65+SUM(X42+Y42)/44+SUM(AJ42+AK42+AM42+AN42+AO42+AP42+AQ42+BR42+BS42+BT42+BU42+BV42+CH42+CI42+CJ42+CM42)/45+SUM(AX42+AY42+AZ42+BA42+BF42+BG42+BH42)/60+SUM(AL42+BZ42)/50</f>
         <v/>
       </c>
       <c r="CQ42" s="38">
-        <f>SUM(R42+S42+BN42+CD42+CE42)/65+SUM(AB42)/36+SUM(AR42+AS42+BW42+BX42+CK42)/40+SUM(BB42+BC42+BI42+BJ42)/60</f>
+        <f>SUM(R42+S42+BN42+CD42+CE42)/65+SUM(AB42)/36+SUM(AR42+AS42+BW42+BX42+CK42+CN42)/40+SUM(BB42+BC42+BI42+BJ42)/60</f>
         <v/>
       </c>
       <c r="CR42" s="38">
@@ -9700,11 +9727,11 @@
         <v/>
       </c>
       <c r="CP43" s="38">
-        <f>SUM(O43+P43+Q43+BL43+BM43+CB43+CC43)/65+SUM(X43+Y43)/44+SUM(AJ43+AK43+AM43+AN43+AO43+AP43+AQ43+BR43+BS43+BT43+BU43+BV43+CH43+CI43+CJ43)/45+SUM(AX43+AY43+AZ43+BA43+BF43+BG43+BH43)/60+SUM(AL43+BZ43)/50</f>
+        <f>SUM(O43+P43+Q43+BL43+BM43+CB43+CC43)/65+SUM(X43+Y43)/44+SUM(AJ43+AK43+AM43+AN43+AO43+AP43+AQ43+BR43+BS43+BT43+BU43+BV43+CH43+CI43+CJ43+CM43)/45+SUM(AX43+AY43+AZ43+BA43+BF43+BG43+BH43)/60+SUM(AL43+BZ43)/50</f>
         <v/>
       </c>
       <c r="CQ43" s="38">
-        <f>SUM(R43+S43+BN43+CD43+CE43)/65+SUM(AB43)/36+SUM(AR43+AS43+BW43+BX43+CK43)/40+SUM(BB43+BC43+BI43+BJ43)/60</f>
+        <f>SUM(R43+S43+BN43+CD43+CE43)/65+SUM(AB43)/36+SUM(AR43+AS43+BW43+BX43+CK43+CN43)/40+SUM(BB43+BC43+BI43+BJ43)/60</f>
         <v/>
       </c>
       <c r="CR43" s="38">
@@ -9859,11 +9886,11 @@
         <v/>
       </c>
       <c r="CP44" s="38">
-        <f>SUM(O44+P44+Q44+BL44+BM44+CB44+CC44)/65+SUM(X44+Y44)/44+SUM(AJ44+AK44+AM44+AN44+AO44+AP44+AQ44+BR44+BS44+BT44+BU44+BV44+CH44+CI44+CJ44)/45+SUM(AX44+AY44+AZ44+BA44+BF44+BG44+BH44)/60+SUM(AL44+BZ44)/50</f>
+        <f>SUM(O44+P44+Q44+BL44+BM44+CB44+CC44)/65+SUM(X44+Y44)/44+SUM(AJ44+AK44+AM44+AN44+AO44+AP44+AQ44+BR44+BS44+BT44+BU44+BV44+CH44+CI44+CJ44+CM44)/45+SUM(AX44+AY44+AZ44+BA44+BF44+BG44+BH44)/60+SUM(AL44+BZ44)/50</f>
         <v/>
       </c>
       <c r="CQ44" s="38">
-        <f>SUM(R44+S44+BN44+CD44+CE44)/65+SUM(AB44)/36+SUM(AR44+AS44+BW44+BX44+CK44)/40+SUM(BB44+BC44+BI44+BJ44)/60</f>
+        <f>SUM(R44+S44+BN44+CD44+CE44)/65+SUM(AB44)/36+SUM(AR44+AS44+BW44+BX44+CK44+CN44)/40+SUM(BB44+BC44+BI44+BJ44)/60</f>
         <v/>
       </c>
       <c r="CR44" s="38">
@@ -10018,11 +10045,11 @@
         <v/>
       </c>
       <c r="CP45" s="38">
-        <f>SUM(O45+P45+Q45+BL45+BM45+CB45+CC45)/65+SUM(X45+Y45)/44+SUM(AJ45+AK45+AM45+AN45+AO45+AP45+AQ45+BR45+BS45+BT45+BU45+BV45+CH45+CI45+CJ45)/45+SUM(AX45+AY45+AZ45+BA45+BF45+BG45+BH45)/60+SUM(AL45+BZ45)/50</f>
+        <f>SUM(O45+P45+Q45+BL45+BM45+CB45+CC45)/65+SUM(X45+Y45)/44+SUM(AJ45+AK45+AM45+AN45+AO45+AP45+AQ45+BR45+BS45+BT45+BU45+BV45+CH45+CI45+CJ45+CM45)/45+SUM(AX45+AY45+AZ45+BA45+BF45+BG45+BH45)/60+SUM(AL45+BZ45)/50</f>
         <v/>
       </c>
       <c r="CQ45" s="38">
-        <f>SUM(R45+S45+BN45+CD45+CE45)/65+SUM(AB45)/36+SUM(AR45+AS45+BW45+BX45+CK45)/40+SUM(BB45+BC45+BI45+BJ45)/60</f>
+        <f>SUM(R45+S45+BN45+CD45+CE45)/65+SUM(AB45)/36+SUM(AR45+AS45+BW45+BX45+CK45+CN45)/40+SUM(BB45+BC45+BI45+BJ45)/60</f>
         <v/>
       </c>
       <c r="CR45" s="38">
@@ -10177,11 +10204,11 @@
         <v/>
       </c>
       <c r="CP46" s="38">
-        <f>SUM(O46+P46+Q46+BL46+BM46+CB46+CC46)/65+SUM(X46+Y46)/44+SUM(AJ46+AK46+AM46+AN46+AO46+AP46+AQ46+BR46+BS46+BT46+BU46+BV46+CH46+CI46+CJ46)/45+SUM(AX46+AY46+AZ46+BA46+BF46+BG46+BH46)/60+SUM(AL46+BZ46)/50</f>
+        <f>SUM(O46+P46+Q46+BL46+BM46+CB46+CC46)/65+SUM(X46+Y46)/44+SUM(AJ46+AK46+AM46+AN46+AO46+AP46+AQ46+BR46+BS46+BT46+BU46+BV46+CH46+CI46+CJ46+CM46)/45+SUM(AX46+AY46+AZ46+BA46+BF46+BG46+BH46)/60+SUM(AL46+BZ46)/50</f>
         <v/>
       </c>
       <c r="CQ46" s="38">
-        <f>SUM(R46+S46+BN46+CD46+CE46)/65+SUM(AB46)/36+SUM(AR46+AS46+BW46+BX46+CK46)/40+SUM(BB46+BC46+BI46+BJ46)/60</f>
+        <f>SUM(R46+S46+BN46+CD46+CE46)/65+SUM(AB46)/36+SUM(AR46+AS46+BW46+BX46+CK46+CN46)/40+SUM(BB46+BC46+BI46+BJ46)/60</f>
         <v/>
       </c>
       <c r="CR46" s="38">
@@ -10336,11 +10363,11 @@
         <v/>
       </c>
       <c r="CP47" s="38">
-        <f>SUM(O47+P47+Q47+BL47+BM47+CB47+CC47)/65+SUM(X47+Y47)/44+SUM(AJ47+AK47+AM47+AN47+AO47+AP47+AQ47+BR47+BS47+BT47+BU47+BV47+CH47+CI47+CJ47)/45+SUM(AX47+AY47+AZ47+BA47+BF47+BG47+BH47)/60+SUM(AL47+BZ47)/50</f>
+        <f>SUM(O47+P47+Q47+BL47+BM47+CB47+CC47)/65+SUM(X47+Y47)/44+SUM(AJ47+AK47+AM47+AN47+AO47+AP47+AQ47+BR47+BS47+BT47+BU47+BV47+CH47+CI47+CJ47+CM47)/45+SUM(AX47+AY47+AZ47+BA47+BF47+BG47+BH47)/60+SUM(AL47+BZ47)/50</f>
         <v/>
       </c>
       <c r="CQ47" s="38">
-        <f>SUM(R47+S47+BN47+CD47+CE47)/65+SUM(AB47)/36+SUM(AR47+AS47+BW47+BX47+CK47)/40+SUM(BB47+BC47+BI47+BJ47)/60</f>
+        <f>SUM(R47+S47+BN47+CD47+CE47)/65+SUM(AB47)/36+SUM(AR47+AS47+BW47+BX47+CK47+CN47)/40+SUM(BB47+BC47+BI47+BJ47)/60</f>
         <v/>
       </c>
       <c r="CR47" s="38">
@@ -10495,11 +10522,11 @@
         <v/>
       </c>
       <c r="CP48" s="38">
-        <f>SUM(O48+P48+Q48+BL48+BM48+CB48+CC48)/65+SUM(X48+Y48)/44+SUM(AJ48+AK48+AM48+AN48+AO48+AP48+AQ48+BR48+BS48+BT48+BU48+BV48+CH48+CI48+CJ48)/45+SUM(AX48+AY48+AZ48+BA48+BF48+BG48+BH48)/60+SUM(AL48+BZ48)/50</f>
+        <f>SUM(O48+P48+Q48+BL48+BM48+CB48+CC48)/65+SUM(X48+Y48)/44+SUM(AJ48+AK48+AM48+AN48+AO48+AP48+AQ48+BR48+BS48+BT48+BU48+BV48+CH48+CI48+CJ48+CM48)/45+SUM(AX48+AY48+AZ48+BA48+BF48+BG48+BH48)/60+SUM(AL48+BZ48)/50</f>
         <v/>
       </c>
       <c r="CQ48" s="38">
-        <f>SUM(R48+S48+BN48+CD48+CE48)/65+SUM(AB48)/36+SUM(AR48+AS48+BW48+BX48+CK48)/40+SUM(BB48+BC48+BI48+BJ48)/60</f>
+        <f>SUM(R48+S48+BN48+CD48+CE48)/65+SUM(AB48)/36+SUM(AR48+AS48+BW48+BX48+CK48+CN48)/40+SUM(BB48+BC48+BI48+BJ48)/60</f>
         <v/>
       </c>
       <c r="CR48" s="38">
@@ -10654,11 +10681,11 @@
         <v/>
       </c>
       <c r="CP49" s="38">
-        <f>SUM(O49+P49+Q49+BL49+BM49+CB49+CC49)/65+SUM(X49+Y49)/44+SUM(AJ49+AK49+AM49+AN49+AO49+AP49+AQ49+BR49+BS49+BT49+BU49+BV49+CH49+CI49+CJ49)/45+SUM(AX49+AY49+AZ49+BA49+BF49+BG49+BH49)/60+SUM(AL49+BZ49)/50</f>
+        <f>SUM(O49+P49+Q49+BL49+BM49+CB49+CC49)/65+SUM(X49+Y49)/44+SUM(AJ49+AK49+AM49+AN49+AO49+AP49+AQ49+BR49+BS49+BT49+BU49+BV49+CH49+CI49+CJ49+CM49)/45+SUM(AX49+AY49+AZ49+BA49+BF49+BG49+BH49)/60+SUM(AL49+BZ49)/50</f>
         <v/>
       </c>
       <c r="CQ49" s="38">
-        <f>SUM(R49+S49+BN49+CD49+CE49)/65+SUM(AB49)/36+SUM(AR49+AS49+BW49+BX49+CK49)/40+SUM(BB49+BC49+BI49+BJ49)/60</f>
+        <f>SUM(R49+S49+BN49+CD49+CE49)/65+SUM(AB49)/36+SUM(AR49+AS49+BW49+BX49+CK49+CN49)/40+SUM(BB49+BC49+BI49+BJ49)/60</f>
         <v/>
       </c>
       <c r="CR49" s="38">
@@ -10813,11 +10840,11 @@
         <v/>
       </c>
       <c r="CP50" s="38">
-        <f>SUM(O50+P50+Q50+BL50+BM50+CB50+CC50)/65+SUM(X50+Y50)/44+SUM(AJ50+AK50+AM50+AN50+AO50+AP50+AQ50+BR50+BS50+BT50+BU50+BV50+CH50+CI50+CJ50)/45+SUM(AX50+AY50+AZ50+BA50+BF50+BG50+BH50)/60+SUM(AL50+BZ50)/50</f>
+        <f>SUM(O50+P50+Q50+BL50+BM50+CB50+CC50)/65+SUM(X50+Y50)/44+SUM(AJ50+AK50+AM50+AN50+AO50+AP50+AQ50+BR50+BS50+BT50+BU50+BV50+CH50+CI50+CJ50+CM50)/45+SUM(AX50+AY50+AZ50+BA50+BF50+BG50+BH50)/60+SUM(AL50+BZ50)/50</f>
         <v/>
       </c>
       <c r="CQ50" s="38">
-        <f>SUM(R50+S50+BN50+CD50+CE50)/65+SUM(AB50)/36+SUM(AR50+AS50+BW50+BX50+CK50)/40+SUM(BB50+BC50+BI50+BJ50)/60</f>
+        <f>SUM(R50+S50+BN50+CD50+CE50)/65+SUM(AB50)/36+SUM(AR50+AS50+BW50+BX50+CK50+CN50)/40+SUM(BB50+BC50+BI50+BJ50)/60</f>
         <v/>
       </c>
       <c r="CR50" s="38">
@@ -10972,11 +10999,11 @@
         <v/>
       </c>
       <c r="CP51" s="38">
-        <f>SUM(O51+P51+Q51+BL51+BM51+CB51+CC51)/65+SUM(X51+Y51)/44+SUM(AJ51+AK51+AM51+AN51+AO51+AP51+AQ51+BR51+BS51+BT51+BU51+BV51+CH51+CI51+CJ51)/45+SUM(AX51+AY51+AZ51+BA51+BF51+BG51+BH51)/60+SUM(AL51+BZ51)/50</f>
+        <f>SUM(O51+P51+Q51+BL51+BM51+CB51+CC51)/65+SUM(X51+Y51)/44+SUM(AJ51+AK51+AM51+AN51+AO51+AP51+AQ51+BR51+BS51+BT51+BU51+BV51+CH51+CI51+CJ51+CM51)/45+SUM(AX51+AY51+AZ51+BA51+BF51+BG51+BH51)/60+SUM(AL51+BZ51)/50</f>
         <v/>
       </c>
       <c r="CQ51" s="38">
-        <f>SUM(R51+S51+BN51+CD51+CE51)/65+SUM(AB51)/36+SUM(AR51+AS51+BW51+BX51+CK51)/40+SUM(BB51+BC51+BI51+BJ51)/60</f>
+        <f>SUM(R51+S51+BN51+CD51+CE51)/65+SUM(AB51)/36+SUM(AR51+AS51+BW51+BX51+CK51+CN51)/40+SUM(BB51+BC51+BI51+BJ51)/60</f>
         <v/>
       </c>
       <c r="CR51" s="38">
@@ -11131,11 +11158,11 @@
         <v/>
       </c>
       <c r="CP52" s="38">
-        <f>SUM(O52+P52+Q52+BL52+BM52+CB52+CC52)/65+SUM(X52+Y52)/44+SUM(AJ52+AK52+AM52+AN52+AO52+AP52+AQ52+BR52+BS52+BT52+BU52+BV52+CH52+CI52+CJ52)/45+SUM(AX52+AY52+AZ52+BA52+BF52+BG52+BH52)/60+SUM(AL52+BZ52)/50</f>
+        <f>SUM(O52+P52+Q52+BL52+BM52+CB52+CC52)/65+SUM(X52+Y52)/44+SUM(AJ52+AK52+AM52+AN52+AO52+AP52+AQ52+BR52+BS52+BT52+BU52+BV52+CH52+CI52+CJ52+CM52)/45+SUM(AX52+AY52+AZ52+BA52+BF52+BG52+BH52)/60+SUM(AL52+BZ52)/50</f>
         <v/>
       </c>
       <c r="CQ52" s="38">
-        <f>SUM(R52+S52+BN52+CD52+CE52)/65+SUM(AB52)/36+SUM(AR52+AS52+BW52+BX52+CK52)/40+SUM(BB52+BC52+BI52+BJ52)/60</f>
+        <f>SUM(R52+S52+BN52+CD52+CE52)/65+SUM(AB52)/36+SUM(AR52+AS52+BW52+BX52+CK52+CN52)/40+SUM(BB52+BC52+BI52+BJ52)/60</f>
         <v/>
       </c>
       <c r="CR52" s="38">
@@ -11290,11 +11317,11 @@
         <v/>
       </c>
       <c r="CP53" s="38">
-        <f>SUM(O53+P53+Q53+BL53+BM53+CB53+CC53)/65+SUM(X53+Y53)/44+SUM(AJ53+AK53+AM53+AN53+AO53+AP53+AQ53+BR53+BS53+BT53+BU53+BV53+CH53+CI53+CJ53)/45+SUM(AX53+AY53+AZ53+BA53+BF53+BG53+BH53)/60+SUM(AL53+BZ53)/50</f>
+        <f>SUM(O53+P53+Q53+BL53+BM53+CB53+CC53)/65+SUM(X53+Y53)/44+SUM(AJ53+AK53+AM53+AN53+AO53+AP53+AQ53+BR53+BS53+BT53+BU53+BV53+CH53+CI53+CJ53+CM53)/45+SUM(AX53+AY53+AZ53+BA53+BF53+BG53+BH53)/60+SUM(AL53+BZ53)/50</f>
         <v/>
       </c>
       <c r="CQ53" s="38">
-        <f>SUM(R53+S53+BN53+CD53+CE53)/65+SUM(AB53)/36+SUM(AR53+AS53+BW53+BX53+CK53)/40+SUM(BB53+BC53+BI53+BJ53)/60</f>
+        <f>SUM(R53+S53+BN53+CD53+CE53)/65+SUM(AB53)/36+SUM(AR53+AS53+BW53+BX53+CK53+CN53)/40+SUM(BB53+BC53+BI53+BJ53)/60</f>
         <v/>
       </c>
       <c r="CR53" s="38">
@@ -11449,11 +11476,11 @@
         <v/>
       </c>
       <c r="CP54" s="38">
-        <f>SUM(O54+P54+Q54+BL54+BM54+CB54+CC54)/65+SUM(X54+Y54)/44+SUM(AJ54+AK54+AM54+AN54+AO54+AP54+AQ54+BR54+BS54+BT54+BU54+BV54+CH54+CI54+CJ54)/45+SUM(AX54+AY54+AZ54+BA54+BF54+BG54+BH54)/60+SUM(AL54+BZ54)/50</f>
+        <f>SUM(O54+P54+Q54+BL54+BM54+CB54+CC54)/65+SUM(X54+Y54)/44+SUM(AJ54+AK54+AM54+AN54+AO54+AP54+AQ54+BR54+BS54+BT54+BU54+BV54+CH54+CI54+CJ54+CM54)/45+SUM(AX54+AY54+AZ54+BA54+BF54+BG54+BH54)/60+SUM(AL54+BZ54)/50</f>
         <v/>
       </c>
       <c r="CQ54" s="38">
-        <f>SUM(R54+S54+BN54+CD54+CE54)/65+SUM(AB54)/36+SUM(AR54+AS54+BW54+BX54+CK54)/40+SUM(BB54+BC54+BI54+BJ54)/60</f>
+        <f>SUM(R54+S54+BN54+CD54+CE54)/65+SUM(AB54)/36+SUM(AR54+AS54+BW54+BX54+CK54+CN54)/40+SUM(BB54+BC54+BI54+BJ54)/60</f>
         <v/>
       </c>
       <c r="CR54" s="38">
@@ -11608,11 +11635,11 @@
         <v/>
       </c>
       <c r="CP55" s="38">
-        <f>SUM(O55+P55+Q55+BL55+BM55+CB55+CC55)/65+SUM(X55+Y55)/44+SUM(AJ55+AK55+AM55+AN55+AO55+AP55+AQ55+BR55+BS55+BT55+BU55+BV55+CH55+CI55+CJ55)/45+SUM(AX55+AY55+AZ55+BA55+BF55+BG55+BH55)/60+SUM(AL55+BZ55)/50</f>
+        <f>SUM(O55+P55+Q55+BL55+BM55+CB55+CC55)/65+SUM(X55+Y55)/44+SUM(AJ55+AK55+AM55+AN55+AO55+AP55+AQ55+BR55+BS55+BT55+BU55+BV55+CH55+CI55+CJ55+CM55)/45+SUM(AX55+AY55+AZ55+BA55+BF55+BG55+BH55)/60+SUM(AL55+BZ55)/50</f>
         <v/>
       </c>
       <c r="CQ55" s="38">
-        <f>SUM(R55+S55+BN55+CD55+CE55)/65+SUM(AB55)/36+SUM(AR55+AS55+BW55+BX55+CK55)/40+SUM(BB55+BC55+BI55+BJ55)/60</f>
+        <f>SUM(R55+S55+BN55+CD55+CE55)/65+SUM(AB55)/36+SUM(AR55+AS55+BW55+BX55+CK55+CN55)/40+SUM(BB55+BC55+BI55+BJ55)/60</f>
         <v/>
       </c>
       <c r="CR55" s="38">
@@ -11767,11 +11794,11 @@
         <v/>
       </c>
       <c r="CP56" s="38">
-        <f>SUM(O56+P56+Q56+BL56+BM56+CB56+CC56)/65+SUM(X56+Y56)/44+SUM(AJ56+AK56+AM56+AN56+AO56+AP56+AQ56+BR56+BS56+BT56+BU56+BV56+CH56+CI56+CJ56)/45+SUM(AX56+AY56+AZ56+BA56+BF56+BG56+BH56)/60+SUM(AL56+BZ56)/50</f>
+        <f>SUM(O56+P56+Q56+BL56+BM56+CB56+CC56)/65+SUM(X56+Y56)/44+SUM(AJ56+AK56+AM56+AN56+AO56+AP56+AQ56+BR56+BS56+BT56+BU56+BV56+CH56+CI56+CJ56+CM56)/45+SUM(AX56+AY56+AZ56+BA56+BF56+BG56+BH56)/60+SUM(AL56+BZ56)/50</f>
         <v/>
       </c>
       <c r="CQ56" s="38">
-        <f>SUM(R56+S56+BN56+CD56+CE56)/65+SUM(AB56)/36+SUM(AR56+AS56+BW56+BX56+CK56)/40+SUM(BB56+BC56+BI56+BJ56)/60</f>
+        <f>SUM(R56+S56+BN56+CD56+CE56)/65+SUM(AB56)/36+SUM(AR56+AS56+BW56+BX56+CK56+CN56)/40+SUM(BB56+BC56+BI56+BJ56)/60</f>
         <v/>
       </c>
       <c r="CR56" s="38">
@@ -11926,11 +11953,11 @@
         <v/>
       </c>
       <c r="CP57" s="38">
-        <f>SUM(O57+P57+Q57+BL57+BM57+CB57+CC57)/65+SUM(X57+Y57)/44+SUM(AJ57+AK57+AM57+AN57+AO57+AP57+AQ57+BR57+BS57+BT57+BU57+BV57+CH57+CI57+CJ57)/45+SUM(AX57+AY57+AZ57+BA57+BF57+BG57+BH57)/60+SUM(AL57+BZ57)/50</f>
+        <f>SUM(O57+P57+Q57+BL57+BM57+CB57+CC57)/65+SUM(X57+Y57)/44+SUM(AJ57+AK57+AM57+AN57+AO57+AP57+AQ57+BR57+BS57+BT57+BU57+BV57+CH57+CI57+CJ57+CM57)/45+SUM(AX57+AY57+AZ57+BA57+BF57+BG57+BH57)/60+SUM(AL57+BZ57)/50</f>
         <v/>
       </c>
       <c r="CQ57" s="38">
-        <f>SUM(R57+S57+BN57+CD57+CE57)/65+SUM(AB57)/36+SUM(AR57+AS57+BW57+BX57+CK57)/40+SUM(BB57+BC57+BI57+BJ57)/60</f>
+        <f>SUM(R57+S57+BN57+CD57+CE57)/65+SUM(AB57)/36+SUM(AR57+AS57+BW57+BX57+CK57+CN57)/40+SUM(BB57+BC57+BI57+BJ57)/60</f>
         <v/>
       </c>
       <c r="CR57" s="38">
@@ -12085,11 +12112,11 @@
         <v/>
       </c>
       <c r="CP58" s="38">
-        <f>SUM(O58+P58+Q58+BL58+BM58+CB58+CC58)/65+SUM(X58+Y58)/44+SUM(AJ58+AK58+AM58+AN58+AO58+AP58+AQ58+BR58+BS58+BT58+BU58+BV58+CH58+CI58+CJ58)/45+SUM(AX58+AY58+AZ58+BA58+BF58+BG58+BH58)/60+SUM(AL58+BZ58)/50</f>
+        <f>SUM(O58+P58+Q58+BL58+BM58+CB58+CC58)/65+SUM(X58+Y58)/44+SUM(AJ58+AK58+AM58+AN58+AO58+AP58+AQ58+BR58+BS58+BT58+BU58+BV58+CH58+CI58+CJ58+CM58)/45+SUM(AX58+AY58+AZ58+BA58+BF58+BG58+BH58)/60+SUM(AL58+BZ58)/50</f>
         <v/>
       </c>
       <c r="CQ58" s="38">
-        <f>SUM(R58+S58+BN58+CD58+CE58)/65+SUM(AB58)/36+SUM(AR58+AS58+BW58+BX58+CK58)/40+SUM(BB58+BC58+BI58+BJ58)/60</f>
+        <f>SUM(R58+S58+BN58+CD58+CE58)/65+SUM(AB58)/36+SUM(AR58+AS58+BW58+BX58+CK58+CN58)/40+SUM(BB58+BC58+BI58+BJ58)/60</f>
         <v/>
       </c>
       <c r="CR58" s="38">
@@ -12244,11 +12271,11 @@
         <v/>
       </c>
       <c r="CP59" s="38">
-        <f>SUM(O59+P59+Q59+BL59+BM59+CB59+CC59)/65+SUM(X59+Y59)/44+SUM(AJ59+AK59+AM59+AN59+AO59+AP59+AQ59+BR59+BS59+BT59+BU59+BV59+CH59+CI59+CJ59)/45+SUM(AX59+AY59+AZ59+BA59+BF59+BG59+BH59)/60+SUM(AL59+BZ59)/50</f>
+        <f>SUM(O59+P59+Q59+BL59+BM59+CB59+CC59)/65+SUM(X59+Y59)/44+SUM(AJ59+AK59+AM59+AN59+AO59+AP59+AQ59+BR59+BS59+BT59+BU59+BV59+CH59+CI59+CJ59+CM59)/45+SUM(AX59+AY59+AZ59+BA59+BF59+BG59+BH59)/60+SUM(AL59+BZ59)/50</f>
         <v/>
       </c>
       <c r="CQ59" s="38">
-        <f>SUM(R59+S59+BN59+CD59+CE59)/65+SUM(AB59)/36+SUM(AR59+AS59+BW59+BX59+CK59)/40+SUM(BB59+BC59+BI59+BJ59)/60</f>
+        <f>SUM(R59+S59+BN59+CD59+CE59)/65+SUM(AB59)/36+SUM(AR59+AS59+BW59+BX59+CK59+CN59)/40+SUM(BB59+BC59+BI59+BJ59)/60</f>
         <v/>
       </c>
       <c r="CR59" s="38">
@@ -12403,11 +12430,11 @@
         <v/>
       </c>
       <c r="CP60" s="38">
-        <f>SUM(O60+P60+Q60+BL60+BM60+CB60+CC60)/65+SUM(X60+Y60)/44+SUM(AJ60+AK60+AM60+AN60+AO60+AP60+AQ60+BR60+BS60+BT60+BU60+BV60+CH60+CI60+CJ60)/45+SUM(AX60+AY60+AZ60+BA60+BF60+BG60+BH60)/60+SUM(AL60+BZ60)/50</f>
+        <f>SUM(O60+P60+Q60+BL60+BM60+CB60+CC60)/65+SUM(X60+Y60)/44+SUM(AJ60+AK60+AM60+AN60+AO60+AP60+AQ60+BR60+BS60+BT60+BU60+BV60+CH60+CI60+CJ60+CM60)/45+SUM(AX60+AY60+AZ60+BA60+BF60+BG60+BH60)/60+SUM(AL60+BZ60)/50</f>
         <v/>
       </c>
       <c r="CQ60" s="38">
-        <f>SUM(R60+S60+BN60+CD60+CE60)/65+SUM(AB60)/36+SUM(AR60+AS60+BW60+BX60+CK60)/40+SUM(BB60+BC60+BI60+BJ60)/60</f>
+        <f>SUM(R60+S60+BN60+CD60+CE60)/65+SUM(AB60)/36+SUM(AR60+AS60+BW60+BX60+CK60+CN60)/40+SUM(BB60+BC60+BI60+BJ60)/60</f>
         <v/>
       </c>
       <c r="CR60" s="38">
@@ -12562,11 +12589,11 @@
         <v/>
       </c>
       <c r="CP61" s="38">
-        <f>SUM(O61+P61+Q61+BL61+BM61+CB61+CC61)/65+SUM(X61+Y61)/44+SUM(AJ61+AK61+AM61+AN61+AO61+AP61+AQ61+BR61+BS61+BT61+BU61+BV61+CH61+CI61+CJ61)/45+SUM(AX61+AY61+AZ61+BA61+BF61+BG61+BH61)/60+SUM(AL61+BZ61)/50</f>
+        <f>SUM(O61+P61+Q61+BL61+BM61+CB61+CC61)/65+SUM(X61+Y61)/44+SUM(AJ61+AK61+AM61+AN61+AO61+AP61+AQ61+BR61+BS61+BT61+BU61+BV61+CH61+CI61+CJ61+CM61)/45+SUM(AX61+AY61+AZ61+BA61+BF61+BG61+BH61)/60+SUM(AL61+BZ61)/50</f>
         <v/>
       </c>
       <c r="CQ61" s="38">
-        <f>SUM(R61+S61+BN61+CD61+CE61)/65+SUM(AB61)/36+SUM(AR61+AS61+BW61+BX61+CK61)/40+SUM(BB61+BC61+BI61+BJ61)/60</f>
+        <f>SUM(R61+S61+BN61+CD61+CE61)/65+SUM(AB61)/36+SUM(AR61+AS61+BW61+BX61+CK61+CN61)/40+SUM(BB61+BC61+BI61+BJ61)/60</f>
         <v/>
       </c>
       <c r="CR61" s="38">
@@ -12721,11 +12748,11 @@
         <v/>
       </c>
       <c r="CP62" s="38">
-        <f>SUM(O62+P62+Q62+BL62+BM62+CB62+CC62)/65+SUM(X62+Y62)/44+SUM(AJ62+AK62+AM62+AN62+AO62+AP62+AQ62+BR62+BS62+BT62+BU62+BV62+CH62+CI62+CJ62)/45+SUM(AX62+AY62+AZ62+BA62+BF62+BG62+BH62)/60+SUM(AL62+BZ62)/50</f>
+        <f>SUM(O62+P62+Q62+BL62+BM62+CB62+CC62)/65+SUM(X62+Y62)/44+SUM(AJ62+AK62+AM62+AN62+AO62+AP62+AQ62+BR62+BS62+BT62+BU62+BV62+CH62+CI62+CJ62+CM62)/45+SUM(AX62+AY62+AZ62+BA62+BF62+BG62+BH62)/60+SUM(AL62+BZ62)/50</f>
         <v/>
       </c>
       <c r="CQ62" s="38">
-        <f>SUM(R62+S62+BN62+CD62+CE62)/65+SUM(AB62)/36+SUM(AR62+AS62+BW62+BX62+CK62)/40+SUM(BB62+BC62+BI62+BJ62)/60</f>
+        <f>SUM(R62+S62+BN62+CD62+CE62)/65+SUM(AB62)/36+SUM(AR62+AS62+BW62+BX62+CK62+CN62)/40+SUM(BB62+BC62+BI62+BJ62)/60</f>
         <v/>
       </c>
       <c r="CR62" s="38">
@@ -12880,11 +12907,11 @@
         <v/>
       </c>
       <c r="CP63" s="38">
-        <f>SUM(O63+P63+Q63+BL63+BM63+CB63+CC63)/65+SUM(X63+Y63)/44+SUM(AJ63+AK63+AM63+AN63+AO63+AP63+AQ63+BR63+BS63+BT63+BU63+BV63+CH63+CI63+CJ63)/45+SUM(AX63+AY63+AZ63+BA63+BF63+BG63+BH63)/60+SUM(AL63+BZ63)/50</f>
+        <f>SUM(O63+P63+Q63+BL63+BM63+CB63+CC63)/65+SUM(X63+Y63)/44+SUM(AJ63+AK63+AM63+AN63+AO63+AP63+AQ63+BR63+BS63+BT63+BU63+BV63+CH63+CI63+CJ63+CM63)/45+SUM(AX63+AY63+AZ63+BA63+BF63+BG63+BH63)/60+SUM(AL63+BZ63)/50</f>
         <v/>
       </c>
       <c r="CQ63" s="38">
-        <f>SUM(R63+S63+BN63+CD63+CE63)/65+SUM(AB63)/36+SUM(AR63+AS63+BW63+BX63+CK63)/40+SUM(BB63+BC63+BI63+BJ63)/60</f>
+        <f>SUM(R63+S63+BN63+CD63+CE63)/65+SUM(AB63)/36+SUM(AR63+AS63+BW63+BX63+CK63+CN63)/40+SUM(BB63+BC63+BI63+BJ63)/60</f>
         <v/>
       </c>
       <c r="CR63" s="38">
@@ -13039,11 +13066,11 @@
         <v/>
       </c>
       <c r="CP64" s="38">
-        <f>SUM(O64+P64+Q64+BL64+BM64+CB64+CC64)/65+SUM(X64+Y64)/44+SUM(AJ64+AK64+AM64+AN64+AO64+AP64+AQ64+BR64+BS64+BT64+BU64+BV64+CH64+CI64+CJ64)/45+SUM(AX64+AY64+AZ64+BA64+BF64+BG64+BH64)/60+SUM(AL64+BZ64)/50</f>
+        <f>SUM(O64+P64+Q64+BL64+BM64+CB64+CC64)/65+SUM(X64+Y64)/44+SUM(AJ64+AK64+AM64+AN64+AO64+AP64+AQ64+BR64+BS64+BT64+BU64+BV64+CH64+CI64+CJ64+CM64)/45+SUM(AX64+AY64+AZ64+BA64+BF64+BG64+BH64)/60+SUM(AL64+BZ64)/50</f>
         <v/>
       </c>
       <c r="CQ64" s="38">
-        <f>SUM(R64+S64+BN64+CD64+CE64)/65+SUM(AB64)/36+SUM(AR64+AS64+BW64+BX64+CK64)/40+SUM(BB64+BC64+BI64+BJ64)/60</f>
+        <f>SUM(R64+S64+BN64+CD64+CE64)/65+SUM(AB64)/36+SUM(AR64+AS64+BW64+BX64+CK64+CN64)/40+SUM(BB64+BC64+BI64+BJ64)/60</f>
         <v/>
       </c>
       <c r="CR64" s="38">
@@ -13198,11 +13225,11 @@
         <v/>
       </c>
       <c r="CP65" s="38">
-        <f>SUM(O65+P65+Q65+BL65+BM65+CB65+CC65)/65+SUM(X65+Y65)/44+SUM(AJ65+AK65+AM65+AN65+AO65+AP65+AQ65+BR65+BS65+BT65+BU65+BV65+CH65+CI65+CJ65)/45+SUM(AX65+AY65+AZ65+BA65+BF65+BG65+BH65)/60+SUM(AL65+BZ65)/50</f>
+        <f>SUM(O65+P65+Q65+BL65+BM65+CB65+CC65)/65+SUM(X65+Y65)/44+SUM(AJ65+AK65+AM65+AN65+AO65+AP65+AQ65+BR65+BS65+BT65+BU65+BV65+CH65+CI65+CJ65+CM65)/45+SUM(AX65+AY65+AZ65+BA65+BF65+BG65+BH65)/60+SUM(AL65+BZ65)/50</f>
         <v/>
       </c>
       <c r="CQ65" s="38">
-        <f>SUM(R65+S65+BN65+CD65+CE65)/65+SUM(AB65)/36+SUM(AR65+AS65+BW65+BX65+CK65)/40+SUM(BB65+BC65+BI65+BJ65)/60</f>
+        <f>SUM(R65+S65+BN65+CD65+CE65)/65+SUM(AB65)/36+SUM(AR65+AS65+BW65+BX65+CK65+CN65)/40+SUM(BB65+BC65+BI65+BJ65)/60</f>
         <v/>
       </c>
       <c r="CR65" s="38">
@@ -13357,11 +13384,11 @@
         <v/>
       </c>
       <c r="CP66" s="38">
-        <f>SUM(O66+P66+Q66+BL66+BM66+CB66+CC66)/65+SUM(X66+Y66)/44+SUM(AJ66+AK66+AM66+AN66+AO66+AP66+AQ66+BR66+BS66+BT66+BU66+BV66+CH66+CI66+CJ66)/45+SUM(AX66+AY66+AZ66+BA66+BF66+BG66+BH66)/60+SUM(AL66+BZ66)/50</f>
+        <f>SUM(O66+P66+Q66+BL66+BM66+CB66+CC66)/65+SUM(X66+Y66)/44+SUM(AJ66+AK66+AM66+AN66+AO66+AP66+AQ66+BR66+BS66+BT66+BU66+BV66+CH66+CI66+CJ66+CM66)/45+SUM(AX66+AY66+AZ66+BA66+BF66+BG66+BH66)/60+SUM(AL66+BZ66)/50</f>
         <v/>
       </c>
       <c r="CQ66" s="38">
-        <f>SUM(R66+S66+BN66+CD66+CE66)/65+SUM(AB66)/36+SUM(AR66+AS66+BW66+BX66+CK66)/40+SUM(BB66+BC66+BI66+BJ66)/60</f>
+        <f>SUM(R66+S66+BN66+CD66+CE66)/65+SUM(AB66)/36+SUM(AR66+AS66+BW66+BX66+CK66+CN66)/40+SUM(BB66+BC66+BI66+BJ66)/60</f>
         <v/>
       </c>
       <c r="CR66" s="38">
@@ -13516,11 +13543,11 @@
         <v/>
       </c>
       <c r="CP67" s="38">
-        <f>SUM(O67+P67+Q67+BL67+BM67+CB67+CC67)/65+SUM(X67+Y67)/44+SUM(AJ67+AK67+AM67+AN67+AO67+AP67+AQ67+BR67+BS67+BT67+BU67+BV67+CH67+CI67+CJ67)/45+SUM(AX67+AY67+AZ67+BA67+BF67+BG67+BH67)/60+SUM(AL67+BZ67)/50</f>
+        <f>SUM(O67+P67+Q67+BL67+BM67+CB67+CC67)/65+SUM(X67+Y67)/44+SUM(AJ67+AK67+AM67+AN67+AO67+AP67+AQ67+BR67+BS67+BT67+BU67+BV67+CH67+CI67+CJ67+CM67)/45+SUM(AX67+AY67+AZ67+BA67+BF67+BG67+BH67)/60+SUM(AL67+BZ67)/50</f>
         <v/>
       </c>
       <c r="CQ67" s="38">
-        <f>SUM(R67+S67+BN67+CD67+CE67)/65+SUM(AB67)/36+SUM(AR67+AS67+BW67+BX67+CK67)/40+SUM(BB67+BC67+BI67+BJ67)/60</f>
+        <f>SUM(R67+S67+BN67+CD67+CE67)/65+SUM(AB67)/36+SUM(AR67+AS67+BW67+BX67+CK67+CN67)/40+SUM(BB67+BC67+BI67+BJ67)/60</f>
         <v/>
       </c>
       <c r="CR67" s="38">
@@ -13675,11 +13702,11 @@
         <v/>
       </c>
       <c r="CP68" s="38">
-        <f>SUM(O68+P68+Q68+BL68+BM68+CB68+CC68)/65+SUM(X68+Y68)/44+SUM(AJ68+AK68+AM68+AN68+AO68+AP68+AQ68+BR68+BS68+BT68+BU68+BV68+CH68+CI68+CJ68)/45+SUM(AX68+AY68+AZ68+BA68+BF68+BG68+BH68)/60+SUM(AL68+BZ68)/50</f>
+        <f>SUM(O68+P68+Q68+BL68+BM68+CB68+CC68)/65+SUM(X68+Y68)/44+SUM(AJ68+AK68+AM68+AN68+AO68+AP68+AQ68+BR68+BS68+BT68+BU68+BV68+CH68+CI68+CJ68+CM68)/45+SUM(AX68+AY68+AZ68+BA68+BF68+BG68+BH68)/60+SUM(AL68+BZ68)/50</f>
         <v/>
       </c>
       <c r="CQ68" s="38">
-        <f>SUM(R68+S68+BN68+CD68+CE68)/65+SUM(AB68)/36+SUM(AR68+AS68+BW68+BX68+CK68)/40+SUM(BB68+BC68+BI68+BJ68)/60</f>
+        <f>SUM(R68+S68+BN68+CD68+CE68)/65+SUM(AB68)/36+SUM(AR68+AS68+BW68+BX68+CK68+CN68)/40+SUM(BB68+BC68+BI68+BJ68)/60</f>
         <v/>
       </c>
       <c r="CR68" s="38">
@@ -13834,11 +13861,11 @@
         <v/>
       </c>
       <c r="CP69" s="38">
-        <f>SUM(O69+P69+Q69+BL69+BM69+CB69+CC69)/65+SUM(X69+Y69)/44+SUM(AJ69+AK69+AM69+AN69+AO69+AP69+AQ69+BR69+BS69+BT69+BU69+BV69+CH69+CI69+CJ69)/45+SUM(AX69+AY69+AZ69+BA69+BF69+BG69+BH69)/60+SUM(AL69+BZ69)/50</f>
+        <f>SUM(O69+P69+Q69+BL69+BM69+CB69+CC69)/65+SUM(X69+Y69)/44+SUM(AJ69+AK69+AM69+AN69+AO69+AP69+AQ69+BR69+BS69+BT69+BU69+BV69+CH69+CI69+CJ69+CM69)/45+SUM(AX69+AY69+AZ69+BA69+BF69+BG69+BH69)/60+SUM(AL69+BZ69)/50</f>
         <v/>
       </c>
       <c r="CQ69" s="38">
-        <f>SUM(R69+S69+BN69+CD69+CE69)/65+SUM(AB69)/36+SUM(AR69+AS69+BW69+BX69+CK69)/40+SUM(BB69+BC69+BI69+BJ69)/60</f>
+        <f>SUM(R69+S69+BN69+CD69+CE69)/65+SUM(AB69)/36+SUM(AR69+AS69+BW69+BX69+CK69+CN69)/40+SUM(BB69+BC69+BI69+BJ69)/60</f>
         <v/>
       </c>
       <c r="CR69" s="38">
@@ -13993,11 +14020,11 @@
         <v/>
       </c>
       <c r="CP70" s="38">
-        <f>SUM(O70+P70+Q70+BL70+BM70+CB70+CC70)/65+SUM(X70+Y70)/44+SUM(AJ70+AK70+AM70+AN70+AO70+AP70+AQ70+BR70+BS70+BT70+BU70+BV70+CH70+CI70+CJ70)/45+SUM(AX70+AY70+AZ70+BA70+BF70+BG70+BH70)/60+SUM(AL70+BZ70)/50</f>
+        <f>SUM(O70+P70+Q70+BL70+BM70+CB70+CC70)/65+SUM(X70+Y70)/44+SUM(AJ70+AK70+AM70+AN70+AO70+AP70+AQ70+BR70+BS70+BT70+BU70+BV70+CH70+CI70+CJ70+CM70)/45+SUM(AX70+AY70+AZ70+BA70+BF70+BG70+BH70)/60+SUM(AL70+BZ70)/50</f>
         <v/>
       </c>
       <c r="CQ70" s="38">
-        <f>SUM(R70+S70+BN70+CD70+CE70)/65+SUM(AB70)/36+SUM(AR70+AS70+BW70+BX70+CK70)/40+SUM(BB70+BC70+BI70+BJ70)/60</f>
+        <f>SUM(R70+S70+BN70+CD70+CE70)/65+SUM(AB70)/36+SUM(AR70+AS70+BW70+BX70+CK70+CN70)/40+SUM(BB70+BC70+BI70+BJ70)/60</f>
         <v/>
       </c>
       <c r="CR70" s="38">
@@ -14152,11 +14179,11 @@
         <v/>
       </c>
       <c r="CP71" s="38">
-        <f>SUM(O71+P71+Q71+BL71+BM71+CB71+CC71)/65+SUM(X71+Y71)/44+SUM(AJ71+AK71+AM71+AN71+AO71+AP71+AQ71+BR71+BS71+BT71+BU71+BV71+CH71+CI71+CJ71)/45+SUM(AX71+AY71+AZ71+BA71+BF71+BG71+BH71)/60+SUM(AL71+BZ71)/50</f>
+        <f>SUM(O71+P71+Q71+BL71+BM71+CB71+CC71)/65+SUM(X71+Y71)/44+SUM(AJ71+AK71+AM71+AN71+AO71+AP71+AQ71+BR71+BS71+BT71+BU71+BV71+CH71+CI71+CJ71+CM71)/45+SUM(AX71+AY71+AZ71+BA71+BF71+BG71+BH71)/60+SUM(AL71+BZ71)/50</f>
         <v/>
       </c>
       <c r="CQ71" s="38">
-        <f>SUM(R71+S71+BN71+CD71+CE71)/65+SUM(AB71)/36+SUM(AR71+AS71+BW71+BX71+CK71)/40+SUM(BB71+BC71+BI71+BJ71)/60</f>
+        <f>SUM(R71+S71+BN71+CD71+CE71)/65+SUM(AB71)/36+SUM(AR71+AS71+BW71+BX71+CK71+CN71)/40+SUM(BB71+BC71+BI71+BJ71)/60</f>
         <v/>
       </c>
       <c r="CR71" s="38">
@@ -14311,11 +14338,11 @@
         <v/>
       </c>
       <c r="CP72" s="38">
-        <f>SUM(O72+P72+Q72+BL72+BM72+CB72+CC72)/65+SUM(X72+Y72)/44+SUM(AJ72+AK72+AM72+AN72+AO72+AP72+AQ72+BR72+BS72+BT72+BU72+BV72+CH72+CI72+CJ72)/45+SUM(AX72+AY72+AZ72+BA72+BF72+BG72+BH72)/60+SUM(AL72+BZ72)/50</f>
+        <f>SUM(O72+P72+Q72+BL72+BM72+CB72+CC72)/65+SUM(X72+Y72)/44+SUM(AJ72+AK72+AM72+AN72+AO72+AP72+AQ72+BR72+BS72+BT72+BU72+BV72+CH72+CI72+CJ72+CM72)/45+SUM(AX72+AY72+AZ72+BA72+BF72+BG72+BH72)/60+SUM(AL72+BZ72)/50</f>
         <v/>
       </c>
       <c r="CQ72" s="38">
-        <f>SUM(R72+S72+BN72+CD72+CE72)/65+SUM(AB72)/36+SUM(AR72+AS72+BW72+BX72+CK72)/40+SUM(BB72+BC72+BI72+BJ72)/60</f>
+        <f>SUM(R72+S72+BN72+CD72+CE72)/65+SUM(AB72)/36+SUM(AR72+AS72+BW72+BX72+CK72+CN72)/40+SUM(BB72+BC72+BI72+BJ72)/60</f>
         <v/>
       </c>
       <c r="CR72" s="38">
@@ -14470,11 +14497,11 @@
         <v/>
       </c>
       <c r="CP73" s="38">
-        <f>SUM(O73+P73+Q73+BL73+BM73+CB73+CC73)/65+SUM(X73+Y73)/44+SUM(AJ73+AK73+AM73+AN73+AO73+AP73+AQ73+BR73+BS73+BT73+BU73+BV73+CH73+CI73+CJ73)/45+SUM(AX73+AY73+AZ73+BA73+BF73+BG73+BH73)/60+SUM(AL73+BZ73)/50</f>
+        <f>SUM(O73+P73+Q73+BL73+BM73+CB73+CC73)/65+SUM(X73+Y73)/44+SUM(AJ73+AK73+AM73+AN73+AO73+AP73+AQ73+BR73+BS73+BT73+BU73+BV73+CH73+CI73+CJ73+CM73)/45+SUM(AX73+AY73+AZ73+BA73+BF73+BG73+BH73)/60+SUM(AL73+BZ73)/50</f>
         <v/>
       </c>
       <c r="CQ73" s="38">
-        <f>SUM(R73+S73+BN73+CD73+CE73)/65+SUM(AB73)/36+SUM(AR73+AS73+BW73+BX73+CK73)/40+SUM(BB73+BC73+BI73+BJ73)/60</f>
+        <f>SUM(R73+S73+BN73+CD73+CE73)/65+SUM(AB73)/36+SUM(AR73+AS73+BW73+BX73+CK73+CN73)/40+SUM(BB73+BC73+BI73+BJ73)/60</f>
         <v/>
       </c>
       <c r="CR73" s="38">
@@ -14629,11 +14656,11 @@
         <v/>
       </c>
       <c r="CP74" s="38">
-        <f>SUM(O74+P74+Q74+BL74+BM74+CB74+CC74)/65+SUM(X74+Y74)/44+SUM(AJ74+AK74+AM74+AN74+AO74+AP74+AQ74+BR74+BS74+BT74+BU74+BV74+CH74+CI74+CJ74)/45+SUM(AX74+AY74+AZ74+BA74+BF74+BG74+BH74)/60+SUM(AL74+BZ74)/50</f>
+        <f>SUM(O74+P74+Q74+BL74+BM74+CB74+CC74)/65+SUM(X74+Y74)/44+SUM(AJ74+AK74+AM74+AN74+AO74+AP74+AQ74+BR74+BS74+BT74+BU74+BV74+CH74+CI74+CJ74+CM74)/45+SUM(AX74+AY74+AZ74+BA74+BF74+BG74+BH74)/60+SUM(AL74+BZ74)/50</f>
         <v/>
       </c>
       <c r="CQ74" s="38">
-        <f>SUM(R74+S74+BN74+CD74+CE74)/65+SUM(AB74)/36+SUM(AR74+AS74+BW74+BX74+CK74)/40+SUM(BB74+BC74+BI74+BJ74)/60</f>
+        <f>SUM(R74+S74+BN74+CD74+CE74)/65+SUM(AB74)/36+SUM(AR74+AS74+BW74+BX74+CK74+CN74)/40+SUM(BB74+BC74+BI74+BJ74)/60</f>
         <v/>
       </c>
       <c r="CR74" s="38">
@@ -14788,11 +14815,11 @@
         <v/>
       </c>
       <c r="CP75" s="38">
-        <f>SUM(O75+P75+Q75+BL75+BM75+CB75+CC75)/65+SUM(X75+Y75)/44+SUM(AJ75+AK75+AM75+AN75+AO75+AP75+AQ75+BR75+BS75+BT75+BU75+BV75+CH75+CI75+CJ75)/45+SUM(AX75+AY75+AZ75+BA75+BF75+BG75+BH75)/60+SUM(AL75+BZ75)/50</f>
+        <f>SUM(O75+P75+Q75+BL75+BM75+CB75+CC75)/65+SUM(X75+Y75)/44+SUM(AJ75+AK75+AM75+AN75+AO75+AP75+AQ75+BR75+BS75+BT75+BU75+BV75+CH75+CI75+CJ75+CM75)/45+SUM(AX75+AY75+AZ75+BA75+BF75+BG75+BH75)/60+SUM(AL75+BZ75)/50</f>
         <v/>
       </c>
       <c r="CQ75" s="38">
-        <f>SUM(R75+S75+BN75+CD75+CE75)/65+SUM(AB75)/36+SUM(AR75+AS75+BW75+BX75+CK75)/40+SUM(BB75+BC75+BI75+BJ75)/60</f>
+        <f>SUM(R75+S75+BN75+CD75+CE75)/65+SUM(AB75)/36+SUM(AR75+AS75+BW75+BX75+CK75+CN75)/40+SUM(BB75+BC75+BI75+BJ75)/60</f>
         <v/>
       </c>
       <c r="CR75" s="38">
@@ -14947,11 +14974,11 @@
         <v/>
       </c>
       <c r="CP76" s="38">
-        <f>SUM(O76+P76+Q76+BL76+BM76+CB76+CC76)/65+SUM(X76+Y76)/44+SUM(AJ76+AK76+AM76+AN76+AO76+AP76+AQ76+BR76+BS76+BT76+BU76+BV76+CH76+CI76+CJ76)/45+SUM(AX76+AY76+AZ76+BA76+BF76+BG76+BH76)/60+SUM(AL76+BZ76)/50</f>
+        <f>SUM(O76+P76+Q76+BL76+BM76+CB76+CC76)/65+SUM(X76+Y76)/44+SUM(AJ76+AK76+AM76+AN76+AO76+AP76+AQ76+BR76+BS76+BT76+BU76+BV76+CH76+CI76+CJ76+CM76)/45+SUM(AX76+AY76+AZ76+BA76+BF76+BG76+BH76)/60+SUM(AL76+BZ76)/50</f>
         <v/>
       </c>
       <c r="CQ76" s="38">
-        <f>SUM(R76+S76+BN76+CD76+CE76)/65+SUM(AB76)/36+SUM(AR76+AS76+BW76+BX76+CK76)/40+SUM(BB76+BC76+BI76+BJ76)/60</f>
+        <f>SUM(R76+S76+BN76+CD76+CE76)/65+SUM(AB76)/36+SUM(AR76+AS76+BW76+BX76+CK76+CN76)/40+SUM(BB76+BC76+BI76+BJ76)/60</f>
         <v/>
       </c>
       <c r="CR76" s="38">
@@ -15106,11 +15133,11 @@
         <v/>
       </c>
       <c r="CP77" s="38">
-        <f>SUM(O77+P77+Q77+BL77+BM77+CB77+CC77)/65+SUM(X77+Y77)/44+SUM(AJ77+AK77+AM77+AN77+AO77+AP77+AQ77+BR77+BS77+BT77+BU77+BV77+CH77+CI77+CJ77)/45+SUM(AX77+AY77+AZ77+BA77+BF77+BG77+BH77)/60+SUM(AL77+BZ77)/50</f>
+        <f>SUM(O77+P77+Q77+BL77+BM77+CB77+CC77)/65+SUM(X77+Y77)/44+SUM(AJ77+AK77+AM77+AN77+AO77+AP77+AQ77+BR77+BS77+BT77+BU77+BV77+CH77+CI77+CJ77+CM77)/45+SUM(AX77+AY77+AZ77+BA77+BF77+BG77+BH77)/60+SUM(AL77+BZ77)/50</f>
         <v/>
       </c>
       <c r="CQ77" s="38">
-        <f>SUM(R77+S77+BN77+CD77+CE77)/65+SUM(AB77)/36+SUM(AR77+AS77+BW77+BX77+CK77)/40+SUM(BB77+BC77+BI77+BJ77)/60</f>
+        <f>SUM(R77+S77+BN77+CD77+CE77)/65+SUM(AB77)/36+SUM(AR77+AS77+BW77+BX77+CK77+CN77)/40+SUM(BB77+BC77+BI77+BJ77)/60</f>
         <v/>
       </c>
       <c r="CR77" s="38">
@@ -15265,11 +15292,11 @@
         <v/>
       </c>
       <c r="CP78" s="38">
-        <f>SUM(O78+P78+Q78+BL78+BM78+CB78+CC78)/65+SUM(X78+Y78)/44+SUM(AJ78+AK78+AM78+AN78+AO78+AP78+AQ78+BR78+BS78+BT78+BU78+BV78+CH78+CI78+CJ78)/45+SUM(AX78+AY78+AZ78+BA78+BF78+BG78+BH78)/60+SUM(AL78+BZ78)/50</f>
+        <f>SUM(O78+P78+Q78+BL78+BM78+CB78+CC78)/65+SUM(X78+Y78)/44+SUM(AJ78+AK78+AM78+AN78+AO78+AP78+AQ78+BR78+BS78+BT78+BU78+BV78+CH78+CI78+CJ78+CM78)/45+SUM(AX78+AY78+AZ78+BA78+BF78+BG78+BH78)/60+SUM(AL78+BZ78)/50</f>
         <v/>
       </c>
       <c r="CQ78" s="38">
-        <f>SUM(R78+S78+BN78+CD78+CE78)/65+SUM(AB78)/36+SUM(AR78+AS78+BW78+BX78+CK78)/40+SUM(BB78+BC78+BI78+BJ78)/60</f>
+        <f>SUM(R78+S78+BN78+CD78+CE78)/65+SUM(AB78)/36+SUM(AR78+AS78+BW78+BX78+CK78+CN78)/40+SUM(BB78+BC78+BI78+BJ78)/60</f>
         <v/>
       </c>
       <c r="CR78" s="38">
@@ -15424,11 +15451,11 @@
         <v/>
       </c>
       <c r="CP79" s="38">
-        <f>SUM(O79+P79+Q79+BL79+BM79+CB79+CC79)/65+SUM(X79+Y79)/44+SUM(AJ79+AK79+AM79+AN79+AO79+AP79+AQ79+BR79+BS79+BT79+BU79+BV79+CH79+CI79+CJ79)/45+SUM(AX79+AY79+AZ79+BA79+BF79+BG79+BH79)/60+SUM(AL79+BZ79)/50</f>
+        <f>SUM(O79+P79+Q79+BL79+BM79+CB79+CC79)/65+SUM(X79+Y79)/44+SUM(AJ79+AK79+AM79+AN79+AO79+AP79+AQ79+BR79+BS79+BT79+BU79+BV79+CH79+CI79+CJ79+CM79)/45+SUM(AX79+AY79+AZ79+BA79+BF79+BG79+BH79)/60+SUM(AL79+BZ79)/50</f>
         <v/>
       </c>
       <c r="CQ79" s="38">
-        <f>SUM(R79+S79+BN79+CD79+CE79)/65+SUM(AB79)/36+SUM(AR79+AS79+BW79+BX79+CK79)/40+SUM(BB79+BC79+BI79+BJ79)/60</f>
+        <f>SUM(R79+S79+BN79+CD79+CE79)/65+SUM(AB79)/36+SUM(AR79+AS79+BW79+BX79+CK79+CN79)/40+SUM(BB79+BC79+BI79+BJ79)/60</f>
         <v/>
       </c>
       <c r="CR79" s="38">
@@ -15583,11 +15610,11 @@
         <v/>
       </c>
       <c r="CP80" s="38">
-        <f>SUM(O80+P80+Q80+BL80+BM80+CB80+CC80)/65+SUM(X80+Y80)/44+SUM(AJ80+AK80+AM80+AN80+AO80+AP80+AQ80+BR80+BS80+BT80+BU80+BV80+CH80+CI80+CJ80)/45+SUM(AX80+AY80+AZ80+BA80+BF80+BG80+BH80)/60+SUM(AL80+BZ80)/50</f>
+        <f>SUM(O80+P80+Q80+BL80+BM80+CB80+CC80)/65+SUM(X80+Y80)/44+SUM(AJ80+AK80+AM80+AN80+AO80+AP80+AQ80+BR80+BS80+BT80+BU80+BV80+CH80+CI80+CJ80+CM80)/45+SUM(AX80+AY80+AZ80+BA80+BF80+BG80+BH80)/60+SUM(AL80+BZ80)/50</f>
         <v/>
       </c>
       <c r="CQ80" s="38">
-        <f>SUM(R80+S80+BN80+CD80+CE80)/65+SUM(AB80)/36+SUM(AR80+AS80+BW80+BX80+CK80)/40+SUM(BB80+BC80+BI80+BJ80)/60</f>
+        <f>SUM(R80+S80+BN80+CD80+CE80)/65+SUM(AB80)/36+SUM(AR80+AS80+BW80+BX80+CK80+CN80)/40+SUM(BB80+BC80+BI80+BJ80)/60</f>
         <v/>
       </c>
       <c r="CR80" s="38">
@@ -15742,11 +15769,11 @@
         <v/>
       </c>
       <c r="CP81" s="38">
-        <f>SUM(O81+P81+Q81+BL81+BM81+CB81+CC81)/65+SUM(X81+Y81)/44+SUM(AJ81+AK81+AM81+AN81+AO81+AP81+AQ81+BR81+BS81+BT81+BU81+BV81+CH81+CI81+CJ81)/45+SUM(AX81+AY81+AZ81+BA81+BF81+BG81+BH81)/60+SUM(AL81+BZ81)/50</f>
+        <f>SUM(O81+P81+Q81+BL81+BM81+CB81+CC81)/65+SUM(X81+Y81)/44+SUM(AJ81+AK81+AM81+AN81+AO81+AP81+AQ81+BR81+BS81+BT81+BU81+BV81+CH81+CI81+CJ81+CM81)/45+SUM(AX81+AY81+AZ81+BA81+BF81+BG81+BH81)/60+SUM(AL81+BZ81)/50</f>
         <v/>
       </c>
       <c r="CQ81" s="38">
-        <f>SUM(R81+S81+BN81+CD81+CE81)/65+SUM(AB81)/36+SUM(AR81+AS81+BW81+BX81+CK81)/40+SUM(BB81+BC81+BI81+BJ81)/60</f>
+        <f>SUM(R81+S81+BN81+CD81+CE81)/65+SUM(AB81)/36+SUM(AR81+AS81+BW81+BX81+CK81+CN81)/40+SUM(BB81+BC81+BI81+BJ81)/60</f>
         <v/>
       </c>
       <c r="CR81" s="38">
@@ -15901,11 +15928,11 @@
         <v/>
       </c>
       <c r="CP82" s="38">
-        <f>SUM(O82+P82+Q82+BL82+BM82+CB82+CC82)/65+SUM(X82+Y82)/44+SUM(AJ82+AK82+AM82+AN82+AO82+AP82+AQ82+BR82+BS82+BT82+BU82+BV82+CH82+CI82+CJ82)/45+SUM(AX82+AY82+AZ82+BA82+BF82+BG82+BH82)/60+SUM(AL82+BZ82)/50</f>
+        <f>SUM(O82+P82+Q82+BL82+BM82+CB82+CC82)/65+SUM(X82+Y82)/44+SUM(AJ82+AK82+AM82+AN82+AO82+AP82+AQ82+BR82+BS82+BT82+BU82+BV82+CH82+CI82+CJ82+CM82)/45+SUM(AX82+AY82+AZ82+BA82+BF82+BG82+BH82)/60+SUM(AL82+BZ82)/50</f>
         <v/>
       </c>
       <c r="CQ82" s="38">
-        <f>SUM(R82+S82+BN82+CD82+CE82)/65+SUM(AB82)/36+SUM(AR82+AS82+BW82+BX82+CK82)/40+SUM(BB82+BC82+BI82+BJ82)/60</f>
+        <f>SUM(R82+S82+BN82+CD82+CE82)/65+SUM(AB82)/36+SUM(AR82+AS82+BW82+BX82+CK82+CN82)/40+SUM(BB82+BC82+BI82+BJ82)/60</f>
         <v/>
       </c>
       <c r="CR82" s="38">
@@ -16060,11 +16087,11 @@
         <v/>
       </c>
       <c r="CP83" s="38">
-        <f>SUM(O83+P83+Q83+BL83+BM83+CB83+CC83)/65+SUM(X83+Y83)/44+SUM(AJ83+AK83+AM83+AN83+AO83+AP83+AQ83+BR83+BS83+BT83+BU83+BV83+CH83+CI83+CJ83)/45+SUM(AX83+AY83+AZ83+BA83+BF83+BG83+BH83)/60+SUM(AL83+BZ83)/50</f>
+        <f>SUM(O83+P83+Q83+BL83+BM83+CB83+CC83)/65+SUM(X83+Y83)/44+SUM(AJ83+AK83+AM83+AN83+AO83+AP83+AQ83+BR83+BS83+BT83+BU83+BV83+CH83+CI83+CJ83+CM83)/45+SUM(AX83+AY83+AZ83+BA83+BF83+BG83+BH83)/60+SUM(AL83+BZ83)/50</f>
         <v/>
       </c>
       <c r="CQ83" s="38">
-        <f>SUM(R83+S83+BN83+CD83+CE83)/65+SUM(AB83)/36+SUM(AR83+AS83+BW83+BX83+CK83)/40+SUM(BB83+BC83+BI83+BJ83)/60</f>
+        <f>SUM(R83+S83+BN83+CD83+CE83)/65+SUM(AB83)/36+SUM(AR83+AS83+BW83+BX83+CK83+CN83)/40+SUM(BB83+BC83+BI83+BJ83)/60</f>
         <v/>
       </c>
       <c r="CR83" s="38">
@@ -16219,11 +16246,11 @@
         <v/>
       </c>
       <c r="CP84" s="38">
-        <f>SUM(O84+P84+Q84+BL84+BM84+CB84+CC84)/65+SUM(X84+Y84)/44+SUM(AJ84+AK84+AM84+AN84+AO84+AP84+AQ84+BR84+BS84+BT84+BU84+BV84+CH84+CI84+CJ84)/45+SUM(AX84+AY84+AZ84+BA84+BF84+BG84+BH84)/60+SUM(AL84+BZ84)/50</f>
+        <f>SUM(O84+P84+Q84+BL84+BM84+CB84+CC84)/65+SUM(X84+Y84)/44+SUM(AJ84+AK84+AM84+AN84+AO84+AP84+AQ84+BR84+BS84+BT84+BU84+BV84+CH84+CI84+CJ84+CM84)/45+SUM(AX84+AY84+AZ84+BA84+BF84+BG84+BH84)/60+SUM(AL84+BZ84)/50</f>
         <v/>
       </c>
       <c r="CQ84" s="38">
-        <f>SUM(R84+S84+BN84+CD84+CE84)/65+SUM(AB84)/36+SUM(AR84+AS84+BW84+BX84+CK84)/40+SUM(BB84+BC84+BI84+BJ84)/60</f>
+        <f>SUM(R84+S84+BN84+CD84+CE84)/65+SUM(AB84)/36+SUM(AR84+AS84+BW84+BX84+CK84+CN84)/40+SUM(BB84+BC84+BI84+BJ84)/60</f>
         <v/>
       </c>
       <c r="CR84" s="38">
@@ -16378,11 +16405,11 @@
         <v/>
       </c>
       <c r="CP85" s="38">
-        <f>SUM(O85+P85+Q85+BL85+BM85+CB85+CC85)/65+SUM(X85+Y85)/44+SUM(AJ85+AK85+AM85+AN85+AO85+AP85+AQ85+BR85+BS85+BT85+BU85+BV85+CH85+CI85+CJ85)/45+SUM(AX85+AY85+AZ85+BA85+BF85+BG85+BH85)/60+SUM(AL85+BZ85)/50</f>
+        <f>SUM(O85+P85+Q85+BL85+BM85+CB85+CC85)/65+SUM(X85+Y85)/44+SUM(AJ85+AK85+AM85+AN85+AO85+AP85+AQ85+BR85+BS85+BT85+BU85+BV85+CH85+CI85+CJ85+CM85)/45+SUM(AX85+AY85+AZ85+BA85+BF85+BG85+BH85)/60+SUM(AL85+BZ85)/50</f>
         <v/>
       </c>
       <c r="CQ85" s="38">
-        <f>SUM(R85+S85+BN85+CD85+CE85)/65+SUM(AB85)/36+SUM(AR85+AS85+BW85+BX85+CK85)/40+SUM(BB85+BC85+BI85+BJ85)/60</f>
+        <f>SUM(R85+S85+BN85+CD85+CE85)/65+SUM(AB85)/36+SUM(AR85+AS85+BW85+BX85+CK85+CN85)/40+SUM(BB85+BC85+BI85+BJ85)/60</f>
         <v/>
       </c>
       <c r="CR85" s="38">
@@ -16537,11 +16564,11 @@
         <v/>
       </c>
       <c r="CP86" s="38">
-        <f>SUM(O86+P86+Q86+BL86+BM86+CB86+CC86)/65+SUM(X86+Y86)/44+SUM(AJ86+AK86+AM86+AN86+AO86+AP86+AQ86+BR86+BS86+BT86+BU86+BV86+CH86+CI86+CJ86)/45+SUM(AX86+AY86+AZ86+BA86+BF86+BG86+BH86)/60+SUM(AL86+BZ86)/50</f>
+        <f>SUM(O86+P86+Q86+BL86+BM86+CB86+CC86)/65+SUM(X86+Y86)/44+SUM(AJ86+AK86+AM86+AN86+AO86+AP86+AQ86+BR86+BS86+BT86+BU86+BV86+CH86+CI86+CJ86+CM86)/45+SUM(AX86+AY86+AZ86+BA86+BF86+BG86+BH86)/60+SUM(AL86+BZ86)/50</f>
         <v/>
       </c>
       <c r="CQ86" s="38">
-        <f>SUM(R86+S86+BN86+CD86+CE86)/65+SUM(AB86)/36+SUM(AR86+AS86+BW86+BX86+CK86)/40+SUM(BB86+BC86+BI86+BJ86)/60</f>
+        <f>SUM(R86+S86+BN86+CD86+CE86)/65+SUM(AB86)/36+SUM(AR86+AS86+BW86+BX86+CK86+CN86)/40+SUM(BB86+BC86+BI86+BJ86)/60</f>
         <v/>
       </c>
       <c r="CR86" s="38">
@@ -16696,11 +16723,11 @@
         <v/>
       </c>
       <c r="CP87" s="38">
-        <f>SUM(O87+P87+Q87+BL87+BM87+CB87+CC87)/65+SUM(X87+Y87)/44+SUM(AJ87+AK87+AM87+AN87+AO87+AP87+AQ87+BR87+BS87+BT87+BU87+BV87+CH87+CI87+CJ87)/45+SUM(AX87+AY87+AZ87+BA87+BF87+BG87+BH87)/60+SUM(AL87+BZ87)/50</f>
+        <f>SUM(O87+P87+Q87+BL87+BM87+CB87+CC87)/65+SUM(X87+Y87)/44+SUM(AJ87+AK87+AM87+AN87+AO87+AP87+AQ87+BR87+BS87+BT87+BU87+BV87+CH87+CI87+CJ87+CM87)/45+SUM(AX87+AY87+AZ87+BA87+BF87+BG87+BH87)/60+SUM(AL87+BZ87)/50</f>
         <v/>
       </c>
       <c r="CQ87" s="38">
-        <f>SUM(R87+S87+BN87+CD87+CE87)/65+SUM(AB87)/36+SUM(AR87+AS87+BW87+BX87+CK87)/40+SUM(BB87+BC87+BI87+BJ87)/60</f>
+        <f>SUM(R87+S87+BN87+CD87+CE87)/65+SUM(AB87)/36+SUM(AR87+AS87+BW87+BX87+CK87+CN87)/40+SUM(BB87+BC87+BI87+BJ87)/60</f>
         <v/>
       </c>
       <c r="CR87" s="38">
@@ -16855,11 +16882,11 @@
         <v/>
       </c>
       <c r="CP88" s="38">
-        <f>SUM(O88+P88+Q88+BL88+BM88+CB88+CC88)/65+SUM(X88+Y88)/44+SUM(AJ88+AK88+AM88+AN88+AO88+AP88+AQ88+BR88+BS88+BT88+BU88+BV88+CH88+CI88+CJ88)/45+SUM(AX88+AY88+AZ88+BA88+BF88+BG88+BH88)/60+SUM(AL88+BZ88)/50</f>
+        <f>SUM(O88+P88+Q88+BL88+BM88+CB88+CC88)/65+SUM(X88+Y88)/44+SUM(AJ88+AK88+AM88+AN88+AO88+AP88+AQ88+BR88+BS88+BT88+BU88+BV88+CH88+CI88+CJ88+CM88)/45+SUM(AX88+AY88+AZ88+BA88+BF88+BG88+BH88)/60+SUM(AL88+BZ88)/50</f>
         <v/>
       </c>
       <c r="CQ88" s="38">
-        <f>SUM(R88+S88+BN88+CD88+CE88)/65+SUM(AB88)/36+SUM(AR88+AS88+BW88+BX88+CK88)/40+SUM(BB88+BC88+BI88+BJ88)/60</f>
+        <f>SUM(R88+S88+BN88+CD88+CE88)/65+SUM(AB88)/36+SUM(AR88+AS88+BW88+BX88+CK88+CN88)/40+SUM(BB88+BC88+BI88+BJ88)/60</f>
         <v/>
       </c>
       <c r="CR88" s="38">
@@ -17014,11 +17041,11 @@
         <v/>
       </c>
       <c r="CP89" s="38">
-        <f>SUM(O89+P89+Q89+BL89+BM89+CB89+CC89)/65+SUM(X89+Y89)/44+SUM(AJ89+AK89+AM89+AN89+AO89+AP89+AQ89+BR89+BS89+BT89+BU89+BV89+CH89+CI89+CJ89)/45+SUM(AX89+AY89+AZ89+BA89+BF89+BG89+BH89)/60+SUM(AL89+BZ89)/50</f>
+        <f>SUM(O89+P89+Q89+BL89+BM89+CB89+CC89)/65+SUM(X89+Y89)/44+SUM(AJ89+AK89+AM89+AN89+AO89+AP89+AQ89+BR89+BS89+BT89+BU89+BV89+CH89+CI89+CJ89+CM89)/45+SUM(AX89+AY89+AZ89+BA89+BF89+BG89+BH89)/60+SUM(AL89+BZ89)/50</f>
         <v/>
       </c>
       <c r="CQ89" s="38">
-        <f>SUM(R89+S89+BN89+CD89+CE89)/65+SUM(AB89)/36+SUM(AR89+AS89+BW89+BX89+CK89)/40+SUM(BB89+BC89+BI89+BJ89)/60</f>
+        <f>SUM(R89+S89+BN89+CD89+CE89)/65+SUM(AB89)/36+SUM(AR89+AS89+BW89+BX89+CK89+CN89)/40+SUM(BB89+BC89+BI89+BJ89)/60</f>
         <v/>
       </c>
       <c r="CR89" s="38">
@@ -17173,11 +17200,11 @@
         <v/>
       </c>
       <c r="CP90" s="38">
-        <f>SUM(O90+P90+Q90+BL90+BM90+CB90+CC90)/65+SUM(X90+Y90)/44+SUM(AJ90+AK90+AM90+AN90+AO90+AP90+AQ90+BR90+BS90+BT90+BU90+BV90+CH90+CI90+CJ90)/45+SUM(AX90+AY90+AZ90+BA90+BF90+BG90+BH90)/60+SUM(AL90+BZ90)/50</f>
+        <f>SUM(O90+P90+Q90+BL90+BM90+CB90+CC90)/65+SUM(X90+Y90)/44+SUM(AJ90+AK90+AM90+AN90+AO90+AP90+AQ90+BR90+BS90+BT90+BU90+BV90+CH90+CI90+CJ90+CM90)/45+SUM(AX90+AY90+AZ90+BA90+BF90+BG90+BH90)/60+SUM(AL90+BZ90)/50</f>
         <v/>
       </c>
       <c r="CQ90" s="38">
-        <f>SUM(R90+S90+BN90+CD90+CE90)/65+SUM(AB90)/36+SUM(AR90+AS90+BW90+BX90+CK90)/40+SUM(BB90+BC90+BI90+BJ90)/60</f>
+        <f>SUM(R90+S90+BN90+CD90+CE90)/65+SUM(AB90)/36+SUM(AR90+AS90+BW90+BX90+CK90+CN90)/40+SUM(BB90+BC90+BI90+BJ90)/60</f>
         <v/>
       </c>
       <c r="CR90" s="38">
@@ -17332,11 +17359,11 @@
         <v/>
       </c>
       <c r="CP91" s="38">
-        <f>SUM(O91+P91+Q91+BL91+BM91+CB91+CC91)/65+SUM(X91+Y91)/44+SUM(AJ91+AK91+AM91+AN91+AO91+AP91+AQ91+BR91+BS91+BT91+BU91+BV91+CH91+CI91+CJ91)/45+SUM(AX91+AY91+AZ91+BA91+BF91+BG91+BH91)/60+SUM(AL91+BZ91)/50</f>
+        <f>SUM(O91+P91+Q91+BL91+BM91+CB91+CC91)/65+SUM(X91+Y91)/44+SUM(AJ91+AK91+AM91+AN91+AO91+AP91+AQ91+BR91+BS91+BT91+BU91+BV91+CH91+CI91+CJ91+CM91)/45+SUM(AX91+AY91+AZ91+BA91+BF91+BG91+BH91)/60+SUM(AL91+BZ91)/50</f>
         <v/>
       </c>
       <c r="CQ91" s="38">
-        <f>SUM(R91+S91+BN91+CD91+CE91)/65+SUM(AB91)/36+SUM(AR91+AS91+BW91+BX91+CK91)/40+SUM(BB91+BC91+BI91+BJ91)/60</f>
+        <f>SUM(R91+S91+BN91+CD91+CE91)/65+SUM(AB91)/36+SUM(AR91+AS91+BW91+BX91+CK91+CN91)/40+SUM(BB91+BC91+BI91+BJ91)/60</f>
         <v/>
       </c>
       <c r="CR91" s="38">
@@ -17491,11 +17518,11 @@
         <v/>
       </c>
       <c r="CP92" s="38">
-        <f>SUM(O92+P92+Q92+BL92+BM92+CB92+CC92)/65+SUM(X92+Y92)/44+SUM(AJ92+AK92+AM92+AN92+AO92+AP92+AQ92+BR92+BS92+BT92+BU92+BV92+CH92+CI92+CJ92)/45+SUM(AX92+AY92+AZ92+BA92+BF92+BG92+BH92)/60+SUM(AL92+BZ92)/50</f>
+        <f>SUM(O92+P92+Q92+BL92+BM92+CB92+CC92)/65+SUM(X92+Y92)/44+SUM(AJ92+AK92+AM92+AN92+AO92+AP92+AQ92+BR92+BS92+BT92+BU92+BV92+CH92+CI92+CJ92+CM92)/45+SUM(AX92+AY92+AZ92+BA92+BF92+BG92+BH92)/60+SUM(AL92+BZ92)/50</f>
         <v/>
       </c>
       <c r="CQ92" s="38">
-        <f>SUM(R92+S92+BN92+CD92+CE92)/65+SUM(AB92)/36+SUM(AR92+AS92+BW92+BX92+CK92)/40+SUM(BB92+BC92+BI92+BJ92)/60</f>
+        <f>SUM(R92+S92+BN92+CD92+CE92)/65+SUM(AB92)/36+SUM(AR92+AS92+BW92+BX92+CK92+CN92)/40+SUM(BB92+BC92+BI92+BJ92)/60</f>
         <v/>
       </c>
       <c r="CR92" s="38">
@@ -17650,11 +17677,11 @@
         <v/>
       </c>
       <c r="CP93" s="38">
-        <f>SUM(O93+P93+Q93+BL93+BM93+CB93+CC93)/65+SUM(X93+Y93)/44+SUM(AJ93+AK93+AM93+AN93+AO93+AP93+AQ93+BR93+BS93+BT93+BU93+BV93+CH93+CI93+CJ93)/45+SUM(AX93+AY93+AZ93+BA93+BF93+BG93+BH93)/60+SUM(AL93+BZ93)/50</f>
+        <f>SUM(O93+P93+Q93+BL93+BM93+CB93+CC93)/65+SUM(X93+Y93)/44+SUM(AJ93+AK93+AM93+AN93+AO93+AP93+AQ93+BR93+BS93+BT93+BU93+BV93+CH93+CI93+CJ93+CM93)/45+SUM(AX93+AY93+AZ93+BA93+BF93+BG93+BH93)/60+SUM(AL93+BZ93)/50</f>
         <v/>
       </c>
       <c r="CQ93" s="38">
-        <f>SUM(R93+S93+BN93+CD93+CE93)/65+SUM(AB93)/36+SUM(AR93+AS93+BW93+BX93+CK93)/40+SUM(BB93+BC93+BI93+BJ93)/60</f>
+        <f>SUM(R93+S93+BN93+CD93+CE93)/65+SUM(AB93)/36+SUM(AR93+AS93+BW93+BX93+CK93+CN93)/40+SUM(BB93+BC93+BI93+BJ93)/60</f>
         <v/>
       </c>
       <c r="CR93" s="38">
@@ -17809,11 +17836,11 @@
         <v/>
       </c>
       <c r="CP94" s="38">
-        <f>SUM(O94+P94+Q94+BL94+BM94+CB94+CC94)/65+SUM(X94+Y94)/44+SUM(AJ94+AK94+AM94+AN94+AO94+AP94+AQ94+BR94+BS94+BT94+BU94+BV94+CH94+CI94+CJ94)/45+SUM(AX94+AY94+AZ94+BA94+BF94+BG94+BH94)/60+SUM(AL94+BZ94)/50</f>
+        <f>SUM(O94+P94+Q94+BL94+BM94+CB94+CC94)/65+SUM(X94+Y94)/44+SUM(AJ94+AK94+AM94+AN94+AO94+AP94+AQ94+BR94+BS94+BT94+BU94+BV94+CH94+CI94+CJ94+CM94)/45+SUM(AX94+AY94+AZ94+BA94+BF94+BG94+BH94)/60+SUM(AL94+BZ94)/50</f>
         <v/>
       </c>
       <c r="CQ94" s="38">
-        <f>SUM(R94+S94+BN94+CD94+CE94)/65+SUM(AB94)/36+SUM(AR94+AS94+BW94+BX94+CK94)/40+SUM(BB94+BC94+BI94+BJ94)/60</f>
+        <f>SUM(R94+S94+BN94+CD94+CE94)/65+SUM(AB94)/36+SUM(AR94+AS94+BW94+BX94+CK94+CN94)/40+SUM(BB94+BC94+BI94+BJ94)/60</f>
         <v/>
       </c>
       <c r="CR94" s="38">
@@ -17968,11 +17995,11 @@
         <v/>
       </c>
       <c r="CP95" s="38">
-        <f>SUM(O95+P95+Q95+BL95+BM95+CB95+CC95)/65+SUM(X95+Y95)/44+SUM(AJ95+AK95+AM95+AN95+AO95+AP95+AQ95+BR95+BS95+BT95+BU95+BV95+CH95+CI95+CJ95)/45+SUM(AX95+AY95+AZ95+BA95+BF95+BG95+BH95)/60+SUM(AL95+BZ95)/50</f>
+        <f>SUM(O95+P95+Q95+BL95+BM95+CB95+CC95)/65+SUM(X95+Y95)/44+SUM(AJ95+AK95+AM95+AN95+AO95+AP95+AQ95+BR95+BS95+BT95+BU95+BV95+CH95+CI95+CJ95+CM95)/45+SUM(AX95+AY95+AZ95+BA95+BF95+BG95+BH95)/60+SUM(AL95+BZ95)/50</f>
         <v/>
       </c>
       <c r="CQ95" s="38">
-        <f>SUM(R95+S95+BN95+CD95+CE95)/65+SUM(AB95)/36+SUM(AR95+AS95+BW95+BX95+CK95)/40+SUM(BB95+BC95+BI95+BJ95)/60</f>
+        <f>SUM(R95+S95+BN95+CD95+CE95)/65+SUM(AB95)/36+SUM(AR95+AS95+BW95+BX95+CK95+CN95)/40+SUM(BB95+BC95+BI95+BJ95)/60</f>
         <v/>
       </c>
       <c r="CR95" s="38">
@@ -18127,11 +18154,11 @@
         <v/>
       </c>
       <c r="CP96" s="38">
-        <f>SUM(O96+P96+Q96+BL96+BM96+CB96+CC96)/65+SUM(X96+Y96)/44+SUM(AJ96+AK96+AM96+AN96+AO96+AP96+AQ96+BR96+BS96+BT96+BU96+BV96+CH96+CI96+CJ96)/45+SUM(AX96+AY96+AZ96+BA96+BF96+BG96+BH96)/60+SUM(AL96+BZ96)/50</f>
+        <f>SUM(O96+P96+Q96+BL96+BM96+CB96+CC96)/65+SUM(X96+Y96)/44+SUM(AJ96+AK96+AM96+AN96+AO96+AP96+AQ96+BR96+BS96+BT96+BU96+BV96+CH96+CI96+CJ96+CM96)/45+SUM(AX96+AY96+AZ96+BA96+BF96+BG96+BH96)/60+SUM(AL96+BZ96)/50</f>
         <v/>
       </c>
       <c r="CQ96" s="38">
-        <f>SUM(R96+S96+BN96+CD96+CE96)/65+SUM(AB96)/36+SUM(AR96+AS96+BW96+BX96+CK96)/40+SUM(BB96+BC96+BI96+BJ96)/60</f>
+        <f>SUM(R96+S96+BN96+CD96+CE96)/65+SUM(AB96)/36+SUM(AR96+AS96+BW96+BX96+CK96+CN96)/40+SUM(BB96+BC96+BI96+BJ96)/60</f>
         <v/>
       </c>
       <c r="CR96" s="38">
@@ -18286,11 +18313,11 @@
         <v/>
       </c>
       <c r="CP97" s="38">
-        <f>SUM(O97+P97+Q97+BL97+BM97+CB97+CC97)/65+SUM(X97+Y97)/44+SUM(AJ97+AK97+AM97+AN97+AO97+AP97+AQ97+BR97+BS97+BT97+BU97+BV97+CH97+CI97+CJ97)/45+SUM(AX97+AY97+AZ97+BA97+BF97+BG97+BH97)/60+SUM(AL97+BZ97)/50</f>
+        <f>SUM(O97+P97+Q97+BL97+BM97+CB97+CC97)/65+SUM(X97+Y97)/44+SUM(AJ97+AK97+AM97+AN97+AO97+AP97+AQ97+BR97+BS97+BT97+BU97+BV97+CH97+CI97+CJ97+CM97)/45+SUM(AX97+AY97+AZ97+BA97+BF97+BG97+BH97)/60+SUM(AL97+BZ97)/50</f>
         <v/>
       </c>
       <c r="CQ97" s="38">
-        <f>SUM(R97+S97+BN97+CD97+CE97)/65+SUM(AB97)/36+SUM(AR97+AS97+BW97+BX97+CK97)/40+SUM(BB97+BC97+BI97+BJ97)/60</f>
+        <f>SUM(R97+S97+BN97+CD97+CE97)/65+SUM(AB97)/36+SUM(AR97+AS97+BW97+BX97+CK97+CN97)/40+SUM(BB97+BC97+BI97+BJ97)/60</f>
         <v/>
       </c>
       <c r="CR97" s="38">
@@ -18445,11 +18472,11 @@
         <v/>
       </c>
       <c r="CP98" s="38">
-        <f>SUM(O98+P98+Q98+BL98+BM98+CB98+CC98)/65+SUM(X98+Y98)/44+SUM(AJ98+AK98+AM98+AN98+AO98+AP98+AQ98+BR98+BS98+BT98+BU98+BV98+CH98+CI98+CJ98)/45+SUM(AX98+AY98+AZ98+BA98+BF98+BG98+BH98)/60+SUM(AL98+BZ98)/50</f>
+        <f>SUM(O98+P98+Q98+BL98+BM98+CB98+CC98)/65+SUM(X98+Y98)/44+SUM(AJ98+AK98+AM98+AN98+AO98+AP98+AQ98+BR98+BS98+BT98+BU98+BV98+CH98+CI98+CJ98+CM98)/45+SUM(AX98+AY98+AZ98+BA98+BF98+BG98+BH98)/60+SUM(AL98+BZ98)/50</f>
         <v/>
       </c>
       <c r="CQ98" s="38">
-        <f>SUM(R98+S98+BN98+CD98+CE98)/65+SUM(AB98)/36+SUM(AR98+AS98+BW98+BX98+CK98)/40+SUM(BB98+BC98+BI98+BJ98)/60</f>
+        <f>SUM(R98+S98+BN98+CD98+CE98)/65+SUM(AB98)/36+SUM(AR98+AS98+BW98+BX98+CK98+CN98)/40+SUM(BB98+BC98+BI98+BJ98)/60</f>
         <v/>
       </c>
       <c r="CR98" s="38">
@@ -18604,11 +18631,11 @@
         <v/>
       </c>
       <c r="CP99" s="38">
-        <f>SUM(O99+P99+Q99+BL99+BM99+CB99+CC99)/65+SUM(X99+Y99)/44+SUM(AJ99+AK99+AM99+AN99+AO99+AP99+AQ99+BR99+BS99+BT99+BU99+BV99+CH99+CI99+CJ99)/45+SUM(AX99+AY99+AZ99+BA99+BF99+BG99+BH99)/60+SUM(AL99+BZ99)/50</f>
+        <f>SUM(O99+P99+Q99+BL99+BM99+CB99+CC99)/65+SUM(X99+Y99)/44+SUM(AJ99+AK99+AM99+AN99+AO99+AP99+AQ99+BR99+BS99+BT99+BU99+BV99+CH99+CI99+CJ99+CM99)/45+SUM(AX99+AY99+AZ99+BA99+BF99+BG99+BH99)/60+SUM(AL99+BZ99)/50</f>
         <v/>
       </c>
       <c r="CQ99" s="38">
-        <f>SUM(R99+S99+BN99+CD99+CE99)/65+SUM(AB99)/36+SUM(AR99+AS99+BW99+BX99+CK99)/40+SUM(BB99+BC99+BI99+BJ99)/60</f>
+        <f>SUM(R99+S99+BN99+CD99+CE99)/65+SUM(AB99)/36+SUM(AR99+AS99+BW99+BX99+CK99+CN99)/40+SUM(BB99+BC99+BI99+BJ99)/60</f>
         <v/>
       </c>
       <c r="CR99" s="38">
@@ -18763,11 +18790,11 @@
         <v/>
       </c>
       <c r="CP100" s="38">
-        <f>SUM(O100+P100+Q100+BL100+BM100+CB100+CC100)/65+SUM(X100+Y100)/44+SUM(AJ100+AK100+AM100+AN100+AO100+AP100+AQ100+BR100+BS100+BT100+BU100+BV100+CH100+CI100+CJ100)/45+SUM(AX100+AY100+AZ100+BA100+BF100+BG100+BH100)/60+SUM(AL100+BZ100)/50</f>
+        <f>SUM(O100+P100+Q100+BL100+BM100+CB100+CC100)/65+SUM(X100+Y100)/44+SUM(AJ100+AK100+AM100+AN100+AO100+AP100+AQ100+BR100+BS100+BT100+BU100+BV100+CH100+CI100+CJ100+CM100)/45+SUM(AX100+AY100+AZ100+BA100+BF100+BG100+BH100)/60+SUM(AL100+BZ100)/50</f>
         <v/>
       </c>
       <c r="CQ100" s="38">
-        <f>SUM(R100+S100+BN100+CD100+CE100)/65+SUM(AB100)/36+SUM(AR100+AS100+BW100+BX100+CK100)/40+SUM(BB100+BC100+BI100+BJ100)/60</f>
+        <f>SUM(R100+S100+BN100+CD100+CE100)/65+SUM(AB100)/36+SUM(AR100+AS100+BW100+BX100+CK100+CN100)/40+SUM(BB100+BC100+BI100+BJ100)/60</f>
         <v/>
       </c>
       <c r="CR100" s="38">
@@ -18922,11 +18949,11 @@
         <v/>
       </c>
       <c r="CP101" s="38">
-        <f>SUM(O101+P101+Q101+BL101+BM101+CB101+CC101)/65+SUM(X101+Y101)/44+SUM(AJ101+AK101+AM101+AN101+AO101+AP101+AQ101+BR101+BS101+BT101+BU101+BV101+CH101+CI101+CJ101)/45+SUM(AX101+AY101+AZ101+BA101+BF101+BG101+BH101)/60+SUM(AL101+BZ101)/50</f>
+        <f>SUM(O101+P101+Q101+BL101+BM101+CB101+CC101)/65+SUM(X101+Y101)/44+SUM(AJ101+AK101+AM101+AN101+AO101+AP101+AQ101+BR101+BS101+BT101+BU101+BV101+CH101+CI101+CJ101+CM101)/45+SUM(AX101+AY101+AZ101+BA101+BF101+BG101+BH101)/60+SUM(AL101+BZ101)/50</f>
         <v/>
       </c>
       <c r="CQ101" s="38">
-        <f>SUM(R101+S101+BN101+CD101+CE101)/65+SUM(AB101)/36+SUM(AR101+AS101+BW101+BX101+CK101)/40+SUM(BB101+BC101+BI101+BJ101)/60</f>
+        <f>SUM(R101+S101+BN101+CD101+CE101)/65+SUM(AB101)/36+SUM(AR101+AS101+BW101+BX101+CK101+CN101)/40+SUM(BB101+BC101+BI101+BJ101)/60</f>
         <v/>
       </c>
       <c r="CR101" s="38">
@@ -19081,11 +19108,11 @@
         <v/>
       </c>
       <c r="CP102" s="38">
-        <f>SUM(O102+P102+Q102+BL102+BM102+CB102+CC102)/65+SUM(X102+Y102)/44+SUM(AJ102+AK102+AM102+AN102+AO102+AP102+AQ102+BR102+BS102+BT102+BU102+BV102+CH102+CI102+CJ102)/45+SUM(AX102+AY102+AZ102+BA102+BF102+BG102+BH102)/60+SUM(AL102+BZ102)/50</f>
+        <f>SUM(O102+P102+Q102+BL102+BM102+CB102+CC102)/65+SUM(X102+Y102)/44+SUM(AJ102+AK102+AM102+AN102+AO102+AP102+AQ102+BR102+BS102+BT102+BU102+BV102+CH102+CI102+CJ102+CM102)/45+SUM(AX102+AY102+AZ102+BA102+BF102+BG102+BH102)/60+SUM(AL102+BZ102)/50</f>
         <v/>
       </c>
       <c r="CQ102" s="38">
-        <f>SUM(R102+S102+BN102+CD102+CE102)/65+SUM(AB102)/36+SUM(AR102+AS102+BW102+BX102+CK102)/40+SUM(BB102+BC102+BI102+BJ102)/60</f>
+        <f>SUM(R102+S102+BN102+CD102+CE102)/65+SUM(AB102)/36+SUM(AR102+AS102+BW102+BX102+CK102+CN102)/40+SUM(BB102+BC102+BI102+BJ102)/60</f>
         <v/>
       </c>
       <c r="CR102" s="38">
@@ -19240,11 +19267,11 @@
         <v/>
       </c>
       <c r="CP103" s="38">
-        <f>SUM(O103+P103+Q103+BL103+BM103+CB103+CC103)/65+SUM(X103+Y103)/44+SUM(AJ103+AK103+AM103+AN103+AO103+AP103+AQ103+BR103+BS103+BT103+BU103+BV103+CH103+CI103+CJ103)/45+SUM(AX103+AY103+AZ103+BA103+BF103+BG103+BH103)/60+SUM(AL103+BZ103)/50</f>
+        <f>SUM(O103+P103+Q103+BL103+BM103+CB103+CC103)/65+SUM(X103+Y103)/44+SUM(AJ103+AK103+AM103+AN103+AO103+AP103+AQ103+BR103+BS103+BT103+BU103+BV103+CH103+CI103+CJ103+CM103)/45+SUM(AX103+AY103+AZ103+BA103+BF103+BG103+BH103)/60+SUM(AL103+BZ103)/50</f>
         <v/>
       </c>
       <c r="CQ103" s="38">
-        <f>SUM(R103+S103+BN103+CD103+CE103)/65+SUM(AB103)/36+SUM(AR103+AS103+BW103+BX103+CK103)/40+SUM(BB103+BC103+BI103+BJ103)/60</f>
+        <f>SUM(R103+S103+BN103+CD103+CE103)/65+SUM(AB103)/36+SUM(AR103+AS103+BW103+BX103+CK103+CN103)/40+SUM(BB103+BC103+BI103+BJ103)/60</f>
         <v/>
       </c>
       <c r="CR103" s="38">
@@ -19399,11 +19426,11 @@
         <v/>
       </c>
       <c r="CP104" s="38">
-        <f>SUM(O104+P104+Q104+BL104+BM104+CB104+CC104)/65+SUM(X104+Y104)/44+SUM(AJ104+AK104+AM104+AN104+AO104+AP104+AQ104+BR104+BS104+BT104+BU104+BV104+CH104+CI104+CJ104)/45+SUM(AX104+AY104+AZ104+BA104+BF104+BG104+BH104)/60+SUM(AL104+BZ104)/50</f>
+        <f>SUM(O104+P104+Q104+BL104+BM104+CB104+CC104)/65+SUM(X104+Y104)/44+SUM(AJ104+AK104+AM104+AN104+AO104+AP104+AQ104+BR104+BS104+BT104+BU104+BV104+CH104+CI104+CJ104+CM104)/45+SUM(AX104+AY104+AZ104+BA104+BF104+BG104+BH104)/60+SUM(AL104+BZ104)/50</f>
         <v/>
       </c>
       <c r="CQ104" s="38">
-        <f>SUM(R104+S104+BN104+CD104+CE104)/65+SUM(AB104)/36+SUM(AR104+AS104+BW104+BX104+CK104)/40+SUM(BB104+BC104+BI104+BJ104)/60</f>
+        <f>SUM(R104+S104+BN104+CD104+CE104)/65+SUM(AB104)/36+SUM(AR104+AS104+BW104+BX104+CK104+CN104)/40+SUM(BB104+BC104+BI104+BJ104)/60</f>
         <v/>
       </c>
       <c r="CR104" s="38">
@@ -19558,11 +19585,11 @@
         <v/>
       </c>
       <c r="CP105" s="38">
-        <f>SUM(O105+P105+Q105+BL105+BM105+CB105+CC105)/65+SUM(X105+Y105)/44+SUM(AJ105+AK105+AM105+AN105+AO105+AP105+AQ105+BR105+BS105+BT105+BU105+BV105+CH105+CI105+CJ105)/45+SUM(AX105+AY105+AZ105+BA105+BF105+BG105+BH105)/60+SUM(AL105+BZ105)/50</f>
+        <f>SUM(O105+P105+Q105+BL105+BM105+CB105+CC105)/65+SUM(X105+Y105)/44+SUM(AJ105+AK105+AM105+AN105+AO105+AP105+AQ105+BR105+BS105+BT105+BU105+BV105+CH105+CI105+CJ105+CM105)/45+SUM(AX105+AY105+AZ105+BA105+BF105+BG105+BH105)/60+SUM(AL105+BZ105)/50</f>
         <v/>
       </c>
       <c r="CQ105" s="38">
-        <f>SUM(R105+S105+BN105+CD105+CE105)/65+SUM(AB105)/36+SUM(AR105+AS105+BW105+BX105+CK105)/40+SUM(BB105+BC105+BI105+BJ105)/60</f>
+        <f>SUM(R105+S105+BN105+CD105+CE105)/65+SUM(AB105)/36+SUM(AR105+AS105+BW105+BX105+CK105+CN105)/40+SUM(BB105+BC105+BI105+BJ105)/60</f>
         <v/>
       </c>
       <c r="CR105" s="38">
@@ -19717,11 +19744,11 @@
         <v/>
       </c>
       <c r="CP106" s="38">
-        <f>SUM(O106+P106+Q106+BL106+BM106+CB106+CC106)/65+SUM(X106+Y106)/44+SUM(AJ106+AK106+AM106+AN106+AO106+AP106+AQ106+BR106+BS106+BT106+BU106+BV106+CH106+CI106+CJ106)/45+SUM(AX106+AY106+AZ106+BA106+BF106+BG106+BH106)/60+SUM(AL106+BZ106)/50</f>
+        <f>SUM(O106+P106+Q106+BL106+BM106+CB106+CC106)/65+SUM(X106+Y106)/44+SUM(AJ106+AK106+AM106+AN106+AO106+AP106+AQ106+BR106+BS106+BT106+BU106+BV106+CH106+CI106+CJ106+CM106)/45+SUM(AX106+AY106+AZ106+BA106+BF106+BG106+BH106)/60+SUM(AL106+BZ106)/50</f>
         <v/>
       </c>
       <c r="CQ106" s="38">
-        <f>SUM(R106+S106+BN106+CD106+CE106)/65+SUM(AB106)/36+SUM(AR106+AS106+BW106+BX106+CK106)/40+SUM(BB106+BC106+BI106+BJ106)/60</f>
+        <f>SUM(R106+S106+BN106+CD106+CE106)/65+SUM(AB106)/36+SUM(AR106+AS106+BW106+BX106+CK106+CN106)/40+SUM(BB106+BC106+BI106+BJ106)/60</f>
         <v/>
       </c>
       <c r="CR106" s="38">
@@ -19876,11 +19903,11 @@
         <v/>
       </c>
       <c r="CP107" s="38">
-        <f>SUM(O107+P107+Q107+BL107+BM107+CB107+CC107)/65+SUM(X107+Y107)/44+SUM(AJ107+AK107+AM107+AN107+AO107+AP107+AQ107+BR107+BS107+BT107+BU107+BV107+CH107+CI107+CJ107)/45+SUM(AX107+AY107+AZ107+BA107+BF107+BG107+BH107)/60+SUM(AL107+BZ107)/50</f>
+        <f>SUM(O107+P107+Q107+BL107+BM107+CB107+CC107)/65+SUM(X107+Y107)/44+SUM(AJ107+AK107+AM107+AN107+AO107+AP107+AQ107+BR107+BS107+BT107+BU107+BV107+CH107+CI107+CJ107+CM107)/45+SUM(AX107+AY107+AZ107+BA107+BF107+BG107+BH107)/60+SUM(AL107+BZ107)/50</f>
         <v/>
       </c>
       <c r="CQ107" s="38">
-        <f>SUM(R107+S107+BN107+CD107+CE107)/65+SUM(AB107)/36+SUM(AR107+AS107+BW107+BX107+CK107)/40+SUM(BB107+BC107+BI107+BJ107)/60</f>
+        <f>SUM(R107+S107+BN107+CD107+CE107)/65+SUM(AB107)/36+SUM(AR107+AS107+BW107+BX107+CK107+CN107)/40+SUM(BB107+BC107+BI107+BJ107)/60</f>
         <v/>
       </c>
       <c r="CR107" s="38">
@@ -20035,11 +20062,11 @@
         <v/>
       </c>
       <c r="CP108" s="38">
-        <f>SUM(O108+P108+Q108+BL108+BM108+CB108+CC108)/65+SUM(X108+Y108)/44+SUM(AJ108+AK108+AM108+AN108+AO108+AP108+AQ108+BR108+BS108+BT108+BU108+BV108+CH108+CI108+CJ108)/45+SUM(AX108+AY108+AZ108+BA108+BF108+BG108+BH108)/60+SUM(AL108+BZ108)/50</f>
+        <f>SUM(O108+P108+Q108+BL108+BM108+CB108+CC108)/65+SUM(X108+Y108)/44+SUM(AJ108+AK108+AM108+AN108+AO108+AP108+AQ108+BR108+BS108+BT108+BU108+BV108+CH108+CI108+CJ108+CM108)/45+SUM(AX108+AY108+AZ108+BA108+BF108+BG108+BH108)/60+SUM(AL108+BZ108)/50</f>
         <v/>
       </c>
       <c r="CQ108" s="38">
-        <f>SUM(R108+S108+BN108+CD108+CE108)/65+SUM(AB108)/36+SUM(AR108+AS108+BW108+BX108+CK108)/40+SUM(BB108+BC108+BI108+BJ108)/60</f>
+        <f>SUM(R108+S108+BN108+CD108+CE108)/65+SUM(AB108)/36+SUM(AR108+AS108+BW108+BX108+CK108+CN108)/40+SUM(BB108+BC108+BI108+BJ108)/60</f>
         <v/>
       </c>
       <c r="CR108" s="38">
@@ -20194,11 +20221,11 @@
         <v/>
       </c>
       <c r="CP109" s="38">
-        <f>SUM(O109+P109+Q109+BL109+BM109+CB109+CC109)/65+SUM(X109+Y109)/44+SUM(AJ109+AK109+AM109+AN109+AO109+AP109+AQ109+BR109+BS109+BT109+BU109+BV109+CH109+CI109+CJ109)/45+SUM(AX109+AY109+AZ109+BA109+BF109+BG109+BH109)/60+SUM(AL109+BZ109)/50</f>
+        <f>SUM(O109+P109+Q109+BL109+BM109+CB109+CC109)/65+SUM(X109+Y109)/44+SUM(AJ109+AK109+AM109+AN109+AO109+AP109+AQ109+BR109+BS109+BT109+BU109+BV109+CH109+CI109+CJ109+CM109)/45+SUM(AX109+AY109+AZ109+BA109+BF109+BG109+BH109)/60+SUM(AL109+BZ109)/50</f>
         <v/>
       </c>
       <c r="CQ109" s="38">
-        <f>SUM(R109+S109+BN109+CD109+CE109)/65+SUM(AB109)/36+SUM(AR109+AS109+BW109+BX109+CK109)/40+SUM(BB109+BC109+BI109+BJ109)/60</f>
+        <f>SUM(R109+S109+BN109+CD109+CE109)/65+SUM(AB109)/36+SUM(AR109+AS109+BW109+BX109+CK109+CN109)/40+SUM(BB109+BC109+BI109+BJ109)/60</f>
         <v/>
       </c>
       <c r="CR109" s="38">
@@ -20353,11 +20380,11 @@
         <v/>
       </c>
       <c r="CP110" s="38">
-        <f>SUM(O110+P110+Q110+BL110+BM110+CB110+CC110)/65+SUM(X110+Y110)/44+SUM(AJ110+AK110+AM110+AN110+AO110+AP110+AQ110+BR110+BS110+BT110+BU110+BV110+CH110+CI110+CJ110)/45+SUM(AX110+AY110+AZ110+BA110+BF110+BG110+BH110)/60+SUM(AL110+BZ110)/50</f>
+        <f>SUM(O110+P110+Q110+BL110+BM110+CB110+CC110)/65+SUM(X110+Y110)/44+SUM(AJ110+AK110+AM110+AN110+AO110+AP110+AQ110+BR110+BS110+BT110+BU110+BV110+CH110+CI110+CJ110+CM110)/45+SUM(AX110+AY110+AZ110+BA110+BF110+BG110+BH110)/60+SUM(AL110+BZ110)/50</f>
         <v/>
       </c>
       <c r="CQ110" s="38">
-        <f>SUM(R110+S110+BN110+CD110+CE110)/65+SUM(AB110)/36+SUM(AR110+AS110+BW110+BX110+CK110)/40+SUM(BB110+BC110+BI110+BJ110)/60</f>
+        <f>SUM(R110+S110+BN110+CD110+CE110)/65+SUM(AB110)/36+SUM(AR110+AS110+BW110+BX110+CK110+CN110)/40+SUM(BB110+BC110+BI110+BJ110)/60</f>
         <v/>
       </c>
       <c r="CR110" s="38">
@@ -20512,11 +20539,11 @@
         <v/>
       </c>
       <c r="CP111" s="38">
-        <f>SUM(O111+P111+Q111+BL111+BM111+CB111+CC111)/65+SUM(X111+Y111)/44+SUM(AJ111+AK111+AM111+AN111+AO111+AP111+AQ111+BR111+BS111+BT111+BU111+BV111+CH111+CI111+CJ111)/45+SUM(AX111+AY111+AZ111+BA111+BF111+BG111+BH111)/60+SUM(AL111+BZ111)/50</f>
+        <f>SUM(O111+P111+Q111+BL111+BM111+CB111+CC111)/65+SUM(X111+Y111)/44+SUM(AJ111+AK111+AM111+AN111+AO111+AP111+AQ111+BR111+BS111+BT111+BU111+BV111+CH111+CI111+CJ111+CM111)/45+SUM(AX111+AY111+AZ111+BA111+BF111+BG111+BH111)/60+SUM(AL111+BZ111)/50</f>
         <v/>
       </c>
       <c r="CQ111" s="38">
-        <f>SUM(R111+S111+BN111+CD111+CE111)/65+SUM(AB111)/36+SUM(AR111+AS111+BW111+BX111+CK111)/40+SUM(BB111+BC111+BI111+BJ111)/60</f>
+        <f>SUM(R111+S111+BN111+CD111+CE111)/65+SUM(AB111)/36+SUM(AR111+AS111+BW111+BX111+CK111+CN111)/40+SUM(BB111+BC111+BI111+BJ111)/60</f>
         <v/>
       </c>
       <c r="CR111" s="38">
@@ -20671,11 +20698,11 @@
         <v/>
       </c>
       <c r="CP112" s="38">
-        <f>SUM(O112+P112+Q112+BL112+BM112+CB112+CC112)/65+SUM(X112+Y112)/44+SUM(AJ112+AK112+AM112+AN112+AO112+AP112+AQ112+BR112+BS112+BT112+BU112+BV112+CH112+CI112+CJ112)/45+SUM(AX112+AY112+AZ112+BA112+BF112+BG112+BH112)/60+SUM(AL112+BZ112)/50</f>
+        <f>SUM(O112+P112+Q112+BL112+BM112+CB112+CC112)/65+SUM(X112+Y112)/44+SUM(AJ112+AK112+AM112+AN112+AO112+AP112+AQ112+BR112+BS112+BT112+BU112+BV112+CH112+CI112+CJ112+CM112)/45+SUM(AX112+AY112+AZ112+BA112+BF112+BG112+BH112)/60+SUM(AL112+BZ112)/50</f>
         <v/>
       </c>
       <c r="CQ112" s="38">
-        <f>SUM(R112+S112+BN112+CD112+CE112)/65+SUM(AB112)/36+SUM(AR112+AS112+BW112+BX112+CK112)/40+SUM(BB112+BC112+BI112+BJ112)/60</f>
+        <f>SUM(R112+S112+BN112+CD112+CE112)/65+SUM(AB112)/36+SUM(AR112+AS112+BW112+BX112+CK112+CN112)/40+SUM(BB112+BC112+BI112+BJ112)/60</f>
         <v/>
       </c>
       <c r="CR112" s="38">
@@ -20830,11 +20857,11 @@
         <v/>
       </c>
       <c r="CP113" s="38">
-        <f>SUM(O113+P113+Q113+BL113+BM113+CB113+CC113)/65+SUM(X113+Y113)/44+SUM(AJ113+AK113+AM113+AN113+AO113+AP113+AQ113+BR113+BS113+BT113+BU113+BV113+CH113+CI113+CJ113)/45+SUM(AX113+AY113+AZ113+BA113+BF113+BG113+BH113)/60+SUM(AL113+BZ113)/50</f>
+        <f>SUM(O113+P113+Q113+BL113+BM113+CB113+CC113)/65+SUM(X113+Y113)/44+SUM(AJ113+AK113+AM113+AN113+AO113+AP113+AQ113+BR113+BS113+BT113+BU113+BV113+CH113+CI113+CJ113+CM113)/45+SUM(AX113+AY113+AZ113+BA113+BF113+BG113+BH113)/60+SUM(AL113+BZ113)/50</f>
         <v/>
       </c>
       <c r="CQ113" s="38">
-        <f>SUM(R113+S113+BN113+CD113+CE113)/65+SUM(AB113)/36+SUM(AR113+AS113+BW113+BX113+CK113)/40+SUM(BB113+BC113+BI113+BJ113)/60</f>
+        <f>SUM(R113+S113+BN113+CD113+CE113)/65+SUM(AB113)/36+SUM(AR113+AS113+BW113+BX113+CK113+CN113)/40+SUM(BB113+BC113+BI113+BJ113)/60</f>
         <v/>
       </c>
       <c r="CR113" s="38">
@@ -20989,11 +21016,11 @@
         <v/>
       </c>
       <c r="CP114" s="38">
-        <f>SUM(O114+P114+Q114+BL114+BM114+CB114+CC114)/65+SUM(X114+Y114)/44+SUM(AJ114+AK114+AM114+AN114+AO114+AP114+AQ114+BR114+BS114+BT114+BU114+BV114+CH114+CI114+CJ114)/45+SUM(AX114+AY114+AZ114+BA114+BF114+BG114+BH114)/60+SUM(AL114+BZ114)/50</f>
+        <f>SUM(O114+P114+Q114+BL114+BM114+CB114+CC114)/65+SUM(X114+Y114)/44+SUM(AJ114+AK114+AM114+AN114+AO114+AP114+AQ114+BR114+BS114+BT114+BU114+BV114+CH114+CI114+CJ114+CM114)/45+SUM(AX114+AY114+AZ114+BA114+BF114+BG114+BH114)/60+SUM(AL114+BZ114)/50</f>
         <v/>
       </c>
       <c r="CQ114" s="38">
-        <f>SUM(R114+S114+BN114+CD114+CE114)/65+SUM(AB114)/36+SUM(AR114+AS114+BW114+BX114+CK114)/40+SUM(BB114+BC114+BI114+BJ114)/60</f>
+        <f>SUM(R114+S114+BN114+CD114+CE114)/65+SUM(AB114)/36+SUM(AR114+AS114+BW114+BX114+CK114+CN114)/40+SUM(BB114+BC114+BI114+BJ114)/60</f>
         <v/>
       </c>
       <c r="CR114" s="38">
@@ -21148,11 +21175,11 @@
         <v/>
       </c>
       <c r="CP115" s="38">
-        <f>SUM(O115+P115+Q115+BL115+BM115+CB115+CC115)/65+SUM(X115+Y115)/44+SUM(AJ115+AK115+AM115+AN115+AO115+AP115+AQ115+BR115+BS115+BT115+BU115+BV115+CH115+CI115+CJ115)/45+SUM(AX115+AY115+AZ115+BA115+BF115+BG115+BH115)/60+SUM(AL115+BZ115)/50</f>
+        <f>SUM(O115+P115+Q115+BL115+BM115+CB115+CC115)/65+SUM(X115+Y115)/44+SUM(AJ115+AK115+AM115+AN115+AO115+AP115+AQ115+BR115+BS115+BT115+BU115+BV115+CH115+CI115+CJ115+CM115)/45+SUM(AX115+AY115+AZ115+BA115+BF115+BG115+BH115)/60+SUM(AL115+BZ115)/50</f>
         <v/>
       </c>
       <c r="CQ115" s="38">
-        <f>SUM(R115+S115+BN115+CD115+CE115)/65+SUM(AB115)/36+SUM(AR115+AS115+BW115+BX115+CK115)/40+SUM(BB115+BC115+BI115+BJ115)/60</f>
+        <f>SUM(R115+S115+BN115+CD115+CE115)/65+SUM(AB115)/36+SUM(AR115+AS115+BW115+BX115+CK115+CN115)/40+SUM(BB115+BC115+BI115+BJ115)/60</f>
         <v/>
       </c>
       <c r="CR115" s="38">
@@ -21307,11 +21334,11 @@
         <v/>
       </c>
       <c r="CP116" s="38">
-        <f>SUM(O116+P116+Q116+BL116+BM116+CB116+CC116)/65+SUM(X116+Y116)/44+SUM(AJ116+AK116+AM116+AN116+AO116+AP116+AQ116+BR116+BS116+BT116+BU116+BV116+CH116+CI116+CJ116)/45+SUM(AX116+AY116+AZ116+BA116+BF116+BG116+BH116)/60+SUM(AL116+BZ116)/50</f>
+        <f>SUM(O116+P116+Q116+BL116+BM116+CB116+CC116)/65+SUM(X116+Y116)/44+SUM(AJ116+AK116+AM116+AN116+AO116+AP116+AQ116+BR116+BS116+BT116+BU116+BV116+CH116+CI116+CJ116+CM116)/45+SUM(AX116+AY116+AZ116+BA116+BF116+BG116+BH116)/60+SUM(AL116+BZ116)/50</f>
         <v/>
       </c>
       <c r="CQ116" s="38">
-        <f>SUM(R116+S116+BN116+CD116+CE116)/65+SUM(AB116)/36+SUM(AR116+AS116+BW116+BX116+CK116)/40+SUM(BB116+BC116+BI116+BJ116)/60</f>
+        <f>SUM(R116+S116+BN116+CD116+CE116)/65+SUM(AB116)/36+SUM(AR116+AS116+BW116+BX116+CK116+CN116)/40+SUM(BB116+BC116+BI116+BJ116)/60</f>
         <v/>
       </c>
       <c r="CR116" s="38">
@@ -21466,11 +21493,11 @@
         <v/>
       </c>
       <c r="CP117" s="38">
-        <f>SUM(O117+P117+Q117+BL117+BM117+CB117+CC117)/65+SUM(X117+Y117)/44+SUM(AJ117+AK117+AM117+AN117+AO117+AP117+AQ117+BR117+BS117+BT117+BU117+BV117+CH117+CI117+CJ117)/45+SUM(AX117+AY117+AZ117+BA117+BF117+BG117+BH117)/60+SUM(AL117+BZ117)/50</f>
+        <f>SUM(O117+P117+Q117+BL117+BM117+CB117+CC117)/65+SUM(X117+Y117)/44+SUM(AJ117+AK117+AM117+AN117+AO117+AP117+AQ117+BR117+BS117+BT117+BU117+BV117+CH117+CI117+CJ117+CM117)/45+SUM(AX117+AY117+AZ117+BA117+BF117+BG117+BH117)/60+SUM(AL117+BZ117)/50</f>
         <v/>
       </c>
       <c r="CQ117" s="38">
-        <f>SUM(R117+S117+BN117+CD117+CE117)/65+SUM(AB117)/36+SUM(AR117+AS117+BW117+BX117+CK117)/40+SUM(BB117+BC117+BI117+BJ117)/60</f>
+        <f>SUM(R117+S117+BN117+CD117+CE117)/65+SUM(AB117)/36+SUM(AR117+AS117+BW117+BX117+CK117+CN117)/40+SUM(BB117+BC117+BI117+BJ117)/60</f>
         <v/>
       </c>
       <c r="CR117" s="38">
@@ -21625,11 +21652,11 @@
         <v/>
       </c>
       <c r="CP118" s="38">
-        <f>SUM(O118+P118+Q118+BL118+BM118+CB118+CC118)/65+SUM(X118+Y118)/44+SUM(AJ118+AK118+AM118+AN118+AO118+AP118+AQ118+BR118+BS118+BT118+BU118+BV118+CH118+CI118+CJ118)/45+SUM(AX118+AY118+AZ118+BA118+BF118+BG118+BH118)/60+SUM(AL118+BZ118)/50</f>
+        <f>SUM(O118+P118+Q118+BL118+BM118+CB118+CC118)/65+SUM(X118+Y118)/44+SUM(AJ118+AK118+AM118+AN118+AO118+AP118+AQ118+BR118+BS118+BT118+BU118+BV118+CH118+CI118+CJ118+CM118)/45+SUM(AX118+AY118+AZ118+BA118+BF118+BG118+BH118)/60+SUM(AL118+BZ118)/50</f>
         <v/>
       </c>
       <c r="CQ118" s="38">
-        <f>SUM(R118+S118+BN118+CD118+CE118)/65+SUM(AB118)/36+SUM(AR118+AS118+BW118+BX118+CK118)/40+SUM(BB118+BC118+BI118+BJ118)/60</f>
+        <f>SUM(R118+S118+BN118+CD118+CE118)/65+SUM(AB118)/36+SUM(AR118+AS118+BW118+BX118+CK118+CN118)/40+SUM(BB118+BC118+BI118+BJ118)/60</f>
         <v/>
       </c>
       <c r="CR118" s="38">
@@ -21784,11 +21811,11 @@
         <v/>
       </c>
       <c r="CP119" s="38">
-        <f>SUM(O119+P119+Q119+BL119+BM119+CB119+CC119)/65+SUM(X119+Y119)/44+SUM(AJ119+AK119+AM119+AN119+AO119+AP119+AQ119+BR119+BS119+BT119+BU119+BV119+CH119+CI119+CJ119)/45+SUM(AX119+AY119+AZ119+BA119+BF119+BG119+BH119)/60+SUM(AL119+BZ119)/50</f>
+        <f>SUM(O119+P119+Q119+BL119+BM119+CB119+CC119)/65+SUM(X119+Y119)/44+SUM(AJ119+AK119+AM119+AN119+AO119+AP119+AQ119+BR119+BS119+BT119+BU119+BV119+CH119+CI119+CJ119+CM119)/45+SUM(AX119+AY119+AZ119+BA119+BF119+BG119+BH119)/60+SUM(AL119+BZ119)/50</f>
         <v/>
       </c>
       <c r="CQ119" s="38">
-        <f>SUM(R119+S119+BN119+CD119+CE119)/65+SUM(AB119)/36+SUM(AR119+AS119+BW119+BX119+CK119)/40+SUM(BB119+BC119+BI119+BJ119)/60</f>
+        <f>SUM(R119+S119+BN119+CD119+CE119)/65+SUM(AB119)/36+SUM(AR119+AS119+BW119+BX119+CK119+CN119)/40+SUM(BB119+BC119+BI119+BJ119)/60</f>
         <v/>
       </c>
       <c r="CR119" s="38">
@@ -21943,11 +21970,11 @@
         <v/>
       </c>
       <c r="CP120" s="38">
-        <f>SUM(O120+P120+Q120+BL120+BM120+CB120+CC120)/65+SUM(X120+Y120)/44+SUM(AJ120+AK120+AM120+AN120+AO120+AP120+AQ120+BR120+BS120+BT120+BU120+BV120+CH120+CI120+CJ120)/45+SUM(AX120+AY120+AZ120+BA120+BF120+BG120+BH120)/60+SUM(AL120+BZ120)/50</f>
+        <f>SUM(O120+P120+Q120+BL120+BM120+CB120+CC120)/65+SUM(X120+Y120)/44+SUM(AJ120+AK120+AM120+AN120+AO120+AP120+AQ120+BR120+BS120+BT120+BU120+BV120+CH120+CI120+CJ120+CM120)/45+SUM(AX120+AY120+AZ120+BA120+BF120+BG120+BH120)/60+SUM(AL120+BZ120)/50</f>
         <v/>
       </c>
       <c r="CQ120" s="38">
-        <f>SUM(R120+S120+BN120+CD120+CE120)/65+SUM(AB120)/36+SUM(AR120+AS120+BW120+BX120+CK120)/40+SUM(BB120+BC120+BI120+BJ120)/60</f>
+        <f>SUM(R120+S120+BN120+CD120+CE120)/65+SUM(AB120)/36+SUM(AR120+AS120+BW120+BX120+CK120+CN120)/40+SUM(BB120+BC120+BI120+BJ120)/60</f>
         <v/>
       </c>
       <c r="CR120" s="38">
@@ -22102,11 +22129,11 @@
         <v/>
       </c>
       <c r="CP121" s="38">
-        <f>SUM(O121+P121+Q121+BL121+BM121+CB121+CC121)/65+SUM(X121+Y121)/44+SUM(AJ121+AK121+AM121+AN121+AO121+AP121+AQ121+BR121+BS121+BT121+BU121+BV121+CH121+CI121+CJ121)/45+SUM(AX121+AY121+AZ121+BA121+BF121+BG121+BH121)/60+SUM(AL121+BZ121)/50</f>
+        <f>SUM(O121+P121+Q121+BL121+BM121+CB121+CC121)/65+SUM(X121+Y121)/44+SUM(AJ121+AK121+AM121+AN121+AO121+AP121+AQ121+BR121+BS121+BT121+BU121+BV121+CH121+CI121+CJ121+CM121)/45+SUM(AX121+AY121+AZ121+BA121+BF121+BG121+BH121)/60+SUM(AL121+BZ121)/50</f>
         <v/>
       </c>
       <c r="CQ121" s="38">
-        <f>SUM(R121+S121+BN121+CD121+CE121)/65+SUM(AB121)/36+SUM(AR121+AS121+BW121+BX121+CK121)/40+SUM(BB121+BC121+BI121+BJ121)/60</f>
+        <f>SUM(R121+S121+BN121+CD121+CE121)/65+SUM(AB121)/36+SUM(AR121+AS121+BW121+BX121+CK121+CN121)/40+SUM(BB121+BC121+BI121+BJ121)/60</f>
         <v/>
       </c>
       <c r="CR121" s="38">
@@ -22261,11 +22288,11 @@
         <v/>
       </c>
       <c r="CP122" s="38">
-        <f>SUM(O122+P122+Q122+BL122+BM122+CB122+CC122)/65+SUM(X122+Y122)/44+SUM(AJ122+AK122+AM122+AN122+AO122+AP122+AQ122+BR122+BS122+BT122+BU122+BV122+CH122+CI122+CJ122)/45+SUM(AX122+AY122+AZ122+BA122+BF122+BG122+BH122)/60+SUM(AL122+BZ122)/50</f>
+        <f>SUM(O122+P122+Q122+BL122+BM122+CB122+CC122)/65+SUM(X122+Y122)/44+SUM(AJ122+AK122+AM122+AN122+AO122+AP122+AQ122+BR122+BS122+BT122+BU122+BV122+CH122+CI122+CJ122+CM122)/45+SUM(AX122+AY122+AZ122+BA122+BF122+BG122+BH122)/60+SUM(AL122+BZ122)/50</f>
         <v/>
       </c>
       <c r="CQ122" s="38">
-        <f>SUM(R122+S122+BN122+CD122+CE122)/65+SUM(AB122)/36+SUM(AR122+AS122+BW122+BX122+CK122)/40+SUM(BB122+BC122+BI122+BJ122)/60</f>
+        <f>SUM(R122+S122+BN122+CD122+CE122)/65+SUM(AB122)/36+SUM(AR122+AS122+BW122+BX122+CK122+CN122)/40+SUM(BB122+BC122+BI122+BJ122)/60</f>
         <v/>
       </c>
       <c r="CR122" s="38">
@@ -22420,11 +22447,11 @@
         <v/>
       </c>
       <c r="CP123" s="38">
-        <f>SUM(O123+P123+Q123+BL123+BM123+CB123+CC123)/65+SUM(X123+Y123)/44+SUM(AJ123+AK123+AM123+AN123+AO123+AP123+AQ123+BR123+BS123+BT123+BU123+BV123+CH123+CI123+CJ123)/45+SUM(AX123+AY123+AZ123+BA123+BF123+BG123+BH123)/60+SUM(AL123+BZ123)/50</f>
+        <f>SUM(O123+P123+Q123+BL123+BM123+CB123+CC123)/65+SUM(X123+Y123)/44+SUM(AJ123+AK123+AM123+AN123+AO123+AP123+AQ123+BR123+BS123+BT123+BU123+BV123+CH123+CI123+CJ123+CM123)/45+SUM(AX123+AY123+AZ123+BA123+BF123+BG123+BH123)/60+SUM(AL123+BZ123)/50</f>
         <v/>
       </c>
       <c r="CQ123" s="38">
-        <f>SUM(R123+S123+BN123+CD123+CE123)/65+SUM(AB123)/36+SUM(AR123+AS123+BW123+BX123+CK123)/40+SUM(BB123+BC123+BI123+BJ123)/60</f>
+        <f>SUM(R123+S123+BN123+CD123+CE123)/65+SUM(AB123)/36+SUM(AR123+AS123+BW123+BX123+CK123+CN123)/40+SUM(BB123+BC123+BI123+BJ123)/60</f>
         <v/>
       </c>
       <c r="CR123" s="38">
@@ -22579,11 +22606,11 @@
         <v/>
       </c>
       <c r="CP124" s="38">
-        <f>SUM(O124+P124+Q124+BL124+BM124+CB124+CC124)/65+SUM(X124+Y124)/44+SUM(AJ124+AK124+AM124+AN124+AO124+AP124+AQ124+BR124+BS124+BT124+BU124+BV124+CH124+CI124+CJ124)/45+SUM(AX124+AY124+AZ124+BA124+BF124+BG124+BH124)/60+SUM(AL124+BZ124)/50</f>
+        <f>SUM(O124+P124+Q124+BL124+BM124+CB124+CC124)/65+SUM(X124+Y124)/44+SUM(AJ124+AK124+AM124+AN124+AO124+AP124+AQ124+BR124+BS124+BT124+BU124+BV124+CH124+CI124+CJ124+CM124)/45+SUM(AX124+AY124+AZ124+BA124+BF124+BG124+BH124)/60+SUM(AL124+BZ124)/50</f>
         <v/>
       </c>
       <c r="CQ124" s="38">
-        <f>SUM(R124+S124+BN124+CD124+CE124)/65+SUM(AB124)/36+SUM(AR124+AS124+BW124+BX124+CK124)/40+SUM(BB124+BC124+BI124+BJ124)/60</f>
+        <f>SUM(R124+S124+BN124+CD124+CE124)/65+SUM(AB124)/36+SUM(AR124+AS124+BW124+BX124+CK124+CN124)/40+SUM(BB124+BC124+BI124+BJ124)/60</f>
         <v/>
       </c>
       <c r="CR124" s="38">
@@ -22738,11 +22765,11 @@
         <v/>
       </c>
       <c r="CP125" s="38">
-        <f>SUM(O125+P125+Q125+BL125+BM125+CB125+CC125)/65+SUM(X125+Y125)/44+SUM(AJ125+AK125+AM125+AN125+AO125+AP125+AQ125+BR125+BS125+BT125+BU125+BV125+CH125+CI125+CJ125)/45+SUM(AX125+AY125+AZ125+BA125+BF125+BG125+BH125)/60+SUM(AL125+BZ125)/50</f>
+        <f>SUM(O125+P125+Q125+BL125+BM125+CB125+CC125)/65+SUM(X125+Y125)/44+SUM(AJ125+AK125+AM125+AN125+AO125+AP125+AQ125+BR125+BS125+BT125+BU125+BV125+CH125+CI125+CJ125+CM125)/45+SUM(AX125+AY125+AZ125+BA125+BF125+BG125+BH125)/60+SUM(AL125+BZ125)/50</f>
         <v/>
       </c>
       <c r="CQ125" s="38">
-        <f>SUM(R125+S125+BN125+CD125+CE125)/65+SUM(AB125)/36+SUM(AR125+AS125+BW125+BX125+CK125)/40+SUM(BB125+BC125+BI125+BJ125)/60</f>
+        <f>SUM(R125+S125+BN125+CD125+CE125)/65+SUM(AB125)/36+SUM(AR125+AS125+BW125+BX125+CK125+CN125)/40+SUM(BB125+BC125+BI125+BJ125)/60</f>
         <v/>
       </c>
       <c r="CR125" s="38">
@@ -22897,11 +22924,11 @@
         <v/>
       </c>
       <c r="CP126" s="38">
-        <f>SUM(O126+P126+Q126+BL126+BM126+CB126+CC126)/65+SUM(X126+Y126)/44+SUM(AJ126+AK126+AM126+AN126+AO126+AP126+AQ126+BR126+BS126+BT126+BU126+BV126+CH126+CI126+CJ126)/45+SUM(AX126+AY126+AZ126+BA126+BF126+BG126+BH126)/60+SUM(AL126+BZ126)/50</f>
+        <f>SUM(O126+P126+Q126+BL126+BM126+CB126+CC126)/65+SUM(X126+Y126)/44+SUM(AJ126+AK126+AM126+AN126+AO126+AP126+AQ126+BR126+BS126+BT126+BU126+BV126+CH126+CI126+CJ126+CM126)/45+SUM(AX126+AY126+AZ126+BA126+BF126+BG126+BH126)/60+SUM(AL126+BZ126)/50</f>
         <v/>
       </c>
       <c r="CQ126" s="38">
-        <f>SUM(R126+S126+BN126+CD126+CE126)/65+SUM(AB126)/36+SUM(AR126+AS126+BW126+BX126+CK126)/40+SUM(BB126+BC126+BI126+BJ126)/60</f>
+        <f>SUM(R126+S126+BN126+CD126+CE126)/65+SUM(AB126)/36+SUM(AR126+AS126+BW126+BX126+CK126+CN126)/40+SUM(BB126+BC126+BI126+BJ126)/60</f>
         <v/>
       </c>
       <c r="CR126" s="38">
@@ -23056,11 +23083,11 @@
         <v/>
       </c>
       <c r="CP127" s="38">
-        <f>SUM(O127+P127+Q127+BL127+BM127+CB127+CC127)/65+SUM(X127+Y127)/44+SUM(AJ127+AK127+AM127+AN127+AO127+AP127+AQ127+BR127+BS127+BT127+BU127+BV127+CH127+CI127+CJ127)/45+SUM(AX127+AY127+AZ127+BA127+BF127+BG127+BH127)/60+SUM(AL127+BZ127)/50</f>
+        <f>SUM(O127+P127+Q127+BL127+BM127+CB127+CC127)/65+SUM(X127+Y127)/44+SUM(AJ127+AK127+AM127+AN127+AO127+AP127+AQ127+BR127+BS127+BT127+BU127+BV127+CH127+CI127+CJ127+CM127)/45+SUM(AX127+AY127+AZ127+BA127+BF127+BG127+BH127)/60+SUM(AL127+BZ127)/50</f>
         <v/>
       </c>
       <c r="CQ127" s="38">
-        <f>SUM(R127+S127+BN127+CD127+CE127)/65+SUM(AB127)/36+SUM(AR127+AS127+BW127+BX127+CK127)/40+SUM(BB127+BC127+BI127+BJ127)/60</f>
+        <f>SUM(R127+S127+BN127+CD127+CE127)/65+SUM(AB127)/36+SUM(AR127+AS127+BW127+BX127+CK127+CN127)/40+SUM(BB127+BC127+BI127+BJ127)/60</f>
         <v/>
       </c>
       <c r="CR127" s="38">
@@ -23215,11 +23242,11 @@
         <v/>
       </c>
       <c r="CP128" s="38">
-        <f>SUM(O128+P128+Q128+BL128+BM128+CB128+CC128)/65+SUM(X128+Y128)/44+SUM(AJ128+AK128+AM128+AN128+AO128+AP128+AQ128+BR128+BS128+BT128+BU128+BV128+CH128+CI128+CJ128)/45+SUM(AX128+AY128+AZ128+BA128+BF128+BG128+BH128)/60+SUM(AL128+BZ128)/50</f>
+        <f>SUM(O128+P128+Q128+BL128+BM128+CB128+CC128)/65+SUM(X128+Y128)/44+SUM(AJ128+AK128+AM128+AN128+AO128+AP128+AQ128+BR128+BS128+BT128+BU128+BV128+CH128+CI128+CJ128+CM128)/45+SUM(AX128+AY128+AZ128+BA128+BF128+BG128+BH128)/60+SUM(AL128+BZ128)/50</f>
         <v/>
       </c>
       <c r="CQ128" s="38">
-        <f>SUM(R128+S128+BN128+CD128+CE128)/65+SUM(AB128)/36+SUM(AR128+AS128+BW128+BX128+CK128)/40+SUM(BB128+BC128+BI128+BJ128)/60</f>
+        <f>SUM(R128+S128+BN128+CD128+CE128)/65+SUM(AB128)/36+SUM(AR128+AS128+BW128+BX128+CK128+CN128)/40+SUM(BB128+BC128+BI128+BJ128)/60</f>
         <v/>
       </c>
       <c r="CR128" s="38">
@@ -23374,11 +23401,11 @@
         <v/>
       </c>
       <c r="CP129" s="38">
-        <f>SUM(O129+P129+Q129+BL129+BM129+CB129+CC129)/65+SUM(X129+Y129)/44+SUM(AJ129+AK129+AM129+AN129+AO129+AP129+AQ129+BR129+BS129+BT129+BU129+BV129+CH129+CI129+CJ129)/45+SUM(AX129+AY129+AZ129+BA129+BF129+BG129+BH129)/60+SUM(AL129+BZ129)/50</f>
+        <f>SUM(O129+P129+Q129+BL129+BM129+CB129+CC129)/65+SUM(X129+Y129)/44+SUM(AJ129+AK129+AM129+AN129+AO129+AP129+AQ129+BR129+BS129+BT129+BU129+BV129+CH129+CI129+CJ129+CM129)/45+SUM(AX129+AY129+AZ129+BA129+BF129+BG129+BH129)/60+SUM(AL129+BZ129)/50</f>
         <v/>
       </c>
       <c r="CQ129" s="38">
-        <f>SUM(R129+S129+BN129+CD129+CE129)/65+SUM(AB129)/36+SUM(AR129+AS129+BW129+BX129+CK129)/40+SUM(BB129+BC129+BI129+BJ129)/60</f>
+        <f>SUM(R129+S129+BN129+CD129+CE129)/65+SUM(AB129)/36+SUM(AR129+AS129+BW129+BX129+CK129+CN129)/40+SUM(BB129+BC129+BI129+BJ129)/60</f>
         <v/>
       </c>
       <c r="CR129" s="38">
@@ -23533,11 +23560,11 @@
         <v/>
       </c>
       <c r="CP130" s="38">
-        <f>SUM(O130+P130+Q130+BL130+BM130+CB130+CC130)/65+SUM(X130+Y130)/44+SUM(AJ130+AK130+AM130+AN130+AO130+AP130+AQ130+BR130+BS130+BT130+BU130+BV130+CH130+CI130+CJ130)/45+SUM(AX130+AY130+AZ130+BA130+BF130+BG130+BH130)/60+SUM(AL130+BZ130)/50</f>
+        <f>SUM(O130+P130+Q130+BL130+BM130+CB130+CC130)/65+SUM(X130+Y130)/44+SUM(AJ130+AK130+AM130+AN130+AO130+AP130+AQ130+BR130+BS130+BT130+BU130+BV130+CH130+CI130+CJ130+CM130)/45+SUM(AX130+AY130+AZ130+BA130+BF130+BG130+BH130)/60+SUM(AL130+BZ130)/50</f>
         <v/>
       </c>
       <c r="CQ130" s="38">
-        <f>SUM(R130+S130+BN130+CD130+CE130)/65+SUM(AB130)/36+SUM(AR130+AS130+BW130+BX130+CK130)/40+SUM(BB130+BC130+BI130+BJ130)/60</f>
+        <f>SUM(R130+S130+BN130+CD130+CE130)/65+SUM(AB130)/36+SUM(AR130+AS130+BW130+BX130+CK130+CN130)/40+SUM(BB130+BC130+BI130+BJ130)/60</f>
         <v/>
       </c>
       <c r="CR130" s="38">
@@ -23692,11 +23719,11 @@
         <v/>
       </c>
       <c r="CP131" s="38">
-        <f>SUM(O131+P131+Q131+BL131+BM131+CB131+CC131)/65+SUM(X131+Y131)/44+SUM(AJ131+AK131+AM131+AN131+AO131+AP131+AQ131+BR131+BS131+BT131+BU131+BV131+CH131+CI131+CJ131)/45+SUM(AX131+AY131+AZ131+BA131+BF131+BG131+BH131)/60+SUM(AL131+BZ131)/50</f>
+        <f>SUM(O131+P131+Q131+BL131+BM131+CB131+CC131)/65+SUM(X131+Y131)/44+SUM(AJ131+AK131+AM131+AN131+AO131+AP131+AQ131+BR131+BS131+BT131+BU131+BV131+CH131+CI131+CJ131+CM131)/45+SUM(AX131+AY131+AZ131+BA131+BF131+BG131+BH131)/60+SUM(AL131+BZ131)/50</f>
         <v/>
       </c>
       <c r="CQ131" s="38">
-        <f>SUM(R131+S131+BN131+CD131+CE131)/65+SUM(AB131)/36+SUM(AR131+AS131+BW131+BX131+CK131)/40+SUM(BB131+BC131+BI131+BJ131)/60</f>
+        <f>SUM(R131+S131+BN131+CD131+CE131)/65+SUM(AB131)/36+SUM(AR131+AS131+BW131+BX131+CK131+CN131)/40+SUM(BB131+BC131+BI131+BJ131)/60</f>
         <v/>
       </c>
       <c r="CR131" s="38">
@@ -23851,11 +23878,11 @@
         <v/>
       </c>
       <c r="CP132" s="38">
-        <f>SUM(O132+P132+Q132+BL132+BM132+CB132+CC132)/65+SUM(X132+Y132)/44+SUM(AJ132+AK132+AM132+AN132+AO132+AP132+AQ132+BR132+BS132+BT132+BU132+BV132+CH132+CI132+CJ132)/45+SUM(AX132+AY132+AZ132+BA132+BF132+BG132+BH132)/60+SUM(AL132+BZ132)/50</f>
+        <f>SUM(O132+P132+Q132+BL132+BM132+CB132+CC132)/65+SUM(X132+Y132)/44+SUM(AJ132+AK132+AM132+AN132+AO132+AP132+AQ132+BR132+BS132+BT132+BU132+BV132+CH132+CI132+CJ132+CM132)/45+SUM(AX132+AY132+AZ132+BA132+BF132+BG132+BH132)/60+SUM(AL132+BZ132)/50</f>
         <v/>
       </c>
       <c r="CQ132" s="38">
-        <f>SUM(R132+S132+BN132+CD132+CE132)/65+SUM(AB132)/36+SUM(AR132+AS132+BW132+BX132+CK132)/40+SUM(BB132+BC132+BI132+BJ132)/60</f>
+        <f>SUM(R132+S132+BN132+CD132+CE132)/65+SUM(AB132)/36+SUM(AR132+AS132+BW132+BX132+CK132+CN132)/40+SUM(BB132+BC132+BI132+BJ132)/60</f>
         <v/>
       </c>
       <c r="CR132" s="38">
@@ -24010,11 +24037,11 @@
         <v/>
       </c>
       <c r="CP133" s="38">
-        <f>SUM(O133+P133+Q133+BL133+BM133+CB133+CC133)/65+SUM(X133+Y133)/44+SUM(AJ133+AK133+AM133+AN133+AO133+AP133+AQ133+BR133+BS133+BT133+BU133+BV133+CH133+CI133+CJ133)/45+SUM(AX133+AY133+AZ133+BA133+BF133+BG133+BH133)/60+SUM(AL133+BZ133)/50</f>
+        <f>SUM(O133+P133+Q133+BL133+BM133+CB133+CC133)/65+SUM(X133+Y133)/44+SUM(AJ133+AK133+AM133+AN133+AO133+AP133+AQ133+BR133+BS133+BT133+BU133+BV133+CH133+CI133+CJ133+CM133)/45+SUM(AX133+AY133+AZ133+BA133+BF133+BG133+BH133)/60+SUM(AL133+BZ133)/50</f>
         <v/>
       </c>
       <c r="CQ133" s="38">
-        <f>SUM(R133+S133+BN133+CD133+CE133)/65+SUM(AB133)/36+SUM(AR133+AS133+BW133+BX133+CK133)/40+SUM(BB133+BC133+BI133+BJ133)/60</f>
+        <f>SUM(R133+S133+BN133+CD133+CE133)/65+SUM(AB133)/36+SUM(AR133+AS133+BW133+BX133+CK133+CN133)/40+SUM(BB133+BC133+BI133+BJ133)/60</f>
         <v/>
       </c>
       <c r="CR133" s="38">

--- a/vtl_template.xlsx
+++ b/vtl_template.xlsx
@@ -3294,24 +3294,24 @@
           <t>590ML           全台4入</t>
         </is>
       </c>
-      <c r="CK5" s="56" t="inlineStr">
+      <c r="CK5" s="55" t="inlineStr">
+        <is>
+          <t>590ML           全台促4入</t>
+        </is>
+      </c>
+      <c r="CL5" s="56" t="inlineStr">
         <is>
           <t>590ML           PX11</t>
         </is>
       </c>
-      <c r="CL5" s="77" t="inlineStr">
+      <c r="CM5" s="56" t="inlineStr">
+        <is>
+          <t>590ML           PX11促</t>
+        </is>
+      </c>
+      <c r="CN5" s="77" t="inlineStr">
         <is>
           <t>590ML           路凱4入</t>
-        </is>
-      </c>
-      <c r="CM5" s="55" t="inlineStr">
-        <is>
-          <t>590ML           全台促4入</t>
-        </is>
-      </c>
-      <c r="CN5" s="56" t="inlineStr">
-        <is>
-          <t>590ML           PX11促</t>
         </is>
       </c>
       <c r="CO5" s="26" t="inlineStr">
@@ -3834,22 +3834,22 @@
       </c>
       <c r="CK6" s="74" t="inlineStr">
         <is>
+          <t>JDP0590 4AB1</t>
+        </is>
+      </c>
+      <c r="CL6" s="74" t="inlineStr">
+        <is>
           <t>JDP0590 1BT1</t>
         </is>
       </c>
-      <c r="CL6" s="74" t="inlineStr">
+      <c r="CM6" s="74" t="inlineStr">
+        <is>
+          <t>JDP0590 1BU1</t>
+        </is>
+      </c>
+      <c r="CN6" s="74" t="inlineStr">
         <is>
           <t>JDP0590 4LC1</t>
-        </is>
-      </c>
-      <c r="CM6" s="74" t="inlineStr">
-        <is>
-          <t>JDP0590 4AB1</t>
-        </is>
-      </c>
-      <c r="CN6" s="74" t="inlineStr">
-        <is>
-          <t>JDP0590 1BU1</t>
         </is>
       </c>
       <c r="CO6" s="144" t="n"/>
@@ -4003,11 +4003,11 @@
         <v/>
       </c>
       <c r="CP7" s="129">
-        <f>SUM(O7+P7+Q7+BL7+BM7+CB7+CC7)/65+SUM(X7+Y7)/44+SUM(AJ7+AK7+AM7+AN7+AO7+AP7+AQ7+BR7+BS7+BT7+BU7+BV7+CH7+CI7+CJ7+CM7)/45+SUM(AX7+AY7+AZ7+BA7+BF7+BG7+BH7)/60+SUM(AL7+BZ7)/50</f>
+        <f>SUM(O7+P7+Q7+BL7+BM7+CB7+CC7)/65+SUM(X7+Y7)/44+SUM(AJ7+AK7+AM7+AN7+AO7+AP7+AQ7+BR7+BS7+BT7+BU7+BV7+CH7+CI7+CJ7+CK7)/45+SUM(AX7+AY7+AZ7+BA7+BF7+BG7+BH7)/60+SUM(AL7+BZ7)/50</f>
         <v/>
       </c>
       <c r="CQ7" s="129">
-        <f>SUM(R7+S7+BN7+CD7+CE7)/65+SUM(AB7)/36+SUM(AR7+AS7+BW7+BX7+CK7+CN7)/40+SUM(BB7+BC7+BI7+BJ7)/60</f>
+        <f>SUM(R7+S7+BN7+CD7+CE7)/65+SUM(AB7)/36+SUM(AR7+AS7+BW7+BX7+CL7+CM7)/40+SUM(BB7+BC7+BI7+BJ7)/60</f>
         <v/>
       </c>
       <c r="CR7" s="129">
@@ -4019,7 +4019,7 @@
         <v/>
       </c>
       <c r="CT7" s="129">
-        <f>SUM(BY7+CL7)/45</f>
+        <f>SUM(BY7+CN7)/45</f>
         <v/>
       </c>
       <c r="CU7" s="130">
@@ -4162,11 +4162,11 @@
         <v/>
       </c>
       <c r="CP8" s="38">
-        <f>SUM(O8+P8+Q8+BL8+BM8+CB8+CC8)/65+SUM(X8+Y8)/44+SUM(AJ8+AK8+AM8+AN8+AO8+AP8+AQ8+BR8+BS8+BT8+BU8+BV8+CH8+CI8+CJ8+CM8)/45+SUM(AX8+AY8+AZ8+BA8+BF8+BG8+BH8)/60+SUM(AL8+BZ8)/50</f>
+        <f>SUM(O8+P8+Q8+BL8+BM8+CB8+CC8)/65+SUM(X8+Y8)/44+SUM(AJ8+AK8+AM8+AN8+AO8+AP8+AQ8+BR8+BS8+BT8+BU8+BV8+CH8+CI8+CJ8+CK8)/45+SUM(AX8+AY8+AZ8+BA8+BF8+BG8+BH8)/60+SUM(AL8+BZ8)/50</f>
         <v/>
       </c>
       <c r="CQ8" s="38">
-        <f>SUM(R8+S8+BN8+CD8+CE8)/65+SUM(AB8)/36+SUM(AR8+AS8+BW8+BX8+CK8+CN8)/40+SUM(BB8+BC8+BI8+BJ8)/60</f>
+        <f>SUM(R8+S8+BN8+CD8+CE8)/65+SUM(AB8)/36+SUM(AR8+AS8+BW8+BX8+CL8+CM8)/40+SUM(BB8+BC8+BI8+BJ8)/60</f>
         <v/>
       </c>
       <c r="CR8" s="38">
@@ -4178,7 +4178,7 @@
         <v/>
       </c>
       <c r="CT8" s="38">
-        <f>SUM(BY8+CL8)/45</f>
+        <f>SUM(BY8+CN8)/45</f>
         <v/>
       </c>
       <c r="CU8" s="83">
@@ -4321,11 +4321,11 @@
         <v/>
       </c>
       <c r="CP9" s="38">
-        <f>SUM(O9+P9+Q9+BL9+BM9+CB9+CC9)/65+SUM(X9+Y9)/44+SUM(AJ9+AK9+AM9+AN9+AO9+AP9+AQ9+BR9+BS9+BT9+BU9+BV9+CH9+CI9+CJ9+CM9)/45+SUM(AX9+AY9+AZ9+BA9+BF9+BG9+BH9)/60+SUM(AL9+BZ9)/50</f>
+        <f>SUM(O9+P9+Q9+BL9+BM9+CB9+CC9)/65+SUM(X9+Y9)/44+SUM(AJ9+AK9+AM9+AN9+AO9+AP9+AQ9+BR9+BS9+BT9+BU9+BV9+CH9+CI9+CJ9+CK9)/45+SUM(AX9+AY9+AZ9+BA9+BF9+BG9+BH9)/60+SUM(AL9+BZ9)/50</f>
         <v/>
       </c>
       <c r="CQ9" s="38">
-        <f>SUM(R9+S9+BN9+CD9+CE9)/65+SUM(AB9)/36+SUM(AR9+AS9+BW9+BX9+CK9+CN9)/40+SUM(BB9+BC9+BI9+BJ9)/60</f>
+        <f>SUM(R9+S9+BN9+CD9+CE9)/65+SUM(AB9)/36+SUM(AR9+AS9+BW9+BX9+CL9+CM9)/40+SUM(BB9+BC9+BI9+BJ9)/60</f>
         <v/>
       </c>
       <c r="CR9" s="38">
@@ -4337,7 +4337,7 @@
         <v/>
       </c>
       <c r="CT9" s="38">
-        <f>SUM(BY9+CL9)/45</f>
+        <f>SUM(BY9+CN9)/45</f>
         <v/>
       </c>
       <c r="CU9" s="83">
@@ -4480,11 +4480,11 @@
         <v/>
       </c>
       <c r="CP10" s="38">
-        <f>SUM(O10+P10+Q10+BL10+BM10+CB10+CC10)/65+SUM(X10+Y10)/44+SUM(AJ10+AK10+AM10+AN10+AO10+AP10+AQ10+BR10+BS10+BT10+BU10+BV10+CH10+CI10+CJ10+CM10)/45+SUM(AX10+AY10+AZ10+BA10+BF10+BG10+BH10)/60+SUM(AL10+BZ10)/50</f>
+        <f>SUM(O10+P10+Q10+BL10+BM10+CB10+CC10)/65+SUM(X10+Y10)/44+SUM(AJ10+AK10+AM10+AN10+AO10+AP10+AQ10+BR10+BS10+BT10+BU10+BV10+CH10+CI10+CJ10+CK10)/45+SUM(AX10+AY10+AZ10+BA10+BF10+BG10+BH10)/60+SUM(AL10+BZ10)/50</f>
         <v/>
       </c>
       <c r="CQ10" s="38">
-        <f>SUM(R10+S10+BN10+CD10+CE10)/65+SUM(AB10)/36+SUM(AR10+AS10+BW10+BX10+CK10+CN10)/40+SUM(BB10+BC10+BI10+BJ10)/60</f>
+        <f>SUM(R10+S10+BN10+CD10+CE10)/65+SUM(AB10)/36+SUM(AR10+AS10+BW10+BX10+CL10+CM10)/40+SUM(BB10+BC10+BI10+BJ10)/60</f>
         <v/>
       </c>
       <c r="CR10" s="38">
@@ -4496,7 +4496,7 @@
         <v/>
       </c>
       <c r="CT10" s="38">
-        <f>SUM(BY10+CL10)/45</f>
+        <f>SUM(BY10+CN10)/45</f>
         <v/>
       </c>
       <c r="CU10" s="83">
@@ -4639,11 +4639,11 @@
         <v/>
       </c>
       <c r="CP11" s="38">
-        <f>SUM(O11+P11+Q11+BL11+BM11+CB11+CC11)/65+SUM(X11+Y11)/44+SUM(AJ11+AK11+AM11+AN11+AO11+AP11+AQ11+BR11+BS11+BT11+BU11+BV11+CH11+CI11+CJ11+CM11)/45+SUM(AX11+AY11+AZ11+BA11+BF11+BG11+BH11)/60+SUM(AL11+BZ11)/50</f>
+        <f>SUM(O11+P11+Q11+BL11+BM11+CB11+CC11)/65+SUM(X11+Y11)/44+SUM(AJ11+AK11+AM11+AN11+AO11+AP11+AQ11+BR11+BS11+BT11+BU11+BV11+CH11+CI11+CJ11+CK11)/45+SUM(AX11+AY11+AZ11+BA11+BF11+BG11+BH11)/60+SUM(AL11+BZ11)/50</f>
         <v/>
       </c>
       <c r="CQ11" s="38">
-        <f>SUM(R11+S11+BN11+CD11+CE11)/65+SUM(AB11)/36+SUM(AR11+AS11+BW11+BX11+CK11+CN11)/40+SUM(BB11+BC11+BI11+BJ11)/60</f>
+        <f>SUM(R11+S11+BN11+CD11+CE11)/65+SUM(AB11)/36+SUM(AR11+AS11+BW11+BX11+CL11+CM11)/40+SUM(BB11+BC11+BI11+BJ11)/60</f>
         <v/>
       </c>
       <c r="CR11" s="38">
@@ -4655,7 +4655,7 @@
         <v/>
       </c>
       <c r="CT11" s="38">
-        <f>SUM(BY11+CL11)/45</f>
+        <f>SUM(BY11+CN11)/45</f>
         <v/>
       </c>
       <c r="CU11" s="83">
@@ -4798,11 +4798,11 @@
         <v/>
       </c>
       <c r="CP12" s="38">
-        <f>SUM(O12+P12+Q12+BL12+BM12+CB12+CC12)/65+SUM(X12+Y12)/44+SUM(AJ12+AK12+AM12+AN12+AO12+AP12+AQ12+BR12+BS12+BT12+BU12+BV12+CH12+CI12+CJ12+CM12)/45+SUM(AX12+AY12+AZ12+BA12+BF12+BG12+BH12)/60+SUM(AL12+BZ12)/50</f>
+        <f>SUM(O12+P12+Q12+BL12+BM12+CB12+CC12)/65+SUM(X12+Y12)/44+SUM(AJ12+AK12+AM12+AN12+AO12+AP12+AQ12+BR12+BS12+BT12+BU12+BV12+CH12+CI12+CJ12+CK12)/45+SUM(AX12+AY12+AZ12+BA12+BF12+BG12+BH12)/60+SUM(AL12+BZ12)/50</f>
         <v/>
       </c>
       <c r="CQ12" s="38">
-        <f>SUM(R12+S12+BN12+CD12+CE12)/65+SUM(AB12)/36+SUM(AR12+AS12+BW12+BX12+CK12+CN12)/40+SUM(BB12+BC12+BI12+BJ12)/60</f>
+        <f>SUM(R12+S12+BN12+CD12+CE12)/65+SUM(AB12)/36+SUM(AR12+AS12+BW12+BX12+CL12+CM12)/40+SUM(BB12+BC12+BI12+BJ12)/60</f>
         <v/>
       </c>
       <c r="CR12" s="38">
@@ -4814,7 +4814,7 @@
         <v/>
       </c>
       <c r="CT12" s="38">
-        <f>SUM(BY12+CL12)/45</f>
+        <f>SUM(BY12+CN12)/45</f>
         <v/>
       </c>
       <c r="CU12" s="83">
@@ -4957,11 +4957,11 @@
         <v/>
       </c>
       <c r="CP13" s="38">
-        <f>SUM(O13+P13+Q13+BL13+BM13+CB13+CC13)/65+SUM(X13+Y13)/44+SUM(AJ13+AK13+AM13+AN13+AO13+AP13+AQ13+BR13+BS13+BT13+BU13+BV13+CH13+CI13+CJ13+CM13)/45+SUM(AX13+AY13+AZ13+BA13+BF13+BG13+BH13)/60+SUM(AL13+BZ13)/50</f>
+        <f>SUM(O13+P13+Q13+BL13+BM13+CB13+CC13)/65+SUM(X13+Y13)/44+SUM(AJ13+AK13+AM13+AN13+AO13+AP13+AQ13+BR13+BS13+BT13+BU13+BV13+CH13+CI13+CJ13+CK13)/45+SUM(AX13+AY13+AZ13+BA13+BF13+BG13+BH13)/60+SUM(AL13+BZ13)/50</f>
         <v/>
       </c>
       <c r="CQ13" s="38">
-        <f>SUM(R13+S13+BN13+CD13+CE13)/65+SUM(AB13)/36+SUM(AR13+AS13+BW13+BX13+CK13+CN13)/40+SUM(BB13+BC13+BI13+BJ13)/60</f>
+        <f>SUM(R13+S13+BN13+CD13+CE13)/65+SUM(AB13)/36+SUM(AR13+AS13+BW13+BX13+CL13+CM13)/40+SUM(BB13+BC13+BI13+BJ13)/60</f>
         <v/>
       </c>
       <c r="CR13" s="38">
@@ -4973,7 +4973,7 @@
         <v/>
       </c>
       <c r="CT13" s="38">
-        <f>SUM(BY13+CL13)/45</f>
+        <f>SUM(BY13+CN13)/45</f>
         <v/>
       </c>
       <c r="CU13" s="83">
@@ -5116,11 +5116,11 @@
         <v/>
       </c>
       <c r="CP14" s="38">
-        <f>SUM(O14+P14+Q14+BL14+BM14+CB14+CC14)/65+SUM(X14+Y14)/44+SUM(AJ14+AK14+AM14+AN14+AO14+AP14+AQ14+BR14+BS14+BT14+BU14+BV14+CH14+CI14+CJ14+CM14)/45+SUM(AX14+AY14+AZ14+BA14+BF14+BG14+BH14)/60+SUM(AL14+BZ14)/50</f>
+        <f>SUM(O14+P14+Q14+BL14+BM14+CB14+CC14)/65+SUM(X14+Y14)/44+SUM(AJ14+AK14+AM14+AN14+AO14+AP14+AQ14+BR14+BS14+BT14+BU14+BV14+CH14+CI14+CJ14+CK14)/45+SUM(AX14+AY14+AZ14+BA14+BF14+BG14+BH14)/60+SUM(AL14+BZ14)/50</f>
         <v/>
       </c>
       <c r="CQ14" s="38">
-        <f>SUM(R14+S14+BN14+CD14+CE14)/65+SUM(AB14)/36+SUM(AR14+AS14+BW14+BX14+CK14+CN14)/40+SUM(BB14+BC14+BI14+BJ14)/60</f>
+        <f>SUM(R14+S14+BN14+CD14+CE14)/65+SUM(AB14)/36+SUM(AR14+AS14+BW14+BX14+CL14+CM14)/40+SUM(BB14+BC14+BI14+BJ14)/60</f>
         <v/>
       </c>
       <c r="CR14" s="38">
@@ -5132,7 +5132,7 @@
         <v/>
       </c>
       <c r="CT14" s="38">
-        <f>SUM(BY14+CL14)/45</f>
+        <f>SUM(BY14+CN14)/45</f>
         <v/>
       </c>
       <c r="CU14" s="83">
@@ -5275,11 +5275,11 @@
         <v/>
       </c>
       <c r="CP15" s="38">
-        <f>SUM(O15+P15+Q15+BL15+BM15+CB15+CC15)/65+SUM(X15+Y15)/44+SUM(AJ15+AK15+AM15+AN15+AO15+AP15+AQ15+BR15+BS15+BT15+BU15+BV15+CH15+CI15+CJ15+CM15)/45+SUM(AX15+AY15+AZ15+BA15+BF15+BG15+BH15)/60+SUM(AL15+BZ15)/50</f>
+        <f>SUM(O15+P15+Q15+BL15+BM15+CB15+CC15)/65+SUM(X15+Y15)/44+SUM(AJ15+AK15+AM15+AN15+AO15+AP15+AQ15+BR15+BS15+BT15+BU15+BV15+CH15+CI15+CJ15+CK15)/45+SUM(AX15+AY15+AZ15+BA15+BF15+BG15+BH15)/60+SUM(AL15+BZ15)/50</f>
         <v/>
       </c>
       <c r="CQ15" s="38">
-        <f>SUM(R15+S15+BN15+CD15+CE15)/65+SUM(AB15)/36+SUM(AR15+AS15+BW15+BX15+CK15+CN15)/40+SUM(BB15+BC15+BI15+BJ15)/60</f>
+        <f>SUM(R15+S15+BN15+CD15+CE15)/65+SUM(AB15)/36+SUM(AR15+AS15+BW15+BX15+CL15+CM15)/40+SUM(BB15+BC15+BI15+BJ15)/60</f>
         <v/>
       </c>
       <c r="CR15" s="38">
@@ -5291,7 +5291,7 @@
         <v/>
       </c>
       <c r="CT15" s="38">
-        <f>SUM(BY15+CL15)/45</f>
+        <f>SUM(BY15+CN15)/45</f>
         <v/>
       </c>
       <c r="CU15" s="83">
@@ -5434,11 +5434,11 @@
         <v/>
       </c>
       <c r="CP16" s="38">
-        <f>SUM(O16+P16+Q16+BL16+BM16+CB16+CC16)/65+SUM(X16+Y16)/44+SUM(AJ16+AK16+AM16+AN16+AO16+AP16+AQ16+BR16+BS16+BT16+BU16+BV16+CH16+CI16+CJ16+CM16)/45+SUM(AX16+AY16+AZ16+BA16+BF16+BG16+BH16)/60+SUM(AL16+BZ16)/50</f>
+        <f>SUM(O16+P16+Q16+BL16+BM16+CB16+CC16)/65+SUM(X16+Y16)/44+SUM(AJ16+AK16+AM16+AN16+AO16+AP16+AQ16+BR16+BS16+BT16+BU16+BV16+CH16+CI16+CJ16+CK16)/45+SUM(AX16+AY16+AZ16+BA16+BF16+BG16+BH16)/60+SUM(AL16+BZ16)/50</f>
         <v/>
       </c>
       <c r="CQ16" s="38">
-        <f>SUM(R16+S16+BN16+CD16+CE16)/65+SUM(AB16)/36+SUM(AR16+AS16+BW16+BX16+CK16+CN16)/40+SUM(BB16+BC16+BI16+BJ16)/60</f>
+        <f>SUM(R16+S16+BN16+CD16+CE16)/65+SUM(AB16)/36+SUM(AR16+AS16+BW16+BX16+CL16+CM16)/40+SUM(BB16+BC16+BI16+BJ16)/60</f>
         <v/>
       </c>
       <c r="CR16" s="38">
@@ -5450,7 +5450,7 @@
         <v/>
       </c>
       <c r="CT16" s="38">
-        <f>SUM(BY16+CL16)/45</f>
+        <f>SUM(BY16+CN16)/45</f>
         <v/>
       </c>
       <c r="CU16" s="83">
@@ -5593,11 +5593,11 @@
         <v/>
       </c>
       <c r="CP17" s="38">
-        <f>SUM(O17+P17+Q17+BL17+BM17+CB17+CC17)/65+SUM(X17+Y17)/44+SUM(AJ17+AK17+AM17+AN17+AO17+AP17+AQ17+BR17+BS17+BT17+BU17+BV17+CH17+CI17+CJ17+CM17)/45+SUM(AX17+AY17+AZ17+BA17+BF17+BG17+BH17)/60+SUM(AL17+BZ17)/50</f>
+        <f>SUM(O17+P17+Q17+BL17+BM17+CB17+CC17)/65+SUM(X17+Y17)/44+SUM(AJ17+AK17+AM17+AN17+AO17+AP17+AQ17+BR17+BS17+BT17+BU17+BV17+CH17+CI17+CJ17+CK17)/45+SUM(AX17+AY17+AZ17+BA17+BF17+BG17+BH17)/60+SUM(AL17+BZ17)/50</f>
         <v/>
       </c>
       <c r="CQ17" s="38">
-        <f>SUM(R17+S17+BN17+CD17+CE17)/65+SUM(AB17)/36+SUM(AR17+AS17+BW17+BX17+CK17+CN17)/40+SUM(BB17+BC17+BI17+BJ17)/60</f>
+        <f>SUM(R17+S17+BN17+CD17+CE17)/65+SUM(AB17)/36+SUM(AR17+AS17+BW17+BX17+CL17+CM17)/40+SUM(BB17+BC17+BI17+BJ17)/60</f>
         <v/>
       </c>
       <c r="CR17" s="38">
@@ -5609,7 +5609,7 @@
         <v/>
       </c>
       <c r="CT17" s="38">
-        <f>SUM(BY17+CL17)/45</f>
+        <f>SUM(BY17+CN17)/45</f>
         <v/>
       </c>
       <c r="CU17" s="83">
@@ -5752,11 +5752,11 @@
         <v/>
       </c>
       <c r="CP18" s="38">
-        <f>SUM(O18+P18+Q18+BL18+BM18+CB18+CC18)/65+SUM(X18+Y18)/44+SUM(AJ18+AK18+AM18+AN18+AO18+AP18+AQ18+BR18+BS18+BT18+BU18+BV18+CH18+CI18+CJ18+CM18)/45+SUM(AX18+AY18+AZ18+BA18+BF18+BG18+BH18)/60+SUM(AL18+BZ18)/50</f>
+        <f>SUM(O18+P18+Q18+BL18+BM18+CB18+CC18)/65+SUM(X18+Y18)/44+SUM(AJ18+AK18+AM18+AN18+AO18+AP18+AQ18+BR18+BS18+BT18+BU18+BV18+CH18+CI18+CJ18+CK18)/45+SUM(AX18+AY18+AZ18+BA18+BF18+BG18+BH18)/60+SUM(AL18+BZ18)/50</f>
         <v/>
       </c>
       <c r="CQ18" s="38">
-        <f>SUM(R18+S18+BN18+CD18+CE18)/65+SUM(AB18)/36+SUM(AR18+AS18+BW18+BX18+CK18+CN18)/40+SUM(BB18+BC18+BI18+BJ18)/60</f>
+        <f>SUM(R18+S18+BN18+CD18+CE18)/65+SUM(AB18)/36+SUM(AR18+AS18+BW18+BX18+CL18+CM18)/40+SUM(BB18+BC18+BI18+BJ18)/60</f>
         <v/>
       </c>
       <c r="CR18" s="38">
@@ -5768,7 +5768,7 @@
         <v/>
       </c>
       <c r="CT18" s="38">
-        <f>SUM(BY18+CL18)/45</f>
+        <f>SUM(BY18+CN18)/45</f>
         <v/>
       </c>
       <c r="CU18" s="83">
@@ -5911,11 +5911,11 @@
         <v/>
       </c>
       <c r="CP19" s="38">
-        <f>SUM(O19+P19+Q19+BL19+BM19+CB19+CC19)/65+SUM(X19+Y19)/44+SUM(AJ19+AK19+AM19+AN19+AO19+AP19+AQ19+BR19+BS19+BT19+BU19+BV19+CH19+CI19+CJ19+CM19)/45+SUM(AX19+AY19+AZ19+BA19+BF19+BG19+BH19)/60+SUM(AL19+BZ19)/50</f>
+        <f>SUM(O19+P19+Q19+BL19+BM19+CB19+CC19)/65+SUM(X19+Y19)/44+SUM(AJ19+AK19+AM19+AN19+AO19+AP19+AQ19+BR19+BS19+BT19+BU19+BV19+CH19+CI19+CJ19+CK19)/45+SUM(AX19+AY19+AZ19+BA19+BF19+BG19+BH19)/60+SUM(AL19+BZ19)/50</f>
         <v/>
       </c>
       <c r="CQ19" s="38">
-        <f>SUM(R19+S19+BN19+CD19+CE19)/65+SUM(AB19)/36+SUM(AR19+AS19+BW19+BX19+CK19+CN19)/40+SUM(BB19+BC19+BI19+BJ19)/60</f>
+        <f>SUM(R19+S19+BN19+CD19+CE19)/65+SUM(AB19)/36+SUM(AR19+AS19+BW19+BX19+CL19+CM19)/40+SUM(BB19+BC19+BI19+BJ19)/60</f>
         <v/>
       </c>
       <c r="CR19" s="38">
@@ -5927,7 +5927,7 @@
         <v/>
       </c>
       <c r="CT19" s="38">
-        <f>SUM(BY19+CL19)/45</f>
+        <f>SUM(BY19+CN19)/45</f>
         <v/>
       </c>
       <c r="CU19" s="83">
@@ -6070,11 +6070,11 @@
         <v/>
       </c>
       <c r="CP20" s="38">
-        <f>SUM(O20+P20+Q20+BL20+BM20+CB20+CC20)/65+SUM(X20+Y20)/44+SUM(AJ20+AK20+AM20+AN20+AO20+AP20+AQ20+BR20+BS20+BT20+BU20+BV20+CH20+CI20+CJ20+CM20)/45+SUM(AX20+AY20+AZ20+BA20+BF20+BG20+BH20)/60+SUM(AL20+BZ20)/50</f>
+        <f>SUM(O20+P20+Q20+BL20+BM20+CB20+CC20)/65+SUM(X20+Y20)/44+SUM(AJ20+AK20+AM20+AN20+AO20+AP20+AQ20+BR20+BS20+BT20+BU20+BV20+CH20+CI20+CJ20+CK20)/45+SUM(AX20+AY20+AZ20+BA20+BF20+BG20+BH20)/60+SUM(AL20+BZ20)/50</f>
         <v/>
       </c>
       <c r="CQ20" s="38">
-        <f>SUM(R20+S20+BN20+CD20+CE20)/65+SUM(AB20)/36+SUM(AR20+AS20+BW20+BX20+CK20+CN20)/40+SUM(BB20+BC20+BI20+BJ20)/60</f>
+        <f>SUM(R20+S20+BN20+CD20+CE20)/65+SUM(AB20)/36+SUM(AR20+AS20+BW20+BX20+CL20+CM20)/40+SUM(BB20+BC20+BI20+BJ20)/60</f>
         <v/>
       </c>
       <c r="CR20" s="38">
@@ -6086,7 +6086,7 @@
         <v/>
       </c>
       <c r="CT20" s="38">
-        <f>SUM(BY20+CL20)/45</f>
+        <f>SUM(BY20+CN20)/45</f>
         <v/>
       </c>
       <c r="CU20" s="83">
@@ -6229,11 +6229,11 @@
         <v/>
       </c>
       <c r="CP21" s="38">
-        <f>SUM(O21+P21+Q21+BL21+BM21+CB21+CC21)/65+SUM(X21+Y21)/44+SUM(AJ21+AK21+AM21+AN21+AO21+AP21+AQ21+BR21+BS21+BT21+BU21+BV21+CH21+CI21+CJ21+CM21)/45+SUM(AX21+AY21+AZ21+BA21+BF21+BG21+BH21)/60+SUM(AL21+BZ21)/50</f>
+        <f>SUM(O21+P21+Q21+BL21+BM21+CB21+CC21)/65+SUM(X21+Y21)/44+SUM(AJ21+AK21+AM21+AN21+AO21+AP21+AQ21+BR21+BS21+BT21+BU21+BV21+CH21+CI21+CJ21+CK21)/45+SUM(AX21+AY21+AZ21+BA21+BF21+BG21+BH21)/60+SUM(AL21+BZ21)/50</f>
         <v/>
       </c>
       <c r="CQ21" s="38">
-        <f>SUM(R21+S21+BN21+CD21+CE21)/65+SUM(AB21)/36+SUM(AR21+AS21+BW21+BX21+CK21+CN21)/40+SUM(BB21+BC21+BI21+BJ21)/60</f>
+        <f>SUM(R21+S21+BN21+CD21+CE21)/65+SUM(AB21)/36+SUM(AR21+AS21+BW21+BX21+CL21+CM21)/40+SUM(BB21+BC21+BI21+BJ21)/60</f>
         <v/>
       </c>
       <c r="CR21" s="38">
@@ -6245,7 +6245,7 @@
         <v/>
       </c>
       <c r="CT21" s="38">
-        <f>SUM(BY21+CL21)/45</f>
+        <f>SUM(BY21+CN21)/45</f>
         <v/>
       </c>
       <c r="CU21" s="83">
@@ -6388,11 +6388,11 @@
         <v/>
       </c>
       <c r="CP22" s="38">
-        <f>SUM(O22+P22+Q22+BL22+BM22+CB22+CC22)/65+SUM(X22+Y22)/44+SUM(AJ22+AK22+AM22+AN22+AO22+AP22+AQ22+BR22+BS22+BT22+BU22+BV22+CH22+CI22+CJ22+CM22)/45+SUM(AX22+AY22+AZ22+BA22+BF22+BG22+BH22)/60+SUM(AL22+BZ22)/50</f>
+        <f>SUM(O22+P22+Q22+BL22+BM22+CB22+CC22)/65+SUM(X22+Y22)/44+SUM(AJ22+AK22+AM22+AN22+AO22+AP22+AQ22+BR22+BS22+BT22+BU22+BV22+CH22+CI22+CJ22+CK22)/45+SUM(AX22+AY22+AZ22+BA22+BF22+BG22+BH22)/60+SUM(AL22+BZ22)/50</f>
         <v/>
       </c>
       <c r="CQ22" s="38">
-        <f>SUM(R22+S22+BN22+CD22+CE22)/65+SUM(AB22)/36+SUM(AR22+AS22+BW22+BX22+CK22+CN22)/40+SUM(BB22+BC22+BI22+BJ22)/60</f>
+        <f>SUM(R22+S22+BN22+CD22+CE22)/65+SUM(AB22)/36+SUM(AR22+AS22+BW22+BX22+CL22+CM22)/40+SUM(BB22+BC22+BI22+BJ22)/60</f>
         <v/>
       </c>
       <c r="CR22" s="38">
@@ -6404,7 +6404,7 @@
         <v/>
       </c>
       <c r="CT22" s="38">
-        <f>SUM(BY22+CL22)/45</f>
+        <f>SUM(BY22+CN22)/45</f>
         <v/>
       </c>
       <c r="CU22" s="83">
@@ -6547,11 +6547,11 @@
         <v/>
       </c>
       <c r="CP23" s="38">
-        <f>SUM(O23+P23+Q23+BL23+BM23+CB23+CC23)/65+SUM(X23+Y23)/44+SUM(AJ23+AK23+AM23+AN23+AO23+AP23+AQ23+BR23+BS23+BT23+BU23+BV23+CH23+CI23+CJ23+CM23)/45+SUM(AX23+AY23+AZ23+BA23+BF23+BG23+BH23)/60+SUM(AL23+BZ23)/50</f>
+        <f>SUM(O23+P23+Q23+BL23+BM23+CB23+CC23)/65+SUM(X23+Y23)/44+SUM(AJ23+AK23+AM23+AN23+AO23+AP23+AQ23+BR23+BS23+BT23+BU23+BV23+CH23+CI23+CJ23+CK23)/45+SUM(AX23+AY23+AZ23+BA23+BF23+BG23+BH23)/60+SUM(AL23+BZ23)/50</f>
         <v/>
       </c>
       <c r="CQ23" s="38">
-        <f>SUM(R23+S23+BN23+CD23+CE23)/65+SUM(AB23)/36+SUM(AR23+AS23+BW23+BX23+CK23+CN23)/40+SUM(BB23+BC23+BI23+BJ23)/60</f>
+        <f>SUM(R23+S23+BN23+CD23+CE23)/65+SUM(AB23)/36+SUM(AR23+AS23+BW23+BX23+CL23+CM23)/40+SUM(BB23+BC23+BI23+BJ23)/60</f>
         <v/>
       </c>
       <c r="CR23" s="38">
@@ -6563,7 +6563,7 @@
         <v/>
       </c>
       <c r="CT23" s="38">
-        <f>SUM(BY23+CL23)/45</f>
+        <f>SUM(BY23+CN23)/45</f>
         <v/>
       </c>
       <c r="CU23" s="83">
@@ -6706,11 +6706,11 @@
         <v/>
       </c>
       <c r="CP24" s="38">
-        <f>SUM(O24+P24+Q24+BL24+BM24+CB24+CC24)/65+SUM(X24+Y24)/44+SUM(AJ24+AK24+AM24+AN24+AO24+AP24+AQ24+BR24+BS24+BT24+BU24+BV24+CH24+CI24+CJ24+CM24)/45+SUM(AX24+AY24+AZ24+BA24+BF24+BG24+BH24)/60+SUM(AL24+BZ24)/50</f>
+        <f>SUM(O24+P24+Q24+BL24+BM24+CB24+CC24)/65+SUM(X24+Y24)/44+SUM(AJ24+AK24+AM24+AN24+AO24+AP24+AQ24+BR24+BS24+BT24+BU24+BV24+CH24+CI24+CJ24+CK24)/45+SUM(AX24+AY24+AZ24+BA24+BF24+BG24+BH24)/60+SUM(AL24+BZ24)/50</f>
         <v/>
       </c>
       <c r="CQ24" s="38">
-        <f>SUM(R24+S24+BN24+CD24+CE24)/65+SUM(AB24)/36+SUM(AR24+AS24+BW24+BX24+CK24+CN24)/40+SUM(BB24+BC24+BI24+BJ24)/60</f>
+        <f>SUM(R24+S24+BN24+CD24+CE24)/65+SUM(AB24)/36+SUM(AR24+AS24+BW24+BX24+CL24+CM24)/40+SUM(BB24+BC24+BI24+BJ24)/60</f>
         <v/>
       </c>
       <c r="CR24" s="38">
@@ -6722,7 +6722,7 @@
         <v/>
       </c>
       <c r="CT24" s="38">
-        <f>SUM(BY24+CL24)/45</f>
+        <f>SUM(BY24+CN24)/45</f>
         <v/>
       </c>
       <c r="CU24" s="83">
@@ -6865,11 +6865,11 @@
         <v/>
       </c>
       <c r="CP25" s="38">
-        <f>SUM(O25+P25+Q25+BL25+BM25+CB25+CC25)/65+SUM(X25+Y25)/44+SUM(AJ25+AK25+AM25+AN25+AO25+AP25+AQ25+BR25+BS25+BT25+BU25+BV25+CH25+CI25+CJ25+CM25)/45+SUM(AX25+AY25+AZ25+BA25+BF25+BG25+BH25)/60+SUM(AL25+BZ25)/50</f>
+        <f>SUM(O25+P25+Q25+BL25+BM25+CB25+CC25)/65+SUM(X25+Y25)/44+SUM(AJ25+AK25+AM25+AN25+AO25+AP25+AQ25+BR25+BS25+BT25+BU25+BV25+CH25+CI25+CJ25+CK25)/45+SUM(AX25+AY25+AZ25+BA25+BF25+BG25+BH25)/60+SUM(AL25+BZ25)/50</f>
         <v/>
       </c>
       <c r="CQ25" s="38">
-        <f>SUM(R25+S25+BN25+CD25+CE25)/65+SUM(AB25)/36+SUM(AR25+AS25+BW25+BX25+CK25+CN25)/40+SUM(BB25+BC25+BI25+BJ25)/60</f>
+        <f>SUM(R25+S25+BN25+CD25+CE25)/65+SUM(AB25)/36+SUM(AR25+AS25+BW25+BX25+CL25+CM25)/40+SUM(BB25+BC25+BI25+BJ25)/60</f>
         <v/>
       </c>
       <c r="CR25" s="38">
@@ -6881,7 +6881,7 @@
         <v/>
       </c>
       <c r="CT25" s="38">
-        <f>SUM(BY25+CL25)/45</f>
+        <f>SUM(BY25+CN25)/45</f>
         <v/>
       </c>
       <c r="CU25" s="83">
@@ -7024,11 +7024,11 @@
         <v/>
       </c>
       <c r="CP26" s="38">
-        <f>SUM(O26+P26+Q26+BL26+BM26+CB26+CC26)/65+SUM(X26+Y26)/44+SUM(AJ26+AK26+AM26+AN26+AO26+AP26+AQ26+BR26+BS26+BT26+BU26+BV26+CH26+CI26+CJ26+CM26)/45+SUM(AX26+AY26+AZ26+BA26+BF26+BG26+BH26)/60+SUM(AL26+BZ26)/50</f>
+        <f>SUM(O26+P26+Q26+BL26+BM26+CB26+CC26)/65+SUM(X26+Y26)/44+SUM(AJ26+AK26+AM26+AN26+AO26+AP26+AQ26+BR26+BS26+BT26+BU26+BV26+CH26+CI26+CJ26+CK26)/45+SUM(AX26+AY26+AZ26+BA26+BF26+BG26+BH26)/60+SUM(AL26+BZ26)/50</f>
         <v/>
       </c>
       <c r="CQ26" s="38">
-        <f>SUM(R26+S26+BN26+CD26+CE26)/65+SUM(AB26)/36+SUM(AR26+AS26+BW26+BX26+CK26+CN26)/40+SUM(BB26+BC26+BI26+BJ26)/60</f>
+        <f>SUM(R26+S26+BN26+CD26+CE26)/65+SUM(AB26)/36+SUM(AR26+AS26+BW26+BX26+CL26+CM26)/40+SUM(BB26+BC26+BI26+BJ26)/60</f>
         <v/>
       </c>
       <c r="CR26" s="38">
@@ -7040,7 +7040,7 @@
         <v/>
       </c>
       <c r="CT26" s="38">
-        <f>SUM(BY26+CL26)/45</f>
+        <f>SUM(BY26+CN26)/45</f>
         <v/>
       </c>
       <c r="CU26" s="83">
@@ -7183,11 +7183,11 @@
         <v/>
       </c>
       <c r="CP27" s="38">
-        <f>SUM(O27+P27+Q27+BL27+BM27+CB27+CC27)/65+SUM(X27+Y27)/44+SUM(AJ27+AK27+AM27+AN27+AO27+AP27+AQ27+BR27+BS27+BT27+BU27+BV27+CH27+CI27+CJ27+CM27)/45+SUM(AX27+AY27+AZ27+BA27+BF27+BG27+BH27)/60+SUM(AL27+BZ27)/50</f>
+        <f>SUM(O27+P27+Q27+BL27+BM27+CB27+CC27)/65+SUM(X27+Y27)/44+SUM(AJ27+AK27+AM27+AN27+AO27+AP27+AQ27+BR27+BS27+BT27+BU27+BV27+CH27+CI27+CJ27+CK27)/45+SUM(AX27+AY27+AZ27+BA27+BF27+BG27+BH27)/60+SUM(AL27+BZ27)/50</f>
         <v/>
       </c>
       <c r="CQ27" s="38">
-        <f>SUM(R27+S27+BN27+CD27+CE27)/65+SUM(AB27)/36+SUM(AR27+AS27+BW27+BX27+CK27+CN27)/40+SUM(BB27+BC27+BI27+BJ27)/60</f>
+        <f>SUM(R27+S27+BN27+CD27+CE27)/65+SUM(AB27)/36+SUM(AR27+AS27+BW27+BX27+CL27+CM27)/40+SUM(BB27+BC27+BI27+BJ27)/60</f>
         <v/>
       </c>
       <c r="CR27" s="38">
@@ -7199,7 +7199,7 @@
         <v/>
       </c>
       <c r="CT27" s="38">
-        <f>SUM(BY27+CL27)/45</f>
+        <f>SUM(BY27+CN27)/45</f>
         <v/>
       </c>
       <c r="CU27" s="83">
@@ -7342,11 +7342,11 @@
         <v/>
       </c>
       <c r="CP28" s="38">
-        <f>SUM(O28+P28+Q28+BL28+BM28+CB28+CC28)/65+SUM(X28+Y28)/44+SUM(AJ28+AK28+AM28+AN28+AO28+AP28+AQ28+BR28+BS28+BT28+BU28+BV28+CH28+CI28+CJ28+CM28)/45+SUM(AX28+AY28+AZ28+BA28+BF28+BG28+BH28)/60+SUM(AL28+BZ28)/50</f>
+        <f>SUM(O28+P28+Q28+BL28+BM28+CB28+CC28)/65+SUM(X28+Y28)/44+SUM(AJ28+AK28+AM28+AN28+AO28+AP28+AQ28+BR28+BS28+BT28+BU28+BV28+CH28+CI28+CJ28+CK28)/45+SUM(AX28+AY28+AZ28+BA28+BF28+BG28+BH28)/60+SUM(AL28+BZ28)/50</f>
         <v/>
       </c>
       <c r="CQ28" s="38">
-        <f>SUM(R28+S28+BN28+CD28+CE28)/65+SUM(AB28)/36+SUM(AR28+AS28+BW28+BX28+CK28+CN28)/40+SUM(BB28+BC28+BI28+BJ28)/60</f>
+        <f>SUM(R28+S28+BN28+CD28+CE28)/65+SUM(AB28)/36+SUM(AR28+AS28+BW28+BX28+CL28+CM28)/40+SUM(BB28+BC28+BI28+BJ28)/60</f>
         <v/>
       </c>
       <c r="CR28" s="38">
@@ -7358,7 +7358,7 @@
         <v/>
       </c>
       <c r="CT28" s="38">
-        <f>SUM(BY28+CL28)/45</f>
+        <f>SUM(BY28+CN28)/45</f>
         <v/>
       </c>
       <c r="CU28" s="83">
@@ -7501,11 +7501,11 @@
         <v/>
       </c>
       <c r="CP29" s="38">
-        <f>SUM(O29+P29+Q29+BL29+BM29+CB29+CC29)/65+SUM(X29+Y29)/44+SUM(AJ29+AK29+AM29+AN29+AO29+AP29+AQ29+BR29+BS29+BT29+BU29+BV29+CH29+CI29+CJ29+CM29)/45+SUM(AX29+AY29+AZ29+BA29+BF29+BG29+BH29)/60+SUM(AL29+BZ29)/50</f>
+        <f>SUM(O29+P29+Q29+BL29+BM29+CB29+CC29)/65+SUM(X29+Y29)/44+SUM(AJ29+AK29+AM29+AN29+AO29+AP29+AQ29+BR29+BS29+BT29+BU29+BV29+CH29+CI29+CJ29+CK29)/45+SUM(AX29+AY29+AZ29+BA29+BF29+BG29+BH29)/60+SUM(AL29+BZ29)/50</f>
         <v/>
       </c>
       <c r="CQ29" s="38">
-        <f>SUM(R29+S29+BN29+CD29+CE29)/65+SUM(AB29)/36+SUM(AR29+AS29+BW29+BX29+CK29+CN29)/40+SUM(BB29+BC29+BI29+BJ29)/60</f>
+        <f>SUM(R29+S29+BN29+CD29+CE29)/65+SUM(AB29)/36+SUM(AR29+AS29+BW29+BX29+CL29+CM29)/40+SUM(BB29+BC29+BI29+BJ29)/60</f>
         <v/>
       </c>
       <c r="CR29" s="38">
@@ -7517,7 +7517,7 @@
         <v/>
       </c>
       <c r="CT29" s="38">
-        <f>SUM(BY29+CL29)/45</f>
+        <f>SUM(BY29+CN29)/45</f>
         <v/>
       </c>
       <c r="CU29" s="83">
@@ -7660,11 +7660,11 @@
         <v/>
       </c>
       <c r="CP30" s="38">
-        <f>SUM(O30+P30+Q30+BL30+BM30+CB30+CC30)/65+SUM(X30+Y30)/44+SUM(AJ30+AK30+AM30+AN30+AO30+AP30+AQ30+BR30+BS30+BT30+BU30+BV30+CH30+CI30+CJ30+CM30)/45+SUM(AX30+AY30+AZ30+BA30+BF30+BG30+BH30)/60+SUM(AL30+BZ30)/50</f>
+        <f>SUM(O30+P30+Q30+BL30+BM30+CB30+CC30)/65+SUM(X30+Y30)/44+SUM(AJ30+AK30+AM30+AN30+AO30+AP30+AQ30+BR30+BS30+BT30+BU30+BV30+CH30+CI30+CJ30+CK30)/45+SUM(AX30+AY30+AZ30+BA30+BF30+BG30+BH30)/60+SUM(AL30+BZ30)/50</f>
         <v/>
       </c>
       <c r="CQ30" s="38">
-        <f>SUM(R30+S30+BN30+CD30+CE30)/65+SUM(AB30)/36+SUM(AR30+AS30+BW30+BX30+CK30+CN30)/40+SUM(BB30+BC30+BI30+BJ30)/60</f>
+        <f>SUM(R30+S30+BN30+CD30+CE30)/65+SUM(AB30)/36+SUM(AR30+AS30+BW30+BX30+CL30+CM30)/40+SUM(BB30+BC30+BI30+BJ30)/60</f>
         <v/>
       </c>
       <c r="CR30" s="38">
@@ -7676,7 +7676,7 @@
         <v/>
       </c>
       <c r="CT30" s="38">
-        <f>SUM(BY30+CL30)/45</f>
+        <f>SUM(BY30+CN30)/45</f>
         <v/>
       </c>
       <c r="CU30" s="83">
@@ -7819,11 +7819,11 @@
         <v/>
       </c>
       <c r="CP31" s="38">
-        <f>SUM(O31+P31+Q31+BL31+BM31+CB31+CC31)/65+SUM(X31+Y31)/44+SUM(AJ31+AK31+AM31+AN31+AO31+AP31+AQ31+BR31+BS31+BT31+BU31+BV31+CH31+CI31+CJ31+CM31)/45+SUM(AX31+AY31+AZ31+BA31+BF31+BG31+BH31)/60+SUM(AL31+BZ31)/50</f>
+        <f>SUM(O31+P31+Q31+BL31+BM31+CB31+CC31)/65+SUM(X31+Y31)/44+SUM(AJ31+AK31+AM31+AN31+AO31+AP31+AQ31+BR31+BS31+BT31+BU31+BV31+CH31+CI31+CJ31+CK31)/45+SUM(AX31+AY31+AZ31+BA31+BF31+BG31+BH31)/60+SUM(AL31+BZ31)/50</f>
         <v/>
       </c>
       <c r="CQ31" s="38">
-        <f>SUM(R31+S31+BN31+CD31+CE31)/65+SUM(AB31)/36+SUM(AR31+AS31+BW31+BX31+CK31+CN31)/40+SUM(BB31+BC31+BI31+BJ31)/60</f>
+        <f>SUM(R31+S31+BN31+CD31+CE31)/65+SUM(AB31)/36+SUM(AR31+AS31+BW31+BX31+CL31+CM31)/40+SUM(BB31+BC31+BI31+BJ31)/60</f>
         <v/>
       </c>
       <c r="CR31" s="38">
@@ -7835,7 +7835,7 @@
         <v/>
       </c>
       <c r="CT31" s="38">
-        <f>SUM(BY31+CL31)/45</f>
+        <f>SUM(BY31+CN31)/45</f>
         <v/>
       </c>
       <c r="CU31" s="83">
@@ -7978,11 +7978,11 @@
         <v/>
       </c>
       <c r="CP32" s="38">
-        <f>SUM(O32+P32+Q32+BL32+BM32+CB32+CC32)/65+SUM(X32+Y32)/44+SUM(AJ32+AK32+AM32+AN32+AO32+AP32+AQ32+BR32+BS32+BT32+BU32+BV32+CH32+CI32+CJ32+CM32)/45+SUM(AX32+AY32+AZ32+BA32+BF32+BG32+BH32)/60+SUM(AL32+BZ32)/50</f>
+        <f>SUM(O32+P32+Q32+BL32+BM32+CB32+CC32)/65+SUM(X32+Y32)/44+SUM(AJ32+AK32+AM32+AN32+AO32+AP32+AQ32+BR32+BS32+BT32+BU32+BV32+CH32+CI32+CJ32+CK32)/45+SUM(AX32+AY32+AZ32+BA32+BF32+BG32+BH32)/60+SUM(AL32+BZ32)/50</f>
         <v/>
       </c>
       <c r="CQ32" s="38">
-        <f>SUM(R32+S32+BN32+CD32+CE32)/65+SUM(AB32)/36+SUM(AR32+AS32+BW32+BX32+CK32+CN32)/40+SUM(BB32+BC32+BI32+BJ32)/60</f>
+        <f>SUM(R32+S32+BN32+CD32+CE32)/65+SUM(AB32)/36+SUM(AR32+AS32+BW32+BX32+CL32+CM32)/40+SUM(BB32+BC32+BI32+BJ32)/60</f>
         <v/>
       </c>
       <c r="CR32" s="38">
@@ -7994,7 +7994,7 @@
         <v/>
       </c>
       <c r="CT32" s="38">
-        <f>SUM(BY32+CL32)/45</f>
+        <f>SUM(BY32+CN32)/45</f>
         <v/>
       </c>
       <c r="CU32" s="83">
@@ -8137,11 +8137,11 @@
         <v/>
       </c>
       <c r="CP33" s="38">
-        <f>SUM(O33+P33+Q33+BL33+BM33+CB33+CC33)/65+SUM(X33+Y33)/44+SUM(AJ33+AK33+AM33+AN33+AO33+AP33+AQ33+BR33+BS33+BT33+BU33+BV33+CH33+CI33+CJ33+CM33)/45+SUM(AX33+AY33+AZ33+BA33+BF33+BG33+BH33)/60+SUM(AL33+BZ33)/50</f>
+        <f>SUM(O33+P33+Q33+BL33+BM33+CB33+CC33)/65+SUM(X33+Y33)/44+SUM(AJ33+AK33+AM33+AN33+AO33+AP33+AQ33+BR33+BS33+BT33+BU33+BV33+CH33+CI33+CJ33+CK33)/45+SUM(AX33+AY33+AZ33+BA33+BF33+BG33+BH33)/60+SUM(AL33+BZ33)/50</f>
         <v/>
       </c>
       <c r="CQ33" s="38">
-        <f>SUM(R33+S33+BN33+CD33+CE33)/65+SUM(AB33)/36+SUM(AR33+AS33+BW33+BX33+CK33+CN33)/40+SUM(BB33+BC33+BI33+BJ33)/60</f>
+        <f>SUM(R33+S33+BN33+CD33+CE33)/65+SUM(AB33)/36+SUM(AR33+AS33+BW33+BX33+CL33+CM33)/40+SUM(BB33+BC33+BI33+BJ33)/60</f>
         <v/>
       </c>
       <c r="CR33" s="38">
@@ -8153,7 +8153,7 @@
         <v/>
       </c>
       <c r="CT33" s="38">
-        <f>SUM(BY33+CL33)/45</f>
+        <f>SUM(BY33+CN33)/45</f>
         <v/>
       </c>
       <c r="CU33" s="83">
@@ -8296,11 +8296,11 @@
         <v/>
       </c>
       <c r="CP34" s="38">
-        <f>SUM(O34+P34+Q34+BL34+BM34+CB34+CC34)/65+SUM(X34+Y34)/44+SUM(AJ34+AK34+AM34+AN34+AO34+AP34+AQ34+BR34+BS34+BT34+BU34+BV34+CH34+CI34+CJ34+CM34)/45+SUM(AX34+AY34+AZ34+BA34+BF34+BG34+BH34)/60+SUM(AL34+BZ34)/50</f>
+        <f>SUM(O34+P34+Q34+BL34+BM34+CB34+CC34)/65+SUM(X34+Y34)/44+SUM(AJ34+AK34+AM34+AN34+AO34+AP34+AQ34+BR34+BS34+BT34+BU34+BV34+CH34+CI34+CJ34+CK34)/45+SUM(AX34+AY34+AZ34+BA34+BF34+BG34+BH34)/60+SUM(AL34+BZ34)/50</f>
         <v/>
       </c>
       <c r="CQ34" s="38">
-        <f>SUM(R34+S34+BN34+CD34+CE34)/65+SUM(AB34)/36+SUM(AR34+AS34+BW34+BX34+CK34+CN34)/40+SUM(BB34+BC34+BI34+BJ34)/60</f>
+        <f>SUM(R34+S34+BN34+CD34+CE34)/65+SUM(AB34)/36+SUM(AR34+AS34+BW34+BX34+CL34+CM34)/40+SUM(BB34+BC34+BI34+BJ34)/60</f>
         <v/>
       </c>
       <c r="CR34" s="38">
@@ -8312,7 +8312,7 @@
         <v/>
       </c>
       <c r="CT34" s="38">
-        <f>SUM(BY34+CL34)/45</f>
+        <f>SUM(BY34+CN34)/45</f>
         <v/>
       </c>
       <c r="CU34" s="83">
@@ -8455,11 +8455,11 @@
         <v/>
       </c>
       <c r="CP35" s="38">
-        <f>SUM(O35+P35+Q35+BL35+BM35+CB35+CC35)/65+SUM(X35+Y35)/44+SUM(AJ35+AK35+AM35+AN35+AO35+AP35+AQ35+BR35+BS35+BT35+BU35+BV35+CH35+CI35+CJ35+CM35)/45+SUM(AX35+AY35+AZ35+BA35+BF35+BG35+BH35)/60+SUM(AL35+BZ35)/50</f>
+        <f>SUM(O35+P35+Q35+BL35+BM35+CB35+CC35)/65+SUM(X35+Y35)/44+SUM(AJ35+AK35+AM35+AN35+AO35+AP35+AQ35+BR35+BS35+BT35+BU35+BV35+CH35+CI35+CJ35+CK35)/45+SUM(AX35+AY35+AZ35+BA35+BF35+BG35+BH35)/60+SUM(AL35+BZ35)/50</f>
         <v/>
       </c>
       <c r="CQ35" s="38">
-        <f>SUM(R35+S35+BN35+CD35+CE35)/65+SUM(AB35)/36+SUM(AR35+AS35+BW35+BX35+CK35+CN35)/40+SUM(BB35+BC35+BI35+BJ35)/60</f>
+        <f>SUM(R35+S35+BN35+CD35+CE35)/65+SUM(AB35)/36+SUM(AR35+AS35+BW35+BX35+CL35+CM35)/40+SUM(BB35+BC35+BI35+BJ35)/60</f>
         <v/>
       </c>
       <c r="CR35" s="38">
@@ -8471,7 +8471,7 @@
         <v/>
       </c>
       <c r="CT35" s="38">
-        <f>SUM(BY35+CL35)/45</f>
+        <f>SUM(BY35+CN35)/45</f>
         <v/>
       </c>
       <c r="CU35" s="83">
@@ -8614,11 +8614,11 @@
         <v/>
       </c>
       <c r="CP36" s="38">
-        <f>SUM(O36+P36+Q36+BL36+BM36+CB36+CC36)/65+SUM(X36+Y36)/44+SUM(AJ36+AK36+AM36+AN36+AO36+AP36+AQ36+BR36+BS36+BT36+BU36+BV36+CH36+CI36+CJ36+CM36)/45+SUM(AX36+AY36+AZ36+BA36+BF36+BG36+BH36)/60+SUM(AL36+BZ36)/50</f>
+        <f>SUM(O36+P36+Q36+BL36+BM36+CB36+CC36)/65+SUM(X36+Y36)/44+SUM(AJ36+AK36+AM36+AN36+AO36+AP36+AQ36+BR36+BS36+BT36+BU36+BV36+CH36+CI36+CJ36+CK36)/45+SUM(AX36+AY36+AZ36+BA36+BF36+BG36+BH36)/60+SUM(AL36+BZ36)/50</f>
         <v/>
       </c>
       <c r="CQ36" s="38">
-        <f>SUM(R36+S36+BN36+CD36+CE36)/65+SUM(AB36)/36+SUM(AR36+AS36+BW36+BX36+CK36+CN36)/40+SUM(BB36+BC36+BI36+BJ36)/60</f>
+        <f>SUM(R36+S36+BN36+CD36+CE36)/65+SUM(AB36)/36+SUM(AR36+AS36+BW36+BX36+CL36+CM36)/40+SUM(BB36+BC36+BI36+BJ36)/60</f>
         <v/>
       </c>
       <c r="CR36" s="38">
@@ -8630,7 +8630,7 @@
         <v/>
       </c>
       <c r="CT36" s="38">
-        <f>SUM(BY36+CL36)/45</f>
+        <f>SUM(BY36+CN36)/45</f>
         <v/>
       </c>
       <c r="CU36" s="83">
@@ -8773,11 +8773,11 @@
         <v/>
       </c>
       <c r="CP37" s="38">
-        <f>SUM(O37+P37+Q37+BL37+BM37+CB37+CC37)/65+SUM(X37+Y37)/44+SUM(AJ37+AK37+AM37+AN37+AO37+AP37+AQ37+BR37+BS37+BT37+BU37+BV37+CH37+CI37+CJ37+CM37)/45+SUM(AX37+AY37+AZ37+BA37+BF37+BG37+BH37)/60+SUM(AL37+BZ37)/50</f>
+        <f>SUM(O37+P37+Q37+BL37+BM37+CB37+CC37)/65+SUM(X37+Y37)/44+SUM(AJ37+AK37+AM37+AN37+AO37+AP37+AQ37+BR37+BS37+BT37+BU37+BV37+CH37+CI37+CJ37+CK37)/45+SUM(AX37+AY37+AZ37+BA37+BF37+BG37+BH37)/60+SUM(AL37+BZ37)/50</f>
         <v/>
       </c>
       <c r="CQ37" s="38">
-        <f>SUM(R37+S37+BN37+CD37+CE37)/65+SUM(AB37)/36+SUM(AR37+AS37+BW37+BX37+CK37+CN37)/40+SUM(BB37+BC37+BI37+BJ37)/60</f>
+        <f>SUM(R37+S37+BN37+CD37+CE37)/65+SUM(AB37)/36+SUM(AR37+AS37+BW37+BX37+CL37+CM37)/40+SUM(BB37+BC37+BI37+BJ37)/60</f>
         <v/>
       </c>
       <c r="CR37" s="38">
@@ -8789,7 +8789,7 @@
         <v/>
       </c>
       <c r="CT37" s="38">
-        <f>SUM(BY37+CL37)/45</f>
+        <f>SUM(BY37+CN37)/45</f>
         <v/>
       </c>
       <c r="CU37" s="83">
@@ -8932,11 +8932,11 @@
         <v/>
       </c>
       <c r="CP38" s="38">
-        <f>SUM(O38+P38+Q38+BL38+BM38+CB38+CC38)/65+SUM(X38+Y38)/44+SUM(AJ38+AK38+AM38+AN38+AO38+AP38+AQ38+BR38+BS38+BT38+BU38+BV38+CH38+CI38+CJ38+CM38)/45+SUM(AX38+AY38+AZ38+BA38+BF38+BG38+BH38)/60+SUM(AL38+BZ38)/50</f>
+        <f>SUM(O38+P38+Q38+BL38+BM38+CB38+CC38)/65+SUM(X38+Y38)/44+SUM(AJ38+AK38+AM38+AN38+AO38+AP38+AQ38+BR38+BS38+BT38+BU38+BV38+CH38+CI38+CJ38+CK38)/45+SUM(AX38+AY38+AZ38+BA38+BF38+BG38+BH38)/60+SUM(AL38+BZ38)/50</f>
         <v/>
       </c>
       <c r="CQ38" s="38">
-        <f>SUM(R38+S38+BN38+CD38+CE38)/65+SUM(AB38)/36+SUM(AR38+AS38+BW38+BX38+CK38+CN38)/40+SUM(BB38+BC38+BI38+BJ38)/60</f>
+        <f>SUM(R38+S38+BN38+CD38+CE38)/65+SUM(AB38)/36+SUM(AR38+AS38+BW38+BX38+CL38+CM38)/40+SUM(BB38+BC38+BI38+BJ38)/60</f>
         <v/>
       </c>
       <c r="CR38" s="38">
@@ -8948,7 +8948,7 @@
         <v/>
       </c>
       <c r="CT38" s="38">
-        <f>SUM(BY38+CL38)/45</f>
+        <f>SUM(BY38+CN38)/45</f>
         <v/>
       </c>
       <c r="CU38" s="83">
@@ -9091,11 +9091,11 @@
         <v/>
       </c>
       <c r="CP39" s="38">
-        <f>SUM(O39+P39+Q39+BL39+BM39+CB39+CC39)/65+SUM(X39+Y39)/44+SUM(AJ39+AK39+AM39+AN39+AO39+AP39+AQ39+BR39+BS39+BT39+BU39+BV39+CH39+CI39+CJ39+CM39)/45+SUM(AX39+AY39+AZ39+BA39+BF39+BG39+BH39)/60+SUM(AL39+BZ39)/50</f>
+        <f>SUM(O39+P39+Q39+BL39+BM39+CB39+CC39)/65+SUM(X39+Y39)/44+SUM(AJ39+AK39+AM39+AN39+AO39+AP39+AQ39+BR39+BS39+BT39+BU39+BV39+CH39+CI39+CJ39+CK39)/45+SUM(AX39+AY39+AZ39+BA39+BF39+BG39+BH39)/60+SUM(AL39+BZ39)/50</f>
         <v/>
       </c>
       <c r="CQ39" s="38">
-        <f>SUM(R39+S39+BN39+CD39+CE39)/65+SUM(AB39)/36+SUM(AR39+AS39+BW39+BX39+CK39+CN39)/40+SUM(BB39+BC39+BI39+BJ39)/60</f>
+        <f>SUM(R39+S39+BN39+CD39+CE39)/65+SUM(AB39)/36+SUM(AR39+AS39+BW39+BX39+CL39+CM39)/40+SUM(BB39+BC39+BI39+BJ39)/60</f>
         <v/>
       </c>
       <c r="CR39" s="38">
@@ -9107,7 +9107,7 @@
         <v/>
       </c>
       <c r="CT39" s="38">
-        <f>SUM(BY39+CL39)/45</f>
+        <f>SUM(BY39+CN39)/45</f>
         <v/>
       </c>
       <c r="CU39" s="83">
@@ -9250,11 +9250,11 @@
         <v/>
       </c>
       <c r="CP40" s="38">
-        <f>SUM(O40+P40+Q40+BL40+BM40+CB40+CC40)/65+SUM(X40+Y40)/44+SUM(AJ40+AK40+AM40+AN40+AO40+AP40+AQ40+BR40+BS40+BT40+BU40+BV40+CH40+CI40+CJ40+CM40)/45+SUM(AX40+AY40+AZ40+BA40+BF40+BG40+BH40)/60+SUM(AL40+BZ40)/50</f>
+        <f>SUM(O40+P40+Q40+BL40+BM40+CB40+CC40)/65+SUM(X40+Y40)/44+SUM(AJ40+AK40+AM40+AN40+AO40+AP40+AQ40+BR40+BS40+BT40+BU40+BV40+CH40+CI40+CJ40+CK40)/45+SUM(AX40+AY40+AZ40+BA40+BF40+BG40+BH40)/60+SUM(AL40+BZ40)/50</f>
         <v/>
       </c>
       <c r="CQ40" s="38">
-        <f>SUM(R40+S40+BN40+CD40+CE40)/65+SUM(AB40)/36+SUM(AR40+AS40+BW40+BX40+CK40+CN40)/40+SUM(BB40+BC40+BI40+BJ40)/60</f>
+        <f>SUM(R40+S40+BN40+CD40+CE40)/65+SUM(AB40)/36+SUM(AR40+AS40+BW40+BX40+CL40+CM40)/40+SUM(BB40+BC40+BI40+BJ40)/60</f>
         <v/>
       </c>
       <c r="CR40" s="38">
@@ -9266,7 +9266,7 @@
         <v/>
       </c>
       <c r="CT40" s="38">
-        <f>SUM(BY40+CL40)/45</f>
+        <f>SUM(BY40+CN40)/45</f>
         <v/>
       </c>
       <c r="CU40" s="83">
@@ -9409,11 +9409,11 @@
         <v/>
       </c>
       <c r="CP41" s="38">
-        <f>SUM(O41+P41+Q41+BL41+BM41+CB41+CC41)/65+SUM(X41+Y41)/44+SUM(AJ41+AK41+AM41+AN41+AO41+AP41+AQ41+BR41+BS41+BT41+BU41+BV41+CH41+CI41+CJ41+CM41)/45+SUM(AX41+AY41+AZ41+BA41+BF41+BG41+BH41)/60+SUM(AL41+BZ41)/50</f>
+        <f>SUM(O41+P41+Q41+BL41+BM41+CB41+CC41)/65+SUM(X41+Y41)/44+SUM(AJ41+AK41+AM41+AN41+AO41+AP41+AQ41+BR41+BS41+BT41+BU41+BV41+CH41+CI41+CJ41+CK41)/45+SUM(AX41+AY41+AZ41+BA41+BF41+BG41+BH41)/60+SUM(AL41+BZ41)/50</f>
         <v/>
       </c>
       <c r="CQ41" s="38">
-        <f>SUM(R41+S41+BN41+CD41+CE41)/65+SUM(AB41)/36+SUM(AR41+AS41+BW41+BX41+CK41+CN41)/40+SUM(BB41+BC41+BI41+BJ41)/60</f>
+        <f>SUM(R41+S41+BN41+CD41+CE41)/65+SUM(AB41)/36+SUM(AR41+AS41+BW41+BX41+CL41+CM41)/40+SUM(BB41+BC41+BI41+BJ41)/60</f>
         <v/>
       </c>
       <c r="CR41" s="38">
@@ -9425,7 +9425,7 @@
         <v/>
       </c>
       <c r="CT41" s="38">
-        <f>SUM(BY41+CL41)/45</f>
+        <f>SUM(BY41+CN41)/45</f>
         <v/>
       </c>
       <c r="CU41" s="83">
@@ -9568,11 +9568,11 @@
         <v/>
       </c>
       <c r="CP42" s="38">
-        <f>SUM(O42+P42+Q42+BL42+BM42+CB42+CC42)/65+SUM(X42+Y42)/44+SUM(AJ42+AK42+AM42+AN42+AO42+AP42+AQ42+BR42+BS42+BT42+BU42+BV42+CH42+CI42+CJ42+CM42)/45+SUM(AX42+AY42+AZ42+BA42+BF42+BG42+BH42)/60+SUM(AL42+BZ42)/50</f>
+        <f>SUM(O42+P42+Q42+BL42+BM42+CB42+CC42)/65+SUM(X42+Y42)/44+SUM(AJ42+AK42+AM42+AN42+AO42+AP42+AQ42+BR42+BS42+BT42+BU42+BV42+CH42+CI42+CJ42+CK42)/45+SUM(AX42+AY42+AZ42+BA42+BF42+BG42+BH42)/60+SUM(AL42+BZ42)/50</f>
         <v/>
       </c>
       <c r="CQ42" s="38">
-        <f>SUM(R42+S42+BN42+CD42+CE42)/65+SUM(AB42)/36+SUM(AR42+AS42+BW42+BX42+CK42+CN42)/40+SUM(BB42+BC42+BI42+BJ42)/60</f>
+        <f>SUM(R42+S42+BN42+CD42+CE42)/65+SUM(AB42)/36+SUM(AR42+AS42+BW42+BX42+CL42+CM42)/40+SUM(BB42+BC42+BI42+BJ42)/60</f>
         <v/>
       </c>
       <c r="CR42" s="38">
@@ -9584,7 +9584,7 @@
         <v/>
       </c>
       <c r="CT42" s="38">
-        <f>SUM(BY42+CL42)/45</f>
+        <f>SUM(BY42+CN42)/45</f>
         <v/>
       </c>
       <c r="CU42" s="83">
@@ -9727,11 +9727,11 @@
         <v/>
       </c>
       <c r="CP43" s="38">
-        <f>SUM(O43+P43+Q43+BL43+BM43+CB43+CC43)/65+SUM(X43+Y43)/44+SUM(AJ43+AK43+AM43+AN43+AO43+AP43+AQ43+BR43+BS43+BT43+BU43+BV43+CH43+CI43+CJ43+CM43)/45+SUM(AX43+AY43+AZ43+BA43+BF43+BG43+BH43)/60+SUM(AL43+BZ43)/50</f>
+        <f>SUM(O43+P43+Q43+BL43+BM43+CB43+CC43)/65+SUM(X43+Y43)/44+SUM(AJ43+AK43+AM43+AN43+AO43+AP43+AQ43+BR43+BS43+BT43+BU43+BV43+CH43+CI43+CJ43+CK43)/45+SUM(AX43+AY43+AZ43+BA43+BF43+BG43+BH43)/60+SUM(AL43+BZ43)/50</f>
         <v/>
       </c>
       <c r="CQ43" s="38">
-        <f>SUM(R43+S43+BN43+CD43+CE43)/65+SUM(AB43)/36+SUM(AR43+AS43+BW43+BX43+CK43+CN43)/40+SUM(BB43+BC43+BI43+BJ43)/60</f>
+        <f>SUM(R43+S43+BN43+CD43+CE43)/65+SUM(AB43)/36+SUM(AR43+AS43+BW43+BX43+CL43+CM43)/40+SUM(BB43+BC43+BI43+BJ43)/60</f>
         <v/>
       </c>
       <c r="CR43" s="38">
@@ -9743,7 +9743,7 @@
         <v/>
       </c>
       <c r="CT43" s="38">
-        <f>SUM(BY43+CL43)/45</f>
+        <f>SUM(BY43+CN43)/45</f>
         <v/>
       </c>
       <c r="CU43" s="83">
@@ -9886,11 +9886,11 @@
         <v/>
       </c>
       <c r="CP44" s="38">
-        <f>SUM(O44+P44+Q44+BL44+BM44+CB44+CC44)/65+SUM(X44+Y44)/44+SUM(AJ44+AK44+AM44+AN44+AO44+AP44+AQ44+BR44+BS44+BT44+BU44+BV44+CH44+CI44+CJ44+CM44)/45+SUM(AX44+AY44+AZ44+BA44+BF44+BG44+BH44)/60+SUM(AL44+BZ44)/50</f>
+        <f>SUM(O44+P44+Q44+BL44+BM44+CB44+CC44)/65+SUM(X44+Y44)/44+SUM(AJ44+AK44+AM44+AN44+AO44+AP44+AQ44+BR44+BS44+BT44+BU44+BV44+CH44+CI44+CJ44+CK44)/45+SUM(AX44+AY44+AZ44+BA44+BF44+BG44+BH44)/60+SUM(AL44+BZ44)/50</f>
         <v/>
       </c>
       <c r="CQ44" s="38">
-        <f>SUM(R44+S44+BN44+CD44+CE44)/65+SUM(AB44)/36+SUM(AR44+AS44+BW44+BX44+CK44+CN44)/40+SUM(BB44+BC44+BI44+BJ44)/60</f>
+        <f>SUM(R44+S44+BN44+CD44+CE44)/65+SUM(AB44)/36+SUM(AR44+AS44+BW44+BX44+CL44+CM44)/40+SUM(BB44+BC44+BI44+BJ44)/60</f>
         <v/>
       </c>
       <c r="CR44" s="38">
@@ -9902,7 +9902,7 @@
         <v/>
       </c>
       <c r="CT44" s="38">
-        <f>SUM(BY44+CL44)/45</f>
+        <f>SUM(BY44+CN44)/45</f>
         <v/>
       </c>
       <c r="CU44" s="83">
@@ -10045,11 +10045,11 @@
         <v/>
       </c>
       <c r="CP45" s="38">
-        <f>SUM(O45+P45+Q45+BL45+BM45+CB45+CC45)/65+SUM(X45+Y45)/44+SUM(AJ45+AK45+AM45+AN45+AO45+AP45+AQ45+BR45+BS45+BT45+BU45+BV45+CH45+CI45+CJ45+CM45)/45+SUM(AX45+AY45+AZ45+BA45+BF45+BG45+BH45)/60+SUM(AL45+BZ45)/50</f>
+        <f>SUM(O45+P45+Q45+BL45+BM45+CB45+CC45)/65+SUM(X45+Y45)/44+SUM(AJ45+AK45+AM45+AN45+AO45+AP45+AQ45+BR45+BS45+BT45+BU45+BV45+CH45+CI45+CJ45+CK45)/45+SUM(AX45+AY45+AZ45+BA45+BF45+BG45+BH45)/60+SUM(AL45+BZ45)/50</f>
         <v/>
       </c>
       <c r="CQ45" s="38">
-        <f>SUM(R45+S45+BN45+CD45+CE45)/65+SUM(AB45)/36+SUM(AR45+AS45+BW45+BX45+CK45+CN45)/40+SUM(BB45+BC45+BI45+BJ45)/60</f>
+        <f>SUM(R45+S45+BN45+CD45+CE45)/65+SUM(AB45)/36+SUM(AR45+AS45+BW45+BX45+CL45+CM45)/40+SUM(BB45+BC45+BI45+BJ45)/60</f>
         <v/>
       </c>
       <c r="CR45" s="38">
@@ -10061,7 +10061,7 @@
         <v/>
       </c>
       <c r="CT45" s="38">
-        <f>SUM(BY45+CL45)/45</f>
+        <f>SUM(BY45+CN45)/45</f>
         <v/>
       </c>
       <c r="CU45" s="83">
@@ -10204,11 +10204,11 @@
         <v/>
       </c>
       <c r="CP46" s="38">
-        <f>SUM(O46+P46+Q46+BL46+BM46+CB46+CC46)/65+SUM(X46+Y46)/44+SUM(AJ46+AK46+AM46+AN46+AO46+AP46+AQ46+BR46+BS46+BT46+BU46+BV46+CH46+CI46+CJ46+CM46)/45+SUM(AX46+AY46+AZ46+BA46+BF46+BG46+BH46)/60+SUM(AL46+BZ46)/50</f>
+        <f>SUM(O46+P46+Q46+BL46+BM46+CB46+CC46)/65+SUM(X46+Y46)/44+SUM(AJ46+AK46+AM46+AN46+AO46+AP46+AQ46+BR46+BS46+BT46+BU46+BV46+CH46+CI46+CJ46+CK46)/45+SUM(AX46+AY46+AZ46+BA46+BF46+BG46+BH46)/60+SUM(AL46+BZ46)/50</f>
         <v/>
       </c>
       <c r="CQ46" s="38">
-        <f>SUM(R46+S46+BN46+CD46+CE46)/65+SUM(AB46)/36+SUM(AR46+AS46+BW46+BX46+CK46+CN46)/40+SUM(BB46+BC46+BI46+BJ46)/60</f>
+        <f>SUM(R46+S46+BN46+CD46+CE46)/65+SUM(AB46)/36+SUM(AR46+AS46+BW46+BX46+CL46+CM46)/40+SUM(BB46+BC46+BI46+BJ46)/60</f>
         <v/>
       </c>
       <c r="CR46" s="38">
@@ -10220,7 +10220,7 @@
         <v/>
       </c>
       <c r="CT46" s="38">
-        <f>SUM(BY46+CL46)/45</f>
+        <f>SUM(BY46+CN46)/45</f>
         <v/>
       </c>
       <c r="CU46" s="83">
@@ -10363,11 +10363,11 @@
         <v/>
       </c>
       <c r="CP47" s="38">
-        <f>SUM(O47+P47+Q47+BL47+BM47+CB47+CC47)/65+SUM(X47+Y47)/44+SUM(AJ47+AK47+AM47+AN47+AO47+AP47+AQ47+BR47+BS47+BT47+BU47+BV47+CH47+CI47+CJ47+CM47)/45+SUM(AX47+AY47+AZ47+BA47+BF47+BG47+BH47)/60+SUM(AL47+BZ47)/50</f>
+        <f>SUM(O47+P47+Q47+BL47+BM47+CB47+CC47)/65+SUM(X47+Y47)/44+SUM(AJ47+AK47+AM47+AN47+AO47+AP47+AQ47+BR47+BS47+BT47+BU47+BV47+CH47+CI47+CJ47+CK47)/45+SUM(AX47+AY47+AZ47+BA47+BF47+BG47+BH47)/60+SUM(AL47+BZ47)/50</f>
         <v/>
       </c>
       <c r="CQ47" s="38">
-        <f>SUM(R47+S47+BN47+CD47+CE47)/65+SUM(AB47)/36+SUM(AR47+AS47+BW47+BX47+CK47+CN47)/40+SUM(BB47+BC47+BI47+BJ47)/60</f>
+        <f>SUM(R47+S47+BN47+CD47+CE47)/65+SUM(AB47)/36+SUM(AR47+AS47+BW47+BX47+CL47+CM47)/40+SUM(BB47+BC47+BI47+BJ47)/60</f>
         <v/>
       </c>
       <c r="CR47" s="38">
@@ -10379,7 +10379,7 @@
         <v/>
       </c>
       <c r="CT47" s="38">
-        <f>SUM(BY47+CL47)/45</f>
+        <f>SUM(BY47+CN47)/45</f>
         <v/>
       </c>
       <c r="CU47" s="83">
@@ -10522,11 +10522,11 @@
         <v/>
       </c>
       <c r="CP48" s="38">
-        <f>SUM(O48+P48+Q48+BL48+BM48+CB48+CC48)/65+SUM(X48+Y48)/44+SUM(AJ48+AK48+AM48+AN48+AO48+AP48+AQ48+BR48+BS48+BT48+BU48+BV48+CH48+CI48+CJ48+CM48)/45+SUM(AX48+AY48+AZ48+BA48+BF48+BG48+BH48)/60+SUM(AL48+BZ48)/50</f>
+        <f>SUM(O48+P48+Q48+BL48+BM48+CB48+CC48)/65+SUM(X48+Y48)/44+SUM(AJ48+AK48+AM48+AN48+AO48+AP48+AQ48+BR48+BS48+BT48+BU48+BV48+CH48+CI48+CJ48+CK48)/45+SUM(AX48+AY48+AZ48+BA48+BF48+BG48+BH48)/60+SUM(AL48+BZ48)/50</f>
         <v/>
       </c>
       <c r="CQ48" s="38">
-        <f>SUM(R48+S48+BN48+CD48+CE48)/65+SUM(AB48)/36+SUM(AR48+AS48+BW48+BX48+CK48+CN48)/40+SUM(BB48+BC48+BI48+BJ48)/60</f>
+        <f>SUM(R48+S48+BN48+CD48+CE48)/65+SUM(AB48)/36+SUM(AR48+AS48+BW48+BX48+CL48+CM48)/40+SUM(BB48+BC48+BI48+BJ48)/60</f>
         <v/>
       </c>
       <c r="CR48" s="38">
@@ -10538,7 +10538,7 @@
         <v/>
       </c>
       <c r="CT48" s="38">
-        <f>SUM(BY48+CL48)/45</f>
+        <f>SUM(BY48+CN48)/45</f>
         <v/>
       </c>
       <c r="CU48" s="83">
@@ -10681,11 +10681,11 @@
         <v/>
       </c>
       <c r="CP49" s="38">
-        <f>SUM(O49+P49+Q49+BL49+BM49+CB49+CC49)/65+SUM(X49+Y49)/44+SUM(AJ49+AK49+AM49+AN49+AO49+AP49+AQ49+BR49+BS49+BT49+BU49+BV49+CH49+CI49+CJ49+CM49)/45+SUM(AX49+AY49+AZ49+BA49+BF49+BG49+BH49)/60+SUM(AL49+BZ49)/50</f>
+        <f>SUM(O49+P49+Q49+BL49+BM49+CB49+CC49)/65+SUM(X49+Y49)/44+SUM(AJ49+AK49+AM49+AN49+AO49+AP49+AQ49+BR49+BS49+BT49+BU49+BV49+CH49+CI49+CJ49+CK49)/45+SUM(AX49+AY49+AZ49+BA49+BF49+BG49+BH49)/60+SUM(AL49+BZ49)/50</f>
         <v/>
       </c>
       <c r="CQ49" s="38">
-        <f>SUM(R49+S49+BN49+CD49+CE49)/65+SUM(AB49)/36+SUM(AR49+AS49+BW49+BX49+CK49+CN49)/40+SUM(BB49+BC49+BI49+BJ49)/60</f>
+        <f>SUM(R49+S49+BN49+CD49+CE49)/65+SUM(AB49)/36+SUM(AR49+AS49+BW49+BX49+CL49+CM49)/40+SUM(BB49+BC49+BI49+BJ49)/60</f>
         <v/>
       </c>
       <c r="CR49" s="38">
@@ -10697,7 +10697,7 @@
         <v/>
       </c>
       <c r="CT49" s="38">
-        <f>SUM(BY49+CL49)/45</f>
+        <f>SUM(BY49+CN49)/45</f>
         <v/>
       </c>
       <c r="CU49" s="83">
@@ -10840,11 +10840,11 @@
         <v/>
       </c>
       <c r="CP50" s="38">
-        <f>SUM(O50+P50+Q50+BL50+BM50+CB50+CC50)/65+SUM(X50+Y50)/44+SUM(AJ50+AK50+AM50+AN50+AO50+AP50+AQ50+BR50+BS50+BT50+BU50+BV50+CH50+CI50+CJ50+CM50)/45+SUM(AX50+AY50+AZ50+BA50+BF50+BG50+BH50)/60+SUM(AL50+BZ50)/50</f>
+        <f>SUM(O50+P50+Q50+BL50+BM50+CB50+CC50)/65+SUM(X50+Y50)/44+SUM(AJ50+AK50+AM50+AN50+AO50+AP50+AQ50+BR50+BS50+BT50+BU50+BV50+CH50+CI50+CJ50+CK50)/45+SUM(AX50+AY50+AZ50+BA50+BF50+BG50+BH50)/60+SUM(AL50+BZ50)/50</f>
         <v/>
       </c>
       <c r="CQ50" s="38">
-        <f>SUM(R50+S50+BN50+CD50+CE50)/65+SUM(AB50)/36+SUM(AR50+AS50+BW50+BX50+CK50+CN50)/40+SUM(BB50+BC50+BI50+BJ50)/60</f>
+        <f>SUM(R50+S50+BN50+CD50+CE50)/65+SUM(AB50)/36+SUM(AR50+AS50+BW50+BX50+CL50+CM50)/40+SUM(BB50+BC50+BI50+BJ50)/60</f>
         <v/>
       </c>
       <c r="CR50" s="38">
@@ -10856,7 +10856,7 @@
         <v/>
       </c>
       <c r="CT50" s="38">
-        <f>SUM(BY50+CL50)/45</f>
+        <f>SUM(BY50+CN50)/45</f>
         <v/>
       </c>
       <c r="CU50" s="83">
@@ -10999,11 +10999,11 @@
         <v/>
       </c>
       <c r="CP51" s="38">
-        <f>SUM(O51+P51+Q51+BL51+BM51+CB51+CC51)/65+SUM(X51+Y51)/44+SUM(AJ51+AK51+AM51+AN51+AO51+AP51+AQ51+BR51+BS51+BT51+BU51+BV51+CH51+CI51+CJ51+CM51)/45+SUM(AX51+AY51+AZ51+BA51+BF51+BG51+BH51)/60+SUM(AL51+BZ51)/50</f>
+        <f>SUM(O51+P51+Q51+BL51+BM51+CB51+CC51)/65+SUM(X51+Y51)/44+SUM(AJ51+AK51+AM51+AN51+AO51+AP51+AQ51+BR51+BS51+BT51+BU51+BV51+CH51+CI51+CJ51+CK51)/45+SUM(AX51+AY51+AZ51+BA51+BF51+BG51+BH51)/60+SUM(AL51+BZ51)/50</f>
         <v/>
       </c>
       <c r="CQ51" s="38">
-        <f>SUM(R51+S51+BN51+CD51+CE51)/65+SUM(AB51)/36+SUM(AR51+AS51+BW51+BX51+CK51+CN51)/40+SUM(BB51+BC51+BI51+BJ51)/60</f>
+        <f>SUM(R51+S51+BN51+CD51+CE51)/65+SUM(AB51)/36+SUM(AR51+AS51+BW51+BX51+CL51+CM51)/40+SUM(BB51+BC51+BI51+BJ51)/60</f>
         <v/>
       </c>
       <c r="CR51" s="38">
@@ -11015,7 +11015,7 @@
         <v/>
       </c>
       <c r="CT51" s="38">
-        <f>SUM(BY51+CL51)/45</f>
+        <f>SUM(BY51+CN51)/45</f>
         <v/>
       </c>
       <c r="CU51" s="83">
@@ -11158,11 +11158,11 @@
         <v/>
       </c>
       <c r="CP52" s="38">
-        <f>SUM(O52+P52+Q52+BL52+BM52+CB52+CC52)/65+SUM(X52+Y52)/44+SUM(AJ52+AK52+AM52+AN52+AO52+AP52+AQ52+BR52+BS52+BT52+BU52+BV52+CH52+CI52+CJ52+CM52)/45+SUM(AX52+AY52+AZ52+BA52+BF52+BG52+BH52)/60+SUM(AL52+BZ52)/50</f>
+        <f>SUM(O52+P52+Q52+BL52+BM52+CB52+CC52)/65+SUM(X52+Y52)/44+SUM(AJ52+AK52+AM52+AN52+AO52+AP52+AQ52+BR52+BS52+BT52+BU52+BV52+CH52+CI52+CJ52+CK52)/45+SUM(AX52+AY52+AZ52+BA52+BF52+BG52+BH52)/60+SUM(AL52+BZ52)/50</f>
         <v/>
       </c>
       <c r="CQ52" s="38">
-        <f>SUM(R52+S52+BN52+CD52+CE52)/65+SUM(AB52)/36+SUM(AR52+AS52+BW52+BX52+CK52+CN52)/40+SUM(BB52+BC52+BI52+BJ52)/60</f>
+        <f>SUM(R52+S52+BN52+CD52+CE52)/65+SUM(AB52)/36+SUM(AR52+AS52+BW52+BX52+CL52+CM52)/40+SUM(BB52+BC52+BI52+BJ52)/60</f>
         <v/>
       </c>
       <c r="CR52" s="38">
@@ -11174,7 +11174,7 @@
         <v/>
       </c>
       <c r="CT52" s="38">
-        <f>SUM(BY52+CL52)/45</f>
+        <f>SUM(BY52+CN52)/45</f>
         <v/>
       </c>
       <c r="CU52" s="83">
@@ -11317,11 +11317,11 @@
         <v/>
       </c>
       <c r="CP53" s="38">
-        <f>SUM(O53+P53+Q53+BL53+BM53+CB53+CC53)/65+SUM(X53+Y53)/44+SUM(AJ53+AK53+AM53+AN53+AO53+AP53+AQ53+BR53+BS53+BT53+BU53+BV53+CH53+CI53+CJ53+CM53)/45+SUM(AX53+AY53+AZ53+BA53+BF53+BG53+BH53)/60+SUM(AL53+BZ53)/50</f>
+        <f>SUM(O53+P53+Q53+BL53+BM53+CB53+CC53)/65+SUM(X53+Y53)/44+SUM(AJ53+AK53+AM53+AN53+AO53+AP53+AQ53+BR53+BS53+BT53+BU53+BV53+CH53+CI53+CJ53+CK53)/45+SUM(AX53+AY53+AZ53+BA53+BF53+BG53+BH53)/60+SUM(AL53+BZ53)/50</f>
         <v/>
       </c>
       <c r="CQ53" s="38">
-        <f>SUM(R53+S53+BN53+CD53+CE53)/65+SUM(AB53)/36+SUM(AR53+AS53+BW53+BX53+CK53+CN53)/40+SUM(BB53+BC53+BI53+BJ53)/60</f>
+        <f>SUM(R53+S53+BN53+CD53+CE53)/65+SUM(AB53)/36+SUM(AR53+AS53+BW53+BX53+CL53+CM53)/40+SUM(BB53+BC53+BI53+BJ53)/60</f>
         <v/>
       </c>
       <c r="CR53" s="38">
@@ -11333,7 +11333,7 @@
         <v/>
       </c>
       <c r="CT53" s="38">
-        <f>SUM(BY53+CL53)/45</f>
+        <f>SUM(BY53+CN53)/45</f>
         <v/>
       </c>
       <c r="CU53" s="83">
@@ -11476,11 +11476,11 @@
         <v/>
       </c>
       <c r="CP54" s="38">
-        <f>SUM(O54+P54+Q54+BL54+BM54+CB54+CC54)/65+SUM(X54+Y54)/44+SUM(AJ54+AK54+AM54+AN54+AO54+AP54+AQ54+BR54+BS54+BT54+BU54+BV54+CH54+CI54+CJ54+CM54)/45+SUM(AX54+AY54+AZ54+BA54+BF54+BG54+BH54)/60+SUM(AL54+BZ54)/50</f>
+        <f>SUM(O54+P54+Q54+BL54+BM54+CB54+CC54)/65+SUM(X54+Y54)/44+SUM(AJ54+AK54+AM54+AN54+AO54+AP54+AQ54+BR54+BS54+BT54+BU54+BV54+CH54+CI54+CJ54+CK54)/45+SUM(AX54+AY54+AZ54+BA54+BF54+BG54+BH54)/60+SUM(AL54+BZ54)/50</f>
         <v/>
       </c>
       <c r="CQ54" s="38">
-        <f>SUM(R54+S54+BN54+CD54+CE54)/65+SUM(AB54)/36+SUM(AR54+AS54+BW54+BX54+CK54+CN54)/40+SUM(BB54+BC54+BI54+BJ54)/60</f>
+        <f>SUM(R54+S54+BN54+CD54+CE54)/65+SUM(AB54)/36+SUM(AR54+AS54+BW54+BX54+CL54+CM54)/40+SUM(BB54+BC54+BI54+BJ54)/60</f>
         <v/>
       </c>
       <c r="CR54" s="38">
@@ -11492,7 +11492,7 @@
         <v/>
       </c>
       <c r="CT54" s="38">
-        <f>SUM(BY54+CL54)/45</f>
+        <f>SUM(BY54+CN54)/45</f>
         <v/>
       </c>
       <c r="CU54" s="83">
@@ -11635,11 +11635,11 @@
         <v/>
       </c>
       <c r="CP55" s="38">
-        <f>SUM(O55+P55+Q55+BL55+BM55+CB55+CC55)/65+SUM(X55+Y55)/44+SUM(AJ55+AK55+AM55+AN55+AO55+AP55+AQ55+BR55+BS55+BT55+BU55+BV55+CH55+CI55+CJ55+CM55)/45+SUM(AX55+AY55+AZ55+BA55+BF55+BG55+BH55)/60+SUM(AL55+BZ55)/50</f>
+        <f>SUM(O55+P55+Q55+BL55+BM55+CB55+CC55)/65+SUM(X55+Y55)/44+SUM(AJ55+AK55+AM55+AN55+AO55+AP55+AQ55+BR55+BS55+BT55+BU55+BV55+CH55+CI55+CJ55+CK55)/45+SUM(AX55+AY55+AZ55+BA55+BF55+BG55+BH55)/60+SUM(AL55+BZ55)/50</f>
         <v/>
       </c>
       <c r="CQ55" s="38">
-        <f>SUM(R55+S55+BN55+CD55+CE55)/65+SUM(AB55)/36+SUM(AR55+AS55+BW55+BX55+CK55+CN55)/40+SUM(BB55+BC55+BI55+BJ55)/60</f>
+        <f>SUM(R55+S55+BN55+CD55+CE55)/65+SUM(AB55)/36+SUM(AR55+AS55+BW55+BX55+CL55+CM55)/40+SUM(BB55+BC55+BI55+BJ55)/60</f>
         <v/>
       </c>
       <c r="CR55" s="38">
@@ -11651,7 +11651,7 @@
         <v/>
       </c>
       <c r="CT55" s="38">
-        <f>SUM(BY55+CL55)/45</f>
+        <f>SUM(BY55+CN55)/45</f>
         <v/>
       </c>
       <c r="CU55" s="83">
@@ -11794,11 +11794,11 @@
         <v/>
       </c>
       <c r="CP56" s="38">
-        <f>SUM(O56+P56+Q56+BL56+BM56+CB56+CC56)/65+SUM(X56+Y56)/44+SUM(AJ56+AK56+AM56+AN56+AO56+AP56+AQ56+BR56+BS56+BT56+BU56+BV56+CH56+CI56+CJ56+CM56)/45+SUM(AX56+AY56+AZ56+BA56+BF56+BG56+BH56)/60+SUM(AL56+BZ56)/50</f>
+        <f>SUM(O56+P56+Q56+BL56+BM56+CB56+CC56)/65+SUM(X56+Y56)/44+SUM(AJ56+AK56+AM56+AN56+AO56+AP56+AQ56+BR56+BS56+BT56+BU56+BV56+CH56+CI56+CJ56+CK56)/45+SUM(AX56+AY56+AZ56+BA56+BF56+BG56+BH56)/60+SUM(AL56+BZ56)/50</f>
         <v/>
       </c>
       <c r="CQ56" s="38">
-        <f>SUM(R56+S56+BN56+CD56+CE56)/65+SUM(AB56)/36+SUM(AR56+AS56+BW56+BX56+CK56+CN56)/40+SUM(BB56+BC56+BI56+BJ56)/60</f>
+        <f>SUM(R56+S56+BN56+CD56+CE56)/65+SUM(AB56)/36+SUM(AR56+AS56+BW56+BX56+CL56+CM56)/40+SUM(BB56+BC56+BI56+BJ56)/60</f>
         <v/>
       </c>
       <c r="CR56" s="38">
@@ -11810,7 +11810,7 @@
         <v/>
       </c>
       <c r="CT56" s="38">
-        <f>SUM(BY56+CL56)/45</f>
+        <f>SUM(BY56+CN56)/45</f>
         <v/>
       </c>
       <c r="CU56" s="83">
@@ -11953,11 +11953,11 @@
         <v/>
       </c>
       <c r="CP57" s="38">
-        <f>SUM(O57+P57+Q57+BL57+BM57+CB57+CC57)/65+SUM(X57+Y57)/44+SUM(AJ57+AK57+AM57+AN57+AO57+AP57+AQ57+BR57+BS57+BT57+BU57+BV57+CH57+CI57+CJ57+CM57)/45+SUM(AX57+AY57+AZ57+BA57+BF57+BG57+BH57)/60+SUM(AL57+BZ57)/50</f>
+        <f>SUM(O57+P57+Q57+BL57+BM57+CB57+CC57)/65+SUM(X57+Y57)/44+SUM(AJ57+AK57+AM57+AN57+AO57+AP57+AQ57+BR57+BS57+BT57+BU57+BV57+CH57+CI57+CJ57+CK57)/45+SUM(AX57+AY57+AZ57+BA57+BF57+BG57+BH57)/60+SUM(AL57+BZ57)/50</f>
         <v/>
       </c>
       <c r="CQ57" s="38">
-        <f>SUM(R57+S57+BN57+CD57+CE57)/65+SUM(AB57)/36+SUM(AR57+AS57+BW57+BX57+CK57+CN57)/40+SUM(BB57+BC57+BI57+BJ57)/60</f>
+        <f>SUM(R57+S57+BN57+CD57+CE57)/65+SUM(AB57)/36+SUM(AR57+AS57+BW57+BX57+CL57+CM57)/40+SUM(BB57+BC57+BI57+BJ57)/60</f>
         <v/>
       </c>
       <c r="CR57" s="38">
@@ -11969,7 +11969,7 @@
         <v/>
       </c>
       <c r="CT57" s="38">
-        <f>SUM(BY57+CL57)/45</f>
+        <f>SUM(BY57+CN57)/45</f>
         <v/>
       </c>
       <c r="CU57" s="83">
@@ -12112,11 +12112,11 @@
         <v/>
       </c>
       <c r="CP58" s="38">
-        <f>SUM(O58+P58+Q58+BL58+BM58+CB58+CC58)/65+SUM(X58+Y58)/44+SUM(AJ58+AK58+AM58+AN58+AO58+AP58+AQ58+BR58+BS58+BT58+BU58+BV58+CH58+CI58+CJ58+CM58)/45+SUM(AX58+AY58+AZ58+BA58+BF58+BG58+BH58)/60+SUM(AL58+BZ58)/50</f>
+        <f>SUM(O58+P58+Q58+BL58+BM58+CB58+CC58)/65+SUM(X58+Y58)/44+SUM(AJ58+AK58+AM58+AN58+AO58+AP58+AQ58+BR58+BS58+BT58+BU58+BV58+CH58+CI58+CJ58+CK58)/45+SUM(AX58+AY58+AZ58+BA58+BF58+BG58+BH58)/60+SUM(AL58+BZ58)/50</f>
         <v/>
       </c>
       <c r="CQ58" s="38">
-        <f>SUM(R58+S58+BN58+CD58+CE58)/65+SUM(AB58)/36+SUM(AR58+AS58+BW58+BX58+CK58+CN58)/40+SUM(BB58+BC58+BI58+BJ58)/60</f>
+        <f>SUM(R58+S58+BN58+CD58+CE58)/65+SUM(AB58)/36+SUM(AR58+AS58+BW58+BX58+CL58+CM58)/40+SUM(BB58+BC58+BI58+BJ58)/60</f>
         <v/>
       </c>
       <c r="CR58" s="38">
@@ -12128,7 +12128,7 @@
         <v/>
       </c>
       <c r="CT58" s="38">
-        <f>SUM(BY58+CL58)/45</f>
+        <f>SUM(BY58+CN58)/45</f>
         <v/>
       </c>
       <c r="CU58" s="83">
@@ -12271,11 +12271,11 @@
         <v/>
       </c>
       <c r="CP59" s="38">
-        <f>SUM(O59+P59+Q59+BL59+BM59+CB59+CC59)/65+SUM(X59+Y59)/44+SUM(AJ59+AK59+AM59+AN59+AO59+AP59+AQ59+BR59+BS59+BT59+BU59+BV59+CH59+CI59+CJ59+CM59)/45+SUM(AX59+AY59+AZ59+BA59+BF59+BG59+BH59)/60+SUM(AL59+BZ59)/50</f>
+        <f>SUM(O59+P59+Q59+BL59+BM59+CB59+CC59)/65+SUM(X59+Y59)/44+SUM(AJ59+AK59+AM59+AN59+AO59+AP59+AQ59+BR59+BS59+BT59+BU59+BV59+CH59+CI59+CJ59+CK59)/45+SUM(AX59+AY59+AZ59+BA59+BF59+BG59+BH59)/60+SUM(AL59+BZ59)/50</f>
         <v/>
       </c>
       <c r="CQ59" s="38">
-        <f>SUM(R59+S59+BN59+CD59+CE59)/65+SUM(AB59)/36+SUM(AR59+AS59+BW59+BX59+CK59+CN59)/40+SUM(BB59+BC59+BI59+BJ59)/60</f>
+        <f>SUM(R59+S59+BN59+CD59+CE59)/65+SUM(AB59)/36+SUM(AR59+AS59+BW59+BX59+CL59+CM59)/40+SUM(BB59+BC59+BI59+BJ59)/60</f>
         <v/>
       </c>
       <c r="CR59" s="38">
@@ -12287,7 +12287,7 @@
         <v/>
       </c>
       <c r="CT59" s="38">
-        <f>SUM(BY59+CL59)/45</f>
+        <f>SUM(BY59+CN59)/45</f>
         <v/>
       </c>
       <c r="CU59" s="83">
@@ -12430,11 +12430,11 @@
         <v/>
       </c>
       <c r="CP60" s="38">
-        <f>SUM(O60+P60+Q60+BL60+BM60+CB60+CC60)/65+SUM(X60+Y60)/44+SUM(AJ60+AK60+AM60+AN60+AO60+AP60+AQ60+BR60+BS60+BT60+BU60+BV60+CH60+CI60+CJ60+CM60)/45+SUM(AX60+AY60+AZ60+BA60+BF60+BG60+BH60)/60+SUM(AL60+BZ60)/50</f>
+        <f>SUM(O60+P60+Q60+BL60+BM60+CB60+CC60)/65+SUM(X60+Y60)/44+SUM(AJ60+AK60+AM60+AN60+AO60+AP60+AQ60+BR60+BS60+BT60+BU60+BV60+CH60+CI60+CJ60+CK60)/45+SUM(AX60+AY60+AZ60+BA60+BF60+BG60+BH60)/60+SUM(AL60+BZ60)/50</f>
         <v/>
       </c>
       <c r="CQ60" s="38">
-        <f>SUM(R60+S60+BN60+CD60+CE60)/65+SUM(AB60)/36+SUM(AR60+AS60+BW60+BX60+CK60+CN60)/40+SUM(BB60+BC60+BI60+BJ60)/60</f>
+        <f>SUM(R60+S60+BN60+CD60+CE60)/65+SUM(AB60)/36+SUM(AR60+AS60+BW60+BX60+CL60+CM60)/40+SUM(BB60+BC60+BI60+BJ60)/60</f>
         <v/>
       </c>
       <c r="CR60" s="38">
@@ -12446,7 +12446,7 @@
         <v/>
       </c>
       <c r="CT60" s="38">
-        <f>SUM(BY60+CL60)/45</f>
+        <f>SUM(BY60+CN60)/45</f>
         <v/>
       </c>
       <c r="CU60" s="83">
@@ -12589,11 +12589,11 @@
         <v/>
       </c>
       <c r="CP61" s="38">
-        <f>SUM(O61+P61+Q61+BL61+BM61+CB61+CC61)/65+SUM(X61+Y61)/44+SUM(AJ61+AK61+AM61+AN61+AO61+AP61+AQ61+BR61+BS61+BT61+BU61+BV61+CH61+CI61+CJ61+CM61)/45+SUM(AX61+AY61+AZ61+BA61+BF61+BG61+BH61)/60+SUM(AL61+BZ61)/50</f>
+        <f>SUM(O61+P61+Q61+BL61+BM61+CB61+CC61)/65+SUM(X61+Y61)/44+SUM(AJ61+AK61+AM61+AN61+AO61+AP61+AQ61+BR61+BS61+BT61+BU61+BV61+CH61+CI61+CJ61+CK61)/45+SUM(AX61+AY61+AZ61+BA61+BF61+BG61+BH61)/60+SUM(AL61+BZ61)/50</f>
         <v/>
       </c>
       <c r="CQ61" s="38">
-        <f>SUM(R61+S61+BN61+CD61+CE61)/65+SUM(AB61)/36+SUM(AR61+AS61+BW61+BX61+CK61+CN61)/40+SUM(BB61+BC61+BI61+BJ61)/60</f>
+        <f>SUM(R61+S61+BN61+CD61+CE61)/65+SUM(AB61)/36+SUM(AR61+AS61+BW61+BX61+CL61+CM61)/40+SUM(BB61+BC61+BI61+BJ61)/60</f>
         <v/>
       </c>
       <c r="CR61" s="38">
@@ -12605,7 +12605,7 @@
         <v/>
       </c>
       <c r="CT61" s="38">
-        <f>SUM(BY61+CL61)/45</f>
+        <f>SUM(BY61+CN61)/45</f>
         <v/>
       </c>
       <c r="CU61" s="83">
@@ -12748,11 +12748,11 @@
         <v/>
       </c>
       <c r="CP62" s="38">
-        <f>SUM(O62+P62+Q62+BL62+BM62+CB62+CC62)/65+SUM(X62+Y62)/44+SUM(AJ62+AK62+AM62+AN62+AO62+AP62+AQ62+BR62+BS62+BT62+BU62+BV62+CH62+CI62+CJ62+CM62)/45+SUM(AX62+AY62+AZ62+BA62+BF62+BG62+BH62)/60+SUM(AL62+BZ62)/50</f>
+        <f>SUM(O62+P62+Q62+BL62+BM62+CB62+CC62)/65+SUM(X62+Y62)/44+SUM(AJ62+AK62+AM62+AN62+AO62+AP62+AQ62+BR62+BS62+BT62+BU62+BV62+CH62+CI62+CJ62+CK62)/45+SUM(AX62+AY62+AZ62+BA62+BF62+BG62+BH62)/60+SUM(AL62+BZ62)/50</f>
         <v/>
       </c>
       <c r="CQ62" s="38">
-        <f>SUM(R62+S62+BN62+CD62+CE62)/65+SUM(AB62)/36+SUM(AR62+AS62+BW62+BX62+CK62+CN62)/40+SUM(BB62+BC62+BI62+BJ62)/60</f>
+        <f>SUM(R62+S62+BN62+CD62+CE62)/65+SUM(AB62)/36+SUM(AR62+AS62+BW62+BX62+CL62+CM62)/40+SUM(BB62+BC62+BI62+BJ62)/60</f>
         <v/>
       </c>
       <c r="CR62" s="38">
@@ -12764,7 +12764,7 @@
         <v/>
       </c>
       <c r="CT62" s="38">
-        <f>SUM(BY62+CL62)/45</f>
+        <f>SUM(BY62+CN62)/45</f>
         <v/>
       </c>
       <c r="CU62" s="83">
@@ -12907,11 +12907,11 @@
         <v/>
       </c>
       <c r="CP63" s="38">
-        <f>SUM(O63+P63+Q63+BL63+BM63+CB63+CC63)/65+SUM(X63+Y63)/44+SUM(AJ63+AK63+AM63+AN63+AO63+AP63+AQ63+BR63+BS63+BT63+BU63+BV63+CH63+CI63+CJ63+CM63)/45+SUM(AX63+AY63+AZ63+BA63+BF63+BG63+BH63)/60+SUM(AL63+BZ63)/50</f>
+        <f>SUM(O63+P63+Q63+BL63+BM63+CB63+CC63)/65+SUM(X63+Y63)/44+SUM(AJ63+AK63+AM63+AN63+AO63+AP63+AQ63+BR63+BS63+BT63+BU63+BV63+CH63+CI63+CJ63+CK63)/45+SUM(AX63+AY63+AZ63+BA63+BF63+BG63+BH63)/60+SUM(AL63+BZ63)/50</f>
         <v/>
       </c>
       <c r="CQ63" s="38">
-        <f>SUM(R63+S63+BN63+CD63+CE63)/65+SUM(AB63)/36+SUM(AR63+AS63+BW63+BX63+CK63+CN63)/40+SUM(BB63+BC63+BI63+BJ63)/60</f>
+        <f>SUM(R63+S63+BN63+CD63+CE63)/65+SUM(AB63)/36+SUM(AR63+AS63+BW63+BX63+CL63+CM63)/40+SUM(BB63+BC63+BI63+BJ63)/60</f>
         <v/>
       </c>
       <c r="CR63" s="38">
@@ -12923,7 +12923,7 @@
         <v/>
       </c>
       <c r="CT63" s="38">
-        <f>SUM(BY63+CL63)/45</f>
+        <f>SUM(BY63+CN63)/45</f>
         <v/>
       </c>
       <c r="CU63" s="83">
@@ -13066,11 +13066,11 @@
         <v/>
       </c>
       <c r="CP64" s="38">
-        <f>SUM(O64+P64+Q64+BL64+BM64+CB64+CC64)/65+SUM(X64+Y64)/44+SUM(AJ64+AK64+AM64+AN64+AO64+AP64+AQ64+BR64+BS64+BT64+BU64+BV64+CH64+CI64+CJ64+CM64)/45+SUM(AX64+AY64+AZ64+BA64+BF64+BG64+BH64)/60+SUM(AL64+BZ64)/50</f>
+        <f>SUM(O64+P64+Q64+BL64+BM64+CB64+CC64)/65+SUM(X64+Y64)/44+SUM(AJ64+AK64+AM64+AN64+AO64+AP64+AQ64+BR64+BS64+BT64+BU64+BV64+CH64+CI64+CJ64+CK64)/45+SUM(AX64+AY64+AZ64+BA64+BF64+BG64+BH64)/60+SUM(AL64+BZ64)/50</f>
         <v/>
       </c>
       <c r="CQ64" s="38">
-        <f>SUM(R64+S64+BN64+CD64+CE64)/65+SUM(AB64)/36+SUM(AR64+AS64+BW64+BX64+CK64+CN64)/40+SUM(BB64+BC64+BI64+BJ64)/60</f>
+        <f>SUM(R64+S64+BN64+CD64+CE64)/65+SUM(AB64)/36+SUM(AR64+AS64+BW64+BX64+CL64+CM64)/40+SUM(BB64+BC64+BI64+BJ64)/60</f>
         <v/>
       </c>
       <c r="CR64" s="38">
@@ -13082,7 +13082,7 @@
         <v/>
       </c>
       <c r="CT64" s="38">
-        <f>SUM(BY64+CL64)/45</f>
+        <f>SUM(BY64+CN64)/45</f>
         <v/>
       </c>
       <c r="CU64" s="83">
@@ -13225,11 +13225,11 @@
         <v/>
       </c>
       <c r="CP65" s="38">
-        <f>SUM(O65+P65+Q65+BL65+BM65+CB65+CC65)/65+SUM(X65+Y65)/44+SUM(AJ65+AK65+AM65+AN65+AO65+AP65+AQ65+BR65+BS65+BT65+BU65+BV65+CH65+CI65+CJ65+CM65)/45+SUM(AX65+AY65+AZ65+BA65+BF65+BG65+BH65)/60+SUM(AL65+BZ65)/50</f>
+        <f>SUM(O65+P65+Q65+BL65+BM65+CB65+CC65)/65+SUM(X65+Y65)/44+SUM(AJ65+AK65+AM65+AN65+AO65+AP65+AQ65+BR65+BS65+BT65+BU65+BV65+CH65+CI65+CJ65+CK65)/45+SUM(AX65+AY65+AZ65+BA65+BF65+BG65+BH65)/60+SUM(AL65+BZ65)/50</f>
         <v/>
       </c>
       <c r="CQ65" s="38">
-        <f>SUM(R65+S65+BN65+CD65+CE65)/65+SUM(AB65)/36+SUM(AR65+AS65+BW65+BX65+CK65+CN65)/40+SUM(BB65+BC65+BI65+BJ65)/60</f>
+        <f>SUM(R65+S65+BN65+CD65+CE65)/65+SUM(AB65)/36+SUM(AR65+AS65+BW65+BX65+CL65+CM65)/40+SUM(BB65+BC65+BI65+BJ65)/60</f>
         <v/>
       </c>
       <c r="CR65" s="38">
@@ -13241,7 +13241,7 @@
         <v/>
       </c>
       <c r="CT65" s="38">
-        <f>SUM(BY65+CL65)/45</f>
+        <f>SUM(BY65+CN65)/45</f>
         <v/>
       </c>
       <c r="CU65" s="83">
@@ -13384,11 +13384,11 @@
         <v/>
       </c>
       <c r="CP66" s="38">
-        <f>SUM(O66+P66+Q66+BL66+BM66+CB66+CC66)/65+SUM(X66+Y66)/44+SUM(AJ66+AK66+AM66+AN66+AO66+AP66+AQ66+BR66+BS66+BT66+BU66+BV66+CH66+CI66+CJ66+CM66)/45+SUM(AX66+AY66+AZ66+BA66+BF66+BG66+BH66)/60+SUM(AL66+BZ66)/50</f>
+        <f>SUM(O66+P66+Q66+BL66+BM66+CB66+CC66)/65+SUM(X66+Y66)/44+SUM(AJ66+AK66+AM66+AN66+AO66+AP66+AQ66+BR66+BS66+BT66+BU66+BV66+CH66+CI66+CJ66+CK66)/45+SUM(AX66+AY66+AZ66+BA66+BF66+BG66+BH66)/60+SUM(AL66+BZ66)/50</f>
         <v/>
       </c>
       <c r="CQ66" s="38">
-        <f>SUM(R66+S66+BN66+CD66+CE66)/65+SUM(AB66)/36+SUM(AR66+AS66+BW66+BX66+CK66+CN66)/40+SUM(BB66+BC66+BI66+BJ66)/60</f>
+        <f>SUM(R66+S66+BN66+CD66+CE66)/65+SUM(AB66)/36+SUM(AR66+AS66+BW66+BX66+CL66+CM66)/40+SUM(BB66+BC66+BI66+BJ66)/60</f>
         <v/>
       </c>
       <c r="CR66" s="38">
@@ -13400,7 +13400,7 @@
         <v/>
       </c>
       <c r="CT66" s="38">
-        <f>SUM(BY66+CL66)/45</f>
+        <f>SUM(BY66+CN66)/45</f>
         <v/>
       </c>
       <c r="CU66" s="83">
@@ -13543,11 +13543,11 @@
         <v/>
       </c>
       <c r="CP67" s="38">
-        <f>SUM(O67+P67+Q67+BL67+BM67+CB67+CC67)/65+SUM(X67+Y67)/44+SUM(AJ67+AK67+AM67+AN67+AO67+AP67+AQ67+BR67+BS67+BT67+BU67+BV67+CH67+CI67+CJ67+CM67)/45+SUM(AX67+AY67+AZ67+BA67+BF67+BG67+BH67)/60+SUM(AL67+BZ67)/50</f>
+        <f>SUM(O67+P67+Q67+BL67+BM67+CB67+CC67)/65+SUM(X67+Y67)/44+SUM(AJ67+AK67+AM67+AN67+AO67+AP67+AQ67+BR67+BS67+BT67+BU67+BV67+CH67+CI67+CJ67+CK67)/45+SUM(AX67+AY67+AZ67+BA67+BF67+BG67+BH67)/60+SUM(AL67+BZ67)/50</f>
         <v/>
       </c>
       <c r="CQ67" s="38">
-        <f>SUM(R67+S67+BN67+CD67+CE67)/65+SUM(AB67)/36+SUM(AR67+AS67+BW67+BX67+CK67+CN67)/40+SUM(BB67+BC67+BI67+BJ67)/60</f>
+        <f>SUM(R67+S67+BN67+CD67+CE67)/65+SUM(AB67)/36+SUM(AR67+AS67+BW67+BX67+CL67+CM67)/40+SUM(BB67+BC67+BI67+BJ67)/60</f>
         <v/>
       </c>
       <c r="CR67" s="38">
@@ -13559,7 +13559,7 @@
         <v/>
       </c>
       <c r="CT67" s="38">
-        <f>SUM(BY67+CL67)/45</f>
+        <f>SUM(BY67+CN67)/45</f>
         <v/>
       </c>
       <c r="CU67" s="83">
@@ -13702,11 +13702,11 @@
         <v/>
       </c>
       <c r="CP68" s="38">
-        <f>SUM(O68+P68+Q68+BL68+BM68+CB68+CC68)/65+SUM(X68+Y68)/44+SUM(AJ68+AK68+AM68+AN68+AO68+AP68+AQ68+BR68+BS68+BT68+BU68+BV68+CH68+CI68+CJ68+CM68)/45+SUM(AX68+AY68+AZ68+BA68+BF68+BG68+BH68)/60+SUM(AL68+BZ68)/50</f>
+        <f>SUM(O68+P68+Q68+BL68+BM68+CB68+CC68)/65+SUM(X68+Y68)/44+SUM(AJ68+AK68+AM68+AN68+AO68+AP68+AQ68+BR68+BS68+BT68+BU68+BV68+CH68+CI68+CJ68+CK68)/45+SUM(AX68+AY68+AZ68+BA68+BF68+BG68+BH68)/60+SUM(AL68+BZ68)/50</f>
         <v/>
       </c>
       <c r="CQ68" s="38">
-        <f>SUM(R68+S68+BN68+CD68+CE68)/65+SUM(AB68)/36+SUM(AR68+AS68+BW68+BX68+CK68+CN68)/40+SUM(BB68+BC68+BI68+BJ68)/60</f>
+        <f>SUM(R68+S68+BN68+CD68+CE68)/65+SUM(AB68)/36+SUM(AR68+AS68+BW68+BX68+CL68+CM68)/40+SUM(BB68+BC68+BI68+BJ68)/60</f>
         <v/>
       </c>
       <c r="CR68" s="38">
@@ -13718,7 +13718,7 @@
         <v/>
       </c>
       <c r="CT68" s="38">
-        <f>SUM(BY68+CL68)/45</f>
+        <f>SUM(BY68+CN68)/45</f>
         <v/>
       </c>
       <c r="CU68" s="83">
@@ -13861,11 +13861,11 @@
         <v/>
       </c>
       <c r="CP69" s="38">
-        <f>SUM(O69+P69+Q69+BL69+BM69+CB69+CC69)/65+SUM(X69+Y69)/44+SUM(AJ69+AK69+AM69+AN69+AO69+AP69+AQ69+BR69+BS69+BT69+BU69+BV69+CH69+CI69+CJ69+CM69)/45+SUM(AX69+AY69+AZ69+BA69+BF69+BG69+BH69)/60+SUM(AL69+BZ69)/50</f>
+        <f>SUM(O69+P69+Q69+BL69+BM69+CB69+CC69)/65+SUM(X69+Y69)/44+SUM(AJ69+AK69+AM69+AN69+AO69+AP69+AQ69+BR69+BS69+BT69+BU69+BV69+CH69+CI69+CJ69+CK69)/45+SUM(AX69+AY69+AZ69+BA69+BF69+BG69+BH69)/60+SUM(AL69+BZ69)/50</f>
         <v/>
       </c>
       <c r="CQ69" s="38">
-        <f>SUM(R69+S69+BN69+CD69+CE69)/65+SUM(AB69)/36+SUM(AR69+AS69+BW69+BX69+CK69+CN69)/40+SUM(BB69+BC69+BI69+BJ69)/60</f>
+        <f>SUM(R69+S69+BN69+CD69+CE69)/65+SUM(AB69)/36+SUM(AR69+AS69+BW69+BX69+CL69+CM69)/40+SUM(BB69+BC69+BI69+BJ69)/60</f>
         <v/>
       </c>
       <c r="CR69" s="38">
@@ -13877,7 +13877,7 @@
         <v/>
       </c>
       <c r="CT69" s="38">
-        <f>SUM(BY69+CL69)/45</f>
+        <f>SUM(BY69+CN69)/45</f>
         <v/>
       </c>
       <c r="CU69" s="83">
@@ -14020,11 +14020,11 @@
         <v/>
       </c>
       <c r="CP70" s="38">
-        <f>SUM(O70+P70+Q70+BL70+BM70+CB70+CC70)/65+SUM(X70+Y70)/44+SUM(AJ70+AK70+AM70+AN70+AO70+AP70+AQ70+BR70+BS70+BT70+BU70+BV70+CH70+CI70+CJ70+CM70)/45+SUM(AX70+AY70+AZ70+BA70+BF70+BG70+BH70)/60+SUM(AL70+BZ70)/50</f>
+        <f>SUM(O70+P70+Q70+BL70+BM70+CB70+CC70)/65+SUM(X70+Y70)/44+SUM(AJ70+AK70+AM70+AN70+AO70+AP70+AQ70+BR70+BS70+BT70+BU70+BV70+CH70+CI70+CJ70+CK70)/45+SUM(AX70+AY70+AZ70+BA70+BF70+BG70+BH70)/60+SUM(AL70+BZ70)/50</f>
         <v/>
       </c>
       <c r="CQ70" s="38">
-        <f>SUM(R70+S70+BN70+CD70+CE70)/65+SUM(AB70)/36+SUM(AR70+AS70+BW70+BX70+CK70+CN70)/40+SUM(BB70+BC70+BI70+BJ70)/60</f>
+        <f>SUM(R70+S70+BN70+CD70+CE70)/65+SUM(AB70)/36+SUM(AR70+AS70+BW70+BX70+CL70+CM70)/40+SUM(BB70+BC70+BI70+BJ70)/60</f>
         <v/>
       </c>
       <c r="CR70" s="38">
@@ -14036,7 +14036,7 @@
         <v/>
       </c>
       <c r="CT70" s="38">
-        <f>SUM(BY70+CL70)/45</f>
+        <f>SUM(BY70+CN70)/45</f>
         <v/>
       </c>
       <c r="CU70" s="83">
@@ -14179,11 +14179,11 @@
         <v/>
       </c>
       <c r="CP71" s="38">
-        <f>SUM(O71+P71+Q71+BL71+BM71+CB71+CC71)/65+SUM(X71+Y71)/44+SUM(AJ71+AK71+AM71+AN71+AO71+AP71+AQ71+BR71+BS71+BT71+BU71+BV71+CH71+CI71+CJ71+CM71)/45+SUM(AX71+AY71+AZ71+BA71+BF71+BG71+BH71)/60+SUM(AL71+BZ71)/50</f>
+        <f>SUM(O71+P71+Q71+BL71+BM71+CB71+CC71)/65+SUM(X71+Y71)/44+SUM(AJ71+AK71+AM71+AN71+AO71+AP71+AQ71+BR71+BS71+BT71+BU71+BV71+CH71+CI71+CJ71+CK71)/45+SUM(AX71+AY71+AZ71+BA71+BF71+BG71+BH71)/60+SUM(AL71+BZ71)/50</f>
         <v/>
       </c>
       <c r="CQ71" s="38">
-        <f>SUM(R71+S71+BN71+CD71+CE71)/65+SUM(AB71)/36+SUM(AR71+AS71+BW71+BX71+CK71+CN71)/40+SUM(BB71+BC71+BI71+BJ71)/60</f>
+        <f>SUM(R71+S71+BN71+CD71+CE71)/65+SUM(AB71)/36+SUM(AR71+AS71+BW71+BX71+CL71+CM71)/40+SUM(BB71+BC71+BI71+BJ71)/60</f>
         <v/>
       </c>
       <c r="CR71" s="38">
@@ -14195,7 +14195,7 @@
         <v/>
       </c>
       <c r="CT71" s="38">
-        <f>SUM(BY71+CL71)/45</f>
+        <f>SUM(BY71+CN71)/45</f>
         <v/>
       </c>
       <c r="CU71" s="83">
@@ -14338,11 +14338,11 @@
         <v/>
       </c>
       <c r="CP72" s="38">
-        <f>SUM(O72+P72+Q72+BL72+BM72+CB72+CC72)/65+SUM(X72+Y72)/44+SUM(AJ72+AK72+AM72+AN72+AO72+AP72+AQ72+BR72+BS72+BT72+BU72+BV72+CH72+CI72+CJ72+CM72)/45+SUM(AX72+AY72+AZ72+BA72+BF72+BG72+BH72)/60+SUM(AL72+BZ72)/50</f>
+        <f>SUM(O72+P72+Q72+BL72+BM72+CB72+CC72)/65+SUM(X72+Y72)/44+SUM(AJ72+AK72+AM72+AN72+AO72+AP72+AQ72+BR72+BS72+BT72+BU72+BV72+CH72+CI72+CJ72+CK72)/45+SUM(AX72+AY72+AZ72+BA72+BF72+BG72+BH72)/60+SUM(AL72+BZ72)/50</f>
         <v/>
       </c>
       <c r="CQ72" s="38">
-        <f>SUM(R72+S72+BN72+CD72+CE72)/65+SUM(AB72)/36+SUM(AR72+AS72+BW72+BX72+CK72+CN72)/40+SUM(BB72+BC72+BI72+BJ72)/60</f>
+        <f>SUM(R72+S72+BN72+CD72+CE72)/65+SUM(AB72)/36+SUM(AR72+AS72+BW72+BX72+CL72+CM72)/40+SUM(BB72+BC72+BI72+BJ72)/60</f>
         <v/>
       </c>
       <c r="CR72" s="38">
@@ -14354,7 +14354,7 @@
         <v/>
       </c>
       <c r="CT72" s="38">
-        <f>SUM(BY72+CL72)/45</f>
+        <f>SUM(BY72+CN72)/45</f>
         <v/>
       </c>
       <c r="CU72" s="83">
@@ -14497,11 +14497,11 @@
         <v/>
       </c>
       <c r="CP73" s="38">
-        <f>SUM(O73+P73+Q73+BL73+BM73+CB73+CC73)/65+SUM(X73+Y73)/44+SUM(AJ73+AK73+AM73+AN73+AO73+AP73+AQ73+BR73+BS73+BT73+BU73+BV73+CH73+CI73+CJ73+CM73)/45+SUM(AX73+AY73+AZ73+BA73+BF73+BG73+BH73)/60+SUM(AL73+BZ73)/50</f>
+        <f>SUM(O73+P73+Q73+BL73+BM73+CB73+CC73)/65+SUM(X73+Y73)/44+SUM(AJ73+AK73+AM73+AN73+AO73+AP73+AQ73+BR73+BS73+BT73+BU73+BV73+CH73+CI73+CJ73+CK73)/45+SUM(AX73+AY73+AZ73+BA73+BF73+BG73+BH73)/60+SUM(AL73+BZ73)/50</f>
         <v/>
       </c>
       <c r="CQ73" s="38">
-        <f>SUM(R73+S73+BN73+CD73+CE73)/65+SUM(AB73)/36+SUM(AR73+AS73+BW73+BX73+CK73+CN73)/40+SUM(BB73+BC73+BI73+BJ73)/60</f>
+        <f>SUM(R73+S73+BN73+CD73+CE73)/65+SUM(AB73)/36+SUM(AR73+AS73+BW73+BX73+CL73+CM73)/40+SUM(BB73+BC73+BI73+BJ73)/60</f>
         <v/>
       </c>
       <c r="CR73" s="38">
@@ -14513,7 +14513,7 @@
         <v/>
       </c>
       <c r="CT73" s="38">
-        <f>SUM(BY73+CL73)/45</f>
+        <f>SUM(BY73+CN73)/45</f>
         <v/>
       </c>
       <c r="CU73" s="83">
@@ -14656,11 +14656,11 @@
         <v/>
       </c>
       <c r="CP74" s="38">
-        <f>SUM(O74+P74+Q74+BL74+BM74+CB74+CC74)/65+SUM(X74+Y74)/44+SUM(AJ74+AK74+AM74+AN74+AO74+AP74+AQ74+BR74+BS74+BT74+BU74+BV74+CH74+CI74+CJ74+CM74)/45+SUM(AX74+AY74+AZ74+BA74+BF74+BG74+BH74)/60+SUM(AL74+BZ74)/50</f>
+        <f>SUM(O74+P74+Q74+BL74+BM74+CB74+CC74)/65+SUM(X74+Y74)/44+SUM(AJ74+AK74+AM74+AN74+AO74+AP74+AQ74+BR74+BS74+BT74+BU74+BV74+CH74+CI74+CJ74+CK74)/45+SUM(AX74+AY74+AZ74+BA74+BF74+BG74+BH74)/60+SUM(AL74+BZ74)/50</f>
         <v/>
       </c>
       <c r="CQ74" s="38">
-        <f>SUM(R74+S74+BN74+CD74+CE74)/65+SUM(AB74)/36+SUM(AR74+AS74+BW74+BX74+CK74+CN74)/40+SUM(BB74+BC74+BI74+BJ74)/60</f>
+        <f>SUM(R74+S74+BN74+CD74+CE74)/65+SUM(AB74)/36+SUM(AR74+AS74+BW74+BX74+CL74+CM74)/40+SUM(BB74+BC74+BI74+BJ74)/60</f>
         <v/>
       </c>
       <c r="CR74" s="38">
@@ -14672,7 +14672,7 @@
         <v/>
       </c>
       <c r="CT74" s="38">
-        <f>SUM(BY74+CL74)/45</f>
+        <f>SUM(BY74+CN74)/45</f>
         <v/>
       </c>
       <c r="CU74" s="83">
@@ -14815,11 +14815,11 @@
         <v/>
       </c>
       <c r="CP75" s="38">
-        <f>SUM(O75+P75+Q75+BL75+BM75+CB75+CC75)/65+SUM(X75+Y75)/44+SUM(AJ75+AK75+AM75+AN75+AO75+AP75+AQ75+BR75+BS75+BT75+BU75+BV75+CH75+CI75+CJ75+CM75)/45+SUM(AX75+AY75+AZ75+BA75+BF75+BG75+BH75)/60+SUM(AL75+BZ75)/50</f>
+        <f>SUM(O75+P75+Q75+BL75+BM75+CB75+CC75)/65+SUM(X75+Y75)/44+SUM(AJ75+AK75+AM75+AN75+AO75+AP75+AQ75+BR75+BS75+BT75+BU75+BV75+CH75+CI75+CJ75+CK75)/45+SUM(AX75+AY75+AZ75+BA75+BF75+BG75+BH75)/60+SUM(AL75+BZ75)/50</f>
         <v/>
       </c>
       <c r="CQ75" s="38">
-        <f>SUM(R75+S75+BN75+CD75+CE75)/65+SUM(AB75)/36+SUM(AR75+AS75+BW75+BX75+CK75+CN75)/40+SUM(BB75+BC75+BI75+BJ75)/60</f>
+        <f>SUM(R75+S75+BN75+CD75+CE75)/65+SUM(AB75)/36+SUM(AR75+AS75+BW75+BX75+CL75+CM75)/40+SUM(BB75+BC75+BI75+BJ75)/60</f>
         <v/>
       </c>
       <c r="CR75" s="38">
@@ -14831,7 +14831,7 @@
         <v/>
       </c>
       <c r="CT75" s="38">
-        <f>SUM(BY75+CL75)/45</f>
+        <f>SUM(BY75+CN75)/45</f>
         <v/>
       </c>
       <c r="CU75" s="83">
@@ -14974,11 +14974,11 @@
         <v/>
       </c>
       <c r="CP76" s="38">
-        <f>SUM(O76+P76+Q76+BL76+BM76+CB76+CC76)/65+SUM(X76+Y76)/44+SUM(AJ76+AK76+AM76+AN76+AO76+AP76+AQ76+BR76+BS76+BT76+BU76+BV76+CH76+CI76+CJ76+CM76)/45+SUM(AX76+AY76+AZ76+BA76+BF76+BG76+BH76)/60+SUM(AL76+BZ76)/50</f>
+        <f>SUM(O76+P76+Q76+BL76+BM76+CB76+CC76)/65+SUM(X76+Y76)/44+SUM(AJ76+AK76+AM76+AN76+AO76+AP76+AQ76+BR76+BS76+BT76+BU76+BV76+CH76+CI76+CJ76+CK76)/45+SUM(AX76+AY76+AZ76+BA76+BF76+BG76+BH76)/60+SUM(AL76+BZ76)/50</f>
         <v/>
       </c>
       <c r="CQ76" s="38">
-        <f>SUM(R76+S76+BN76+CD76+CE76)/65+SUM(AB76)/36+SUM(AR76+AS76+BW76+BX76+CK76+CN76)/40+SUM(BB76+BC76+BI76+BJ76)/60</f>
+        <f>SUM(R76+S76+BN76+CD76+CE76)/65+SUM(AB76)/36+SUM(AR76+AS76+BW76+BX76+CL76+CM76)/40+SUM(BB76+BC76+BI76+BJ76)/60</f>
         <v/>
       </c>
       <c r="CR76" s="38">
@@ -14990,7 +14990,7 @@
         <v/>
       </c>
       <c r="CT76" s="38">
-        <f>SUM(BY76+CL76)/45</f>
+        <f>SUM(BY76+CN76)/45</f>
         <v/>
       </c>
       <c r="CU76" s="83">
@@ -15133,11 +15133,11 @@
         <v/>
       </c>
       <c r="CP77" s="38">
-        <f>SUM(O77+P77+Q77+BL77+BM77+CB77+CC77)/65+SUM(X77+Y77)/44+SUM(AJ77+AK77+AM77+AN77+AO77+AP77+AQ77+BR77+BS77+BT77+BU77+BV77+CH77+CI77+CJ77+CM77)/45+SUM(AX77+AY77+AZ77+BA77+BF77+BG77+BH77)/60+SUM(AL77+BZ77)/50</f>
+        <f>SUM(O77+P77+Q77+BL77+BM77+CB77+CC77)/65+SUM(X77+Y77)/44+SUM(AJ77+AK77+AM77+AN77+AO77+AP77+AQ77+BR77+BS77+BT77+BU77+BV77+CH77+CI77+CJ77+CK77)/45+SUM(AX77+AY77+AZ77+BA77+BF77+BG77+BH77)/60+SUM(AL77+BZ77)/50</f>
         <v/>
       </c>
       <c r="CQ77" s="38">
-        <f>SUM(R77+S77+BN77+CD77+CE77)/65+SUM(AB77)/36+SUM(AR77+AS77+BW77+BX77+CK77+CN77)/40+SUM(BB77+BC77+BI77+BJ77)/60</f>
+        <f>SUM(R77+S77+BN77+CD77+CE77)/65+SUM(AB77)/36+SUM(AR77+AS77+BW77+BX77+CL77+CM77)/40+SUM(BB77+BC77+BI77+BJ77)/60</f>
         <v/>
       </c>
       <c r="CR77" s="38">
@@ -15149,7 +15149,7 @@
         <v/>
       </c>
       <c r="CT77" s="38">
-        <f>SUM(BY77+CL77)/45</f>
+        <f>SUM(BY77+CN77)/45</f>
         <v/>
       </c>
       <c r="CU77" s="83">
@@ -15292,11 +15292,11 @@
         <v/>
       </c>
       <c r="CP78" s="38">
-        <f>SUM(O78+P78+Q78+BL78+BM78+CB78+CC78)/65+SUM(X78+Y78)/44+SUM(AJ78+AK78+AM78+AN78+AO78+AP78+AQ78+BR78+BS78+BT78+BU78+BV78+CH78+CI78+CJ78+CM78)/45+SUM(AX78+AY78+AZ78+BA78+BF78+BG78+BH78)/60+SUM(AL78+BZ78)/50</f>
+        <f>SUM(O78+P78+Q78+BL78+BM78+CB78+CC78)/65+SUM(X78+Y78)/44+SUM(AJ78+AK78+AM78+AN78+AO78+AP78+AQ78+BR78+BS78+BT78+BU78+BV78+CH78+CI78+CJ78+CK78)/45+SUM(AX78+AY78+AZ78+BA78+BF78+BG78+BH78)/60+SUM(AL78+BZ78)/50</f>
         <v/>
       </c>
       <c r="CQ78" s="38">
-        <f>SUM(R78+S78+BN78+CD78+CE78)/65+SUM(AB78)/36+SUM(AR78+AS78+BW78+BX78+CK78+CN78)/40+SUM(BB78+BC78+BI78+BJ78)/60</f>
+        <f>SUM(R78+S78+BN78+CD78+CE78)/65+SUM(AB78)/36+SUM(AR78+AS78+BW78+BX78+CL78+CM78)/40+SUM(BB78+BC78+BI78+BJ78)/60</f>
         <v/>
       </c>
       <c r="CR78" s="38">
@@ -15308,7 +15308,7 @@
         <v/>
       </c>
       <c r="CT78" s="38">
-        <f>SUM(BY78+CL78)/45</f>
+        <f>SUM(BY78+CN78)/45</f>
         <v/>
       </c>
       <c r="CU78" s="83">
@@ -15451,11 +15451,11 @@
         <v/>
       </c>
       <c r="CP79" s="38">
-        <f>SUM(O79+P79+Q79+BL79+BM79+CB79+CC79)/65+SUM(X79+Y79)/44+SUM(AJ79+AK79+AM79+AN79+AO79+AP79+AQ79+BR79+BS79+BT79+BU79+BV79+CH79+CI79+CJ79+CM79)/45+SUM(AX79+AY79+AZ79+BA79+BF79+BG79+BH79)/60+SUM(AL79+BZ79)/50</f>
+        <f>SUM(O79+P79+Q79+BL79+BM79+CB79+CC79)/65+SUM(X79+Y79)/44+SUM(AJ79+AK79+AM79+AN79+AO79+AP79+AQ79+BR79+BS79+BT79+BU79+BV79+CH79+CI79+CJ79+CK79)/45+SUM(AX79+AY79+AZ79+BA79+BF79+BG79+BH79)/60+SUM(AL79+BZ79)/50</f>
         <v/>
       </c>
       <c r="CQ79" s="38">
-        <f>SUM(R79+S79+BN79+CD79+CE79)/65+SUM(AB79)/36+SUM(AR79+AS79+BW79+BX79+CK79+CN79)/40+SUM(BB79+BC79+BI79+BJ79)/60</f>
+        <f>SUM(R79+S79+BN79+CD79+CE79)/65+SUM(AB79)/36+SUM(AR79+AS79+BW79+BX79+CL79+CM79)/40+SUM(BB79+BC79+BI79+BJ79)/60</f>
         <v/>
       </c>
       <c r="CR79" s="38">
@@ -15467,7 +15467,7 @@
         <v/>
       </c>
       <c r="CT79" s="38">
-        <f>SUM(BY79+CL79)/45</f>
+        <f>SUM(BY79+CN79)/45</f>
         <v/>
       </c>
       <c r="CU79" s="83">
@@ -15610,11 +15610,11 @@
         <v/>
       </c>
       <c r="CP80" s="38">
-        <f>SUM(O80+P80+Q80+BL80+BM80+CB80+CC80)/65+SUM(X80+Y80)/44+SUM(AJ80+AK80+AM80+AN80+AO80+AP80+AQ80+BR80+BS80+BT80+BU80+BV80+CH80+CI80+CJ80+CM80)/45+SUM(AX80+AY80+AZ80+BA80+BF80+BG80+BH80)/60+SUM(AL80+BZ80)/50</f>
+        <f>SUM(O80+P80+Q80+BL80+BM80+CB80+CC80)/65+SUM(X80+Y80)/44+SUM(AJ80+AK80+AM80+AN80+AO80+AP80+AQ80+BR80+BS80+BT80+BU80+BV80+CH80+CI80+CJ80+CK80)/45+SUM(AX80+AY80+AZ80+BA80+BF80+BG80+BH80)/60+SUM(AL80+BZ80)/50</f>
         <v/>
       </c>
       <c r="CQ80" s="38">
-        <f>SUM(R80+S80+BN80+CD80+CE80)/65+SUM(AB80)/36+SUM(AR80+AS80+BW80+BX80+CK80+CN80)/40+SUM(BB80+BC80+BI80+BJ80)/60</f>
+        <f>SUM(R80+S80+BN80+CD80+CE80)/65+SUM(AB80)/36+SUM(AR80+AS80+BW80+BX80+CL80+CM80)/40+SUM(BB80+BC80+BI80+BJ80)/60</f>
         <v/>
       </c>
       <c r="CR80" s="38">
@@ -15626,7 +15626,7 @@
         <v/>
       </c>
       <c r="CT80" s="38">
-        <f>SUM(BY80+CL80)/45</f>
+        <f>SUM(BY80+CN80)/45</f>
         <v/>
       </c>
       <c r="CU80" s="83">
@@ -15769,11 +15769,11 @@
         <v/>
       </c>
       <c r="CP81" s="38">
-        <f>SUM(O81+P81+Q81+BL81+BM81+CB81+CC81)/65+SUM(X81+Y81)/44+SUM(AJ81+AK81+AM81+AN81+AO81+AP81+AQ81+BR81+BS81+BT81+BU81+BV81+CH81+CI81+CJ81+CM81)/45+SUM(AX81+AY81+AZ81+BA81+BF81+BG81+BH81)/60+SUM(AL81+BZ81)/50</f>
+        <f>SUM(O81+P81+Q81+BL81+BM81+CB81+CC81)/65+SUM(X81+Y81)/44+SUM(AJ81+AK81+AM81+AN81+AO81+AP81+AQ81+BR81+BS81+BT81+BU81+BV81+CH81+CI81+CJ81+CK81)/45+SUM(AX81+AY81+AZ81+BA81+BF81+BG81+BH81)/60+SUM(AL81+BZ81)/50</f>
         <v/>
       </c>
       <c r="CQ81" s="38">
-        <f>SUM(R81+S81+BN81+CD81+CE81)/65+SUM(AB81)/36+SUM(AR81+AS81+BW81+BX81+CK81+CN81)/40+SUM(BB81+BC81+BI81+BJ81)/60</f>
+        <f>SUM(R81+S81+BN81+CD81+CE81)/65+SUM(AB81)/36+SUM(AR81+AS81+BW81+BX81+CL81+CM81)/40+SUM(BB81+BC81+BI81+BJ81)/60</f>
         <v/>
       </c>
       <c r="CR81" s="38">
@@ -15785,7 +15785,7 @@
         <v/>
       </c>
       <c r="CT81" s="38">
-        <f>SUM(BY81+CL81)/45</f>
+        <f>SUM(BY81+CN81)/45</f>
         <v/>
       </c>
       <c r="CU81" s="83">
@@ -15928,11 +15928,11 @@
         <v/>
       </c>
       <c r="CP82" s="38">
-        <f>SUM(O82+P82+Q82+BL82+BM82+CB82+CC82)/65+SUM(X82+Y82)/44+SUM(AJ82+AK82+AM82+AN82+AO82+AP82+AQ82+BR82+BS82+BT82+BU82+BV82+CH82+CI82+CJ82+CM82)/45+SUM(AX82+AY82+AZ82+BA82+BF82+BG82+BH82)/60+SUM(AL82+BZ82)/50</f>
+        <f>SUM(O82+P82+Q82+BL82+BM82+CB82+CC82)/65+SUM(X82+Y82)/44+SUM(AJ82+AK82+AM82+AN82+AO82+AP82+AQ82+BR82+BS82+BT82+BU82+BV82+CH82+CI82+CJ82+CK82)/45+SUM(AX82+AY82+AZ82+BA82+BF82+BG82+BH82)/60+SUM(AL82+BZ82)/50</f>
         <v/>
       </c>
       <c r="CQ82" s="38">
-        <f>SUM(R82+S82+BN82+CD82+CE82)/65+SUM(AB82)/36+SUM(AR82+AS82+BW82+BX82+CK82+CN82)/40+SUM(BB82+BC82+BI82+BJ82)/60</f>
+        <f>SUM(R82+S82+BN82+CD82+CE82)/65+SUM(AB82)/36+SUM(AR82+AS82+BW82+BX82+CL82+CM82)/40+SUM(BB82+BC82+BI82+BJ82)/60</f>
         <v/>
       </c>
       <c r="CR82" s="38">
@@ -15944,7 +15944,7 @@
         <v/>
       </c>
       <c r="CT82" s="38">
-        <f>SUM(BY82+CL82)/45</f>
+        <f>SUM(BY82+CN82)/45</f>
         <v/>
       </c>
       <c r="CU82" s="83">
@@ -16087,11 +16087,11 @@
         <v/>
       </c>
       <c r="CP83" s="38">
-        <f>SUM(O83+P83+Q83+BL83+BM83+CB83+CC83)/65+SUM(X83+Y83)/44+SUM(AJ83+AK83+AM83+AN83+AO83+AP83+AQ83+BR83+BS83+BT83+BU83+BV83+CH83+CI83+CJ83+CM83)/45+SUM(AX83+AY83+AZ83+BA83+BF83+BG83+BH83)/60+SUM(AL83+BZ83)/50</f>
+        <f>SUM(O83+P83+Q83+BL83+BM83+CB83+CC83)/65+SUM(X83+Y83)/44+SUM(AJ83+AK83+AM83+AN83+AO83+AP83+AQ83+BR83+BS83+BT83+BU83+BV83+CH83+CI83+CJ83+CK83)/45+SUM(AX83+AY83+AZ83+BA83+BF83+BG83+BH83)/60+SUM(AL83+BZ83)/50</f>
         <v/>
       </c>
       <c r="CQ83" s="38">
-        <f>SUM(R83+S83+BN83+CD83+CE83)/65+SUM(AB83)/36+SUM(AR83+AS83+BW83+BX83+CK83+CN83)/40+SUM(BB83+BC83+BI83+BJ83)/60</f>
+        <f>SUM(R83+S83+BN83+CD83+CE83)/65+SUM(AB83)/36+SUM(AR83+AS83+BW83+BX83+CL83+CM83)/40+SUM(BB83+BC83+BI83+BJ83)/60</f>
         <v/>
       </c>
       <c r="CR83" s="38">
@@ -16103,7 +16103,7 @@
         <v/>
       </c>
       <c r="CT83" s="38">
-        <f>SUM(BY83+CL83)/45</f>
+        <f>SUM(BY83+CN83)/45</f>
         <v/>
       </c>
       <c r="CU83" s="83">
@@ -16246,11 +16246,11 @@
         <v/>
       </c>
       <c r="CP84" s="38">
-        <f>SUM(O84+P84+Q84+BL84+BM84+CB84+CC84)/65+SUM(X84+Y84)/44+SUM(AJ84+AK84+AM84+AN84+AO84+AP84+AQ84+BR84+BS84+BT84+BU84+BV84+CH84+CI84+CJ84+CM84)/45+SUM(AX84+AY84+AZ84+BA84+BF84+BG84+BH84)/60+SUM(AL84+BZ84)/50</f>
+        <f>SUM(O84+P84+Q84+BL84+BM84+CB84+CC84)/65+SUM(X84+Y84)/44+SUM(AJ84+AK84+AM84+AN84+AO84+AP84+AQ84+BR84+BS84+BT84+BU84+BV84+CH84+CI84+CJ84+CK84)/45+SUM(AX84+AY84+AZ84+BA84+BF84+BG84+BH84)/60+SUM(AL84+BZ84)/50</f>
         <v/>
       </c>
       <c r="CQ84" s="38">
-        <f>SUM(R84+S84+BN84+CD84+CE84)/65+SUM(AB84)/36+SUM(AR84+AS84+BW84+BX84+CK84+CN84)/40+SUM(BB84+BC84+BI84+BJ84)/60</f>
+        <f>SUM(R84+S84+BN84+CD84+CE84)/65+SUM(AB84)/36+SUM(AR84+AS84+BW84+BX84+CL84+CM84)/40+SUM(BB84+BC84+BI84+BJ84)/60</f>
         <v/>
       </c>
       <c r="CR84" s="38">
@@ -16262,7 +16262,7 @@
         <v/>
       </c>
       <c r="CT84" s="38">
-        <f>SUM(BY84+CL84)/45</f>
+        <f>SUM(BY84+CN84)/45</f>
         <v/>
       </c>
       <c r="CU84" s="83">
@@ -16405,11 +16405,11 @@
         <v/>
       </c>
       <c r="CP85" s="38">
-        <f>SUM(O85+P85+Q85+BL85+BM85+CB85+CC85)/65+SUM(X85+Y85)/44+SUM(AJ85+AK85+AM85+AN85+AO85+AP85+AQ85+BR85+BS85+BT85+BU85+BV85+CH85+CI85+CJ85+CM85)/45+SUM(AX85+AY85+AZ85+BA85+BF85+BG85+BH85)/60+SUM(AL85+BZ85)/50</f>
+        <f>SUM(O85+P85+Q85+BL85+BM85+CB85+CC85)/65+SUM(X85+Y85)/44+SUM(AJ85+AK85+AM85+AN85+AO85+AP85+AQ85+BR85+BS85+BT85+BU85+BV85+CH85+CI85+CJ85+CK85)/45+SUM(AX85+AY85+AZ85+BA85+BF85+BG85+BH85)/60+SUM(AL85+BZ85)/50</f>
         <v/>
       </c>
       <c r="CQ85" s="38">
-        <f>SUM(R85+S85+BN85+CD85+CE85)/65+SUM(AB85)/36+SUM(AR85+AS85+BW85+BX85+CK85+CN85)/40+SUM(BB85+BC85+BI85+BJ85)/60</f>
+        <f>SUM(R85+S85+BN85+CD85+CE85)/65+SUM(AB85)/36+SUM(AR85+AS85+BW85+BX85+CL85+CM85)/40+SUM(BB85+BC85+BI85+BJ85)/60</f>
         <v/>
       </c>
       <c r="CR85" s="38">
@@ -16421,7 +16421,7 @@
         <v/>
       </c>
       <c r="CT85" s="38">
-        <f>SUM(BY85+CL85)/45</f>
+        <f>SUM(BY85+CN85)/45</f>
         <v/>
       </c>
       <c r="CU85" s="83">
@@ -16564,11 +16564,11 @@
         <v/>
       </c>
       <c r="CP86" s="38">
-        <f>SUM(O86+P86+Q86+BL86+BM86+CB86+CC86)/65+SUM(X86+Y86)/44+SUM(AJ86+AK86+AM86+AN86+AO86+AP86+AQ86+BR86+BS86+BT86+BU86+BV86+CH86+CI86+CJ86+CM86)/45+SUM(AX86+AY86+AZ86+BA86+BF86+BG86+BH86)/60+SUM(AL86+BZ86)/50</f>
+        <f>SUM(O86+P86+Q86+BL86+BM86+CB86+CC86)/65+SUM(X86+Y86)/44+SUM(AJ86+AK86+AM86+AN86+AO86+AP86+AQ86+BR86+BS86+BT86+BU86+BV86+CH86+CI86+CJ86+CK86)/45+SUM(AX86+AY86+AZ86+BA86+BF86+BG86+BH86)/60+SUM(AL86+BZ86)/50</f>
         <v/>
       </c>
       <c r="CQ86" s="38">
-        <f>SUM(R86+S86+BN86+CD86+CE86)/65+SUM(AB86)/36+SUM(AR86+AS86+BW86+BX86+CK86+CN86)/40+SUM(BB86+BC86+BI86+BJ86)/60</f>
+        <f>SUM(R86+S86+BN86+CD86+CE86)/65+SUM(AB86)/36+SUM(AR86+AS86+BW86+BX86+CL86+CM86)/40+SUM(BB86+BC86+BI86+BJ86)/60</f>
         <v/>
       </c>
       <c r="CR86" s="38">
@@ -16580,7 +16580,7 @@
         <v/>
       </c>
       <c r="CT86" s="38">
-        <f>SUM(BY86+CL86)/45</f>
+        <f>SUM(BY86+CN86)/45</f>
         <v/>
       </c>
       <c r="CU86" s="83">
@@ -16723,11 +16723,11 @@
         <v/>
       </c>
       <c r="CP87" s="38">
-        <f>SUM(O87+P87+Q87+BL87+BM87+CB87+CC87)/65+SUM(X87+Y87)/44+SUM(AJ87+AK87+AM87+AN87+AO87+AP87+AQ87+BR87+BS87+BT87+BU87+BV87+CH87+CI87+CJ87+CM87)/45+SUM(AX87+AY87+AZ87+BA87+BF87+BG87+BH87)/60+SUM(AL87+BZ87)/50</f>
+        <f>SUM(O87+P87+Q87+BL87+BM87+CB87+CC87)/65+SUM(X87+Y87)/44+SUM(AJ87+AK87+AM87+AN87+AO87+AP87+AQ87+BR87+BS87+BT87+BU87+BV87+CH87+CI87+CJ87+CK87)/45+SUM(AX87+AY87+AZ87+BA87+BF87+BG87+BH87)/60+SUM(AL87+BZ87)/50</f>
         <v/>
       </c>
       <c r="CQ87" s="38">
-        <f>SUM(R87+S87+BN87+CD87+CE87)/65+SUM(AB87)/36+SUM(AR87+AS87+BW87+BX87+CK87+CN87)/40+SUM(BB87+BC87+BI87+BJ87)/60</f>
+        <f>SUM(R87+S87+BN87+CD87+CE87)/65+SUM(AB87)/36+SUM(AR87+AS87+BW87+BX87+CL87+CM87)/40+SUM(BB87+BC87+BI87+BJ87)/60</f>
         <v/>
       </c>
       <c r="CR87" s="38">
@@ -16739,7 +16739,7 @@
         <v/>
       </c>
       <c r="CT87" s="38">
-        <f>SUM(BY87+CL87)/45</f>
+        <f>SUM(BY87+CN87)/45</f>
         <v/>
       </c>
       <c r="CU87" s="83">
@@ -16882,11 +16882,11 @@
         <v/>
       </c>
       <c r="CP88" s="38">
-        <f>SUM(O88+P88+Q88+BL88+BM88+CB88+CC88)/65+SUM(X88+Y88)/44+SUM(AJ88+AK88+AM88+AN88+AO88+AP88+AQ88+BR88+BS88+BT88+BU88+BV88+CH88+CI88+CJ88+CM88)/45+SUM(AX88+AY88+AZ88+BA88+BF88+BG88+BH88)/60+SUM(AL88+BZ88)/50</f>
+        <f>SUM(O88+P88+Q88+BL88+BM88+CB88+CC88)/65+SUM(X88+Y88)/44+SUM(AJ88+AK88+AM88+AN88+AO88+AP88+AQ88+BR88+BS88+BT88+BU88+BV88+CH88+CI88+CJ88+CK88)/45+SUM(AX88+AY88+AZ88+BA88+BF88+BG88+BH88)/60+SUM(AL88+BZ88)/50</f>
         <v/>
       </c>
       <c r="CQ88" s="38">
-        <f>SUM(R88+S88+BN88+CD88+CE88)/65+SUM(AB88)/36+SUM(AR88+AS88+BW88+BX88+CK88+CN88)/40+SUM(BB88+BC88+BI88+BJ88)/60</f>
+        <f>SUM(R88+S88+BN88+CD88+CE88)/65+SUM(AB88)/36+SUM(AR88+AS88+BW88+BX88+CL88+CM88)/40+SUM(BB88+BC88+BI88+BJ88)/60</f>
         <v/>
       </c>
       <c r="CR88" s="38">
@@ -16898,7 +16898,7 @@
         <v/>
       </c>
       <c r="CT88" s="38">
-        <f>SUM(BY88+CL88)/45</f>
+        <f>SUM(BY88+CN88)/45</f>
         <v/>
       </c>
       <c r="CU88" s="83">
@@ -17041,11 +17041,11 @@
         <v/>
       </c>
       <c r="CP89" s="38">
-        <f>SUM(O89+P89+Q89+BL89+BM89+CB89+CC89)/65+SUM(X89+Y89)/44+SUM(AJ89+AK89+AM89+AN89+AO89+AP89+AQ89+BR89+BS89+BT89+BU89+BV89+CH89+CI89+CJ89+CM89)/45+SUM(AX89+AY89+AZ89+BA89+BF89+BG89+BH89)/60+SUM(AL89+BZ89)/50</f>
+        <f>SUM(O89+P89+Q89+BL89+BM89+CB89+CC89)/65+SUM(X89+Y89)/44+SUM(AJ89+AK89+AM89+AN89+AO89+AP89+AQ89+BR89+BS89+BT89+BU89+BV89+CH89+CI89+CJ89+CK89)/45+SUM(AX89+AY89+AZ89+BA89+BF89+BG89+BH89)/60+SUM(AL89+BZ89)/50</f>
         <v/>
       </c>
       <c r="CQ89" s="38">
-        <f>SUM(R89+S89+BN89+CD89+CE89)/65+SUM(AB89)/36+SUM(AR89+AS89+BW89+BX89+CK89+CN89)/40+SUM(BB89+BC89+BI89+BJ89)/60</f>
+        <f>SUM(R89+S89+BN89+CD89+CE89)/65+SUM(AB89)/36+SUM(AR89+AS89+BW89+BX89+CL89+CM89)/40+SUM(BB89+BC89+BI89+BJ89)/60</f>
         <v/>
       </c>
       <c r="CR89" s="38">
@@ -17057,7 +17057,7 @@
         <v/>
       </c>
       <c r="CT89" s="38">
-        <f>SUM(BY89+CL89)/45</f>
+        <f>SUM(BY89+CN89)/45</f>
         <v/>
       </c>
       <c r="CU89" s="83">
@@ -17200,11 +17200,11 @@
         <v/>
       </c>
       <c r="CP90" s="38">
-        <f>SUM(O90+P90+Q90+BL90+BM90+CB90+CC90)/65+SUM(X90+Y90)/44+SUM(AJ90+AK90+AM90+AN90+AO90+AP90+AQ90+BR90+BS90+BT90+BU90+BV90+CH90+CI90+CJ90+CM90)/45+SUM(AX90+AY90+AZ90+BA90+BF90+BG90+BH90)/60+SUM(AL90+BZ90)/50</f>
+        <f>SUM(O90+P90+Q90+BL90+BM90+CB90+CC90)/65+SUM(X90+Y90)/44+SUM(AJ90+AK90+AM90+AN90+AO90+AP90+AQ90+BR90+BS90+BT90+BU90+BV90+CH90+CI90+CJ90+CK90)/45+SUM(AX90+AY90+AZ90+BA90+BF90+BG90+BH90)/60+SUM(AL90+BZ90)/50</f>
         <v/>
       </c>
       <c r="CQ90" s="38">
-        <f>SUM(R90+S90+BN90+CD90+CE90)/65+SUM(AB90)/36+SUM(AR90+AS90+BW90+BX90+CK90+CN90)/40+SUM(BB90+BC90+BI90+BJ90)/60</f>
+        <f>SUM(R90+S90+BN90+CD90+CE90)/65+SUM(AB90)/36+SUM(AR90+AS90+BW90+BX90+CL90+CM90)/40+SUM(BB90+BC90+BI90+BJ90)/60</f>
         <v/>
       </c>
       <c r="CR90" s="38">
@@ -17216,7 +17216,7 @@
         <v/>
       </c>
       <c r="CT90" s="38">
-        <f>SUM(BY90+CL90)/45</f>
+        <f>SUM(BY90+CN90)/45</f>
         <v/>
       </c>
       <c r="CU90" s="83">
@@ -17359,11 +17359,11 @@
         <v/>
       </c>
       <c r="CP91" s="38">
-        <f>SUM(O91+P91+Q91+BL91+BM91+CB91+CC91)/65+SUM(X91+Y91)/44+SUM(AJ91+AK91+AM91+AN91+AO91+AP91+AQ91+BR91+BS91+BT91+BU91+BV91+CH91+CI91+CJ91+CM91)/45+SUM(AX91+AY91+AZ91+BA91+BF91+BG91+BH91)/60+SUM(AL91+BZ91)/50</f>
+        <f>SUM(O91+P91+Q91+BL91+BM91+CB91+CC91)/65+SUM(X91+Y91)/44+SUM(AJ91+AK91+AM91+AN91+AO91+AP91+AQ91+BR91+BS91+BT91+BU91+BV91+CH91+CI91+CJ91+CK91)/45+SUM(AX91+AY91+AZ91+BA91+BF91+BG91+BH91)/60+SUM(AL91+BZ91)/50</f>
         <v/>
       </c>
       <c r="CQ91" s="38">
-        <f>SUM(R91+S91+BN91+CD91+CE91)/65+SUM(AB91)/36+SUM(AR91+AS91+BW91+BX91+CK91+CN91)/40+SUM(BB91+BC91+BI91+BJ91)/60</f>
+        <f>SUM(R91+S91+BN91+CD91+CE91)/65+SUM(AB91)/36+SUM(AR91+AS91+BW91+BX91+CL91+CM91)/40+SUM(BB91+BC91+BI91+BJ91)/60</f>
         <v/>
       </c>
       <c r="CR91" s="38">
@@ -17375,7 +17375,7 @@
         <v/>
       </c>
       <c r="CT91" s="38">
-        <f>SUM(BY91+CL91)/45</f>
+        <f>SUM(BY91+CN91)/45</f>
         <v/>
       </c>
       <c r="CU91" s="83">
@@ -17518,11 +17518,11 @@
         <v/>
       </c>
       <c r="CP92" s="38">
-        <f>SUM(O92+P92+Q92+BL92+BM92+CB92+CC92)/65+SUM(X92+Y92)/44+SUM(AJ92+AK92+AM92+AN92+AO92+AP92+AQ92+BR92+BS92+BT92+BU92+BV92+CH92+CI92+CJ92+CM92)/45+SUM(AX92+AY92+AZ92+BA92+BF92+BG92+BH92)/60+SUM(AL92+BZ92)/50</f>
+        <f>SUM(O92+P92+Q92+BL92+BM92+CB92+CC92)/65+SUM(X92+Y92)/44+SUM(AJ92+AK92+AM92+AN92+AO92+AP92+AQ92+BR92+BS92+BT92+BU92+BV92+CH92+CI92+CJ92+CK92)/45+SUM(AX92+AY92+AZ92+BA92+BF92+BG92+BH92)/60+SUM(AL92+BZ92)/50</f>
         <v/>
       </c>
       <c r="CQ92" s="38">
-        <f>SUM(R92+S92+BN92+CD92+CE92)/65+SUM(AB92)/36+SUM(AR92+AS92+BW92+BX92+CK92+CN92)/40+SUM(BB92+BC92+BI92+BJ92)/60</f>
+        <f>SUM(R92+S92+BN92+CD92+CE92)/65+SUM(AB92)/36+SUM(AR92+AS92+BW92+BX92+CL92+CM92)/40+SUM(BB92+BC92+BI92+BJ92)/60</f>
         <v/>
       </c>
       <c r="CR92" s="38">
@@ -17534,7 +17534,7 @@
         <v/>
       </c>
       <c r="CT92" s="38">
-        <f>SUM(BY92+CL92)/45</f>
+        <f>SUM(BY92+CN92)/45</f>
         <v/>
       </c>
       <c r="CU92" s="83">
@@ -17677,11 +17677,11 @@
         <v/>
       </c>
       <c r="CP93" s="38">
-        <f>SUM(O93+P93+Q93+BL93+BM93+CB93+CC93)/65+SUM(X93+Y93)/44+SUM(AJ93+AK93+AM93+AN93+AO93+AP93+AQ93+BR93+BS93+BT93+BU93+BV93+CH93+CI93+CJ93+CM93)/45+SUM(AX93+AY93+AZ93+BA93+BF93+BG93+BH93)/60+SUM(AL93+BZ93)/50</f>
+        <f>SUM(O93+P93+Q93+BL93+BM93+CB93+CC93)/65+SUM(X93+Y93)/44+SUM(AJ93+AK93+AM93+AN93+AO93+AP93+AQ93+BR93+BS93+BT93+BU93+BV93+CH93+CI93+CJ93+CK93)/45+SUM(AX93+AY93+AZ93+BA93+BF93+BG93+BH93)/60+SUM(AL93+BZ93)/50</f>
         <v/>
       </c>
       <c r="CQ93" s="38">
-        <f>SUM(R93+S93+BN93+CD93+CE93)/65+SUM(AB93)/36+SUM(AR93+AS93+BW93+BX93+CK93+CN93)/40+SUM(BB93+BC93+BI93+BJ93)/60</f>
+        <f>SUM(R93+S93+BN93+CD93+CE93)/65+SUM(AB93)/36+SUM(AR93+AS93+BW93+BX93+CL93+CM93)/40+SUM(BB93+BC93+BI93+BJ93)/60</f>
         <v/>
       </c>
       <c r="CR93" s="38">
@@ -17693,7 +17693,7 @@
         <v/>
       </c>
       <c r="CT93" s="38">
-        <f>SUM(BY93+CL93)/45</f>
+        <f>SUM(BY93+CN93)/45</f>
         <v/>
       </c>
       <c r="CU93" s="83">
@@ -17836,11 +17836,11 @@
         <v/>
       </c>
       <c r="CP94" s="38">
-        <f>SUM(O94+P94+Q94+BL94+BM94+CB94+CC94)/65+SUM(X94+Y94)/44+SUM(AJ94+AK94+AM94+AN94+AO94+AP94+AQ94+BR94+BS94+BT94+BU94+BV94+CH94+CI94+CJ94+CM94)/45+SUM(AX94+AY94+AZ94+BA94+BF94+BG94+BH94)/60+SUM(AL94+BZ94)/50</f>
+        <f>SUM(O94+P94+Q94+BL94+BM94+CB94+CC94)/65+SUM(X94+Y94)/44+SUM(AJ94+AK94+AM94+AN94+AO94+AP94+AQ94+BR94+BS94+BT94+BU94+BV94+CH94+CI94+CJ94+CK94)/45+SUM(AX94+AY94+AZ94+BA94+BF94+BG94+BH94)/60+SUM(AL94+BZ94)/50</f>
         <v/>
       </c>
       <c r="CQ94" s="38">
-        <f>SUM(R94+S94+BN94+CD94+CE94)/65+SUM(AB94)/36+SUM(AR94+AS94+BW94+BX94+CK94+CN94)/40+SUM(BB94+BC94+BI94+BJ94)/60</f>
+        <f>SUM(R94+S94+BN94+CD94+CE94)/65+SUM(AB94)/36+SUM(AR94+AS94+BW94+BX94+CL94+CM94)/40+SUM(BB94+BC94+BI94+BJ94)/60</f>
         <v/>
       </c>
       <c r="CR94" s="38">
@@ -17852,7 +17852,7 @@
         <v/>
       </c>
       <c r="CT94" s="38">
-        <f>SUM(BY94+CL94)/45</f>
+        <f>SUM(BY94+CN94)/45</f>
         <v/>
       </c>
       <c r="CU94" s="83">
@@ -17995,11 +17995,11 @@
         <v/>
       </c>
       <c r="CP95" s="38">
-        <f>SUM(O95+P95+Q95+BL95+BM95+CB95+CC95)/65+SUM(X95+Y95)/44+SUM(AJ95+AK95+AM95+AN95+AO95+AP95+AQ95+BR95+BS95+BT95+BU95+BV95+CH95+CI95+CJ95+CM95)/45+SUM(AX95+AY95+AZ95+BA95+BF95+BG95+BH95)/60+SUM(AL95+BZ95)/50</f>
+        <f>SUM(O95+P95+Q95+BL95+BM95+CB95+CC95)/65+SUM(X95+Y95)/44+SUM(AJ95+AK95+AM95+AN95+AO95+AP95+AQ95+BR95+BS95+BT95+BU95+BV95+CH95+CI95+CJ95+CK95)/45+SUM(AX95+AY95+AZ95+BA95+BF95+BG95+BH95)/60+SUM(AL95+BZ95)/50</f>
         <v/>
       </c>
       <c r="CQ95" s="38">
-        <f>SUM(R95+S95+BN95+CD95+CE95)/65+SUM(AB95)/36+SUM(AR95+AS95+BW95+BX95+CK95+CN95)/40+SUM(BB95+BC95+BI95+BJ95)/60</f>
+        <f>SUM(R95+S95+BN95+CD95+CE95)/65+SUM(AB95)/36+SUM(AR95+AS95+BW95+BX95+CL95+CM95)/40+SUM(BB95+BC95+BI95+BJ95)/60</f>
         <v/>
       </c>
       <c r="CR95" s="38">
@@ -18011,7 +18011,7 @@
         <v/>
       </c>
       <c r="CT95" s="38">
-        <f>SUM(BY95+CL95)/45</f>
+        <f>SUM(BY95+CN95)/45</f>
         <v/>
       </c>
       <c r="CU95" s="83">
@@ -18154,11 +18154,11 @@
         <v/>
       </c>
       <c r="CP96" s="38">
-        <f>SUM(O96+P96+Q96+BL96+BM96+CB96+CC96)/65+SUM(X96+Y96)/44+SUM(AJ96+AK96+AM96+AN96+AO96+AP96+AQ96+BR96+BS96+BT96+BU96+BV96+CH96+CI96+CJ96+CM96)/45+SUM(AX96+AY96+AZ96+BA96+BF96+BG96+BH96)/60+SUM(AL96+BZ96)/50</f>
+        <f>SUM(O96+P96+Q96+BL96+BM96+CB96+CC96)/65+SUM(X96+Y96)/44+SUM(AJ96+AK96+AM96+AN96+AO96+AP96+AQ96+BR96+BS96+BT96+BU96+BV96+CH96+CI96+CJ96+CK96)/45+SUM(AX96+AY96+AZ96+BA96+BF96+BG96+BH96)/60+SUM(AL96+BZ96)/50</f>
         <v/>
       </c>
       <c r="CQ96" s="38">
-        <f>SUM(R96+S96+BN96+CD96+CE96)/65+SUM(AB96)/36+SUM(AR96+AS96+BW96+BX96+CK96+CN96)/40+SUM(BB96+BC96+BI96+BJ96)/60</f>
+        <f>SUM(R96+S96+BN96+CD96+CE96)/65+SUM(AB96)/36+SUM(AR96+AS96+BW96+BX96+CL96+CM96)/40+SUM(BB96+BC96+BI96+BJ96)/60</f>
         <v/>
       </c>
       <c r="CR96" s="38">
@@ -18170,7 +18170,7 @@
         <v/>
       </c>
       <c r="CT96" s="38">
-        <f>SUM(BY96+CL96)/45</f>
+        <f>SUM(BY96+CN96)/45</f>
         <v/>
       </c>
       <c r="CU96" s="83">
@@ -18313,11 +18313,11 @@
         <v/>
       </c>
       <c r="CP97" s="38">
-        <f>SUM(O97+P97+Q97+BL97+BM97+CB97+CC97)/65+SUM(X97+Y97)/44+SUM(AJ97+AK97+AM97+AN97+AO97+AP97+AQ97+BR97+BS97+BT97+BU97+BV97+CH97+CI97+CJ97+CM97)/45+SUM(AX97+AY97+AZ97+BA97+BF97+BG97+BH97)/60+SUM(AL97+BZ97)/50</f>
+        <f>SUM(O97+P97+Q97+BL97+BM97+CB97+CC97)/65+SUM(X97+Y97)/44+SUM(AJ97+AK97+AM97+AN97+AO97+AP97+AQ97+BR97+BS97+BT97+BU97+BV97+CH97+CI97+CJ97+CK97)/45+SUM(AX97+AY97+AZ97+BA97+BF97+BG97+BH97)/60+SUM(AL97+BZ97)/50</f>
         <v/>
       </c>
       <c r="CQ97" s="38">
-        <f>SUM(R97+S97+BN97+CD97+CE97)/65+SUM(AB97)/36+SUM(AR97+AS97+BW97+BX97+CK97+CN97)/40+SUM(BB97+BC97+BI97+BJ97)/60</f>
+        <f>SUM(R97+S97+BN97+CD97+CE97)/65+SUM(AB97)/36+SUM(AR97+AS97+BW97+BX97+CL97+CM97)/40+SUM(BB97+BC97+BI97+BJ97)/60</f>
         <v/>
       </c>
       <c r="CR97" s="38">
@@ -18329,7 +18329,7 @@
         <v/>
       </c>
       <c r="CT97" s="38">
-        <f>SUM(BY97+CL97)/45</f>
+        <f>SUM(BY97+CN97)/45</f>
         <v/>
       </c>
       <c r="CU97" s="83">
@@ -18472,11 +18472,11 @@
         <v/>
       </c>
       <c r="CP98" s="38">
-        <f>SUM(O98+P98+Q98+BL98+BM98+CB98+CC98)/65+SUM(X98+Y98)/44+SUM(AJ98+AK98+AM98+AN98+AO98+AP98+AQ98+BR98+BS98+BT98+BU98+BV98+CH98+CI98+CJ98+CM98)/45+SUM(AX98+AY98+AZ98+BA98+BF98+BG98+BH98)/60+SUM(AL98+BZ98)/50</f>
+        <f>SUM(O98+P98+Q98+BL98+BM98+CB98+CC98)/65+SUM(X98+Y98)/44+SUM(AJ98+AK98+AM98+AN98+AO98+AP98+AQ98+BR98+BS98+BT98+BU98+BV98+CH98+CI98+CJ98+CK98)/45+SUM(AX98+AY98+AZ98+BA98+BF98+BG98+BH98)/60+SUM(AL98+BZ98)/50</f>
         <v/>
       </c>
       <c r="CQ98" s="38">
-        <f>SUM(R98+S98+BN98+CD98+CE98)/65+SUM(AB98)/36+SUM(AR98+AS98+BW98+BX98+CK98+CN98)/40+SUM(BB98+BC98+BI98+BJ98)/60</f>
+        <f>SUM(R98+S98+BN98+CD98+CE98)/65+SUM(AB98)/36+SUM(AR98+AS98+BW98+BX98+CL98+CM98)/40+SUM(BB98+BC98+BI98+BJ98)/60</f>
         <v/>
       </c>
       <c r="CR98" s="38">
@@ -18488,7 +18488,7 @@
         <v/>
       </c>
       <c r="CT98" s="38">
-        <f>SUM(BY98+CL98)/45</f>
+        <f>SUM(BY98+CN98)/45</f>
         <v/>
       </c>
       <c r="CU98" s="83">
@@ -18631,11 +18631,11 @@
         <v/>
       </c>
       <c r="CP99" s="38">
-        <f>SUM(O99+P99+Q99+BL99+BM99+CB99+CC99)/65+SUM(X99+Y99)/44+SUM(AJ99+AK99+AM99+AN99+AO99+AP99+AQ99+BR99+BS99+BT99+BU99+BV99+CH99+CI99+CJ99+CM99)/45+SUM(AX99+AY99+AZ99+BA99+BF99+BG99+BH99)/60+SUM(AL99+BZ99)/50</f>
+        <f>SUM(O99+P99+Q99+BL99+BM99+CB99+CC99)/65+SUM(X99+Y99)/44+SUM(AJ99+AK99+AM99+AN99+AO99+AP99+AQ99+BR99+BS99+BT99+BU99+BV99+CH99+CI99+CJ99+CK99)/45+SUM(AX99+AY99+AZ99+BA99+BF99+BG99+BH99)/60+SUM(AL99+BZ99)/50</f>
         <v/>
       </c>
       <c r="CQ99" s="38">
-        <f>SUM(R99+S99+BN99+CD99+CE99)/65+SUM(AB99)/36+SUM(AR99+AS99+BW99+BX99+CK99+CN99)/40+SUM(BB99+BC99+BI99+BJ99)/60</f>
+        <f>SUM(R99+S99+BN99+CD99+CE99)/65+SUM(AB99)/36+SUM(AR99+AS99+BW99+BX99+CL99+CM99)/40+SUM(BB99+BC99+BI99+BJ99)/60</f>
         <v/>
       </c>
       <c r="CR99" s="38">
@@ -18647,7 +18647,7 @@
         <v/>
       </c>
       <c r="CT99" s="38">
-        <f>SUM(BY99+CL99)/45</f>
+        <f>SUM(BY99+CN99)/45</f>
         <v/>
       </c>
       <c r="CU99" s="83">
@@ -18790,11 +18790,11 @@
         <v/>
       </c>
       <c r="CP100" s="38">
-        <f>SUM(O100+P100+Q100+BL100+BM100+CB100+CC100)/65+SUM(X100+Y100)/44+SUM(AJ100+AK100+AM100+AN100+AO100+AP100+AQ100+BR100+BS100+BT100+BU100+BV100+CH100+CI100+CJ100+CM100)/45+SUM(AX100+AY100+AZ100+BA100+BF100+BG100+BH100)/60+SUM(AL100+BZ100)/50</f>
+        <f>SUM(O100+P100+Q100+BL100+BM100+CB100+CC100)/65+SUM(X100+Y100)/44+SUM(AJ100+AK100+AM100+AN100+AO100+AP100+AQ100+BR100+BS100+BT100+BU100+BV100+CH100+CI100+CJ100+CK100)/45+SUM(AX100+AY100+AZ100+BA100+BF100+BG100+BH100)/60+SUM(AL100+BZ100)/50</f>
         <v/>
       </c>
       <c r="CQ100" s="38">
-        <f>SUM(R100+S100+BN100+CD100+CE100)/65+SUM(AB100)/36+SUM(AR100+AS100+BW100+BX100+CK100+CN100)/40+SUM(BB100+BC100+BI100+BJ100)/60</f>
+        <f>SUM(R100+S100+BN100+CD100+CE100)/65+SUM(AB100)/36+SUM(AR100+AS100+BW100+BX100+CL100+CM100)/40+SUM(BB100+BC100+BI100+BJ100)/60</f>
         <v/>
       </c>
       <c r="CR100" s="38">
@@ -18806,7 +18806,7 @@
         <v/>
       </c>
       <c r="CT100" s="38">
-        <f>SUM(BY100+CL100)/45</f>
+        <f>SUM(BY100+CN100)/45</f>
         <v/>
       </c>
       <c r="CU100" s="83">
@@ -18949,11 +18949,11 @@
         <v/>
       </c>
       <c r="CP101" s="38">
-        <f>SUM(O101+P101+Q101+BL101+BM101+CB101+CC101)/65+SUM(X101+Y101)/44+SUM(AJ101+AK101+AM101+AN101+AO101+AP101+AQ101+BR101+BS101+BT101+BU101+BV101+CH101+CI101+CJ101+CM101)/45+SUM(AX101+AY101+AZ101+BA101+BF101+BG101+BH101)/60+SUM(AL101+BZ101)/50</f>
+        <f>SUM(O101+P101+Q101+BL101+BM101+CB101+CC101)/65+SUM(X101+Y101)/44+SUM(AJ101+AK101+AM101+AN101+AO101+AP101+AQ101+BR101+BS101+BT101+BU101+BV101+CH101+CI101+CJ101+CK101)/45+SUM(AX101+AY101+AZ101+BA101+BF101+BG101+BH101)/60+SUM(AL101+BZ101)/50</f>
         <v/>
       </c>
       <c r="CQ101" s="38">
-        <f>SUM(R101+S101+BN101+CD101+CE101)/65+SUM(AB101)/36+SUM(AR101+AS101+BW101+BX101+CK101+CN101)/40+SUM(BB101+BC101+BI101+BJ101)/60</f>
+        <f>SUM(R101+S101+BN101+CD101+CE101)/65+SUM(AB101)/36+SUM(AR101+AS101+BW101+BX101+CL101+CM101)/40+SUM(BB101+BC101+BI101+BJ101)/60</f>
         <v/>
       </c>
       <c r="CR101" s="38">
@@ -18965,7 +18965,7 @@
         <v/>
       </c>
       <c r="CT101" s="38">
-        <f>SUM(BY101+CL101)/45</f>
+        <f>SUM(BY101+CN101)/45</f>
         <v/>
       </c>
       <c r="CU101" s="83">
@@ -19108,11 +19108,11 @@
         <v/>
       </c>
       <c r="CP102" s="38">
-        <f>SUM(O102+P102+Q102+BL102+BM102+CB102+CC102)/65+SUM(X102+Y102)/44+SUM(AJ102+AK102+AM102+AN102+AO102+AP102+AQ102+BR102+BS102+BT102+BU102+BV102+CH102+CI102+CJ102+CM102)/45+SUM(AX102+AY102+AZ102+BA102+BF102+BG102+BH102)/60+SUM(AL102+BZ102)/50</f>
+        <f>SUM(O102+P102+Q102+BL102+BM102+CB102+CC102)/65+SUM(X102+Y102)/44+SUM(AJ102+AK102+AM102+AN102+AO102+AP102+AQ102+BR102+BS102+BT102+BU102+BV102+CH102+CI102+CJ102+CK102)/45+SUM(AX102+AY102+AZ102+BA102+BF102+BG102+BH102)/60+SUM(AL102+BZ102)/50</f>
         <v/>
       </c>
       <c r="CQ102" s="38">
-        <f>SUM(R102+S102+BN102+CD102+CE102)/65+SUM(AB102)/36+SUM(AR102+AS102+BW102+BX102+CK102+CN102)/40+SUM(BB102+BC102+BI102+BJ102)/60</f>
+        <f>SUM(R102+S102+BN102+CD102+CE102)/65+SUM(AB102)/36+SUM(AR102+AS102+BW102+BX102+CL102+CM102)/40+SUM(BB102+BC102+BI102+BJ102)/60</f>
         <v/>
       </c>
       <c r="CR102" s="38">
@@ -19124,7 +19124,7 @@
         <v/>
       </c>
       <c r="CT102" s="38">
-        <f>SUM(BY102+CL102)/45</f>
+        <f>SUM(BY102+CN102)/45</f>
         <v/>
       </c>
       <c r="CU102" s="83">
@@ -19267,11 +19267,11 @@
         <v/>
       </c>
       <c r="CP103" s="38">
-        <f>SUM(O103+P103+Q103+BL103+BM103+CB103+CC103)/65+SUM(X103+Y103)/44+SUM(AJ103+AK103+AM103+AN103+AO103+AP103+AQ103+BR103+BS103+BT103+BU103+BV103+CH103+CI103+CJ103+CM103)/45+SUM(AX103+AY103+AZ103+BA103+BF103+BG103+BH103)/60+SUM(AL103+BZ103)/50</f>
+        <f>SUM(O103+P103+Q103+BL103+BM103+CB103+CC103)/65+SUM(X103+Y103)/44+SUM(AJ103+AK103+AM103+AN103+AO103+AP103+AQ103+BR103+BS103+BT103+BU103+BV103+CH103+CI103+CJ103+CK103)/45+SUM(AX103+AY103+AZ103+BA103+BF103+BG103+BH103)/60+SUM(AL103+BZ103)/50</f>
         <v/>
       </c>
       <c r="CQ103" s="38">
-        <f>SUM(R103+S103+BN103+CD103+CE103)/65+SUM(AB103)/36+SUM(AR103+AS103+BW103+BX103+CK103+CN103)/40+SUM(BB103+BC103+BI103+BJ103)/60</f>
+        <f>SUM(R103+S103+BN103+CD103+CE103)/65+SUM(AB103)/36+SUM(AR103+AS103+BW103+BX103+CL103+CM103)/40+SUM(BB103+BC103+BI103+BJ103)/60</f>
         <v/>
       </c>
       <c r="CR103" s="38">
@@ -19283,7 +19283,7 @@
         <v/>
       </c>
       <c r="CT103" s="38">
-        <f>SUM(BY103+CL103)/45</f>
+        <f>SUM(BY103+CN103)/45</f>
         <v/>
       </c>
       <c r="CU103" s="83">
@@ -19426,11 +19426,11 @@
         <v/>
       </c>
       <c r="CP104" s="38">
-        <f>SUM(O104+P104+Q104+BL104+BM104+CB104+CC104)/65+SUM(X104+Y104)/44+SUM(AJ104+AK104+AM104+AN104+AO104+AP104+AQ104+BR104+BS104+BT104+BU104+BV104+CH104+CI104+CJ104+CM104)/45+SUM(AX104+AY104+AZ104+BA104+BF104+BG104+BH104)/60+SUM(AL104+BZ104)/50</f>
+        <f>SUM(O104+P104+Q104+BL104+BM104+CB104+CC104)/65+SUM(X104+Y104)/44+SUM(AJ104+AK104+AM104+AN104+AO104+AP104+AQ104+BR104+BS104+BT104+BU104+BV104+CH104+CI104+CJ104+CK104)/45+SUM(AX104+AY104+AZ104+BA104+BF104+BG104+BH104)/60+SUM(AL104+BZ104)/50</f>
         <v/>
       </c>
       <c r="CQ104" s="38">
-        <f>SUM(R104+S104+BN104+CD104+CE104)/65+SUM(AB104)/36+SUM(AR104+AS104+BW104+BX104+CK104+CN104)/40+SUM(BB104+BC104+BI104+BJ104)/60</f>
+        <f>SUM(R104+S104+BN104+CD104+CE104)/65+SUM(AB104)/36+SUM(AR104+AS104+BW104+BX104+CL104+CM104)/40+SUM(BB104+BC104+BI104+BJ104)/60</f>
         <v/>
       </c>
       <c r="CR104" s="38">
@@ -19442,7 +19442,7 @@
         <v/>
       </c>
       <c r="CT104" s="38">
-        <f>SUM(BY104+CL104)/45</f>
+        <f>SUM(BY104+CN104)/45</f>
         <v/>
       </c>
       <c r="CU104" s="83">
@@ -19585,11 +19585,11 @@
         <v/>
       </c>
       <c r="CP105" s="38">
-        <f>SUM(O105+P105+Q105+BL105+BM105+CB105+CC105)/65+SUM(X105+Y105)/44+SUM(AJ105+AK105+AM105+AN105+AO105+AP105+AQ105+BR105+BS105+BT105+BU105+BV105+CH105+CI105+CJ105+CM105)/45+SUM(AX105+AY105+AZ105+BA105+BF105+BG105+BH105)/60+SUM(AL105+BZ105)/50</f>
+        <f>SUM(O105+P105+Q105+BL105+BM105+CB105+CC105)/65+SUM(X105+Y105)/44+SUM(AJ105+AK105+AM105+AN105+AO105+AP105+AQ105+BR105+BS105+BT105+BU105+BV105+CH105+CI105+CJ105+CK105)/45+SUM(AX105+AY105+AZ105+BA105+BF105+BG105+BH105)/60+SUM(AL105+BZ105)/50</f>
         <v/>
       </c>
       <c r="CQ105" s="38">
-        <f>SUM(R105+S105+BN105+CD105+CE105)/65+SUM(AB105)/36+SUM(AR105+AS105+BW105+BX105+CK105+CN105)/40+SUM(BB105+BC105+BI105+BJ105)/60</f>
+        <f>SUM(R105+S105+BN105+CD105+CE105)/65+SUM(AB105)/36+SUM(AR105+AS105+BW105+BX105+CL105+CM105)/40+SUM(BB105+BC105+BI105+BJ105)/60</f>
         <v/>
       </c>
       <c r="CR105" s="38">
@@ -19601,7 +19601,7 @@
         <v/>
       </c>
       <c r="CT105" s="38">
-        <f>SUM(BY105+CL105)/45</f>
+        <f>SUM(BY105+CN105)/45</f>
         <v/>
       </c>
       <c r="CU105" s="83">
@@ -19744,11 +19744,11 @@
         <v/>
       </c>
       <c r="CP106" s="38">
-        <f>SUM(O106+P106+Q106+BL106+BM106+CB106+CC106)/65+SUM(X106+Y106)/44+SUM(AJ106+AK106+AM106+AN106+AO106+AP106+AQ106+BR106+BS106+BT106+BU106+BV106+CH106+CI106+CJ106+CM106)/45+SUM(AX106+AY106+AZ106+BA106+BF106+BG106+BH106)/60+SUM(AL106+BZ106)/50</f>
+        <f>SUM(O106+P106+Q106+BL106+BM106+CB106+CC106)/65+SUM(X106+Y106)/44+SUM(AJ106+AK106+AM106+AN106+AO106+AP106+AQ106+BR106+BS106+BT106+BU106+BV106+CH106+CI106+CJ106+CK106)/45+SUM(AX106+AY106+AZ106+BA106+BF106+BG106+BH106)/60+SUM(AL106+BZ106)/50</f>
         <v/>
       </c>
       <c r="CQ106" s="38">
-        <f>SUM(R106+S106+BN106+CD106+CE106)/65+SUM(AB106)/36+SUM(AR106+AS106+BW106+BX106+CK106+CN106)/40+SUM(BB106+BC106+BI106+BJ106)/60</f>
+        <f>SUM(R106+S106+BN106+CD106+CE106)/65+SUM(AB106)/36+SUM(AR106+AS106+BW106+BX106+CL106+CM106)/40+SUM(BB106+BC106+BI106+BJ106)/60</f>
         <v/>
       </c>
       <c r="CR106" s="38">
@@ -19760,7 +19760,7 @@
         <v/>
       </c>
       <c r="CT106" s="38">
-        <f>SUM(BY106+CL106)/45</f>
+        <f>SUM(BY106+CN106)/45</f>
         <v/>
       </c>
       <c r="CU106" s="83">
@@ -19903,11 +19903,11 @@
         <v/>
       </c>
       <c r="CP107" s="38">
-        <f>SUM(O107+P107+Q107+BL107+BM107+CB107+CC107)/65+SUM(X107+Y107)/44+SUM(AJ107+AK107+AM107+AN107+AO107+AP107+AQ107+BR107+BS107+BT107+BU107+BV107+CH107+CI107+CJ107+CM107)/45+SUM(AX107+AY107+AZ107+BA107+BF107+BG107+BH107)/60+SUM(AL107+BZ107)/50</f>
+        <f>SUM(O107+P107+Q107+BL107+BM107+CB107+CC107)/65+SUM(X107+Y107)/44+SUM(AJ107+AK107+AM107+AN107+AO107+AP107+AQ107+BR107+BS107+BT107+BU107+BV107+CH107+CI107+CJ107+CK107)/45+SUM(AX107+AY107+AZ107+BA107+BF107+BG107+BH107)/60+SUM(AL107+BZ107)/50</f>
         <v/>
       </c>
       <c r="CQ107" s="38">
-        <f>SUM(R107+S107+BN107+CD107+CE107)/65+SUM(AB107)/36+SUM(AR107+AS107+BW107+BX107+CK107+CN107)/40+SUM(BB107+BC107+BI107+BJ107)/60</f>
+        <f>SUM(R107+S107+BN107+CD107+CE107)/65+SUM(AB107)/36+SUM(AR107+AS107+BW107+BX107+CL107+CM107)/40+SUM(BB107+BC107+BI107+BJ107)/60</f>
         <v/>
       </c>
       <c r="CR107" s="38">
@@ -19919,7 +19919,7 @@
         <v/>
       </c>
       <c r="CT107" s="38">
-        <f>SUM(BY107+CL107)/45</f>
+        <f>SUM(BY107+CN107)/45</f>
         <v/>
       </c>
       <c r="CU107" s="83">
@@ -20062,11 +20062,11 @@
         <v/>
       </c>
       <c r="CP108" s="38">
-        <f>SUM(O108+P108+Q108+BL108+BM108+CB108+CC108)/65+SUM(X108+Y108)/44+SUM(AJ108+AK108+AM108+AN108+AO108+AP108+AQ108+BR108+BS108+BT108+BU108+BV108+CH108+CI108+CJ108+CM108)/45+SUM(AX108+AY108+AZ108+BA108+BF108+BG108+BH108)/60+SUM(AL108+BZ108)/50</f>
+        <f>SUM(O108+P108+Q108+BL108+BM108+CB108+CC108)/65+SUM(X108+Y108)/44+SUM(AJ108+AK108+AM108+AN108+AO108+AP108+AQ108+BR108+BS108+BT108+BU108+BV108+CH108+CI108+CJ108+CK108)/45+SUM(AX108+AY108+AZ108+BA108+BF108+BG108+BH108)/60+SUM(AL108+BZ108)/50</f>
         <v/>
       </c>
       <c r="CQ108" s="38">
-        <f>SUM(R108+S108+BN108+CD108+CE108)/65+SUM(AB108)/36+SUM(AR108+AS108+BW108+BX108+CK108+CN108)/40+SUM(BB108+BC108+BI108+BJ108)/60</f>
+        <f>SUM(R108+S108+BN108+CD108+CE108)/65+SUM(AB108)/36+SUM(AR108+AS108+BW108+BX108+CL108+CM108)/40+SUM(BB108+BC108+BI108+BJ108)/60</f>
         <v/>
       </c>
       <c r="CR108" s="38">
@@ -20078,7 +20078,7 @@
         <v/>
       </c>
       <c r="CT108" s="38">
-        <f>SUM(BY108+CL108)/45</f>
+        <f>SUM(BY108+CN108)/45</f>
         <v/>
       </c>
       <c r="CU108" s="83">
@@ -20221,11 +20221,11 @@
         <v/>
       </c>
       <c r="CP109" s="38">
-        <f>SUM(O109+P109+Q109+BL109+BM109+CB109+CC109)/65+SUM(X109+Y109)/44+SUM(AJ109+AK109+AM109+AN109+AO109+AP109+AQ109+BR109+BS109+BT109+BU109+BV109+CH109+CI109+CJ109+CM109)/45+SUM(AX109+AY109+AZ109+BA109+BF109+BG109+BH109)/60+SUM(AL109+BZ109)/50</f>
+        <f>SUM(O109+P109+Q109+BL109+BM109+CB109+CC109)/65+SUM(X109+Y109)/44+SUM(AJ109+AK109+AM109+AN109+AO109+AP109+AQ109+BR109+BS109+BT109+BU109+BV109+CH109+CI109+CJ109+CK109)/45+SUM(AX109+AY109+AZ109+BA109+BF109+BG109+BH109)/60+SUM(AL109+BZ109)/50</f>
         <v/>
       </c>
       <c r="CQ109" s="38">
-        <f>SUM(R109+S109+BN109+CD109+CE109)/65+SUM(AB109)/36+SUM(AR109+AS109+BW109+BX109+CK109+CN109)/40+SUM(BB109+BC109+BI109+BJ109)/60</f>
+        <f>SUM(R109+S109+BN109+CD109+CE109)/65+SUM(AB109)/36+SUM(AR109+AS109+BW109+BX109+CL109+CM109)/40+SUM(BB109+BC109+BI109+BJ109)/60</f>
         <v/>
       </c>
       <c r="CR109" s="38">
@@ -20237,7 +20237,7 @@
         <v/>
       </c>
       <c r="CT109" s="38">
-        <f>SUM(BY109+CL109)/45</f>
+        <f>SUM(BY109+CN109)/45</f>
         <v/>
       </c>
       <c r="CU109" s="83">
@@ -20380,11 +20380,11 @@
         <v/>
       </c>
       <c r="CP110" s="38">
-        <f>SUM(O110+P110+Q110+BL110+BM110+CB110+CC110)/65+SUM(X110+Y110)/44+SUM(AJ110+AK110+AM110+AN110+AO110+AP110+AQ110+BR110+BS110+BT110+BU110+BV110+CH110+CI110+CJ110+CM110)/45+SUM(AX110+AY110+AZ110+BA110+BF110+BG110+BH110)/60+SUM(AL110+BZ110)/50</f>
+        <f>SUM(O110+P110+Q110+BL110+BM110+CB110+CC110)/65+SUM(X110+Y110)/44+SUM(AJ110+AK110+AM110+AN110+AO110+AP110+AQ110+BR110+BS110+BT110+BU110+BV110+CH110+CI110+CJ110+CK110)/45+SUM(AX110+AY110+AZ110+BA110+BF110+BG110+BH110)/60+SUM(AL110+BZ110)/50</f>
         <v/>
       </c>
       <c r="CQ110" s="38">
-        <f>SUM(R110+S110+BN110+CD110+CE110)/65+SUM(AB110)/36+SUM(AR110+AS110+BW110+BX110+CK110+CN110)/40+SUM(BB110+BC110+BI110+BJ110)/60</f>
+        <f>SUM(R110+S110+BN110+CD110+CE110)/65+SUM(AB110)/36+SUM(AR110+AS110+BW110+BX110+CL110+CM110)/40+SUM(BB110+BC110+BI110+BJ110)/60</f>
         <v/>
       </c>
       <c r="CR110" s="38">
@@ -20396,7 +20396,7 @@
         <v/>
       </c>
       <c r="CT110" s="38">
-        <f>SUM(BY110+CL110)/45</f>
+        <f>SUM(BY110+CN110)/45</f>
         <v/>
       </c>
       <c r="CU110" s="83">
@@ -20539,11 +20539,11 @@
         <v/>
       </c>
       <c r="CP111" s="38">
-        <f>SUM(O111+P111+Q111+BL111+BM111+CB111+CC111)/65+SUM(X111+Y111)/44+SUM(AJ111+AK111+AM111+AN111+AO111+AP111+AQ111+BR111+BS111+BT111+BU111+BV111+CH111+CI111+CJ111+CM111)/45+SUM(AX111+AY111+AZ111+BA111+BF111+BG111+BH111)/60+SUM(AL111+BZ111)/50</f>
+        <f>SUM(O111+P111+Q111+BL111+BM111+CB111+CC111)/65+SUM(X111+Y111)/44+SUM(AJ111+AK111+AM111+AN111+AO111+AP111+AQ111+BR111+BS111+BT111+BU111+BV111+CH111+CI111+CJ111+CK111)/45+SUM(AX111+AY111+AZ111+BA111+BF111+BG111+BH111)/60+SUM(AL111+BZ111)/50</f>
         <v/>
       </c>
       <c r="CQ111" s="38">
-        <f>SUM(R111+S111+BN111+CD111+CE111)/65+SUM(AB111)/36+SUM(AR111+AS111+BW111+BX111+CK111+CN111)/40+SUM(BB111+BC111+BI111+BJ111)/60</f>
+        <f>SUM(R111+S111+BN111+CD111+CE111)/65+SUM(AB111)/36+SUM(AR111+AS111+BW111+BX111+CL111+CM111)/40+SUM(BB111+BC111+BI111+BJ111)/60</f>
         <v/>
       </c>
       <c r="CR111" s="38">
@@ -20555,7 +20555,7 @@
         <v/>
       </c>
       <c r="CT111" s="38">
-        <f>SUM(BY111+CL111)/45</f>
+        <f>SUM(BY111+CN111)/45</f>
         <v/>
       </c>
       <c r="CU111" s="83">
@@ -20698,11 +20698,11 @@
         <v/>
       </c>
       <c r="CP112" s="38">
-        <f>SUM(O112+P112+Q112+BL112+BM112+CB112+CC112)/65+SUM(X112+Y112)/44+SUM(AJ112+AK112+AM112+AN112+AO112+AP112+AQ112+BR112+BS112+BT112+BU112+BV112+CH112+CI112+CJ112+CM112)/45+SUM(AX112+AY112+AZ112+BA112+BF112+BG112+BH112)/60+SUM(AL112+BZ112)/50</f>
+        <f>SUM(O112+P112+Q112+BL112+BM112+CB112+CC112)/65+SUM(X112+Y112)/44+SUM(AJ112+AK112+AM112+AN112+AO112+AP112+AQ112+BR112+BS112+BT112+BU112+BV112+CH112+CI112+CJ112+CK112)/45+SUM(AX112+AY112+AZ112+BA112+BF112+BG112+BH112)/60+SUM(AL112+BZ112)/50</f>
         <v/>
       </c>
       <c r="CQ112" s="38">
-        <f>SUM(R112+S112+BN112+CD112+CE112)/65+SUM(AB112)/36+SUM(AR112+AS112+BW112+BX112+CK112+CN112)/40+SUM(BB112+BC112+BI112+BJ112)/60</f>
+        <f>SUM(R112+S112+BN112+CD112+CE112)/65+SUM(AB112)/36+SUM(AR112+AS112+BW112+BX112+CL112+CM112)/40+SUM(BB112+BC112+BI112+BJ112)/60</f>
         <v/>
       </c>
       <c r="CR112" s="38">
@@ -20714,7 +20714,7 @@
         <v/>
       </c>
       <c r="CT112" s="38">
-        <f>SUM(BY112+CL112)/45</f>
+        <f>SUM(BY112+CN112)/45</f>
         <v/>
       </c>
       <c r="CU112" s="83">
@@ -20857,11 +20857,11 @@
         <v/>
       </c>
       <c r="CP113" s="38">
-        <f>SUM(O113+P113+Q113+BL113+BM113+CB113+CC113)/65+SUM(X113+Y113)/44+SUM(AJ113+AK113+AM113+AN113+AO113+AP113+AQ113+BR113+BS113+BT113+BU113+BV113+CH113+CI113+CJ113+CM113)/45+SUM(AX113+AY113+AZ113+BA113+BF113+BG113+BH113)/60+SUM(AL113+BZ113)/50</f>
+        <f>SUM(O113+P113+Q113+BL113+BM113+CB113+CC113)/65+SUM(X113+Y113)/44+SUM(AJ113+AK113+AM113+AN113+AO113+AP113+AQ113+BR113+BS113+BT113+BU113+BV113+CH113+CI113+CJ113+CK113)/45+SUM(AX113+AY113+AZ113+BA113+BF113+BG113+BH113)/60+SUM(AL113+BZ113)/50</f>
         <v/>
       </c>
       <c r="CQ113" s="38">
-        <f>SUM(R113+S113+BN113+CD113+CE113)/65+SUM(AB113)/36+SUM(AR113+AS113+BW113+BX113+CK113+CN113)/40+SUM(BB113+BC113+BI113+BJ113)/60</f>
+        <f>SUM(R113+S113+BN113+CD113+CE113)/65+SUM(AB113)/36+SUM(AR113+AS113+BW113+BX113+CL113+CM113)/40+SUM(BB113+BC113+BI113+BJ113)/60</f>
         <v/>
       </c>
       <c r="CR113" s="38">
@@ -20873,7 +20873,7 @@
         <v/>
       </c>
       <c r="CT113" s="38">
-        <f>SUM(BY113+CL113)/45</f>
+        <f>SUM(BY113+CN113)/45</f>
         <v/>
       </c>
       <c r="CU113" s="83">
@@ -21016,11 +21016,11 @@
         <v/>
       </c>
       <c r="CP114" s="38">
-        <f>SUM(O114+P114+Q114+BL114+BM114+CB114+CC114)/65+SUM(X114+Y114)/44+SUM(AJ114+AK114+AM114+AN114+AO114+AP114+AQ114+BR114+BS114+BT114+BU114+BV114+CH114+CI114+CJ114+CM114)/45+SUM(AX114+AY114+AZ114+BA114+BF114+BG114+BH114)/60+SUM(AL114+BZ114)/50</f>
+        <f>SUM(O114+P114+Q114+BL114+BM114+CB114+CC114)/65+SUM(X114+Y114)/44+SUM(AJ114+AK114+AM114+AN114+AO114+AP114+AQ114+BR114+BS114+BT114+BU114+BV114+CH114+CI114+CJ114+CK114)/45+SUM(AX114+AY114+AZ114+BA114+BF114+BG114+BH114)/60+SUM(AL114+BZ114)/50</f>
         <v/>
       </c>
       <c r="CQ114" s="38">
-        <f>SUM(R114+S114+BN114+CD114+CE114)/65+SUM(AB114)/36+SUM(AR114+AS114+BW114+BX114+CK114+CN114)/40+SUM(BB114+BC114+BI114+BJ114)/60</f>
+        <f>SUM(R114+S114+BN114+CD114+CE114)/65+SUM(AB114)/36+SUM(AR114+AS114+BW114+BX114+CL114+CM114)/40+SUM(BB114+BC114+BI114+BJ114)/60</f>
         <v/>
       </c>
       <c r="CR114" s="38">
@@ -21032,7 +21032,7 @@
         <v/>
       </c>
       <c r="CT114" s="38">
-        <f>SUM(BY114+CL114)/45</f>
+        <f>SUM(BY114+CN114)/45</f>
         <v/>
       </c>
       <c r="CU114" s="83">
@@ -21175,11 +21175,11 @@
         <v/>
       </c>
       <c r="CP115" s="38">
-        <f>SUM(O115+P115+Q115+BL115+BM115+CB115+CC115)/65+SUM(X115+Y115)/44+SUM(AJ115+AK115+AM115+AN115+AO115+AP115+AQ115+BR115+BS115+BT115+BU115+BV115+CH115+CI115+CJ115+CM115)/45+SUM(AX115+AY115+AZ115+BA115+BF115+BG115+BH115)/60+SUM(AL115+BZ115)/50</f>
+        <f>SUM(O115+P115+Q115+BL115+BM115+CB115+CC115)/65+SUM(X115+Y115)/44+SUM(AJ115+AK115+AM115+AN115+AO115+AP115+AQ115+BR115+BS115+BT115+BU115+BV115+CH115+CI115+CJ115+CK115)/45+SUM(AX115+AY115+AZ115+BA115+BF115+BG115+BH115)/60+SUM(AL115+BZ115)/50</f>
         <v/>
       </c>
       <c r="CQ115" s="38">
-        <f>SUM(R115+S115+BN115+CD115+CE115)/65+SUM(AB115)/36+SUM(AR115+AS115+BW115+BX115+CK115+CN115)/40+SUM(BB115+BC115+BI115+BJ115)/60</f>
+        <f>SUM(R115+S115+BN115+CD115+CE115)/65+SUM(AB115)/36+SUM(AR115+AS115+BW115+BX115+CL115+CM115)/40+SUM(BB115+BC115+BI115+BJ115)/60</f>
         <v/>
       </c>
       <c r="CR115" s="38">
@@ -21191,7 +21191,7 @@
         <v/>
       </c>
       <c r="CT115" s="38">
-        <f>SUM(BY115+CL115)/45</f>
+        <f>SUM(BY115+CN115)/45</f>
         <v/>
       </c>
       <c r="CU115" s="83">
@@ -21334,11 +21334,11 @@
         <v/>
       </c>
       <c r="CP116" s="38">
-        <f>SUM(O116+P116+Q116+BL116+BM116+CB116+CC116)/65+SUM(X116+Y116)/44+SUM(AJ116+AK116+AM116+AN116+AO116+AP116+AQ116+BR116+BS116+BT116+BU116+BV116+CH116+CI116+CJ116+CM116)/45+SUM(AX116+AY116+AZ116+BA116+BF116+BG116+BH116)/60+SUM(AL116+BZ116)/50</f>
+        <f>SUM(O116+P116+Q116+BL116+BM116+CB116+CC116)/65+SUM(X116+Y116)/44+SUM(AJ116+AK116+AM116+AN116+AO116+AP116+AQ116+BR116+BS116+BT116+BU116+BV116+CH116+CI116+CJ116+CK116)/45+SUM(AX116+AY116+AZ116+BA116+BF116+BG116+BH116)/60+SUM(AL116+BZ116)/50</f>
         <v/>
       </c>
       <c r="CQ116" s="38">
-        <f>SUM(R116+S116+BN116+CD116+CE116)/65+SUM(AB116)/36+SUM(AR116+AS116+BW116+BX116+CK116+CN116)/40+SUM(BB116+BC116+BI116+BJ116)/60</f>
+        <f>SUM(R116+S116+BN116+CD116+CE116)/65+SUM(AB116)/36+SUM(AR116+AS116+BW116+BX116+CL116+CM116)/40+SUM(BB116+BC116+BI116+BJ116)/60</f>
         <v/>
       </c>
       <c r="CR116" s="38">
@@ -21350,7 +21350,7 @@
         <v/>
       </c>
       <c r="CT116" s="38">
-        <f>SUM(BY116+CL116)/45</f>
+        <f>SUM(BY116+CN116)/45</f>
         <v/>
       </c>
       <c r="CU116" s="83">
@@ -21493,11 +21493,11 @@
         <v/>
       </c>
       <c r="CP117" s="38">
-        <f>SUM(O117+P117+Q117+BL117+BM117+CB117+CC117)/65+SUM(X117+Y117)/44+SUM(AJ117+AK117+AM117+AN117+AO117+AP117+AQ117+BR117+BS117+BT117+BU117+BV117+CH117+CI117+CJ117+CM117)/45+SUM(AX117+AY117+AZ117+BA117+BF117+BG117+BH117)/60+SUM(AL117+BZ117)/50</f>
+        <f>SUM(O117+P117+Q117+BL117+BM117+CB117+CC117)/65+SUM(X117+Y117)/44+SUM(AJ117+AK117+AM117+AN117+AO117+AP117+AQ117+BR117+BS117+BT117+BU117+BV117+CH117+CI117+CJ117+CK117)/45+SUM(AX117+AY117+AZ117+BA117+BF117+BG117+BH117)/60+SUM(AL117+BZ117)/50</f>
         <v/>
       </c>
       <c r="CQ117" s="38">
-        <f>SUM(R117+S117+BN117+CD117+CE117)/65+SUM(AB117)/36+SUM(AR117+AS117+BW117+BX117+CK117+CN117)/40+SUM(BB117+BC117+BI117+BJ117)/60</f>
+        <f>SUM(R117+S117+BN117+CD117+CE117)/65+SUM(AB117)/36+SUM(AR117+AS117+BW117+BX117+CL117+CM117)/40+SUM(BB117+BC117+BI117+BJ117)/60</f>
         <v/>
       </c>
       <c r="CR117" s="38">
@@ -21509,7 +21509,7 @@
         <v/>
       </c>
       <c r="CT117" s="38">
-        <f>SUM(BY117+CL117)/45</f>
+        <f>SUM(BY117+CN117)/45</f>
         <v/>
       </c>
       <c r="CU117" s="83">
@@ -21652,11 +21652,11 @@
         <v/>
       </c>
       <c r="CP118" s="38">
-        <f>SUM(O118+P118+Q118+BL118+BM118+CB118+CC118)/65+SUM(X118+Y118)/44+SUM(AJ118+AK118+AM118+AN118+AO118+AP118+AQ118+BR118+BS118+BT118+BU118+BV118+CH118+CI118+CJ118+CM118)/45+SUM(AX118+AY118+AZ118+BA118+BF118+BG118+BH118)/60+SUM(AL118+BZ118)/50</f>
+        <f>SUM(O118+P118+Q118+BL118+BM118+CB118+CC118)/65+SUM(X118+Y118)/44+SUM(AJ118+AK118+AM118+AN118+AO118+AP118+AQ118+BR118+BS118+BT118+BU118+BV118+CH118+CI118+CJ118+CK118)/45+SUM(AX118+AY118+AZ118+BA118+BF118+BG118+BH118)/60+SUM(AL118+BZ118)/50</f>
         <v/>
       </c>
       <c r="CQ118" s="38">
-        <f>SUM(R118+S118+BN118+CD118+CE118)/65+SUM(AB118)/36+SUM(AR118+AS118+BW118+BX118+CK118+CN118)/40+SUM(BB118+BC118+BI118+BJ118)/60</f>
+        <f>SUM(R118+S118+BN118+CD118+CE118)/65+SUM(AB118)/36+SUM(AR118+AS118+BW118+BX118+CL118+CM118)/40+SUM(BB118+BC118+BI118+BJ118)/60</f>
         <v/>
       </c>
       <c r="CR118" s="38">
@@ -21668,7 +21668,7 @@
         <v/>
       </c>
       <c r="CT118" s="38">
-        <f>SUM(BY118+CL118)/45</f>
+        <f>SUM(BY118+CN118)/45</f>
         <v/>
       </c>
       <c r="CU118" s="83">
@@ -21811,11 +21811,11 @@
         <v/>
       </c>
       <c r="CP119" s="38">
-        <f>SUM(O119+P119+Q119+BL119+BM119+CB119+CC119)/65+SUM(X119+Y119)/44+SUM(AJ119+AK119+AM119+AN119+AO119+AP119+AQ119+BR119+BS119+BT119+BU119+BV119+CH119+CI119+CJ119+CM119)/45+SUM(AX119+AY119+AZ119+BA119+BF119+BG119+BH119)/60+SUM(AL119+BZ119)/50</f>
+        <f>SUM(O119+P119+Q119+BL119+BM119+CB119+CC119)/65+SUM(X119+Y119)/44+SUM(AJ119+AK119+AM119+AN119+AO119+AP119+AQ119+BR119+BS119+BT119+BU119+BV119+CH119+CI119+CJ119+CK119)/45+SUM(AX119+AY119+AZ119+BA119+BF119+BG119+BH119)/60+SUM(AL119+BZ119)/50</f>
         <v/>
       </c>
       <c r="CQ119" s="38">
-        <f>SUM(R119+S119+BN119+CD119+CE119)/65+SUM(AB119)/36+SUM(AR119+AS119+BW119+BX119+CK119+CN119)/40+SUM(BB119+BC119+BI119+BJ119)/60</f>
+        <f>SUM(R119+S119+BN119+CD119+CE119)/65+SUM(AB119)/36+SUM(AR119+AS119+BW119+BX119+CL119+CM119)/40+SUM(BB119+BC119+BI119+BJ119)/60</f>
         <v/>
       </c>
       <c r="CR119" s="38">
@@ -21827,7 +21827,7 @@
         <v/>
       </c>
       <c r="CT119" s="38">
-        <f>SUM(BY119+CL119)/45</f>
+        <f>SUM(BY119+CN119)/45</f>
         <v/>
       </c>
       <c r="CU119" s="83">
@@ -21970,11 +21970,11 @@
         <v/>
       </c>
       <c r="CP120" s="38">
-        <f>SUM(O120+P120+Q120+BL120+BM120+CB120+CC120)/65+SUM(X120+Y120)/44+SUM(AJ120+AK120+AM120+AN120+AO120+AP120+AQ120+BR120+BS120+BT120+BU120+BV120+CH120+CI120+CJ120+CM120)/45+SUM(AX120+AY120+AZ120+BA120+BF120+BG120+BH120)/60+SUM(AL120+BZ120)/50</f>
+        <f>SUM(O120+P120+Q120+BL120+BM120+CB120+CC120)/65+SUM(X120+Y120)/44+SUM(AJ120+AK120+AM120+AN120+AO120+AP120+AQ120+BR120+BS120+BT120+BU120+BV120+CH120+CI120+CJ120+CK120)/45+SUM(AX120+AY120+AZ120+BA120+BF120+BG120+BH120)/60+SUM(AL120+BZ120)/50</f>
         <v/>
       </c>
       <c r="CQ120" s="38">
-        <f>SUM(R120+S120+BN120+CD120+CE120)/65+SUM(AB120)/36+SUM(AR120+AS120+BW120+BX120+CK120+CN120)/40+SUM(BB120+BC120+BI120+BJ120)/60</f>
+        <f>SUM(R120+S120+BN120+CD120+CE120)/65+SUM(AB120)/36+SUM(AR120+AS120+BW120+BX120+CL120+CM120)/40+SUM(BB120+BC120+BI120+BJ120)/60</f>
         <v/>
       </c>
       <c r="CR120" s="38">
@@ -21986,7 +21986,7 @@
         <v/>
       </c>
       <c r="CT120" s="38">
-        <f>SUM(BY120+CL120)/45</f>
+        <f>SUM(BY120+CN120)/45</f>
         <v/>
       </c>
       <c r="CU120" s="83">
@@ -22129,11 +22129,11 @@
         <v/>
       </c>
       <c r="CP121" s="38">
-        <f>SUM(O121+P121+Q121+BL121+BM121+CB121+CC121)/65+SUM(X121+Y121)/44+SUM(AJ121+AK121+AM121+AN121+AO121+AP121+AQ121+BR121+BS121+BT121+BU121+BV121+CH121+CI121+CJ121+CM121)/45+SUM(AX121+AY121+AZ121+BA121+BF121+BG121+BH121)/60+SUM(AL121+BZ121)/50</f>
+        <f>SUM(O121+P121+Q121+BL121+BM121+CB121+CC121)/65+SUM(X121+Y121)/44+SUM(AJ121+AK121+AM121+AN121+AO121+AP121+AQ121+BR121+BS121+BT121+BU121+BV121+CH121+CI121+CJ121+CK121)/45+SUM(AX121+AY121+AZ121+BA121+BF121+BG121+BH121)/60+SUM(AL121+BZ121)/50</f>
         <v/>
       </c>
       <c r="CQ121" s="38">
-        <f>SUM(R121+S121+BN121+CD121+CE121)/65+SUM(AB121)/36+SUM(AR121+AS121+BW121+BX121+CK121+CN121)/40+SUM(BB121+BC121+BI121+BJ121)/60</f>
+        <f>SUM(R121+S121+BN121+CD121+CE121)/65+SUM(AB121)/36+SUM(AR121+AS121+BW121+BX121+CL121+CM121)/40+SUM(BB121+BC121+BI121+BJ121)/60</f>
         <v/>
       </c>
       <c r="CR121" s="38">
@@ -22145,7 +22145,7 @@
         <v/>
       </c>
       <c r="CT121" s="38">
-        <f>SUM(BY121+CL121)/45</f>
+        <f>SUM(BY121+CN121)/45</f>
         <v/>
       </c>
       <c r="CU121" s="83">
@@ -22288,11 +22288,11 @@
         <v/>
       </c>
       <c r="CP122" s="38">
-        <f>SUM(O122+P122+Q122+BL122+BM122+CB122+CC122)/65+SUM(X122+Y122)/44+SUM(AJ122+AK122+AM122+AN122+AO122+AP122+AQ122+BR122+BS122+BT122+BU122+BV122+CH122+CI122+CJ122+CM122)/45+SUM(AX122+AY122+AZ122+BA122+BF122+BG122+BH122)/60+SUM(AL122+BZ122)/50</f>
+        <f>SUM(O122+P122+Q122+BL122+BM122+CB122+CC122)/65+SUM(X122+Y122)/44+SUM(AJ122+AK122+AM122+AN122+AO122+AP122+AQ122+BR122+BS122+BT122+BU122+BV122+CH122+CI122+CJ122+CK122)/45+SUM(AX122+AY122+AZ122+BA122+BF122+BG122+BH122)/60+SUM(AL122+BZ122)/50</f>
         <v/>
       </c>
       <c r="CQ122" s="38">
-        <f>SUM(R122+S122+BN122+CD122+CE122)/65+SUM(AB122)/36+SUM(AR122+AS122+BW122+BX122+CK122+CN122)/40+SUM(BB122+BC122+BI122+BJ122)/60</f>
+        <f>SUM(R122+S122+BN122+CD122+CE122)/65+SUM(AB122)/36+SUM(AR122+AS122+BW122+BX122+CL122+CM122)/40+SUM(BB122+BC122+BI122+BJ122)/60</f>
         <v/>
       </c>
       <c r="CR122" s="38">
@@ -22304,7 +22304,7 @@
         <v/>
       </c>
       <c r="CT122" s="38">
-        <f>SUM(BY122+CL122)/45</f>
+        <f>SUM(BY122+CN122)/45</f>
         <v/>
       </c>
       <c r="CU122" s="83">
@@ -22447,11 +22447,11 @@
         <v/>
       </c>
       <c r="CP123" s="38">
-        <f>SUM(O123+P123+Q123+BL123+BM123+CB123+CC123)/65+SUM(X123+Y123)/44+SUM(AJ123+AK123+AM123+AN123+AO123+AP123+AQ123+BR123+BS123+BT123+BU123+BV123+CH123+CI123+CJ123+CM123)/45+SUM(AX123+AY123+AZ123+BA123+BF123+BG123+BH123)/60+SUM(AL123+BZ123)/50</f>
+        <f>SUM(O123+P123+Q123+BL123+BM123+CB123+CC123)/65+SUM(X123+Y123)/44+SUM(AJ123+AK123+AM123+AN123+AO123+AP123+AQ123+BR123+BS123+BT123+BU123+BV123+CH123+CI123+CJ123+CK123)/45+SUM(AX123+AY123+AZ123+BA123+BF123+BG123+BH123)/60+SUM(AL123+BZ123)/50</f>
         <v/>
       </c>
       <c r="CQ123" s="38">
-        <f>SUM(R123+S123+BN123+CD123+CE123)/65+SUM(AB123)/36+SUM(AR123+AS123+BW123+BX123+CK123+CN123)/40+SUM(BB123+BC123+BI123+BJ123)/60</f>
+        <f>SUM(R123+S123+BN123+CD123+CE123)/65+SUM(AB123)/36+SUM(AR123+AS123+BW123+BX123+CL123+CM123)/40+SUM(BB123+BC123+BI123+BJ123)/60</f>
         <v/>
       </c>
       <c r="CR123" s="38">
@@ -22463,7 +22463,7 @@
         <v/>
       </c>
       <c r="CT123" s="38">
-        <f>SUM(BY123+CL123)/45</f>
+        <f>SUM(BY123+CN123)/45</f>
         <v/>
       </c>
       <c r="CU123" s="83">
@@ -22606,11 +22606,11 @@
         <v/>
       </c>
       <c r="CP124" s="38">
-        <f>SUM(O124+P124+Q124+BL124+BM124+CB124+CC124)/65+SUM(X124+Y124)/44+SUM(AJ124+AK124+AM124+AN124+AO124+AP124+AQ124+BR124+BS124+BT124+BU124+BV124+CH124+CI124+CJ124+CM124)/45+SUM(AX124+AY124+AZ124+BA124+BF124+BG124+BH124)/60+SUM(AL124+BZ124)/50</f>
+        <f>SUM(O124+P124+Q124+BL124+BM124+CB124+CC124)/65+SUM(X124+Y124)/44+SUM(AJ124+AK124+AM124+AN124+AO124+AP124+AQ124+BR124+BS124+BT124+BU124+BV124+CH124+CI124+CJ124+CK124)/45+SUM(AX124+AY124+AZ124+BA124+BF124+BG124+BH124)/60+SUM(AL124+BZ124)/50</f>
         <v/>
       </c>
       <c r="CQ124" s="38">
-        <f>SUM(R124+S124+BN124+CD124+CE124)/65+SUM(AB124)/36+SUM(AR124+AS124+BW124+BX124+CK124+CN124)/40+SUM(BB124+BC124+BI124+BJ124)/60</f>
+        <f>SUM(R124+S124+BN124+CD124+CE124)/65+SUM(AB124)/36+SUM(AR124+AS124+BW124+BX124+CL124+CM124)/40+SUM(BB124+BC124+BI124+BJ124)/60</f>
         <v/>
       </c>
       <c r="CR124" s="38">
@@ -22622,7 +22622,7 @@
         <v/>
       </c>
       <c r="CT124" s="38">
-        <f>SUM(BY124+CL124)/45</f>
+        <f>SUM(BY124+CN124)/45</f>
         <v/>
       </c>
       <c r="CU124" s="83">
@@ -22765,11 +22765,11 @@
         <v/>
       </c>
       <c r="CP125" s="38">
-        <f>SUM(O125+P125+Q125+BL125+BM125+CB125+CC125)/65+SUM(X125+Y125)/44+SUM(AJ125+AK125+AM125+AN125+AO125+AP125+AQ125+BR125+BS125+BT125+BU125+BV125+CH125+CI125+CJ125+CM125)/45+SUM(AX125+AY125+AZ125+BA125+BF125+BG125+BH125)/60+SUM(AL125+BZ125)/50</f>
+        <f>SUM(O125+P125+Q125+BL125+BM125+CB125+CC125)/65+SUM(X125+Y125)/44+SUM(AJ125+AK125+AM125+AN125+AO125+AP125+AQ125+BR125+BS125+BT125+BU125+BV125+CH125+CI125+CJ125+CK125)/45+SUM(AX125+AY125+AZ125+BA125+BF125+BG125+BH125)/60+SUM(AL125+BZ125)/50</f>
         <v/>
       </c>
       <c r="CQ125" s="38">
-        <f>SUM(R125+S125+BN125+CD125+CE125)/65+SUM(AB125)/36+SUM(AR125+AS125+BW125+BX125+CK125+CN125)/40+SUM(BB125+BC125+BI125+BJ125)/60</f>
+        <f>SUM(R125+S125+BN125+CD125+CE125)/65+SUM(AB125)/36+SUM(AR125+AS125+BW125+BX125+CL125+CM125)/40+SUM(BB125+BC125+BI125+BJ125)/60</f>
         <v/>
       </c>
       <c r="CR125" s="38">
@@ -22781,7 +22781,7 @@
         <v/>
       </c>
       <c r="CT125" s="38">
-        <f>SUM(BY125+CL125)/45</f>
+        <f>SUM(BY125+CN125)/45</f>
         <v/>
       </c>
       <c r="CU125" s="83">
@@ -22924,11 +22924,11 @@
         <v/>
       </c>
       <c r="CP126" s="38">
-        <f>SUM(O126+P126+Q126+BL126+BM126+CB126+CC126)/65+SUM(X126+Y126)/44+SUM(AJ126+AK126+AM126+AN126+AO126+AP126+AQ126+BR126+BS126+BT126+BU126+BV126+CH126+CI126+CJ126+CM126)/45+SUM(AX126+AY126+AZ126+BA126+BF126+BG126+BH126)/60+SUM(AL126+BZ126)/50</f>
+        <f>SUM(O126+P126+Q126+BL126+BM126+CB126+CC126)/65+SUM(X126+Y126)/44+SUM(AJ126+AK126+AM126+AN126+AO126+AP126+AQ126+BR126+BS126+BT126+BU126+BV126+CH126+CI126+CJ126+CK126)/45+SUM(AX126+AY126+AZ126+BA126+BF126+BG126+BH126)/60+SUM(AL126+BZ126)/50</f>
         <v/>
       </c>
       <c r="CQ126" s="38">
-        <f>SUM(R126+S126+BN126+CD126+CE126)/65+SUM(AB126)/36+SUM(AR126+AS126+BW126+BX126+CK126+CN126)/40+SUM(BB126+BC126+BI126+BJ126)/60</f>
+        <f>SUM(R126+S126+BN126+CD126+CE126)/65+SUM(AB126)/36+SUM(AR126+AS126+BW126+BX126+CL126+CM126)/40+SUM(BB126+BC126+BI126+BJ126)/60</f>
         <v/>
       </c>
       <c r="CR126" s="38">
@@ -22940,7 +22940,7 @@
         <v/>
       </c>
       <c r="CT126" s="38">
-        <f>SUM(BY126+CL126)/45</f>
+        <f>SUM(BY126+CN126)/45</f>
         <v/>
       </c>
       <c r="CU126" s="83">
@@ -23083,11 +23083,11 @@
         <v/>
       </c>
       <c r="CP127" s="38">
-        <f>SUM(O127+P127+Q127+BL127+BM127+CB127+CC127)/65+SUM(X127+Y127)/44+SUM(AJ127+AK127+AM127+AN127+AO127+AP127+AQ127+BR127+BS127+BT127+BU127+BV127+CH127+CI127+CJ127+CM127)/45+SUM(AX127+AY127+AZ127+BA127+BF127+BG127+BH127)/60+SUM(AL127+BZ127)/50</f>
+        <f>SUM(O127+P127+Q127+BL127+BM127+CB127+CC127)/65+SUM(X127+Y127)/44+SUM(AJ127+AK127+AM127+AN127+AO127+AP127+AQ127+BR127+BS127+BT127+BU127+BV127+CH127+CI127+CJ127+CK127)/45+SUM(AX127+AY127+AZ127+BA127+BF127+BG127+BH127)/60+SUM(AL127+BZ127)/50</f>
         <v/>
       </c>
       <c r="CQ127" s="38">
-        <f>SUM(R127+S127+BN127+CD127+CE127)/65+SUM(AB127)/36+SUM(AR127+AS127+BW127+BX127+CK127+CN127)/40+SUM(BB127+BC127+BI127+BJ127)/60</f>
+        <f>SUM(R127+S127+BN127+CD127+CE127)/65+SUM(AB127)/36+SUM(AR127+AS127+BW127+BX127+CL127+CM127)/40+SUM(BB127+BC127+BI127+BJ127)/60</f>
         <v/>
       </c>
       <c r="CR127" s="38">
@@ -23099,7 +23099,7 @@
         <v/>
       </c>
       <c r="CT127" s="38">
-        <f>SUM(BY127+CL127)/45</f>
+        <f>SUM(BY127+CN127)/45</f>
         <v/>
       </c>
       <c r="CU127" s="83">
@@ -23242,11 +23242,11 @@
         <v/>
       </c>
       <c r="CP128" s="38">
-        <f>SUM(O128+P128+Q128+BL128+BM128+CB128+CC128)/65+SUM(X128+Y128)/44+SUM(AJ128+AK128+AM128+AN128+AO128+AP128+AQ128+BR128+BS128+BT128+BU128+BV128+CH128+CI128+CJ128+CM128)/45+SUM(AX128+AY128+AZ128+BA128+BF128+BG128+BH128)/60+SUM(AL128+BZ128)/50</f>
+        <f>SUM(O128+P128+Q128+BL128+BM128+CB128+CC128)/65+SUM(X128+Y128)/44+SUM(AJ128+AK128+AM128+AN128+AO128+AP128+AQ128+BR128+BS128+BT128+BU128+BV128+CH128+CI128+CJ128+CK128)/45+SUM(AX128+AY128+AZ128+BA128+BF128+BG128+BH128)/60+SUM(AL128+BZ128)/50</f>
         <v/>
       </c>
       <c r="CQ128" s="38">
-        <f>SUM(R128+S128+BN128+CD128+CE128)/65+SUM(AB128)/36+SUM(AR128+AS128+BW128+BX128+CK128+CN128)/40+SUM(BB128+BC128+BI128+BJ128)/60</f>
+        <f>SUM(R128+S128+BN128+CD128+CE128)/65+SUM(AB128)/36+SUM(AR128+AS128+BW128+BX128+CL128+CM128)/40+SUM(BB128+BC128+BI128+BJ128)/60</f>
         <v/>
       </c>
       <c r="CR128" s="38">
@@ -23258,7 +23258,7 @@
         <v/>
       </c>
       <c r="CT128" s="38">
-        <f>SUM(BY128+CL128)/45</f>
+        <f>SUM(BY128+CN128)/45</f>
         <v/>
       </c>
       <c r="CU128" s="83">
@@ -23401,11 +23401,11 @@
         <v/>
       </c>
       <c r="CP129" s="38">
-        <f>SUM(O129+P129+Q129+BL129+BM129+CB129+CC129)/65+SUM(X129+Y129)/44+SUM(AJ129+AK129+AM129+AN129+AO129+AP129+AQ129+BR129+BS129+BT129+BU129+BV129+CH129+CI129+CJ129+CM129)/45+SUM(AX129+AY129+AZ129+BA129+BF129+BG129+BH129)/60+SUM(AL129+BZ129)/50</f>
+        <f>SUM(O129+P129+Q129+BL129+BM129+CB129+CC129)/65+SUM(X129+Y129)/44+SUM(AJ129+AK129+AM129+AN129+AO129+AP129+AQ129+BR129+BS129+BT129+BU129+BV129+CH129+CI129+CJ129+CK129)/45+SUM(AX129+AY129+AZ129+BA129+BF129+BG129+BH129)/60+SUM(AL129+BZ129)/50</f>
         <v/>
       </c>
       <c r="CQ129" s="38">
-        <f>SUM(R129+S129+BN129+CD129+CE129)/65+SUM(AB129)/36+SUM(AR129+AS129+BW129+BX129+CK129+CN129)/40+SUM(BB129+BC129+BI129+BJ129)/60</f>
+        <f>SUM(R129+S129+BN129+CD129+CE129)/65+SUM(AB129)/36+SUM(AR129+AS129+BW129+BX129+CL129+CM129)/40+SUM(BB129+BC129+BI129+BJ129)/60</f>
         <v/>
       </c>
       <c r="CR129" s="38">
@@ -23417,7 +23417,7 @@
         <v/>
       </c>
       <c r="CT129" s="38">
-        <f>SUM(BY129+CL129)/45</f>
+        <f>SUM(BY129+CN129)/45</f>
         <v/>
       </c>
       <c r="CU129" s="83">
@@ -23560,11 +23560,11 @@
         <v/>
       </c>
       <c r="CP130" s="38">
-        <f>SUM(O130+P130+Q130+BL130+BM130+CB130+CC130)/65+SUM(X130+Y130)/44+SUM(AJ130+AK130+AM130+AN130+AO130+AP130+AQ130+BR130+BS130+BT130+BU130+BV130+CH130+CI130+CJ130+CM130)/45+SUM(AX130+AY130+AZ130+BA130+BF130+BG130+BH130)/60+SUM(AL130+BZ130)/50</f>
+        <f>SUM(O130+P130+Q130+BL130+BM130+CB130+CC130)/65+SUM(X130+Y130)/44+SUM(AJ130+AK130+AM130+AN130+AO130+AP130+AQ130+BR130+BS130+BT130+BU130+BV130+CH130+CI130+CJ130+CK130)/45+SUM(AX130+AY130+AZ130+BA130+BF130+BG130+BH130)/60+SUM(AL130+BZ130)/50</f>
         <v/>
       </c>
       <c r="CQ130" s="38">
-        <f>SUM(R130+S130+BN130+CD130+CE130)/65+SUM(AB130)/36+SUM(AR130+AS130+BW130+BX130+CK130+CN130)/40+SUM(BB130+BC130+BI130+BJ130)/60</f>
+        <f>SUM(R130+S130+BN130+CD130+CE130)/65+SUM(AB130)/36+SUM(AR130+AS130+BW130+BX130+CL130+CM130)/40+SUM(BB130+BC130+BI130+BJ130)/60</f>
         <v/>
       </c>
       <c r="CR130" s="38">
@@ -23576,7 +23576,7 @@
         <v/>
       </c>
       <c r="CT130" s="38">
-        <f>SUM(BY130+CL130)/45</f>
+        <f>SUM(BY130+CN130)/45</f>
         <v/>
       </c>
       <c r="CU130" s="83">
@@ -23719,11 +23719,11 @@
         <v/>
       </c>
       <c r="CP131" s="38">
-        <f>SUM(O131+P131+Q131+BL131+BM131+CB131+CC131)/65+SUM(X131+Y131)/44+SUM(AJ131+AK131+AM131+AN131+AO131+AP131+AQ131+BR131+BS131+BT131+BU131+BV131+CH131+CI131+CJ131+CM131)/45+SUM(AX131+AY131+AZ131+BA131+BF131+BG131+BH131)/60+SUM(AL131+BZ131)/50</f>
+        <f>SUM(O131+P131+Q131+BL131+BM131+CB131+CC131)/65+SUM(X131+Y131)/44+SUM(AJ131+AK131+AM131+AN131+AO131+AP131+AQ131+BR131+BS131+BT131+BU131+BV131+CH131+CI131+CJ131+CK131)/45+SUM(AX131+AY131+AZ131+BA131+BF131+BG131+BH131)/60+SUM(AL131+BZ131)/50</f>
         <v/>
       </c>
       <c r="CQ131" s="38">
-        <f>SUM(R131+S131+BN131+CD131+CE131)/65+SUM(AB131)/36+SUM(AR131+AS131+BW131+BX131+CK131+CN131)/40+SUM(BB131+BC131+BI131+BJ131)/60</f>
+        <f>SUM(R131+S131+BN131+CD131+CE131)/65+SUM(AB131)/36+SUM(AR131+AS131+BW131+BX131+CL131+CM131)/40+SUM(BB131+BC131+BI131+BJ131)/60</f>
         <v/>
       </c>
       <c r="CR131" s="38">
@@ -23735,7 +23735,7 @@
         <v/>
       </c>
       <c r="CT131" s="38">
-        <f>SUM(BY131+CL131)/45</f>
+        <f>SUM(BY131+CN131)/45</f>
         <v/>
       </c>
       <c r="CU131" s="83">
@@ -23878,11 +23878,11 @@
         <v/>
       </c>
       <c r="CP132" s="38">
-        <f>SUM(O132+P132+Q132+BL132+BM132+CB132+CC132)/65+SUM(X132+Y132)/44+SUM(AJ132+AK132+AM132+AN132+AO132+AP132+AQ132+BR132+BS132+BT132+BU132+BV132+CH132+CI132+CJ132+CM132)/45+SUM(AX132+AY132+AZ132+BA132+BF132+BG132+BH132)/60+SUM(AL132+BZ132)/50</f>
+        <f>SUM(O132+P132+Q132+BL132+BM132+CB132+CC132)/65+SUM(X132+Y132)/44+SUM(AJ132+AK132+AM132+AN132+AO132+AP132+AQ132+BR132+BS132+BT132+BU132+BV132+CH132+CI132+CJ132+CK132)/45+SUM(AX132+AY132+AZ132+BA132+BF132+BG132+BH132)/60+SUM(AL132+BZ132)/50</f>
         <v/>
       </c>
       <c r="CQ132" s="38">
-        <f>SUM(R132+S132+BN132+CD132+CE132)/65+SUM(AB132)/36+SUM(AR132+AS132+BW132+BX132+CK132+CN132)/40+SUM(BB132+BC132+BI132+BJ132)/60</f>
+        <f>SUM(R132+S132+BN132+CD132+CE132)/65+SUM(AB132)/36+SUM(AR132+AS132+BW132+BX132+CL132+CM132)/40+SUM(BB132+BC132+BI132+BJ132)/60</f>
         <v/>
       </c>
       <c r="CR132" s="38">
@@ -23894,7 +23894,7 @@
         <v/>
       </c>
       <c r="CT132" s="38">
-        <f>SUM(BY132+CL132)/45</f>
+        <f>SUM(BY132+CN132)/45</f>
         <v/>
       </c>
       <c r="CU132" s="83">
@@ -24037,11 +24037,11 @@
         <v/>
       </c>
       <c r="CP133" s="38">
-        <f>SUM(O133+P133+Q133+BL133+BM133+CB133+CC133)/65+SUM(X133+Y133)/44+SUM(AJ133+AK133+AM133+AN133+AO133+AP133+AQ133+BR133+BS133+BT133+BU133+BV133+CH133+CI133+CJ133+CM133)/45+SUM(AX133+AY133+AZ133+BA133+BF133+BG133+BH133)/60+SUM(AL133+BZ133)/50</f>
+        <f>SUM(O133+P133+Q133+BL133+BM133+CB133+CC133)/65+SUM(X133+Y133)/44+SUM(AJ133+AK133+AM133+AN133+AO133+AP133+AQ133+BR133+BS133+BT133+BU133+BV133+CH133+CI133+CJ133+CK133)/45+SUM(AX133+AY133+AZ133+BA133+BF133+BG133+BH133)/60+SUM(AL133+BZ133)/50</f>
         <v/>
       </c>
       <c r="CQ133" s="38">
-        <f>SUM(R133+S133+BN133+CD133+CE133)/65+SUM(AB133)/36+SUM(AR133+AS133+BW133+BX133+CK133+CN133)/40+SUM(BB133+BC133+BI133+BJ133)/60</f>
+        <f>SUM(R133+S133+BN133+CD133+CE133)/65+SUM(AB133)/36+SUM(AR133+AS133+BW133+BX133+CL133+CM133)/40+SUM(BB133+BC133+BI133+BJ133)/60</f>
         <v/>
       </c>
       <c r="CR133" s="38">
@@ -24053,7 +24053,7 @@
         <v/>
       </c>
       <c r="CT133" s="38">
-        <f>SUM(BY133+CL133)/45</f>
+        <f>SUM(BY133+CN133)/45</f>
         <v/>
       </c>
       <c r="CU133" s="83">
@@ -24217,11 +24217,11 @@
       <c r="CK134" s="158" t="n"/>
       <c r="CL134" s="158" t="n"/>
       <c r="CM134" s="158">
+        <f>SUM(CK7:CK133)</f>
+        <v/>
+      </c>
+      <c r="CN134" s="158">
         <f>SUM(CM7:CM133)</f>
-        <v/>
-      </c>
-      <c r="CN134" s="158">
-        <f>SUM(CN7:CN133)</f>
         <v/>
       </c>
       <c r="CO134" s="158">
